--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8432" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A73C37-4139-4A7A-875E-A30DF2B395FE}"/>
+  <xr:revisionPtr revIDLastSave="8618" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9346A013-6D14-43BE-AF65-3816727D0C86}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Vessel Schedule" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$163</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="ActualBeyond">PeriodInActual*(#REF!&gt;0)</definedName>
     <definedName name="PercentComplete">PercentCompleteBeyond*PeriodInPlan</definedName>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="469">
   <si>
     <t xml:space="preserve">Top Hole </t>
   </si>
@@ -1664,6 +1664,26 @@
     <t>GL 05c Outer Production Riser</t>
   </si>
   <si>
+    <t>GL 06 Run Upper Tieback</t>
+  </si>
+  <si>
+    <t>MB 09 Completions</t>
+  </si>
+  <si>
+    <t>GL 01 Set Sump Packer on E-line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+GL 03 Install Lower Completion</t>
+  </si>
+  <si>
+    <t>GL 05 Install Upper Completion, Install Hanger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+GL 07 Set MLTH, displace well</t>
+  </si>
+  <si>
     <t>P101</t>
   </si>
   <si>
@@ -1677,9 +1697,6 @@
   </si>
   <si>
     <t>MC940 Vito- GL01 Mobilize/Transit</t>
-  </si>
-  <si>
-    <t>GL 06 Run Upper Tieback</t>
   </si>
   <si>
     <t>ESA</t>
@@ -1729,7 +1746,82 @@
     <t>OWIRS Demobilization (Extra Boat Required)</t>
   </si>
   <si>
-    <t>Rig Idle</t>
+    <t>GA23 Slot Recovery</t>
+  </si>
+  <si>
+    <t>GL 01 OSV / slot recovery equipment</t>
+  </si>
+  <si>
+    <t>GA23 Drill Bypass</t>
+  </si>
+  <si>
+    <t>GL 02 Post Idle Period ll Drill 12 1/4" hole section</t>
+  </si>
+  <si>
+    <t>H&amp;P 205 Rig Idle</t>
+  </si>
+  <si>
+    <t>GL 05 OSV / H&amp;P 2nd start up vessel 96 Hours</t>
+  </si>
+  <si>
+    <t>GL 10 FUTURE CAISSON OSV: Phase 1, startup and pull 2-7/8"</t>
+  </si>
+  <si>
+    <t>GL 11 FUTURE CAISSON OSV: Phase 2, Pull 7-5/8" &amp; ESP</t>
+  </si>
+  <si>
+    <t>GL 12 FUTURE CAISSON OSV: Phase X1, Clean Out Run (if required)</t>
+  </si>
+  <si>
+    <t>GL 13 FUTURE CAISSON OSV: Phase X2, Waireline caisson caliper log</t>
+  </si>
+  <si>
+    <t>GL 14 FUTURE CAISSON OSV: Phase 3 , Rerun ESP &amp; Tbg</t>
+  </si>
+  <si>
+    <t>A-23 Slot Recovery</t>
+  </si>
+  <si>
+    <t>GL 07 Install 13-5/8" TA Packer, N/D BOPs, Run Inner Drilling Riser</t>
+  </si>
+  <si>
+    <t>A-23 St2 Drill</t>
+  </si>
+  <si>
+    <t>GL 01 Exit 13-3/8" Casing</t>
+  </si>
+  <si>
+    <t>GL 02 Drill 12.25" x 14.75" Hole section</t>
+  </si>
+  <si>
+    <t>GL 03 Run 11-7/8" Liner and Cement</t>
+  </si>
+  <si>
+    <t>GL 04 Drill 10.625" Pilot Hole section</t>
+  </si>
+  <si>
+    <t>GL 05 Abandon 10.625" Pilot Hole</t>
+  </si>
+  <si>
+    <t>GL 06 Drill 10.625" Sidetrack Hole section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+GL 07 Install 7-5/8" Liner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+GL 08 TA Well and Pull Inner Drilling Riser</t>
+  </si>
+  <si>
+    <t>GL 09 Install Lower Tieback</t>
+  </si>
+  <si>
+    <t>GL 10 TA Well, Pull ODR, Run Production Riser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+GL 11 Run Upper Tieback</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -1829,9 +1921,6 @@
   </si>
   <si>
     <t>Spot Hire 5</t>
-  </si>
-  <si>
-    <t>GL 02 Post Idle Period ll Drill 12 1/4" hole section</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1930,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -3317,7 +3406,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="552">
+  <cellXfs count="553">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4498,198 +4587,27 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="27" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="27" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4732,45 +4650,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4798,78 +4677,6 @@
     <xf numFmtId="0" fontId="10" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4887,6 +4694,291 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -25698,10 +25790,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25935,7 +26023,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:DG60"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1"/>
     <col min="2" max="2" width="27.375" style="1" customWidth="1"/>
@@ -25958,7 +26046,7 @@
     <col min="112" max="16384" width="11.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:111">
       <c r="A1" s="40"/>
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
@@ -25988,7 +26076,7 @@
       <c r="Y1" s="40"/>
       <c r="Z1" s="40"/>
     </row>
-    <row r="2" spans="1:111" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:111" ht="15.75">
       <c r="A2" s="40"/>
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
@@ -26020,7 +26108,7 @@
       <c r="Y2" s="40"/>
       <c r="Z2" s="40"/>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:111">
       <c r="A3" s="40"/>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
@@ -26050,7 +26138,7 @@
       <c r="Y3" s="40"/>
       <c r="Z3" s="40"/>
     </row>
-    <row r="4" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:111">
       <c r="A4" s="40"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -26080,7 +26168,7 @@
       <c r="Y4" s="40"/>
       <c r="Z4" s="40"/>
     </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:111">
       <c r="A5" s="40"/>
       <c r="B5" s="34"/>
       <c r="C5" s="6" t="s">
@@ -26109,7 +26197,7 @@
       <c r="Y5" s="40"/>
       <c r="Z5" s="40"/>
     </row>
-    <row r="6" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:111" ht="15.75" thickBot="1">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -26137,29 +26225,29 @@
       <c r="Y6" s="40"/>
       <c r="Z6" s="40"/>
     </row>
-    <row r="7" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:111" ht="15.75" thickBot="1">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="428">
+      <c r="G7" s="459">
         <v>2025</v>
       </c>
-      <c r="H7" s="429"/>
-      <c r="I7" s="429"/>
-      <c r="J7" s="429"/>
-      <c r="K7" s="429"/>
-      <c r="L7" s="429"/>
-      <c r="M7" s="429"/>
-      <c r="N7" s="430"/>
-      <c r="O7" s="431">
+      <c r="H7" s="460"/>
+      <c r="I7" s="460"/>
+      <c r="J7" s="460"/>
+      <c r="K7" s="460"/>
+      <c r="L7" s="460"/>
+      <c r="M7" s="460"/>
+      <c r="N7" s="461"/>
+      <c r="O7" s="462">
         <v>2026</v>
       </c>
-      <c r="P7" s="432"/>
-      <c r="Q7" s="432"/>
-      <c r="R7" s="433"/>
+      <c r="P7" s="463"/>
+      <c r="Q7" s="463"/>
+      <c r="R7" s="464"/>
       <c r="S7" s="40"/>
       <c r="T7" s="40"/>
       <c r="U7" s="40"/>
@@ -26169,31 +26257,31 @@
       <c r="Y7" s="40"/>
       <c r="Z7" s="40"/>
     </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:111">
       <c r="A8" s="40"/>
       <c r="B8" s="40"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="436" t="s">
+      <c r="G8" s="465" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="437"/>
-      <c r="I8" s="437"/>
-      <c r="J8" s="437"/>
-      <c r="K8" s="438" t="s">
+      <c r="H8" s="466"/>
+      <c r="I8" s="466"/>
+      <c r="J8" s="466"/>
+      <c r="K8" s="467" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="438"/>
-      <c r="M8" s="438"/>
-      <c r="N8" s="438"/>
-      <c r="O8" s="447" t="s">
+      <c r="L8" s="467"/>
+      <c r="M8" s="467"/>
+      <c r="N8" s="467"/>
+      <c r="O8" s="468" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="447"/>
-      <c r="Q8" s="447"/>
-      <c r="R8" s="448"/>
+      <c r="P8" s="468"/>
+      <c r="Q8" s="468"/>
+      <c r="R8" s="469"/>
       <c r="S8" s="40"/>
       <c r="T8" s="40"/>
       <c r="U8" s="40"/>
@@ -26288,7 +26376,7 @@
       <c r="DF8" s="8"/>
       <c r="DG8" s="8"/>
     </row>
-    <row r="9" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:111" ht="15.75" thickBot="1">
       <c r="A9" s="40"/>
       <c r="B9" s="18" t="s">
         <v>9</v>
@@ -26411,9 +26499,9 @@
       <c r="DF9" s="9"/>
       <c r="DG9" s="9"/>
     </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:111">
       <c r="A10" s="40"/>
-      <c r="B10" s="439" t="s">
+      <c r="B10" s="428" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -26534,9 +26622,9 @@
       <c r="DF10" s="9"/>
       <c r="DG10" s="9"/>
     </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:111">
       <c r="A11" s="40"/>
-      <c r="B11" s="440"/>
+      <c r="B11" s="470"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
@@ -26657,9 +26745,9 @@
       <c r="DF11" s="9"/>
       <c r="DG11" s="9"/>
     </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:111">
       <c r="A12" s="40"/>
-      <c r="B12" s="440"/>
+      <c r="B12" s="470"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -26778,9 +26866,9 @@
       <c r="DF12" s="9"/>
       <c r="DG12" s="9"/>
     </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:111">
       <c r="A13" s="40"/>
-      <c r="B13" s="440"/>
+      <c r="B13" s="470"/>
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
@@ -26899,9 +26987,9 @@
       <c r="DF13" s="9"/>
       <c r="DG13" s="9"/>
     </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:111">
       <c r="A14" s="40"/>
-      <c r="B14" s="440"/>
+      <c r="B14" s="470"/>
       <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
@@ -27022,9 +27110,9 @@
       <c r="DF14" s="9"/>
       <c r="DG14" s="9"/>
     </row>
-    <row r="15" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:111" ht="15.75" thickBot="1">
       <c r="A15" s="40"/>
-      <c r="B15" s="441"/>
+      <c r="B15" s="471"/>
       <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
@@ -27143,9 +27231,9 @@
       <c r="DF15" s="9"/>
       <c r="DG15" s="9"/>
     </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:111">
       <c r="A16" s="40"/>
-      <c r="B16" s="434" t="s">
+      <c r="B16" s="427" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -27266,9 +27354,9 @@
       <c r="DF16" s="9"/>
       <c r="DG16" s="9"/>
     </row>
-    <row r="17" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:111">
       <c r="A17" s="40"/>
-      <c r="B17" s="435"/>
+      <c r="B17" s="472"/>
       <c r="C17" s="7" t="s">
         <v>27</v>
       </c>
@@ -27387,9 +27475,9 @@
       <c r="DF17" s="9"/>
       <c r="DG17" s="9"/>
     </row>
-    <row r="18" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:111" ht="15.75" thickBot="1">
       <c r="A18" s="40"/>
-      <c r="B18" s="435"/>
+      <c r="B18" s="472"/>
       <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
@@ -27508,9 +27596,9 @@
       <c r="DF18" s="9"/>
       <c r="DG18" s="9"/>
     </row>
-    <row r="19" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:111">
       <c r="A19" s="40"/>
-      <c r="B19" s="434" t="s">
+      <c r="B19" s="427" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -27631,9 +27719,9 @@
       <c r="DF19" s="9"/>
       <c r="DG19" s="9"/>
     </row>
-    <row r="20" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:111" ht="15.75" thickBot="1">
       <c r="A20" s="40"/>
-      <c r="B20" s="435"/>
+      <c r="B20" s="472"/>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
@@ -27752,9 +27840,9 @@
       <c r="DF20" s="9"/>
       <c r="DG20" s="9"/>
     </row>
-    <row r="21" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:111">
       <c r="A21" s="40"/>
-      <c r="B21" s="434" t="s">
+      <c r="B21" s="427" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -27875,9 +27963,9 @@
       <c r="DF21" s="9"/>
       <c r="DG21" s="9"/>
     </row>
-    <row r="22" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:111">
       <c r="A22" s="40"/>
-      <c r="B22" s="435"/>
+      <c r="B22" s="472"/>
       <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
@@ -27996,9 +28084,9 @@
       <c r="DF22" s="9"/>
       <c r="DG22" s="9"/>
     </row>
-    <row r="23" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:111" ht="15.75" thickBot="1">
       <c r="A23" s="40"/>
-      <c r="B23" s="435"/>
+      <c r="B23" s="472"/>
       <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
@@ -28018,11 +28106,11 @@
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
-      <c r="N23" s="444"/>
-      <c r="O23" s="444"/>
-      <c r="P23" s="444"/>
-      <c r="Q23" s="444"/>
-      <c r="R23" s="445"/>
+      <c r="N23" s="473"/>
+      <c r="O23" s="473"/>
+      <c r="P23" s="473"/>
+      <c r="Q23" s="473"/>
+      <c r="R23" s="474"/>
       <c r="S23" s="40"/>
       <c r="T23" s="40"/>
       <c r="U23" s="40"/>
@@ -28032,9 +28120,9 @@
       <c r="Y23" s="40"/>
       <c r="Z23" s="40"/>
     </row>
-    <row r="24" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:111">
       <c r="A24" s="40"/>
-      <c r="B24" s="434" t="s">
+      <c r="B24" s="427" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -28052,12 +28140,12 @@
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
-      <c r="J24" s="446"/>
-      <c r="K24" s="446"/>
-      <c r="L24" s="446"/>
-      <c r="M24" s="446"/>
-      <c r="N24" s="446"/>
-      <c r="O24" s="446"/>
+      <c r="J24" s="475"/>
+      <c r="K24" s="475"/>
+      <c r="L24" s="475"/>
+      <c r="M24" s="475"/>
+      <c r="N24" s="475"/>
+      <c r="O24" s="475"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="14"/>
@@ -28070,9 +28158,9 @@
       <c r="Y24" s="40"/>
       <c r="Z24" s="40"/>
     </row>
-    <row r="25" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:111" ht="15.75" thickBot="1">
       <c r="A25" s="40"/>
-      <c r="B25" s="435"/>
+      <c r="B25" s="472"/>
       <c r="C25" s="7" t="s">
         <v>44</v>
       </c>
@@ -28093,10 +28181,10 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
-      <c r="O25" s="442"/>
-      <c r="P25" s="442"/>
-      <c r="Q25" s="442"/>
-      <c r="R25" s="443"/>
+      <c r="O25" s="476"/>
+      <c r="P25" s="476"/>
+      <c r="Q25" s="476"/>
+      <c r="R25" s="477"/>
       <c r="S25" s="40"/>
       <c r="T25" s="40"/>
       <c r="U25" s="40"/>
@@ -28106,7 +28194,7 @@
       <c r="Y25" s="40"/>
       <c r="Z25" s="40"/>
     </row>
-    <row r="26" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:111" ht="15.75" thickBot="1">
       <c r="A26" s="40"/>
       <c r="B26" s="46" t="s">
         <v>20</v>
@@ -28146,7 +28234,7 @@
       <c r="Y26" s="40"/>
       <c r="Z26" s="40"/>
     </row>
-    <row r="27" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:111" ht="15.75" thickBot="1">
       <c r="A27" s="40"/>
       <c r="B27" s="32" t="s">
         <v>47</v>
@@ -28184,7 +28272,7 @@
       <c r="Y27" s="40"/>
       <c r="Z27" s="40"/>
     </row>
-    <row r="28" spans="1:111" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:111" ht="20.25" customHeight="1" thickBot="1">
       <c r="A28" s="40"/>
       <c r="B28" s="39" t="s">
         <v>50</v>
@@ -28222,7 +28310,7 @@
       <c r="Y28" s="40"/>
       <c r="Z28" s="40"/>
     </row>
-    <row r="29" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:111" ht="15.75" thickBot="1">
       <c r="A29" s="40"/>
       <c r="B29" s="46" t="s">
         <v>52</v>
@@ -28262,8 +28350,8 @@
       </c>
       <c r="Z29" s="40"/>
     </row>
-    <row r="30" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="427" t="s">
+    <row r="30" spans="1:111" ht="15.75" thickBot="1">
+      <c r="B30" s="478" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="33" t="s">
@@ -28299,9 +28387,9 @@
       <c r="Y30" s="40"/>
       <c r="Z30" s="40"/>
     </row>
-    <row r="31" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:111" ht="15.75" thickBot="1">
       <c r="A31" s="40"/>
-      <c r="B31" s="427"/>
+      <c r="B31" s="478"/>
       <c r="C31" s="33" t="s">
         <v>48</v>
       </c>
@@ -28335,7 +28423,7 @@
       <c r="Y31" s="40"/>
       <c r="Z31" s="40"/>
     </row>
-    <row r="32" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:111" ht="15.75" thickBot="1">
       <c r="A32" s="40"/>
       <c r="B32" s="46" t="s">
         <v>57</v>
@@ -28373,7 +28461,7 @@
       <c r="Y32" s="40"/>
       <c r="Z32" s="40"/>
     </row>
-    <row r="33" spans="1:26" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="19.5" customHeight="1" thickBot="1">
       <c r="A33" s="40"/>
       <c r="B33" s="62" t="s">
         <v>60</v>
@@ -28411,7 +28499,7 @@
       <c r="Y33" s="40"/>
       <c r="Z33" s="40"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="15.75" thickBot="1">
       <c r="A34" s="40"/>
       <c r="B34" s="46" t="s">
         <v>62</v>
@@ -28449,7 +28537,7 @@
       <c r="Y34" s="40"/>
       <c r="Z34" s="40"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="15.75" thickBot="1">
       <c r="A35" s="40"/>
       <c r="B35" s="46" t="s">
         <v>64</v>
@@ -28489,7 +28577,7 @@
       <c r="Y35" s="40"/>
       <c r="Z35" s="40"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26">
       <c r="A36" s="40"/>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -28519,7 +28607,7 @@
       <c r="Y36" s="40"/>
       <c r="Z36" s="40"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26">
       <c r="A37" s="40"/>
       <c r="B37" s="40"/>
       <c r="C37" s="40"/>
@@ -28551,7 +28639,7 @@
       <c r="Y37" s="40"/>
       <c r="Z37" s="40"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26">
       <c r="A38" s="40"/>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -28579,7 +28667,7 @@
       <c r="Y38" s="40"/>
       <c r="Z38" s="40"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26">
       <c r="A39" s="40"/>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -28607,7 +28695,7 @@
       <c r="Y39" s="40"/>
       <c r="Z39" s="40"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26">
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
       <c r="D40" s="40"/>
@@ -28634,7 +28722,7 @@
       <c r="Y40" s="40"/>
       <c r="Z40" s="40"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26">
       <c r="A41" s="40"/>
       <c r="B41" s="40"/>
       <c r="C41" s="40"/>
@@ -28662,7 +28750,7 @@
       <c r="Y41" s="40"/>
       <c r="Z41" s="40"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26">
       <c r="A42" s="40"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -28690,7 +28778,7 @@
       <c r="Y42" s="40"/>
       <c r="Z42" s="40"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26">
       <c r="A43" s="40"/>
       <c r="B43" s="40"/>
       <c r="C43" s="40"/>
@@ -28718,7 +28806,7 @@
       <c r="Y43" s="40"/>
       <c r="Z43" s="40"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26">
       <c r="A44" s="40"/>
       <c r="B44" s="40"/>
       <c r="C44" s="40"/>
@@ -28746,7 +28834,7 @@
       <c r="Y44" s="40"/>
       <c r="Z44" s="40"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26">
       <c r="A45" s="40"/>
       <c r="B45" s="40"/>
       <c r="C45" s="40"/>
@@ -28774,7 +28862,7 @@
       <c r="Y45" s="40"/>
       <c r="Z45" s="40"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26">
       <c r="A46" s="40"/>
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
@@ -28802,7 +28890,7 @@
       <c r="Y46" s="40"/>
       <c r="Z46" s="40"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26">
       <c r="A47" s="40"/>
       <c r="B47" s="40"/>
       <c r="C47" s="40"/>
@@ -28830,7 +28918,7 @@
       <c r="Y47" s="40"/>
       <c r="Z47" s="40"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26">
       <c r="A48" s="40"/>
       <c r="B48" s="40"/>
       <c r="C48" s="40"/>
@@ -28858,40 +28946,40 @@
       <c r="Y48" s="40"/>
       <c r="Z48" s="40"/>
     </row>
-    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="21:21">
       <c r="U49" s="40"/>
     </row>
-    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="21:21">
       <c r="U50" s="40"/>
     </row>
-    <row r="51" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="21:21">
       <c r="U51" s="40"/>
     </row>
-    <row r="52" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="21:21">
       <c r="U52" s="40"/>
     </row>
-    <row r="53" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="21:21">
       <c r="U53" s="40"/>
     </row>
-    <row r="54" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="21:21">
       <c r="U54" s="40"/>
     </row>
-    <row r="55" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="21:21">
       <c r="U55" s="40"/>
     </row>
-    <row r="56" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="21:21">
       <c r="U56" s="40"/>
     </row>
-    <row r="57" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="21:21">
       <c r="U57" s="40"/>
     </row>
-    <row r="58" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="21:21">
       <c r="U58" s="40"/>
     </row>
-    <row r="59" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="21:21">
       <c r="U59" s="40"/>
     </row>
-    <row r="60" spans="21:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="21:21">
       <c r="U60" s="40"/>
     </row>
   </sheetData>
@@ -28920,7 +29008,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31789BA3-7E08-4BBD-8F4F-2CBDF359F836}">
   <dimension ref="A1:BS69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="14.375" customWidth="1"/>
@@ -28942,7 +29030,7 @@
     <col min="44" max="44" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:71" s="1" customFormat="1">
       <c r="A1" s="40"/>
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
@@ -28978,7 +29066,7 @@
       <c r="AO1" s="40"/>
       <c r="AP1" s="40"/>
     </row>
-    <row r="2" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:71" s="1" customFormat="1">
       <c r="A2" s="40"/>
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
@@ -29016,7 +29104,7 @@
       <c r="AO2" s="40"/>
       <c r="AP2" s="40"/>
     </row>
-    <row r="3" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:71" s="1" customFormat="1">
       <c r="A3" s="40"/>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
@@ -29052,7 +29140,7 @@
       <c r="AO3" s="40"/>
       <c r="AP3" s="40"/>
     </row>
-    <row r="4" spans="1:71" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:71" s="1" customFormat="1" ht="15.75">
       <c r="A4" s="40"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -29090,7 +29178,7 @@
       <c r="AO4" s="40"/>
       <c r="AP4" s="40"/>
     </row>
-    <row r="5" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:71" s="1" customFormat="1">
       <c r="A5" s="40"/>
       <c r="B5" s="162"/>
       <c r="C5" s="6" t="s">
@@ -29130,7 +29218,7 @@
       <c r="AO5" s="40"/>
       <c r="AP5" s="40"/>
     </row>
-    <row r="6" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:71" s="1" customFormat="1">
       <c r="A6" s="40"/>
       <c r="B6" s="128"/>
       <c r="C6" s="131" t="s">
@@ -29178,7 +29266,7 @@
       <c r="AO6" s="40"/>
       <c r="AP6" s="40"/>
     </row>
-    <row r="7" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:71" s="1" customFormat="1">
       <c r="A7" s="40"/>
       <c r="B7" s="152"/>
       <c r="C7" s="131" t="s">
@@ -29187,58 +29275,58 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="461">
+      <c r="G7" s="479">
         <v>2026</v>
       </c>
-      <c r="H7" s="461"/>
-      <c r="I7" s="461"/>
-      <c r="J7" s="461"/>
-      <c r="K7" s="461"/>
-      <c r="L7" s="461"/>
-      <c r="M7" s="461"/>
-      <c r="N7" s="461"/>
-      <c r="O7" s="461"/>
-      <c r="P7" s="461"/>
-      <c r="Q7" s="461"/>
-      <c r="R7" s="461"/>
-      <c r="S7" s="461"/>
-      <c r="T7" s="461"/>
-      <c r="U7" s="461"/>
-      <c r="V7" s="461"/>
-      <c r="W7" s="461"/>
-      <c r="X7" s="461"/>
-      <c r="Y7" s="461"/>
-      <c r="Z7" s="461"/>
-      <c r="AA7" s="461"/>
-      <c r="AB7" s="461"/>
-      <c r="AC7" s="461"/>
-      <c r="AD7" s="461"/>
-      <c r="AE7" s="461"/>
-      <c r="AF7" s="461"/>
-      <c r="AG7" s="461"/>
-      <c r="AH7" s="461"/>
-      <c r="AI7" s="461"/>
-      <c r="AJ7" s="461"/>
-      <c r="AK7" s="461"/>
-      <c r="AL7" s="461"/>
-      <c r="AM7" s="461"/>
-      <c r="AN7" s="461"/>
-      <c r="AO7" s="461"/>
-      <c r="AP7" s="461"/>
-      <c r="AQ7" s="461"/>
-      <c r="AR7" s="461"/>
-      <c r="AS7" s="461"/>
-      <c r="AT7" s="461"/>
-      <c r="AU7" s="461"/>
-      <c r="AV7" s="461"/>
-      <c r="AW7" s="461"/>
-      <c r="AX7" s="461"/>
-      <c r="AY7" s="461"/>
-      <c r="AZ7" s="461"/>
-      <c r="BA7" s="461"/>
-      <c r="BB7" s="461"/>
+      <c r="H7" s="479"/>
+      <c r="I7" s="479"/>
+      <c r="J7" s="479"/>
+      <c r="K7" s="479"/>
+      <c r="L7" s="479"/>
+      <c r="M7" s="479"/>
+      <c r="N7" s="479"/>
+      <c r="O7" s="479"/>
+      <c r="P7" s="479"/>
+      <c r="Q7" s="479"/>
+      <c r="R7" s="479"/>
+      <c r="S7" s="479"/>
+      <c r="T7" s="479"/>
+      <c r="U7" s="479"/>
+      <c r="V7" s="479"/>
+      <c r="W7" s="479"/>
+      <c r="X7" s="479"/>
+      <c r="Y7" s="479"/>
+      <c r="Z7" s="479"/>
+      <c r="AA7" s="479"/>
+      <c r="AB7" s="479"/>
+      <c r="AC7" s="479"/>
+      <c r="AD7" s="479"/>
+      <c r="AE7" s="479"/>
+      <c r="AF7" s="479"/>
+      <c r="AG7" s="479"/>
+      <c r="AH7" s="479"/>
+      <c r="AI7" s="479"/>
+      <c r="AJ7" s="479"/>
+      <c r="AK7" s="479"/>
+      <c r="AL7" s="479"/>
+      <c r="AM7" s="479"/>
+      <c r="AN7" s="479"/>
+      <c r="AO7" s="479"/>
+      <c r="AP7" s="479"/>
+      <c r="AQ7" s="479"/>
+      <c r="AR7" s="479"/>
+      <c r="AS7" s="479"/>
+      <c r="AT7" s="479"/>
+      <c r="AU7" s="479"/>
+      <c r="AV7" s="479"/>
+      <c r="AW7" s="479"/>
+      <c r="AX7" s="479"/>
+      <c r="AY7" s="479"/>
+      <c r="AZ7" s="479"/>
+      <c r="BA7" s="479"/>
+      <c r="BB7" s="479"/>
     </row>
-    <row r="8" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:71" s="1" customFormat="1">
       <c r="A8" s="40"/>
       <c r="B8" s="167"/>
       <c r="C8" s="131" t="s">
@@ -29247,78 +29335,78 @@
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="473" t="s">
+      <c r="G8" s="480" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="473"/>
-      <c r="I8" s="473"/>
-      <c r="J8" s="473"/>
-      <c r="K8" s="468" t="s">
+      <c r="H8" s="480"/>
+      <c r="I8" s="480"/>
+      <c r="J8" s="480"/>
+      <c r="K8" s="481" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="468"/>
-      <c r="M8" s="468"/>
-      <c r="N8" s="468"/>
-      <c r="O8" s="469" t="s">
+      <c r="L8" s="481"/>
+      <c r="M8" s="481"/>
+      <c r="N8" s="481"/>
+      <c r="O8" s="482" t="s">
         <v>74</v>
       </c>
-      <c r="P8" s="469"/>
-      <c r="Q8" s="469"/>
-      <c r="R8" s="469"/>
-      <c r="S8" s="467" t="s">
+      <c r="P8" s="482"/>
+      <c r="Q8" s="482"/>
+      <c r="R8" s="482"/>
+      <c r="S8" s="483" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="467"/>
-      <c r="U8" s="467"/>
-      <c r="V8" s="467"/>
-      <c r="W8" s="468" t="s">
+      <c r="T8" s="483"/>
+      <c r="U8" s="483"/>
+      <c r="V8" s="483"/>
+      <c r="W8" s="481" t="s">
         <v>76</v>
       </c>
-      <c r="X8" s="468"/>
-      <c r="Y8" s="468"/>
-      <c r="Z8" s="468"/>
-      <c r="AA8" s="469" t="s">
+      <c r="X8" s="481"/>
+      <c r="Y8" s="481"/>
+      <c r="Z8" s="481"/>
+      <c r="AA8" s="482" t="s">
         <v>77</v>
       </c>
-      <c r="AB8" s="469"/>
-      <c r="AC8" s="469"/>
-      <c r="AD8" s="469"/>
-      <c r="AE8" s="466" t="s">
+      <c r="AB8" s="482"/>
+      <c r="AC8" s="482"/>
+      <c r="AD8" s="482"/>
+      <c r="AE8" s="484" t="s">
         <v>78</v>
       </c>
-      <c r="AF8" s="466"/>
-      <c r="AG8" s="466"/>
-      <c r="AH8" s="466"/>
-      <c r="AI8" s="462" t="s">
+      <c r="AF8" s="484"/>
+      <c r="AG8" s="484"/>
+      <c r="AH8" s="484"/>
+      <c r="AI8" s="485" t="s">
         <v>79</v>
       </c>
-      <c r="AJ8" s="462"/>
-      <c r="AK8" s="462"/>
-      <c r="AL8" s="462"/>
-      <c r="AM8" s="463" t="s">
+      <c r="AJ8" s="485"/>
+      <c r="AK8" s="485"/>
+      <c r="AL8" s="485"/>
+      <c r="AM8" s="486" t="s">
         <v>80</v>
       </c>
-      <c r="AN8" s="463"/>
-      <c r="AO8" s="463"/>
-      <c r="AP8" s="463"/>
-      <c r="AQ8" s="462" t="s">
+      <c r="AN8" s="486"/>
+      <c r="AO8" s="486"/>
+      <c r="AP8" s="486"/>
+      <c r="AQ8" s="485" t="s">
         <v>81</v>
       </c>
-      <c r="AR8" s="462"/>
-      <c r="AS8" s="462"/>
-      <c r="AT8" s="462"/>
-      <c r="AU8" s="463" t="s">
+      <c r="AR8" s="485"/>
+      <c r="AS8" s="485"/>
+      <c r="AT8" s="485"/>
+      <c r="AU8" s="486" t="s">
         <v>82</v>
       </c>
-      <c r="AV8" s="463"/>
-      <c r="AW8" s="463"/>
-      <c r="AX8" s="463"/>
-      <c r="AY8" s="462" t="s">
+      <c r="AV8" s="486"/>
+      <c r="AW8" s="486"/>
+      <c r="AX8" s="486"/>
+      <c r="AY8" s="485" t="s">
         <v>83</v>
       </c>
-      <c r="AZ8" s="462"/>
-      <c r="BA8" s="462"/>
-      <c r="BB8" s="462"/>
+      <c r="AZ8" s="485"/>
+      <c r="BA8" s="485"/>
+      <c r="BB8" s="485"/>
       <c r="BC8" s="8"/>
       <c r="BD8" s="8"/>
       <c r="BE8" s="8"/>
@@ -29337,7 +29425,7 @@
       <c r="BR8" s="8"/>
       <c r="BS8" s="8"/>
     </row>
-    <row r="9" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A9" s="40"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -29506,7 +29594,7 @@
       <c r="BR9" s="8"/>
       <c r="BS9" s="8"/>
     </row>
-    <row r="10" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A10" s="40"/>
       <c r="B10" s="289" t="s">
         <v>9</v>
@@ -29535,42 +29623,42 @@
       <c r="P10" s="231"/>
       <c r="Q10" s="231"/>
       <c r="R10" s="378"/>
-      <c r="S10" s="470"/>
-      <c r="T10" s="471"/>
-      <c r="U10" s="471"/>
-      <c r="V10" s="471"/>
-      <c r="W10" s="471"/>
-      <c r="X10" s="471"/>
-      <c r="Y10" s="471"/>
-      <c r="Z10" s="471"/>
-      <c r="AA10" s="471"/>
-      <c r="AB10" s="471"/>
-      <c r="AC10" s="471"/>
-      <c r="AD10" s="472"/>
-      <c r="AE10" s="464"/>
-      <c r="AF10" s="465"/>
-      <c r="AG10" s="465"/>
-      <c r="AH10" s="465"/>
-      <c r="AI10" s="465"/>
-      <c r="AJ10" s="465"/>
-      <c r="AK10" s="465"/>
-      <c r="AL10" s="465"/>
-      <c r="AM10" s="465"/>
-      <c r="AN10" s="465"/>
-      <c r="AO10" s="465"/>
-      <c r="AP10" s="465"/>
-      <c r="AQ10" s="464"/>
-      <c r="AR10" s="465"/>
-      <c r="AS10" s="465"/>
-      <c r="AT10" s="465"/>
-      <c r="AU10" s="465"/>
-      <c r="AV10" s="465"/>
-      <c r="AW10" s="465"/>
-      <c r="AX10" s="465"/>
-      <c r="AY10" s="465"/>
-      <c r="AZ10" s="465"/>
-      <c r="BA10" s="465"/>
-      <c r="BB10" s="465"/>
+      <c r="S10" s="487"/>
+      <c r="T10" s="488"/>
+      <c r="U10" s="488"/>
+      <c r="V10" s="488"/>
+      <c r="W10" s="488"/>
+      <c r="X10" s="488"/>
+      <c r="Y10" s="488"/>
+      <c r="Z10" s="488"/>
+      <c r="AA10" s="488"/>
+      <c r="AB10" s="488"/>
+      <c r="AC10" s="488"/>
+      <c r="AD10" s="489"/>
+      <c r="AE10" s="490"/>
+      <c r="AF10" s="491"/>
+      <c r="AG10" s="491"/>
+      <c r="AH10" s="491"/>
+      <c r="AI10" s="491"/>
+      <c r="AJ10" s="491"/>
+      <c r="AK10" s="491"/>
+      <c r="AL10" s="491"/>
+      <c r="AM10" s="491"/>
+      <c r="AN10" s="491"/>
+      <c r="AO10" s="491"/>
+      <c r="AP10" s="491"/>
+      <c r="AQ10" s="490"/>
+      <c r="AR10" s="491"/>
+      <c r="AS10" s="491"/>
+      <c r="AT10" s="491"/>
+      <c r="AU10" s="491"/>
+      <c r="AV10" s="491"/>
+      <c r="AW10" s="491"/>
+      <c r="AX10" s="491"/>
+      <c r="AY10" s="491"/>
+      <c r="AZ10" s="491"/>
+      <c r="BA10" s="491"/>
+      <c r="BB10" s="491"/>
       <c r="BC10" s="9"/>
       <c r="BD10" s="9"/>
       <c r="BE10" s="9"/>
@@ -29589,7 +29677,7 @@
       <c r="BR10" s="9"/>
       <c r="BS10" s="9"/>
     </row>
-    <row r="11" spans="1:71" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:71" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A11" s="150"/>
       <c r="B11" s="62" t="s">
         <v>84</v>
@@ -29655,7 +29743,7 @@
       <c r="BA11" s="38"/>
       <c r="BB11" s="42"/>
     </row>
-    <row r="12" spans="1:71" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:71" ht="30.75" thickBot="1">
       <c r="A12" s="150"/>
       <c r="B12" s="62" t="s">
         <v>85</v>
@@ -29721,7 +29809,7 @@
       <c r="BA12" s="38"/>
       <c r="BB12" s="42"/>
     </row>
-    <row r="13" spans="1:71" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:71" ht="27" customHeight="1" thickBot="1">
       <c r="A13" s="150"/>
       <c r="B13" s="62" t="s">
         <v>86</v>
@@ -29787,7 +29875,7 @@
       <c r="BA13" s="38"/>
       <c r="BB13" s="42"/>
     </row>
-    <row r="14" spans="1:71" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:71" ht="30.75" thickBot="1">
       <c r="A14" s="150"/>
       <c r="B14" s="39" t="s">
         <v>87</v>
@@ -29853,9 +29941,9 @@
       <c r="BA14" s="150"/>
       <c r="BB14" s="177"/>
     </row>
-    <row r="15" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:71" ht="15" customHeight="1">
       <c r="A15" s="150"/>
-      <c r="B15" s="434" t="s">
+      <c r="B15" s="427" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="116" t="s">
@@ -29925,9 +30013,9 @@
       <c r="BA15" s="150"/>
       <c r="BB15" s="177"/>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:71">
       <c r="A16" s="150"/>
-      <c r="B16" s="434"/>
+      <c r="B16" s="427"/>
       <c r="C16" s="116" t="s">
         <v>42</v>
       </c>
@@ -29989,9 +30077,9 @@
       <c r="BA16" s="150"/>
       <c r="BB16" s="177"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54">
       <c r="A17" s="150"/>
-      <c r="B17" s="434"/>
+      <c r="B17" s="427"/>
       <c r="C17" s="220" t="s">
         <v>23</v>
       </c>
@@ -30053,9 +30141,9 @@
       <c r="BA17" s="150"/>
       <c r="BB17" s="177"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54">
       <c r="A18" s="150"/>
-      <c r="B18" s="434"/>
+      <c r="B18" s="427"/>
       <c r="C18" s="223" t="s">
         <v>91</v>
       </c>
@@ -30117,9 +30205,9 @@
       <c r="BA18" s="150"/>
       <c r="BB18" s="177"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54">
       <c r="A19" s="150"/>
-      <c r="B19" s="434"/>
+      <c r="B19" s="427"/>
       <c r="C19" s="359" t="s">
         <v>93</v>
       </c>
@@ -30181,9 +30269,9 @@
       <c r="BA19" s="150"/>
       <c r="BB19" s="177"/>
     </row>
-    <row r="20" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="15.75" thickBot="1">
       <c r="A20" s="150"/>
-      <c r="B20" s="434"/>
+      <c r="B20" s="427"/>
       <c r="C20" s="359" t="s">
         <v>93</v>
       </c>
@@ -30245,9 +30333,9 @@
       <c r="BA20" s="150"/>
       <c r="BB20" s="177"/>
     </row>
-    <row r="21" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" ht="15" customHeight="1">
       <c r="A21" s="150"/>
-      <c r="B21" s="434" t="s">
+      <c r="B21" s="427" t="s">
         <v>96</v>
       </c>
       <c r="C21" s="117" t="s">
@@ -30315,9 +30403,9 @@
       <c r="BA21" s="150"/>
       <c r="BB21" s="177"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54">
       <c r="A22" s="150"/>
-      <c r="B22" s="434"/>
+      <c r="B22" s="427"/>
       <c r="C22" s="117" t="s">
         <v>27</v>
       </c>
@@ -30383,9 +30471,9 @@
       <c r="BA22" s="150"/>
       <c r="BB22" s="177"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:54">
       <c r="A23" s="150"/>
-      <c r="B23" s="434"/>
+      <c r="B23" s="427"/>
       <c r="C23" s="117" t="s">
         <v>27</v>
       </c>
@@ -30447,9 +30535,9 @@
       <c r="BA23" s="150"/>
       <c r="BB23" s="177"/>
     </row>
-    <row r="24" spans="1:54" s="164" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54" s="164" customFormat="1">
       <c r="A24" s="265"/>
-      <c r="B24" s="434"/>
+      <c r="B24" s="427"/>
       <c r="C24" s="117" t="s">
         <v>27</v>
       </c>
@@ -30514,9 +30602,9 @@
       <c r="BA24" s="265"/>
       <c r="BB24" s="177"/>
     </row>
-    <row r="25" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" ht="15.75" thickBot="1">
       <c r="A25" s="150"/>
-      <c r="B25" s="434"/>
+      <c r="B25" s="427"/>
       <c r="C25" s="117" t="s">
         <v>27</v>
       </c>
@@ -30578,9 +30666,9 @@
       <c r="BA25" s="150"/>
       <c r="BB25" s="177"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:54">
       <c r="A26" s="150"/>
-      <c r="B26" s="434" t="s">
+      <c r="B26" s="427" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -30648,9 +30736,9 @@
       <c r="BA26" s="150"/>
       <c r="BB26" s="177"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:54">
       <c r="A27" s="150"/>
-      <c r="B27" s="434"/>
+      <c r="B27" s="427"/>
       <c r="C27" s="7" t="s">
         <v>38</v>
       </c>
@@ -30712,9 +30800,9 @@
       <c r="BA27" s="150"/>
       <c r="BB27" s="177"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:54">
       <c r="A28" s="150"/>
-      <c r="B28" s="434"/>
+      <c r="B28" s="427"/>
       <c r="C28" s="7" t="s">
         <v>38</v>
       </c>
@@ -30776,9 +30864,9 @@
       <c r="BA28" s="150"/>
       <c r="BB28" s="177"/>
     </row>
-    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="15.75" thickBot="1">
       <c r="A29" s="150"/>
-      <c r="B29" s="435"/>
+      <c r="B29" s="472"/>
       <c r="C29" s="7" t="s">
         <v>38</v>
       </c>
@@ -30842,9 +30930,9 @@
       <c r="BA29" s="150"/>
       <c r="BB29" s="177"/>
     </row>
-    <row r="30" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:54" ht="15" customHeight="1">
       <c r="A30" s="150"/>
-      <c r="B30" s="439" t="s">
+      <c r="B30" s="428" t="s">
         <v>106</v>
       </c>
       <c r="C30" s="116" t="s">
@@ -30908,9 +30996,9 @@
       <c r="BA30" s="150"/>
       <c r="BB30" s="177"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:54">
       <c r="A31" s="150"/>
-      <c r="B31" s="489"/>
+      <c r="B31" s="432"/>
       <c r="C31" s="116" t="s">
         <v>44</v>
       </c>
@@ -30972,9 +31060,9 @@
       <c r="BA31" s="150"/>
       <c r="BB31" s="177"/>
     </row>
-    <row r="32" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" ht="15.75" thickBot="1">
       <c r="A32" s="150"/>
-      <c r="B32" s="489"/>
+      <c r="B32" s="432"/>
       <c r="C32" s="363" t="s">
         <v>44</v>
       </c>
@@ -31036,9 +31124,9 @@
       <c r="BA32" s="150"/>
       <c r="BB32" s="177"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:54">
       <c r="A33" s="150"/>
-      <c r="B33" s="490"/>
+      <c r="B33" s="433"/>
       <c r="C33" s="363" t="s">
         <v>44</v>
       </c>
@@ -31099,9 +31187,9 @@
       <c r="BA33" s="150"/>
       <c r="BB33" s="177"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:54">
       <c r="A34" s="150"/>
-      <c r="B34" s="435" t="s">
+      <c r="B34" s="472" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="116" t="s">
@@ -31167,9 +31255,9 @@
       <c r="BA34" s="150"/>
       <c r="BB34" s="177"/>
     </row>
-    <row r="35" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" ht="15.75" thickBot="1">
       <c r="A35" s="150"/>
-      <c r="B35" s="435"/>
+      <c r="B35" s="472"/>
       <c r="C35" s="116" t="s">
         <v>27</v>
       </c>
@@ -31231,7 +31319,7 @@
       <c r="BA35" s="150"/>
       <c r="BB35" s="177"/>
     </row>
-    <row r="36" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" ht="15.75" thickBot="1">
       <c r="A36" s="150"/>
       <c r="B36" s="32" t="s">
         <v>112</v>
@@ -31299,9 +31387,9 @@
       <c r="BA36" s="150"/>
       <c r="BB36" s="177"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:54">
       <c r="A37" s="150"/>
-      <c r="B37" s="435" t="s">
+      <c r="B37" s="472" t="s">
         <v>115</v>
       </c>
       <c r="C37" s="116" t="s">
@@ -31365,9 +31453,9 @@
       <c r="BA37" s="150"/>
       <c r="BB37" s="177"/>
     </row>
-    <row r="38" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" ht="15.75" thickBot="1">
       <c r="A38" s="150"/>
-      <c r="B38" s="435"/>
+      <c r="B38" s="472"/>
       <c r="C38" s="116" t="s">
         <v>20</v>
       </c>
@@ -31429,9 +31517,9 @@
       <c r="BA38" s="150"/>
       <c r="BB38" s="177"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:54">
       <c r="A39" s="150"/>
-      <c r="B39" s="522" t="s">
+      <c r="B39" s="492" t="s">
         <v>118</v>
       </c>
       <c r="C39" s="116" t="s">
@@ -31495,9 +31583,9 @@
       <c r="BA39" s="150"/>
       <c r="BB39" s="177"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:54">
       <c r="A40" s="150"/>
-      <c r="B40" s="522"/>
+      <c r="B40" s="492"/>
       <c r="C40" s="116" t="s">
         <v>113</v>
       </c>
@@ -31559,9 +31647,9 @@
       <c r="BA40" s="150"/>
       <c r="BB40" s="177"/>
     </row>
-    <row r="41" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" ht="15.75" thickBot="1">
       <c r="A41" s="150"/>
-      <c r="B41" s="522"/>
+      <c r="B41" s="492"/>
       <c r="C41" s="116" t="s">
         <v>113</v>
       </c>
@@ -31623,9 +31711,9 @@
       <c r="BA41" s="150"/>
       <c r="BB41" s="177"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:54">
       <c r="A42" s="150"/>
-      <c r="B42" s="500" t="s">
+      <c r="B42" s="493" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="223" t="s">
@@ -31689,9 +31777,9 @@
       <c r="BA42" s="150"/>
       <c r="BB42" s="177"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:54">
       <c r="A43" s="150"/>
-      <c r="B43" s="500"/>
+      <c r="B43" s="493"/>
       <c r="C43" s="223" t="s">
         <v>113</v>
       </c>
@@ -31753,9 +31841,9 @@
       <c r="BA43" s="150"/>
       <c r="BB43" s="177"/>
     </row>
-    <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" ht="15.75" thickBot="1">
       <c r="A44" s="150"/>
-      <c r="B44" s="500"/>
+      <c r="B44" s="493"/>
       <c r="C44" s="223" t="s">
         <v>113</v>
       </c>
@@ -31817,7 +31905,7 @@
       <c r="BA44" s="150"/>
       <c r="BB44" s="177"/>
     </row>
-    <row r="45" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" ht="15.75" thickBot="1">
       <c r="A45" s="150"/>
       <c r="B45" s="121" t="s">
         <v>64</v>
@@ -31883,7 +31971,7 @@
       <c r="BA45" s="150"/>
       <c r="BB45" s="177"/>
     </row>
-    <row r="46" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" ht="15.75" thickBot="1">
       <c r="A46" s="150"/>
       <c r="B46" s="121" t="s">
         <v>27</v>
@@ -31949,7 +32037,7 @@
       <c r="BA46" s="150"/>
       <c r="BB46" s="177"/>
     </row>
-    <row r="47" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" ht="15.75" thickBot="1">
       <c r="A47" s="150"/>
       <c r="B47" s="121" t="s">
         <v>128</v>
@@ -32015,7 +32103,7 @@
       <c r="BA47" s="314"/>
       <c r="BB47" s="315"/>
     </row>
-    <row r="48" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" ht="15.75" thickBot="1">
       <c r="A48" s="150" t="s">
         <v>18</v>
       </c>
@@ -32076,51 +32164,51 @@
       <c r="BA48" s="314"/>
       <c r="BB48" s="315"/>
     </row>
-    <row r="49" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" ht="19.5" thickBot="1">
       <c r="A49" s="150"/>
-      <c r="B49" s="501" t="s">
+      <c r="B49" s="494" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="502"/>
-      <c r="D49" s="502"/>
-      <c r="E49" s="502"/>
-      <c r="F49" s="503"/>
-      <c r="G49" s="477" t="s">
+      <c r="C49" s="495"/>
+      <c r="D49" s="495"/>
+      <c r="E49" s="495"/>
+      <c r="F49" s="496"/>
+      <c r="G49" s="497" t="s">
         <v>132</v>
       </c>
-      <c r="H49" s="478"/>
-      <c r="I49" s="478"/>
-      <c r="J49" s="479"/>
-      <c r="K49" s="477" t="s">
+      <c r="H49" s="498"/>
+      <c r="I49" s="498"/>
+      <c r="J49" s="499"/>
+      <c r="K49" s="497" t="s">
         <v>133</v>
       </c>
-      <c r="L49" s="478"/>
-      <c r="M49" s="478"/>
-      <c r="N49" s="479"/>
-      <c r="O49" s="477" t="s">
+      <c r="L49" s="498"/>
+      <c r="M49" s="498"/>
+      <c r="N49" s="499"/>
+      <c r="O49" s="497" t="s">
         <v>134</v>
       </c>
-      <c r="P49" s="478"/>
-      <c r="Q49" s="478"/>
-      <c r="R49" s="479"/>
-      <c r="S49" s="477" t="s">
+      <c r="P49" s="498"/>
+      <c r="Q49" s="498"/>
+      <c r="R49" s="499"/>
+      <c r="S49" s="497" t="s">
         <v>135</v>
       </c>
-      <c r="T49" s="478"/>
-      <c r="U49" s="478"/>
-      <c r="V49" s="479"/>
-      <c r="W49" s="477" t="s">
+      <c r="T49" s="498"/>
+      <c r="U49" s="498"/>
+      <c r="V49" s="499"/>
+      <c r="W49" s="497" t="s">
         <v>133</v>
       </c>
-      <c r="X49" s="478"/>
-      <c r="Y49" s="478"/>
-      <c r="Z49" s="479"/>
-      <c r="AA49" s="477" t="s">
+      <c r="X49" s="498"/>
+      <c r="Y49" s="498"/>
+      <c r="Z49" s="499"/>
+      <c r="AA49" s="497" t="s">
         <v>136</v>
       </c>
-      <c r="AB49" s="478"/>
-      <c r="AC49" s="478"/>
-      <c r="AD49" s="479"/>
+      <c r="AB49" s="498"/>
+      <c r="AC49" s="498"/>
+      <c r="AD49" s="499"/>
       <c r="AE49" s="192"/>
       <c r="AF49" s="192"/>
       <c r="AG49" s="192"/>
@@ -32146,51 +32234,51 @@
       <c r="BA49" s="192"/>
       <c r="BB49" s="193"/>
     </row>
-    <row r="50" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" ht="19.5" thickBot="1">
       <c r="A50" s="150"/>
-      <c r="B50" s="474" t="s">
+      <c r="B50" s="500" t="s">
         <v>137</v>
       </c>
-      <c r="C50" s="475"/>
-      <c r="D50" s="475"/>
-      <c r="E50" s="475"/>
-      <c r="F50" s="476"/>
-      <c r="G50" s="455" t="s">
+      <c r="C50" s="501"/>
+      <c r="D50" s="501"/>
+      <c r="E50" s="501"/>
+      <c r="F50" s="502"/>
+      <c r="G50" s="503" t="s">
         <v>136</v>
       </c>
-      <c r="H50" s="456"/>
-      <c r="I50" s="456"/>
-      <c r="J50" s="457"/>
-      <c r="K50" s="455" t="s">
+      <c r="H50" s="504"/>
+      <c r="I50" s="504"/>
+      <c r="J50" s="505"/>
+      <c r="K50" s="503" t="s">
         <v>138</v>
       </c>
-      <c r="L50" s="456"/>
-      <c r="M50" s="456"/>
-      <c r="N50" s="457"/>
-      <c r="O50" s="474" t="s">
+      <c r="L50" s="504"/>
+      <c r="M50" s="504"/>
+      <c r="N50" s="505"/>
+      <c r="O50" s="500" t="s">
         <v>139</v>
       </c>
-      <c r="P50" s="475"/>
-      <c r="Q50" s="475"/>
-      <c r="R50" s="476"/>
-      <c r="S50" s="474" t="s">
+      <c r="P50" s="501"/>
+      <c r="Q50" s="501"/>
+      <c r="R50" s="502"/>
+      <c r="S50" s="500" t="s">
         <v>138</v>
       </c>
-      <c r="T50" s="475"/>
-      <c r="U50" s="475"/>
-      <c r="V50" s="476"/>
-      <c r="W50" s="474" t="s">
+      <c r="T50" s="501"/>
+      <c r="U50" s="501"/>
+      <c r="V50" s="502"/>
+      <c r="W50" s="500" t="s">
         <v>138</v>
       </c>
-      <c r="X50" s="475"/>
-      <c r="Y50" s="475"/>
-      <c r="Z50" s="476"/>
-      <c r="AA50" s="474" t="s">
+      <c r="X50" s="501"/>
+      <c r="Y50" s="501"/>
+      <c r="Z50" s="502"/>
+      <c r="AA50" s="500" t="s">
         <v>138</v>
       </c>
-      <c r="AB50" s="475"/>
-      <c r="AC50" s="475"/>
-      <c r="AD50" s="476"/>
+      <c r="AB50" s="501"/>
+      <c r="AC50" s="501"/>
+      <c r="AD50" s="502"/>
       <c r="AE50" s="192"/>
       <c r="AF50" s="192"/>
       <c r="AG50" s="192"/>
@@ -32216,47 +32304,47 @@
       <c r="BA50" s="192"/>
       <c r="BB50" s="193"/>
     </row>
-    <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1">
       <c r="A51" s="150"/>
-      <c r="B51" s="449" t="s">
+      <c r="B51" s="506" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="450"/>
-      <c r="D51" s="450"/>
-      <c r="E51" s="450"/>
-      <c r="F51" s="451"/>
-      <c r="G51" s="458" t="s">
+      <c r="C51" s="507"/>
+      <c r="D51" s="507"/>
+      <c r="E51" s="507"/>
+      <c r="F51" s="508"/>
+      <c r="G51" s="509" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="459"/>
-      <c r="I51" s="459"/>
-      <c r="J51" s="460"/>
-      <c r="K51" s="483" t="s">
+      <c r="H51" s="510"/>
+      <c r="I51" s="510"/>
+      <c r="J51" s="511"/>
+      <c r="K51" s="512" t="s">
         <v>142</v>
       </c>
-      <c r="L51" s="484"/>
-      <c r="M51" s="484"/>
-      <c r="N51" s="485"/>
-      <c r="O51" s="449" t="s">
+      <c r="L51" s="513"/>
+      <c r="M51" s="513"/>
+      <c r="N51" s="514"/>
+      <c r="O51" s="506" t="s">
         <v>143</v>
       </c>
-      <c r="P51" s="450"/>
-      <c r="Q51" s="450"/>
-      <c r="R51" s="451"/>
-      <c r="S51" s="449"/>
-      <c r="T51" s="450"/>
-      <c r="U51" s="450"/>
-      <c r="V51" s="451"/>
-      <c r="W51" s="449" t="s">
+      <c r="P51" s="507"/>
+      <c r="Q51" s="507"/>
+      <c r="R51" s="508"/>
+      <c r="S51" s="506"/>
+      <c r="T51" s="507"/>
+      <c r="U51" s="507"/>
+      <c r="V51" s="508"/>
+      <c r="W51" s="506" t="s">
         <v>143</v>
       </c>
-      <c r="X51" s="450"/>
-      <c r="Y51" s="450"/>
-      <c r="Z51" s="451"/>
-      <c r="AA51" s="449"/>
-      <c r="AB51" s="450"/>
-      <c r="AC51" s="450"/>
-      <c r="AD51" s="524"/>
+      <c r="X51" s="507"/>
+      <c r="Y51" s="507"/>
+      <c r="Z51" s="508"/>
+      <c r="AA51" s="506"/>
+      <c r="AB51" s="507"/>
+      <c r="AC51" s="507"/>
+      <c r="AD51" s="515"/>
       <c r="AE51" s="192"/>
       <c r="AF51" s="192"/>
       <c r="AG51" s="192"/>
@@ -32282,45 +32370,45 @@
       <c r="BA51" s="192"/>
       <c r="BB51" s="193"/>
     </row>
-    <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1">
       <c r="A52" s="150"/>
-      <c r="B52" s="452" t="s">
+      <c r="B52" s="516" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="453"/>
-      <c r="D52" s="453"/>
-      <c r="E52" s="453"/>
-      <c r="F52" s="454"/>
-      <c r="G52" s="480" t="s">
+      <c r="C52" s="517"/>
+      <c r="D52" s="517"/>
+      <c r="E52" s="517"/>
+      <c r="F52" s="518"/>
+      <c r="G52" s="519" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="481"/>
-      <c r="I52" s="481"/>
-      <c r="J52" s="482"/>
-      <c r="K52" s="486" t="s">
+      <c r="H52" s="520"/>
+      <c r="I52" s="520"/>
+      <c r="J52" s="521"/>
+      <c r="K52" s="429" t="s">
         <v>146</v>
       </c>
-      <c r="L52" s="487"/>
-      <c r="M52" s="487"/>
-      <c r="N52" s="488"/>
-      <c r="O52" s="486" t="s">
+      <c r="L52" s="430"/>
+      <c r="M52" s="430"/>
+      <c r="N52" s="431"/>
+      <c r="O52" s="429" t="s">
         <v>147</v>
       </c>
-      <c r="P52" s="487"/>
-      <c r="Q52" s="487"/>
-      <c r="R52" s="488"/>
-      <c r="S52" s="452"/>
-      <c r="T52" s="453"/>
-      <c r="U52" s="453"/>
-      <c r="V52" s="454"/>
-      <c r="W52" s="452"/>
-      <c r="X52" s="453"/>
-      <c r="Y52" s="453"/>
-      <c r="Z52" s="454"/>
-      <c r="AA52" s="452"/>
-      <c r="AB52" s="453"/>
-      <c r="AC52" s="453"/>
-      <c r="AD52" s="523"/>
+      <c r="P52" s="430"/>
+      <c r="Q52" s="430"/>
+      <c r="R52" s="431"/>
+      <c r="S52" s="516"/>
+      <c r="T52" s="517"/>
+      <c r="U52" s="517"/>
+      <c r="V52" s="518"/>
+      <c r="W52" s="516"/>
+      <c r="X52" s="517"/>
+      <c r="Y52" s="517"/>
+      <c r="Z52" s="518"/>
+      <c r="AA52" s="516"/>
+      <c r="AB52" s="517"/>
+      <c r="AC52" s="517"/>
+      <c r="AD52" s="522"/>
       <c r="AE52" s="192"/>
       <c r="AF52" s="192"/>
       <c r="AG52" s="192"/>
@@ -32346,51 +32434,51 @@
       <c r="BA52" s="192"/>
       <c r="BB52" s="193"/>
     </row>
-    <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:54" ht="15" customHeight="1">
       <c r="A53" s="150"/>
-      <c r="B53" s="504" t="s">
+      <c r="B53" s="523" t="s">
         <v>148</v>
       </c>
-      <c r="C53" s="505"/>
-      <c r="D53" s="505"/>
-      <c r="E53" s="505"/>
-      <c r="F53" s="506"/>
-      <c r="G53" s="513" t="s">
+      <c r="C53" s="524"/>
+      <c r="D53" s="524"/>
+      <c r="E53" s="524"/>
+      <c r="F53" s="525"/>
+      <c r="G53" s="443" t="s">
         <v>149</v>
       </c>
-      <c r="H53" s="514"/>
-      <c r="I53" s="514"/>
-      <c r="J53" s="515"/>
-      <c r="K53" s="513" t="s">
+      <c r="H53" s="444"/>
+      <c r="I53" s="444"/>
+      <c r="J53" s="445"/>
+      <c r="K53" s="443" t="s">
         <v>150</v>
       </c>
-      <c r="L53" s="514"/>
-      <c r="M53" s="514"/>
-      <c r="N53" s="515"/>
-      <c r="O53" s="491" t="s">
+      <c r="L53" s="444"/>
+      <c r="M53" s="444"/>
+      <c r="N53" s="445"/>
+      <c r="O53" s="434" t="s">
         <v>151</v>
       </c>
-      <c r="P53" s="492"/>
-      <c r="Q53" s="492"/>
-      <c r="R53" s="493"/>
-      <c r="S53" s="491" t="s">
+      <c r="P53" s="435"/>
+      <c r="Q53" s="435"/>
+      <c r="R53" s="436"/>
+      <c r="S53" s="434" t="s">
         <v>152</v>
       </c>
-      <c r="T53" s="492"/>
-      <c r="U53" s="492"/>
-      <c r="V53" s="493"/>
-      <c r="W53" s="491" t="s">
+      <c r="T53" s="435"/>
+      <c r="U53" s="435"/>
+      <c r="V53" s="436"/>
+      <c r="W53" s="434" t="s">
         <v>153</v>
       </c>
-      <c r="X53" s="492"/>
-      <c r="Y53" s="492"/>
-      <c r="Z53" s="493"/>
-      <c r="AA53" s="491" t="s">
+      <c r="X53" s="435"/>
+      <c r="Y53" s="435"/>
+      <c r="Z53" s="436"/>
+      <c r="AA53" s="434" t="s">
         <v>154</v>
       </c>
-      <c r="AB53" s="492"/>
-      <c r="AC53" s="492"/>
-      <c r="AD53" s="493"/>
+      <c r="AB53" s="435"/>
+      <c r="AC53" s="435"/>
+      <c r="AD53" s="436"/>
       <c r="AE53" s="150"/>
       <c r="AF53" s="150"/>
       <c r="AG53" s="150"/>
@@ -32418,37 +32506,37 @@
       <c r="BA53" s="150"/>
       <c r="BB53" s="150"/>
     </row>
-    <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:54" ht="15" customHeight="1">
       <c r="A54" s="150"/>
-      <c r="B54" s="507"/>
-      <c r="C54" s="508"/>
-      <c r="D54" s="508"/>
-      <c r="E54" s="508"/>
-      <c r="F54" s="509"/>
-      <c r="G54" s="516"/>
-      <c r="H54" s="517"/>
-      <c r="I54" s="517"/>
-      <c r="J54" s="518"/>
-      <c r="K54" s="516"/>
-      <c r="L54" s="517"/>
-      <c r="M54" s="517"/>
-      <c r="N54" s="518"/>
-      <c r="O54" s="494"/>
-      <c r="P54" s="495"/>
-      <c r="Q54" s="495"/>
-      <c r="R54" s="496"/>
-      <c r="S54" s="494"/>
-      <c r="T54" s="495"/>
-      <c r="U54" s="495"/>
-      <c r="V54" s="496"/>
-      <c r="W54" s="494"/>
-      <c r="X54" s="495"/>
-      <c r="Y54" s="495"/>
-      <c r="Z54" s="496"/>
-      <c r="AA54" s="494"/>
-      <c r="AB54" s="495"/>
-      <c r="AC54" s="495"/>
-      <c r="AD54" s="496"/>
+      <c r="B54" s="526"/>
+      <c r="C54" s="527"/>
+      <c r="D54" s="527"/>
+      <c r="E54" s="527"/>
+      <c r="F54" s="528"/>
+      <c r="G54" s="446"/>
+      <c r="H54" s="447"/>
+      <c r="I54" s="447"/>
+      <c r="J54" s="448"/>
+      <c r="K54" s="446"/>
+      <c r="L54" s="447"/>
+      <c r="M54" s="447"/>
+      <c r="N54" s="448"/>
+      <c r="O54" s="437"/>
+      <c r="P54" s="438"/>
+      <c r="Q54" s="438"/>
+      <c r="R54" s="439"/>
+      <c r="S54" s="437"/>
+      <c r="T54" s="438"/>
+      <c r="U54" s="438"/>
+      <c r="V54" s="439"/>
+      <c r="W54" s="437"/>
+      <c r="X54" s="438"/>
+      <c r="Y54" s="438"/>
+      <c r="Z54" s="439"/>
+      <c r="AA54" s="437"/>
+      <c r="AB54" s="438"/>
+      <c r="AC54" s="438"/>
+      <c r="AD54" s="439"/>
       <c r="AE54" s="150"/>
       <c r="AF54" s="150"/>
       <c r="AG54" s="150"/>
@@ -32474,36 +32562,36 @@
       <c r="BA54" s="150"/>
       <c r="BB54" s="150"/>
     </row>
-    <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="507"/>
-      <c r="C55" s="508"/>
-      <c r="D55" s="508"/>
-      <c r="E55" s="508"/>
-      <c r="F55" s="509"/>
-      <c r="G55" s="516"/>
-      <c r="H55" s="517"/>
-      <c r="I55" s="517"/>
-      <c r="J55" s="518"/>
-      <c r="K55" s="516"/>
-      <c r="L55" s="517"/>
-      <c r="M55" s="517"/>
-      <c r="N55" s="518"/>
-      <c r="O55" s="494"/>
-      <c r="P55" s="495"/>
-      <c r="Q55" s="495"/>
-      <c r="R55" s="496"/>
-      <c r="S55" s="494"/>
-      <c r="T55" s="495"/>
-      <c r="U55" s="495"/>
-      <c r="V55" s="496"/>
-      <c r="W55" s="494"/>
-      <c r="X55" s="495"/>
-      <c r="Y55" s="495"/>
-      <c r="Z55" s="496"/>
-      <c r="AA55" s="494"/>
-      <c r="AB55" s="495"/>
-      <c r="AC55" s="495"/>
-      <c r="AD55" s="496"/>
+    <row r="55" spans="1:54" ht="15" customHeight="1">
+      <c r="B55" s="526"/>
+      <c r="C55" s="527"/>
+      <c r="D55" s="527"/>
+      <c r="E55" s="527"/>
+      <c r="F55" s="528"/>
+      <c r="G55" s="446"/>
+      <c r="H55" s="447"/>
+      <c r="I55" s="447"/>
+      <c r="J55" s="448"/>
+      <c r="K55" s="446"/>
+      <c r="L55" s="447"/>
+      <c r="M55" s="447"/>
+      <c r="N55" s="448"/>
+      <c r="O55" s="437"/>
+      <c r="P55" s="438"/>
+      <c r="Q55" s="438"/>
+      <c r="R55" s="439"/>
+      <c r="S55" s="437"/>
+      <c r="T55" s="438"/>
+      <c r="U55" s="438"/>
+      <c r="V55" s="439"/>
+      <c r="W55" s="437"/>
+      <c r="X55" s="438"/>
+      <c r="Y55" s="438"/>
+      <c r="Z55" s="439"/>
+      <c r="AA55" s="437"/>
+      <c r="AB55" s="438"/>
+      <c r="AC55" s="438"/>
+      <c r="AD55" s="439"/>
       <c r="AE55" s="150"/>
       <c r="AF55" s="150"/>
       <c r="AG55" s="150"/>
@@ -32529,439 +32617,439 @@
       <c r="BA55" s="150"/>
       <c r="BB55" s="150"/>
     </row>
-    <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="507"/>
-      <c r="C56" s="508"/>
-      <c r="D56" s="508"/>
-      <c r="E56" s="508"/>
-      <c r="F56" s="509"/>
-      <c r="G56" s="516"/>
-      <c r="H56" s="517"/>
-      <c r="I56" s="517"/>
-      <c r="J56" s="518"/>
-      <c r="K56" s="516"/>
-      <c r="L56" s="517"/>
-      <c r="M56" s="517"/>
-      <c r="N56" s="518"/>
-      <c r="O56" s="494"/>
-      <c r="P56" s="495"/>
-      <c r="Q56" s="495"/>
-      <c r="R56" s="496"/>
-      <c r="S56" s="494"/>
-      <c r="T56" s="495"/>
-      <c r="U56" s="495"/>
-      <c r="V56" s="496"/>
-      <c r="W56" s="494"/>
-      <c r="X56" s="495"/>
-      <c r="Y56" s="495"/>
-      <c r="Z56" s="496"/>
-      <c r="AA56" s="494"/>
-      <c r="AB56" s="495"/>
-      <c r="AC56" s="495"/>
-      <c r="AD56" s="496"/>
+    <row r="56" spans="1:54" ht="15" customHeight="1">
+      <c r="B56" s="526"/>
+      <c r="C56" s="527"/>
+      <c r="D56" s="527"/>
+      <c r="E56" s="527"/>
+      <c r="F56" s="528"/>
+      <c r="G56" s="446"/>
+      <c r="H56" s="447"/>
+      <c r="I56" s="447"/>
+      <c r="J56" s="448"/>
+      <c r="K56" s="446"/>
+      <c r="L56" s="447"/>
+      <c r="M56" s="447"/>
+      <c r="N56" s="448"/>
+      <c r="O56" s="437"/>
+      <c r="P56" s="438"/>
+      <c r="Q56" s="438"/>
+      <c r="R56" s="439"/>
+      <c r="S56" s="437"/>
+      <c r="T56" s="438"/>
+      <c r="U56" s="438"/>
+      <c r="V56" s="439"/>
+      <c r="W56" s="437"/>
+      <c r="X56" s="438"/>
+      <c r="Y56" s="438"/>
+      <c r="Z56" s="439"/>
+      <c r="AA56" s="437"/>
+      <c r="AB56" s="438"/>
+      <c r="AC56" s="438"/>
+      <c r="AD56" s="439"/>
     </row>
-    <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="507"/>
-      <c r="C57" s="508"/>
-      <c r="D57" s="508"/>
-      <c r="E57" s="508"/>
-      <c r="F57" s="509"/>
-      <c r="G57" s="516"/>
-      <c r="H57" s="517"/>
-      <c r="I57" s="517"/>
-      <c r="J57" s="518"/>
-      <c r="K57" s="516"/>
-      <c r="L57" s="517"/>
-      <c r="M57" s="517"/>
-      <c r="N57" s="518"/>
-      <c r="O57" s="494"/>
-      <c r="P57" s="495"/>
-      <c r="Q57" s="495"/>
-      <c r="R57" s="496"/>
-      <c r="S57" s="494"/>
-      <c r="T57" s="495"/>
-      <c r="U57" s="495"/>
-      <c r="V57" s="496"/>
-      <c r="W57" s="494"/>
-      <c r="X57" s="495"/>
-      <c r="Y57" s="495"/>
-      <c r="Z57" s="496"/>
-      <c r="AA57" s="494"/>
-      <c r="AB57" s="495"/>
-      <c r="AC57" s="495"/>
-      <c r="AD57" s="496"/>
+    <row r="57" spans="1:54" ht="15" customHeight="1">
+      <c r="B57" s="526"/>
+      <c r="C57" s="527"/>
+      <c r="D57" s="527"/>
+      <c r="E57" s="527"/>
+      <c r="F57" s="528"/>
+      <c r="G57" s="446"/>
+      <c r="H57" s="447"/>
+      <c r="I57" s="447"/>
+      <c r="J57" s="448"/>
+      <c r="K57" s="446"/>
+      <c r="L57" s="447"/>
+      <c r="M57" s="447"/>
+      <c r="N57" s="448"/>
+      <c r="O57" s="437"/>
+      <c r="P57" s="438"/>
+      <c r="Q57" s="438"/>
+      <c r="R57" s="439"/>
+      <c r="S57" s="437"/>
+      <c r="T57" s="438"/>
+      <c r="U57" s="438"/>
+      <c r="V57" s="439"/>
+      <c r="W57" s="437"/>
+      <c r="X57" s="438"/>
+      <c r="Y57" s="438"/>
+      <c r="Z57" s="439"/>
+      <c r="AA57" s="437"/>
+      <c r="AB57" s="438"/>
+      <c r="AC57" s="438"/>
+      <c r="AD57" s="439"/>
     </row>
-    <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="507"/>
-      <c r="C58" s="508"/>
-      <c r="D58" s="508"/>
-      <c r="E58" s="508"/>
-      <c r="F58" s="509"/>
-      <c r="G58" s="516"/>
-      <c r="H58" s="517"/>
-      <c r="I58" s="517"/>
-      <c r="J58" s="518"/>
-      <c r="K58" s="516"/>
-      <c r="L58" s="517"/>
-      <c r="M58" s="517"/>
-      <c r="N58" s="518"/>
-      <c r="O58" s="494"/>
-      <c r="P58" s="495"/>
-      <c r="Q58" s="495"/>
-      <c r="R58" s="496"/>
-      <c r="S58" s="494"/>
-      <c r="T58" s="495"/>
-      <c r="U58" s="495"/>
-      <c r="V58" s="496"/>
-      <c r="W58" s="494"/>
-      <c r="X58" s="495"/>
-      <c r="Y58" s="495"/>
-      <c r="Z58" s="496"/>
-      <c r="AA58" s="494"/>
-      <c r="AB58" s="495"/>
-      <c r="AC58" s="495"/>
-      <c r="AD58" s="496"/>
+    <row r="58" spans="1:54" ht="15" customHeight="1">
+      <c r="B58" s="526"/>
+      <c r="C58" s="527"/>
+      <c r="D58" s="527"/>
+      <c r="E58" s="527"/>
+      <c r="F58" s="528"/>
+      <c r="G58" s="446"/>
+      <c r="H58" s="447"/>
+      <c r="I58" s="447"/>
+      <c r="J58" s="448"/>
+      <c r="K58" s="446"/>
+      <c r="L58" s="447"/>
+      <c r="M58" s="447"/>
+      <c r="N58" s="448"/>
+      <c r="O58" s="437"/>
+      <c r="P58" s="438"/>
+      <c r="Q58" s="438"/>
+      <c r="R58" s="439"/>
+      <c r="S58" s="437"/>
+      <c r="T58" s="438"/>
+      <c r="U58" s="438"/>
+      <c r="V58" s="439"/>
+      <c r="W58" s="437"/>
+      <c r="X58" s="438"/>
+      <c r="Y58" s="438"/>
+      <c r="Z58" s="439"/>
+      <c r="AA58" s="437"/>
+      <c r="AB58" s="438"/>
+      <c r="AC58" s="438"/>
+      <c r="AD58" s="439"/>
     </row>
-    <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="507"/>
-      <c r="C59" s="508"/>
-      <c r="D59" s="508"/>
-      <c r="E59" s="508"/>
-      <c r="F59" s="509"/>
-      <c r="G59" s="516"/>
-      <c r="H59" s="517"/>
-      <c r="I59" s="517"/>
-      <c r="J59" s="518"/>
-      <c r="K59" s="516"/>
-      <c r="L59" s="517"/>
-      <c r="M59" s="517"/>
-      <c r="N59" s="518"/>
-      <c r="O59" s="494"/>
-      <c r="P59" s="495"/>
-      <c r="Q59" s="495"/>
-      <c r="R59" s="496"/>
-      <c r="S59" s="494"/>
-      <c r="T59" s="495"/>
-      <c r="U59" s="495"/>
-      <c r="V59" s="496"/>
-      <c r="W59" s="494"/>
-      <c r="X59" s="495"/>
-      <c r="Y59" s="495"/>
-      <c r="Z59" s="496"/>
-      <c r="AA59" s="494"/>
-      <c r="AB59" s="495"/>
-      <c r="AC59" s="495"/>
-      <c r="AD59" s="496"/>
+    <row r="59" spans="1:54" ht="15" customHeight="1">
+      <c r="B59" s="526"/>
+      <c r="C59" s="527"/>
+      <c r="D59" s="527"/>
+      <c r="E59" s="527"/>
+      <c r="F59" s="528"/>
+      <c r="G59" s="446"/>
+      <c r="H59" s="447"/>
+      <c r="I59" s="447"/>
+      <c r="J59" s="448"/>
+      <c r="K59" s="446"/>
+      <c r="L59" s="447"/>
+      <c r="M59" s="447"/>
+      <c r="N59" s="448"/>
+      <c r="O59" s="437"/>
+      <c r="P59" s="438"/>
+      <c r="Q59" s="438"/>
+      <c r="R59" s="439"/>
+      <c r="S59" s="437"/>
+      <c r="T59" s="438"/>
+      <c r="U59" s="438"/>
+      <c r="V59" s="439"/>
+      <c r="W59" s="437"/>
+      <c r="X59" s="438"/>
+      <c r="Y59" s="438"/>
+      <c r="Z59" s="439"/>
+      <c r="AA59" s="437"/>
+      <c r="AB59" s="438"/>
+      <c r="AC59" s="438"/>
+      <c r="AD59" s="439"/>
     </row>
-    <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="507"/>
-      <c r="C60" s="508"/>
-      <c r="D60" s="508"/>
-      <c r="E60" s="508"/>
-      <c r="F60" s="509"/>
-      <c r="G60" s="516"/>
-      <c r="H60" s="517"/>
-      <c r="I60" s="517"/>
-      <c r="J60" s="518"/>
-      <c r="K60" s="516"/>
-      <c r="L60" s="517"/>
-      <c r="M60" s="517"/>
-      <c r="N60" s="518"/>
-      <c r="O60" s="494"/>
-      <c r="P60" s="495"/>
-      <c r="Q60" s="495"/>
-      <c r="R60" s="496"/>
-      <c r="S60" s="494"/>
-      <c r="T60" s="495"/>
-      <c r="U60" s="495"/>
-      <c r="V60" s="496"/>
-      <c r="W60" s="494"/>
-      <c r="X60" s="495"/>
-      <c r="Y60" s="495"/>
-      <c r="Z60" s="496"/>
-      <c r="AA60" s="494"/>
-      <c r="AB60" s="495"/>
-      <c r="AC60" s="495"/>
-      <c r="AD60" s="496"/>
+    <row r="60" spans="1:54" ht="15" customHeight="1">
+      <c r="B60" s="526"/>
+      <c r="C60" s="527"/>
+      <c r="D60" s="527"/>
+      <c r="E60" s="527"/>
+      <c r="F60" s="528"/>
+      <c r="G60" s="446"/>
+      <c r="H60" s="447"/>
+      <c r="I60" s="447"/>
+      <c r="J60" s="448"/>
+      <c r="K60" s="446"/>
+      <c r="L60" s="447"/>
+      <c r="M60" s="447"/>
+      <c r="N60" s="448"/>
+      <c r="O60" s="437"/>
+      <c r="P60" s="438"/>
+      <c r="Q60" s="438"/>
+      <c r="R60" s="439"/>
+      <c r="S60" s="437"/>
+      <c r="T60" s="438"/>
+      <c r="U60" s="438"/>
+      <c r="V60" s="439"/>
+      <c r="W60" s="437"/>
+      <c r="X60" s="438"/>
+      <c r="Y60" s="438"/>
+      <c r="Z60" s="439"/>
+      <c r="AA60" s="437"/>
+      <c r="AB60" s="438"/>
+      <c r="AC60" s="438"/>
+      <c r="AD60" s="439"/>
     </row>
-    <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="507"/>
-      <c r="C61" s="508"/>
-      <c r="D61" s="508"/>
-      <c r="E61" s="508"/>
-      <c r="F61" s="509"/>
-      <c r="G61" s="516"/>
-      <c r="H61" s="517"/>
-      <c r="I61" s="517"/>
-      <c r="J61" s="518"/>
-      <c r="K61" s="516"/>
-      <c r="L61" s="517"/>
-      <c r="M61" s="517"/>
-      <c r="N61" s="518"/>
-      <c r="O61" s="494"/>
-      <c r="P61" s="495"/>
-      <c r="Q61" s="495"/>
-      <c r="R61" s="496"/>
-      <c r="S61" s="494"/>
-      <c r="T61" s="495"/>
-      <c r="U61" s="495"/>
-      <c r="V61" s="496"/>
-      <c r="W61" s="494"/>
-      <c r="X61" s="495"/>
-      <c r="Y61" s="495"/>
-      <c r="Z61" s="496"/>
-      <c r="AA61" s="494"/>
-      <c r="AB61" s="495"/>
-      <c r="AC61" s="495"/>
-      <c r="AD61" s="496"/>
+    <row r="61" spans="1:54" ht="15" customHeight="1">
+      <c r="B61" s="526"/>
+      <c r="C61" s="527"/>
+      <c r="D61" s="527"/>
+      <c r="E61" s="527"/>
+      <c r="F61" s="528"/>
+      <c r="G61" s="446"/>
+      <c r="H61" s="447"/>
+      <c r="I61" s="447"/>
+      <c r="J61" s="448"/>
+      <c r="K61" s="446"/>
+      <c r="L61" s="447"/>
+      <c r="M61" s="447"/>
+      <c r="N61" s="448"/>
+      <c r="O61" s="437"/>
+      <c r="P61" s="438"/>
+      <c r="Q61" s="438"/>
+      <c r="R61" s="439"/>
+      <c r="S61" s="437"/>
+      <c r="T61" s="438"/>
+      <c r="U61" s="438"/>
+      <c r="V61" s="439"/>
+      <c r="W61" s="437"/>
+      <c r="X61" s="438"/>
+      <c r="Y61" s="438"/>
+      <c r="Z61" s="439"/>
+      <c r="AA61" s="437"/>
+      <c r="AB61" s="438"/>
+      <c r="AC61" s="438"/>
+      <c r="AD61" s="439"/>
     </row>
-    <row r="62" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="507"/>
-      <c r="C62" s="508"/>
-      <c r="D62" s="508"/>
-      <c r="E62" s="508"/>
-      <c r="F62" s="509"/>
-      <c r="G62" s="516"/>
-      <c r="H62" s="517"/>
-      <c r="I62" s="517"/>
-      <c r="J62" s="518"/>
-      <c r="K62" s="516"/>
-      <c r="L62" s="517"/>
-      <c r="M62" s="517"/>
-      <c r="N62" s="518"/>
-      <c r="O62" s="494"/>
-      <c r="P62" s="495"/>
-      <c r="Q62" s="495"/>
-      <c r="R62" s="496"/>
-      <c r="S62" s="494"/>
-      <c r="T62" s="495"/>
-      <c r="U62" s="495"/>
-      <c r="V62" s="496"/>
-      <c r="W62" s="494"/>
-      <c r="X62" s="495"/>
-      <c r="Y62" s="495"/>
-      <c r="Z62" s="496"/>
-      <c r="AA62" s="494"/>
-      <c r="AB62" s="495"/>
-      <c r="AC62" s="495"/>
-      <c r="AD62" s="496"/>
+    <row r="62" spans="1:54" ht="52.5" customHeight="1">
+      <c r="B62" s="526"/>
+      <c r="C62" s="527"/>
+      <c r="D62" s="527"/>
+      <c r="E62" s="527"/>
+      <c r="F62" s="528"/>
+      <c r="G62" s="446"/>
+      <c r="H62" s="447"/>
+      <c r="I62" s="447"/>
+      <c r="J62" s="448"/>
+      <c r="K62" s="446"/>
+      <c r="L62" s="447"/>
+      <c r="M62" s="447"/>
+      <c r="N62" s="448"/>
+      <c r="O62" s="437"/>
+      <c r="P62" s="438"/>
+      <c r="Q62" s="438"/>
+      <c r="R62" s="439"/>
+      <c r="S62" s="437"/>
+      <c r="T62" s="438"/>
+      <c r="U62" s="438"/>
+      <c r="V62" s="439"/>
+      <c r="W62" s="437"/>
+      <c r="X62" s="438"/>
+      <c r="Y62" s="438"/>
+      <c r="Z62" s="439"/>
+      <c r="AA62" s="437"/>
+      <c r="AB62" s="438"/>
+      <c r="AC62" s="438"/>
+      <c r="AD62" s="439"/>
     </row>
-    <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="507"/>
-      <c r="C63" s="508"/>
-      <c r="D63" s="508"/>
-      <c r="E63" s="508"/>
-      <c r="F63" s="509"/>
-      <c r="G63" s="516"/>
-      <c r="H63" s="517"/>
-      <c r="I63" s="517"/>
-      <c r="J63" s="518"/>
-      <c r="K63" s="516"/>
-      <c r="L63" s="517"/>
-      <c r="M63" s="517"/>
-      <c r="N63" s="518"/>
-      <c r="O63" s="494"/>
-      <c r="P63" s="495"/>
-      <c r="Q63" s="495"/>
-      <c r="R63" s="496"/>
-      <c r="S63" s="494"/>
-      <c r="T63" s="495"/>
-      <c r="U63" s="495"/>
-      <c r="V63" s="496"/>
-      <c r="W63" s="494"/>
-      <c r="X63" s="495"/>
-      <c r="Y63" s="495"/>
-      <c r="Z63" s="496"/>
-      <c r="AA63" s="494"/>
-      <c r="AB63" s="495"/>
-      <c r="AC63" s="495"/>
-      <c r="AD63" s="496"/>
+    <row r="63" spans="1:54" ht="15" customHeight="1">
+      <c r="B63" s="526"/>
+      <c r="C63" s="527"/>
+      <c r="D63" s="527"/>
+      <c r="E63" s="527"/>
+      <c r="F63" s="528"/>
+      <c r="G63" s="446"/>
+      <c r="H63" s="447"/>
+      <c r="I63" s="447"/>
+      <c r="J63" s="448"/>
+      <c r="K63" s="446"/>
+      <c r="L63" s="447"/>
+      <c r="M63" s="447"/>
+      <c r="N63" s="448"/>
+      <c r="O63" s="437"/>
+      <c r="P63" s="438"/>
+      <c r="Q63" s="438"/>
+      <c r="R63" s="439"/>
+      <c r="S63" s="437"/>
+      <c r="T63" s="438"/>
+      <c r="U63" s="438"/>
+      <c r="V63" s="439"/>
+      <c r="W63" s="437"/>
+      <c r="X63" s="438"/>
+      <c r="Y63" s="438"/>
+      <c r="Z63" s="439"/>
+      <c r="AA63" s="437"/>
+      <c r="AB63" s="438"/>
+      <c r="AC63" s="438"/>
+      <c r="AD63" s="439"/>
     </row>
-    <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="507"/>
-      <c r="C64" s="508"/>
-      <c r="D64" s="508"/>
-      <c r="E64" s="508"/>
-      <c r="F64" s="509"/>
-      <c r="G64" s="516"/>
-      <c r="H64" s="517"/>
-      <c r="I64" s="517"/>
-      <c r="J64" s="518"/>
-      <c r="K64" s="516"/>
-      <c r="L64" s="517"/>
-      <c r="M64" s="517"/>
-      <c r="N64" s="518"/>
-      <c r="O64" s="494"/>
-      <c r="P64" s="495"/>
-      <c r="Q64" s="495"/>
-      <c r="R64" s="496"/>
-      <c r="S64" s="494"/>
-      <c r="T64" s="495"/>
-      <c r="U64" s="495"/>
-      <c r="V64" s="496"/>
-      <c r="W64" s="494"/>
-      <c r="X64" s="495"/>
-      <c r="Y64" s="495"/>
-      <c r="Z64" s="496"/>
-      <c r="AA64" s="494"/>
-      <c r="AB64" s="495"/>
-      <c r="AC64" s="495"/>
-      <c r="AD64" s="496"/>
+    <row r="64" spans="1:54" ht="15" customHeight="1">
+      <c r="B64" s="526"/>
+      <c r="C64" s="527"/>
+      <c r="D64" s="527"/>
+      <c r="E64" s="527"/>
+      <c r="F64" s="528"/>
+      <c r="G64" s="446"/>
+      <c r="H64" s="447"/>
+      <c r="I64" s="447"/>
+      <c r="J64" s="448"/>
+      <c r="K64" s="446"/>
+      <c r="L64" s="447"/>
+      <c r="M64" s="447"/>
+      <c r="N64" s="448"/>
+      <c r="O64" s="437"/>
+      <c r="P64" s="438"/>
+      <c r="Q64" s="438"/>
+      <c r="R64" s="439"/>
+      <c r="S64" s="437"/>
+      <c r="T64" s="438"/>
+      <c r="U64" s="438"/>
+      <c r="V64" s="439"/>
+      <c r="W64" s="437"/>
+      <c r="X64" s="438"/>
+      <c r="Y64" s="438"/>
+      <c r="Z64" s="439"/>
+      <c r="AA64" s="437"/>
+      <c r="AB64" s="438"/>
+      <c r="AC64" s="438"/>
+      <c r="AD64" s="439"/>
     </row>
-    <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="507"/>
-      <c r="C65" s="508"/>
-      <c r="D65" s="508"/>
-      <c r="E65" s="508"/>
-      <c r="F65" s="509"/>
-      <c r="G65" s="516"/>
-      <c r="H65" s="517"/>
-      <c r="I65" s="517"/>
-      <c r="J65" s="518"/>
-      <c r="K65" s="516"/>
-      <c r="L65" s="517"/>
-      <c r="M65" s="517"/>
-      <c r="N65" s="518"/>
-      <c r="O65" s="494"/>
-      <c r="P65" s="495"/>
-      <c r="Q65" s="495"/>
-      <c r="R65" s="496"/>
-      <c r="S65" s="494"/>
-      <c r="T65" s="495"/>
-      <c r="U65" s="495"/>
-      <c r="V65" s="496"/>
-      <c r="W65" s="494"/>
-      <c r="X65" s="495"/>
-      <c r="Y65" s="495"/>
-      <c r="Z65" s="496"/>
-      <c r="AA65" s="494"/>
-      <c r="AB65" s="495"/>
-      <c r="AC65" s="495"/>
-      <c r="AD65" s="496"/>
+    <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1">
+      <c r="B65" s="526"/>
+      <c r="C65" s="527"/>
+      <c r="D65" s="527"/>
+      <c r="E65" s="527"/>
+      <c r="F65" s="528"/>
+      <c r="G65" s="446"/>
+      <c r="H65" s="447"/>
+      <c r="I65" s="447"/>
+      <c r="J65" s="448"/>
+      <c r="K65" s="446"/>
+      <c r="L65" s="447"/>
+      <c r="M65" s="447"/>
+      <c r="N65" s="448"/>
+      <c r="O65" s="437"/>
+      <c r="P65" s="438"/>
+      <c r="Q65" s="438"/>
+      <c r="R65" s="439"/>
+      <c r="S65" s="437"/>
+      <c r="T65" s="438"/>
+      <c r="U65" s="438"/>
+      <c r="V65" s="439"/>
+      <c r="W65" s="437"/>
+      <c r="X65" s="438"/>
+      <c r="Y65" s="438"/>
+      <c r="Z65" s="439"/>
+      <c r="AA65" s="437"/>
+      <c r="AB65" s="438"/>
+      <c r="AC65" s="438"/>
+      <c r="AD65" s="439"/>
     </row>
-    <row r="66" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="507"/>
-      <c r="C66" s="508"/>
-      <c r="D66" s="508"/>
-      <c r="E66" s="508"/>
-      <c r="F66" s="509"/>
-      <c r="G66" s="516"/>
-      <c r="H66" s="517"/>
-      <c r="I66" s="517"/>
-      <c r="J66" s="518"/>
-      <c r="K66" s="516"/>
-      <c r="L66" s="517"/>
-      <c r="M66" s="517"/>
-      <c r="N66" s="518"/>
-      <c r="O66" s="494"/>
-      <c r="P66" s="495"/>
-      <c r="Q66" s="495"/>
-      <c r="R66" s="496"/>
-      <c r="S66" s="494"/>
-      <c r="T66" s="495"/>
-      <c r="U66" s="495"/>
-      <c r="V66" s="496"/>
-      <c r="W66" s="494"/>
-      <c r="X66" s="495"/>
-      <c r="Y66" s="495"/>
-      <c r="Z66" s="496"/>
-      <c r="AA66" s="494"/>
-      <c r="AB66" s="495"/>
-      <c r="AC66" s="495"/>
-      <c r="AD66" s="496"/>
+    <row r="66" spans="2:30" ht="15" customHeight="1">
+      <c r="B66" s="526"/>
+      <c r="C66" s="527"/>
+      <c r="D66" s="527"/>
+      <c r="E66" s="527"/>
+      <c r="F66" s="528"/>
+      <c r="G66" s="446"/>
+      <c r="H66" s="447"/>
+      <c r="I66" s="447"/>
+      <c r="J66" s="448"/>
+      <c r="K66" s="446"/>
+      <c r="L66" s="447"/>
+      <c r="M66" s="447"/>
+      <c r="N66" s="448"/>
+      <c r="O66" s="437"/>
+      <c r="P66" s="438"/>
+      <c r="Q66" s="438"/>
+      <c r="R66" s="439"/>
+      <c r="S66" s="437"/>
+      <c r="T66" s="438"/>
+      <c r="U66" s="438"/>
+      <c r="V66" s="439"/>
+      <c r="W66" s="437"/>
+      <c r="X66" s="438"/>
+      <c r="Y66" s="438"/>
+      <c r="Z66" s="439"/>
+      <c r="AA66" s="437"/>
+      <c r="AB66" s="438"/>
+      <c r="AC66" s="438"/>
+      <c r="AD66" s="439"/>
     </row>
-    <row r="67" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="507"/>
-      <c r="C67" s="508"/>
-      <c r="D67" s="508"/>
-      <c r="E67" s="508"/>
-      <c r="F67" s="509"/>
-      <c r="G67" s="516"/>
-      <c r="H67" s="517"/>
-      <c r="I67" s="517"/>
-      <c r="J67" s="518"/>
-      <c r="K67" s="516"/>
-      <c r="L67" s="517"/>
-      <c r="M67" s="517"/>
-      <c r="N67" s="518"/>
-      <c r="O67" s="494"/>
-      <c r="P67" s="495"/>
-      <c r="Q67" s="495"/>
-      <c r="R67" s="496"/>
-      <c r="S67" s="494"/>
-      <c r="T67" s="495"/>
-      <c r="U67" s="495"/>
-      <c r="V67" s="496"/>
-      <c r="W67" s="494"/>
-      <c r="X67" s="495"/>
-      <c r="Y67" s="495"/>
-      <c r="Z67" s="496"/>
-      <c r="AA67" s="494"/>
-      <c r="AB67" s="495"/>
-      <c r="AC67" s="495"/>
-      <c r="AD67" s="496"/>
+    <row r="67" spans="2:30" ht="15" customHeight="1">
+      <c r="B67" s="526"/>
+      <c r="C67" s="527"/>
+      <c r="D67" s="527"/>
+      <c r="E67" s="527"/>
+      <c r="F67" s="528"/>
+      <c r="G67" s="446"/>
+      <c r="H67" s="447"/>
+      <c r="I67" s="447"/>
+      <c r="J67" s="448"/>
+      <c r="K67" s="446"/>
+      <c r="L67" s="447"/>
+      <c r="M67" s="447"/>
+      <c r="N67" s="448"/>
+      <c r="O67" s="437"/>
+      <c r="P67" s="438"/>
+      <c r="Q67" s="438"/>
+      <c r="R67" s="439"/>
+      <c r="S67" s="437"/>
+      <c r="T67" s="438"/>
+      <c r="U67" s="438"/>
+      <c r="V67" s="439"/>
+      <c r="W67" s="437"/>
+      <c r="X67" s="438"/>
+      <c r="Y67" s="438"/>
+      <c r="Z67" s="439"/>
+      <c r="AA67" s="437"/>
+      <c r="AB67" s="438"/>
+      <c r="AC67" s="438"/>
+      <c r="AD67" s="439"/>
     </row>
-    <row r="68" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="507"/>
-      <c r="C68" s="508"/>
-      <c r="D68" s="508"/>
-      <c r="E68" s="508"/>
-      <c r="F68" s="509"/>
-      <c r="G68" s="516"/>
-      <c r="H68" s="517"/>
-      <c r="I68" s="517"/>
-      <c r="J68" s="518"/>
-      <c r="K68" s="516"/>
-      <c r="L68" s="517"/>
-      <c r="M68" s="517"/>
-      <c r="N68" s="518"/>
-      <c r="O68" s="494"/>
-      <c r="P68" s="495"/>
-      <c r="Q68" s="495"/>
-      <c r="R68" s="496"/>
-      <c r="S68" s="494"/>
-      <c r="T68" s="495"/>
-      <c r="U68" s="495"/>
-      <c r="V68" s="496"/>
-      <c r="W68" s="494"/>
-      <c r="X68" s="495"/>
-      <c r="Y68" s="495"/>
-      <c r="Z68" s="496"/>
-      <c r="AA68" s="494"/>
-      <c r="AB68" s="495"/>
-      <c r="AC68" s="495"/>
-      <c r="AD68" s="496"/>
+    <row r="68" spans="2:30" ht="15.75" customHeight="1">
+      <c r="B68" s="526"/>
+      <c r="C68" s="527"/>
+      <c r="D68" s="527"/>
+      <c r="E68" s="527"/>
+      <c r="F68" s="528"/>
+      <c r="G68" s="446"/>
+      <c r="H68" s="447"/>
+      <c r="I68" s="447"/>
+      <c r="J68" s="448"/>
+      <c r="K68" s="446"/>
+      <c r="L68" s="447"/>
+      <c r="M68" s="447"/>
+      <c r="N68" s="448"/>
+      <c r="O68" s="437"/>
+      <c r="P68" s="438"/>
+      <c r="Q68" s="438"/>
+      <c r="R68" s="439"/>
+      <c r="S68" s="437"/>
+      <c r="T68" s="438"/>
+      <c r="U68" s="438"/>
+      <c r="V68" s="439"/>
+      <c r="W68" s="437"/>
+      <c r="X68" s="438"/>
+      <c r="Y68" s="438"/>
+      <c r="Z68" s="439"/>
+      <c r="AA68" s="437"/>
+      <c r="AB68" s="438"/>
+      <c r="AC68" s="438"/>
+      <c r="AD68" s="439"/>
     </row>
-    <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="510"/>
-      <c r="C69" s="511"/>
-      <c r="D69" s="511"/>
-      <c r="E69" s="511"/>
-      <c r="F69" s="512"/>
-      <c r="G69" s="519"/>
-      <c r="H69" s="520"/>
-      <c r="I69" s="520"/>
-      <c r="J69" s="521"/>
-      <c r="K69" s="519"/>
-      <c r="L69" s="520"/>
-      <c r="M69" s="520"/>
-      <c r="N69" s="521"/>
-      <c r="O69" s="497"/>
-      <c r="P69" s="498"/>
-      <c r="Q69" s="498"/>
-      <c r="R69" s="499"/>
-      <c r="S69" s="497"/>
-      <c r="T69" s="498"/>
-      <c r="U69" s="498"/>
-      <c r="V69" s="499"/>
-      <c r="W69" s="497"/>
-      <c r="X69" s="498"/>
-      <c r="Y69" s="498"/>
-      <c r="Z69" s="499"/>
-      <c r="AA69" s="497"/>
-      <c r="AB69" s="498"/>
-      <c r="AC69" s="498"/>
-      <c r="AD69" s="499"/>
+    <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B69" s="529"/>
+      <c r="C69" s="530"/>
+      <c r="D69" s="530"/>
+      <c r="E69" s="530"/>
+      <c r="F69" s="531"/>
+      <c r="G69" s="449"/>
+      <c r="H69" s="450"/>
+      <c r="I69" s="450"/>
+      <c r="J69" s="451"/>
+      <c r="K69" s="449"/>
+      <c r="L69" s="450"/>
+      <c r="M69" s="450"/>
+      <c r="N69" s="451"/>
+      <c r="O69" s="440"/>
+      <c r="P69" s="441"/>
+      <c r="Q69" s="441"/>
+      <c r="R69" s="442"/>
+      <c r="S69" s="440"/>
+      <c r="T69" s="441"/>
+      <c r="U69" s="441"/>
+      <c r="V69" s="442"/>
+      <c r="W69" s="440"/>
+      <c r="X69" s="441"/>
+      <c r="Y69" s="441"/>
+      <c r="Z69" s="442"/>
+      <c r="AA69" s="440"/>
+      <c r="AB69" s="441"/>
+      <c r="AC69" s="441"/>
+      <c r="AD69" s="442"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -33035,7 +33123,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C108CD-255B-4DDA-A6DD-9C6B6781DBDE}">
   <dimension ref="B1:R50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
@@ -33043,7 +33131,7 @@
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18">
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -33066,7 +33154,7 @@
       <c r="Q1" s="40"/>
       <c r="R1" s="40"/>
     </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18">
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
         <v>1</v>
@@ -33086,7 +33174,7 @@
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18">
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -33107,7 +33195,7 @@
       <c r="Q3" s="40"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="15.75">
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -33130,7 +33218,7 @@
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18">
       <c r="B5" s="162"/>
       <c r="C5" s="6" t="s">
         <v>5</v>
@@ -33153,7 +33241,7 @@
       <c r="Q5" s="40"/>
       <c r="R5" s="40"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18">
       <c r="B6" s="128"/>
       <c r="C6" s="131" t="s">
         <v>69</v>
@@ -33176,7 +33264,7 @@
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18">
       <c r="B7" s="152"/>
       <c r="C7" s="131" t="s">
         <v>70</v>
@@ -33184,26 +33272,26 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="531" t="s">
+      <c r="G7" s="532" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="532"/>
-      <c r="I7" s="532"/>
-      <c r="J7" s="533"/>
-      <c r="K7" s="528" t="s">
+      <c r="H7" s="533"/>
+      <c r="I7" s="533"/>
+      <c r="J7" s="534"/>
+      <c r="K7" s="535" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="529"/>
-      <c r="M7" s="529"/>
-      <c r="N7" s="530"/>
-      <c r="O7" s="525" t="s">
+      <c r="L7" s="536"/>
+      <c r="M7" s="536"/>
+      <c r="N7" s="537"/>
+      <c r="O7" s="538" t="s">
         <v>76</v>
       </c>
-      <c r="P7" s="526"/>
-      <c r="Q7" s="526"/>
-      <c r="R7" s="527"/>
+      <c r="P7" s="539"/>
+      <c r="Q7" s="539"/>
+      <c r="R7" s="540"/>
     </row>
-    <row r="8" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:18" ht="15.75" thickBot="1">
       <c r="B8" s="167"/>
       <c r="C8" s="131" t="s">
         <v>71</v>
@@ -33248,7 +33336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:18" ht="15.75" thickBot="1">
       <c r="B9" s="289" t="s">
         <v>9</v>
       </c>
@@ -33277,7 +33365,7 @@
       <c r="Q9" s="231"/>
       <c r="R9" s="231"/>
     </row>
-    <row r="10" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:18" ht="15.75" thickBot="1">
       <c r="B10" s="141" t="s">
         <v>157</v>
       </c>
@@ -33306,7 +33394,7 @@
       <c r="Q10" s="52"/>
       <c r="R10" s="230"/>
     </row>
-    <row r="11" spans="2:18" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:18" ht="45.75" thickBot="1">
       <c r="B11" s="141" t="s">
         <v>85</v>
       </c>
@@ -33335,7 +33423,7 @@
       <c r="Q11" s="38"/>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="2:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:18" ht="30.75" thickBot="1">
       <c r="B12" s="141" t="s">
         <v>158</v>
       </c>
@@ -33364,7 +33452,7 @@
       <c r="Q12" s="38"/>
       <c r="R12" s="42"/>
     </row>
-    <row r="13" spans="2:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:18" ht="30.75" thickBot="1">
       <c r="B13" s="134" t="s">
         <v>87</v>
       </c>
@@ -33393,8 +33481,8 @@
       <c r="Q13" s="139"/>
       <c r="R13" s="224"/>
     </row>
-    <row r="14" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="538" t="s">
+    <row r="14" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B14" s="541" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="146" t="s">
@@ -33422,8 +33510,8 @@
       <c r="Q14" s="265"/>
       <c r="R14" s="266"/>
     </row>
-    <row r="15" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="539"/>
+    <row r="15" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B15" s="542"/>
       <c r="C15" s="228" t="s">
         <v>93</v>
       </c>
@@ -33449,8 +33537,8 @@
       <c r="Q15" s="149"/>
       <c r="R15" s="267"/>
     </row>
-    <row r="16" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="538" t="s">
+    <row r="16" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B16" s="541" t="s">
         <v>160</v>
       </c>
       <c r="C16" s="263" t="s">
@@ -33478,8 +33566,8 @@
       <c r="Q16" s="148"/>
       <c r="R16" s="264"/>
     </row>
-    <row r="17" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="540"/>
+    <row r="17" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B17" s="543"/>
       <c r="C17" s="296" t="s">
         <v>27</v>
       </c>
@@ -33509,8 +33597,8 @@
       </c>
       <c r="R17" s="271"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="541" t="s">
+    <row r="18" spans="2:18">
+      <c r="B18" s="544" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="122" t="s">
@@ -33538,8 +33626,8 @@
       <c r="Q18" s="265"/>
       <c r="R18" s="266"/>
     </row>
-    <row r="19" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="542"/>
+    <row r="19" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B19" s="545"/>
       <c r="C19" s="123" t="s">
         <v>38</v>
       </c>
@@ -33567,8 +33655,8 @@
       <c r="Q19" s="265"/>
       <c r="R19" s="266"/>
     </row>
-    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="541" t="s">
+    <row r="20" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B20" s="544" t="s">
         <v>162</v>
       </c>
       <c r="C20" s="119" t="s">
@@ -33596,8 +33684,8 @@
       <c r="Q20" s="148"/>
       <c r="R20" s="264"/>
     </row>
-    <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="542"/>
+    <row r="21" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B21" s="545"/>
       <c r="C21" s="284" t="s">
         <v>44</v>
       </c>
@@ -33623,7 +33711,7 @@
       <c r="Q21" s="274"/>
       <c r="R21" s="275"/>
     </row>
-    <row r="22" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:18" ht="15.75" thickBot="1">
       <c r="B22" s="135" t="s">
         <v>112</v>
       </c>
@@ -33654,8 +33742,8 @@
       <c r="Q22" s="265"/>
       <c r="R22" s="266"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="543" t="s">
+    <row r="23" spans="2:18">
+      <c r="B23" s="546" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="119" t="s">
@@ -33683,8 +33771,8 @@
       <c r="Q23" s="148"/>
       <c r="R23" s="264"/>
     </row>
-    <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="544"/>
+    <row r="24" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B24" s="547"/>
       <c r="C24" s="124" t="s">
         <v>20</v>
       </c>
@@ -33710,8 +33798,8 @@
       <c r="Q24" s="219"/>
       <c r="R24" s="281"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="538" t="s">
+    <row r="25" spans="2:18">
+      <c r="B25" s="541" t="s">
         <v>163</v>
       </c>
       <c r="C25" s="119" t="s">
@@ -33739,8 +33827,8 @@
       <c r="Q25" s="22"/>
       <c r="R25" s="23"/>
     </row>
-    <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="539"/>
+    <row r="26" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B26" s="542"/>
       <c r="C26" s="124" t="s">
         <v>113</v>
       </c>
@@ -33766,7 +33854,7 @@
       <c r="Q26" s="16"/>
       <c r="R26" s="24"/>
     </row>
-    <row r="27" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:18" ht="15.75" thickBot="1">
       <c r="B27" s="305" t="s">
         <v>122</v>
       </c>
@@ -33795,7 +33883,7 @@
       <c r="Q27" s="160"/>
       <c r="R27" s="278"/>
     </row>
-    <row r="28" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:18" ht="15.75" thickBot="1">
       <c r="B28" s="307" t="s">
         <v>64</v>
       </c>
@@ -33824,7 +33912,7 @@
       <c r="Q28" s="197"/>
       <c r="R28" s="198"/>
     </row>
-    <row r="29" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:18" ht="15.75" thickBot="1">
       <c r="B29" s="171" t="s">
         <v>27</v>
       </c>
@@ -33853,440 +33941,440 @@
       <c r="Q29" s="173"/>
       <c r="R29" s="312"/>
     </row>
-    <row r="30" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="501" t="s">
+    <row r="30" spans="2:18" ht="19.5" thickBot="1">
+      <c r="B30" s="494" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="502"/>
-      <c r="D30" s="502"/>
-      <c r="E30" s="502"/>
-      <c r="F30" s="502"/>
-      <c r="G30" s="501" t="s">
+      <c r="C30" s="495"/>
+      <c r="D30" s="495"/>
+      <c r="E30" s="495"/>
+      <c r="F30" s="495"/>
+      <c r="G30" s="494" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="502"/>
-      <c r="I30" s="502"/>
-      <c r="J30" s="537"/>
-      <c r="K30" s="477" t="s">
+      <c r="H30" s="495"/>
+      <c r="I30" s="495"/>
+      <c r="J30" s="548"/>
+      <c r="K30" s="497" t="s">
         <v>135</v>
       </c>
-      <c r="L30" s="478"/>
-      <c r="M30" s="478"/>
-      <c r="N30" s="479"/>
-      <c r="O30" s="477"/>
-      <c r="P30" s="478"/>
-      <c r="Q30" s="478"/>
-      <c r="R30" s="479"/>
+      <c r="L30" s="498"/>
+      <c r="M30" s="498"/>
+      <c r="N30" s="499"/>
+      <c r="O30" s="497"/>
+      <c r="P30" s="498"/>
+      <c r="Q30" s="498"/>
+      <c r="R30" s="499"/>
     </row>
-    <row r="31" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="474" t="s">
+    <row r="31" spans="2:18" ht="19.5" thickBot="1">
+      <c r="B31" s="500" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="475"/>
-      <c r="D31" s="475"/>
-      <c r="E31" s="475"/>
-      <c r="F31" s="475"/>
-      <c r="G31" s="474" t="s">
+      <c r="C31" s="501"/>
+      <c r="D31" s="501"/>
+      <c r="E31" s="501"/>
+      <c r="F31" s="501"/>
+      <c r="G31" s="500" t="s">
         <v>139</v>
       </c>
-      <c r="H31" s="475"/>
-      <c r="I31" s="475"/>
-      <c r="J31" s="545"/>
-      <c r="K31" s="474" t="s">
+      <c r="H31" s="501"/>
+      <c r="I31" s="501"/>
+      <c r="J31" s="549"/>
+      <c r="K31" s="500" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="475"/>
-      <c r="M31" s="475"/>
-      <c r="N31" s="545"/>
-      <c r="O31" s="474" t="s">
+      <c r="L31" s="501"/>
+      <c r="M31" s="501"/>
+      <c r="N31" s="549"/>
+      <c r="O31" s="500" t="s">
         <v>138</v>
       </c>
-      <c r="P31" s="475"/>
-      <c r="Q31" s="475"/>
-      <c r="R31" s="545"/>
+      <c r="P31" s="501"/>
+      <c r="Q31" s="501"/>
+      <c r="R31" s="549"/>
     </row>
-    <row r="32" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="449" t="s">
+    <row r="32" spans="2:18" ht="19.5" thickBot="1">
+      <c r="B32" s="506" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="450"/>
-      <c r="D32" s="450"/>
-      <c r="E32" s="450"/>
-      <c r="F32" s="450"/>
-      <c r="G32" s="449" t="s">
+      <c r="C32" s="507"/>
+      <c r="D32" s="507"/>
+      <c r="E32" s="507"/>
+      <c r="F32" s="507"/>
+      <c r="G32" s="506" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="450"/>
-      <c r="I32" s="450"/>
-      <c r="J32" s="524"/>
-      <c r="K32" s="449" t="s">
+      <c r="H32" s="507"/>
+      <c r="I32" s="507"/>
+      <c r="J32" s="515"/>
+      <c r="K32" s="506" t="s">
         <v>142</v>
       </c>
-      <c r="L32" s="450"/>
-      <c r="M32" s="450"/>
-      <c r="N32" s="524"/>
-      <c r="O32" s="449" t="s">
+      <c r="L32" s="507"/>
+      <c r="M32" s="507"/>
+      <c r="N32" s="515"/>
+      <c r="O32" s="506" t="s">
         <v>142</v>
       </c>
-      <c r="P32" s="450"/>
-      <c r="Q32" s="450"/>
-      <c r="R32" s="524"/>
+      <c r="P32" s="507"/>
+      <c r="Q32" s="507"/>
+      <c r="R32" s="515"/>
     </row>
-    <row r="33" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="534" t="s">
+    <row r="33" spans="2:18" ht="19.5" thickBot="1">
+      <c r="B33" s="550" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="535"/>
-      <c r="D33" s="535"/>
-      <c r="E33" s="535"/>
-      <c r="F33" s="536"/>
-      <c r="G33" s="452" t="s">
+      <c r="C33" s="551"/>
+      <c r="D33" s="551"/>
+      <c r="E33" s="551"/>
+      <c r="F33" s="552"/>
+      <c r="G33" s="516" t="s">
         <v>147</v>
       </c>
-      <c r="H33" s="453"/>
-      <c r="I33" s="453"/>
-      <c r="J33" s="523"/>
-      <c r="K33" s="452" t="s">
+      <c r="H33" s="517"/>
+      <c r="I33" s="517"/>
+      <c r="J33" s="522"/>
+      <c r="K33" s="516" t="s">
         <v>165</v>
       </c>
-      <c r="L33" s="453"/>
-      <c r="M33" s="453"/>
-      <c r="N33" s="523"/>
-      <c r="O33" s="452"/>
-      <c r="P33" s="453"/>
-      <c r="Q33" s="453"/>
-      <c r="R33" s="523"/>
+      <c r="L33" s="517"/>
+      <c r="M33" s="517"/>
+      <c r="N33" s="522"/>
+      <c r="O33" s="516"/>
+      <c r="P33" s="517"/>
+      <c r="Q33" s="517"/>
+      <c r="R33" s="522"/>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="504" t="s">
+    <row r="34" spans="2:18">
+      <c r="B34" s="523" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="505"/>
-      <c r="D34" s="505"/>
-      <c r="E34" s="505"/>
-      <c r="F34" s="506"/>
-      <c r="G34" s="491" t="s">
+      <c r="C34" s="524"/>
+      <c r="D34" s="524"/>
+      <c r="E34" s="524"/>
+      <c r="F34" s="525"/>
+      <c r="G34" s="434" t="s">
         <v>151</v>
       </c>
-      <c r="H34" s="492"/>
-      <c r="I34" s="492"/>
-      <c r="J34" s="493"/>
-      <c r="K34" s="491" t="s">
+      <c r="H34" s="435"/>
+      <c r="I34" s="435"/>
+      <c r="J34" s="436"/>
+      <c r="K34" s="434" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="492"/>
-      <c r="M34" s="492"/>
-      <c r="N34" s="493"/>
-      <c r="O34" s="491" t="s">
+      <c r="L34" s="435"/>
+      <c r="M34" s="435"/>
+      <c r="N34" s="436"/>
+      <c r="O34" s="434" t="s">
         <v>166</v>
       </c>
-      <c r="P34" s="492"/>
-      <c r="Q34" s="492"/>
-      <c r="R34" s="493"/>
+      <c r="P34" s="435"/>
+      <c r="Q34" s="435"/>
+      <c r="R34" s="436"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="507"/>
-      <c r="C35" s="508"/>
-      <c r="D35" s="508"/>
-      <c r="E35" s="508"/>
-      <c r="F35" s="509"/>
-      <c r="G35" s="494"/>
-      <c r="H35" s="495"/>
-      <c r="I35" s="495"/>
-      <c r="J35" s="496"/>
-      <c r="K35" s="494"/>
-      <c r="L35" s="495"/>
-      <c r="M35" s="495"/>
-      <c r="N35" s="496"/>
-      <c r="O35" s="494"/>
-      <c r="P35" s="495"/>
-      <c r="Q35" s="495"/>
-      <c r="R35" s="496"/>
+    <row r="35" spans="2:18">
+      <c r="B35" s="526"/>
+      <c r="C35" s="527"/>
+      <c r="D35" s="527"/>
+      <c r="E35" s="527"/>
+      <c r="F35" s="528"/>
+      <c r="G35" s="437"/>
+      <c r="H35" s="438"/>
+      <c r="I35" s="438"/>
+      <c r="J35" s="439"/>
+      <c r="K35" s="437"/>
+      <c r="L35" s="438"/>
+      <c r="M35" s="438"/>
+      <c r="N35" s="439"/>
+      <c r="O35" s="437"/>
+      <c r="P35" s="438"/>
+      <c r="Q35" s="438"/>
+      <c r="R35" s="439"/>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="507"/>
-      <c r="C36" s="508"/>
-      <c r="D36" s="508"/>
-      <c r="E36" s="508"/>
-      <c r="F36" s="509"/>
-      <c r="G36" s="494"/>
-      <c r="H36" s="495"/>
-      <c r="I36" s="495"/>
-      <c r="J36" s="496"/>
-      <c r="K36" s="494"/>
-      <c r="L36" s="495"/>
-      <c r="M36" s="495"/>
-      <c r="N36" s="496"/>
-      <c r="O36" s="494"/>
-      <c r="P36" s="495"/>
-      <c r="Q36" s="495"/>
-      <c r="R36" s="496"/>
+    <row r="36" spans="2:18">
+      <c r="B36" s="526"/>
+      <c r="C36" s="527"/>
+      <c r="D36" s="527"/>
+      <c r="E36" s="527"/>
+      <c r="F36" s="528"/>
+      <c r="G36" s="437"/>
+      <c r="H36" s="438"/>
+      <c r="I36" s="438"/>
+      <c r="J36" s="439"/>
+      <c r="K36" s="437"/>
+      <c r="L36" s="438"/>
+      <c r="M36" s="438"/>
+      <c r="N36" s="439"/>
+      <c r="O36" s="437"/>
+      <c r="P36" s="438"/>
+      <c r="Q36" s="438"/>
+      <c r="R36" s="439"/>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="507"/>
-      <c r="C37" s="508"/>
-      <c r="D37" s="508"/>
-      <c r="E37" s="508"/>
-      <c r="F37" s="509"/>
-      <c r="G37" s="494"/>
-      <c r="H37" s="495"/>
-      <c r="I37" s="495"/>
-      <c r="J37" s="496"/>
-      <c r="K37" s="494"/>
-      <c r="L37" s="495"/>
-      <c r="M37" s="495"/>
-      <c r="N37" s="496"/>
-      <c r="O37" s="494"/>
-      <c r="P37" s="495"/>
-      <c r="Q37" s="495"/>
-      <c r="R37" s="496"/>
+    <row r="37" spans="2:18">
+      <c r="B37" s="526"/>
+      <c r="C37" s="527"/>
+      <c r="D37" s="527"/>
+      <c r="E37" s="527"/>
+      <c r="F37" s="528"/>
+      <c r="G37" s="437"/>
+      <c r="H37" s="438"/>
+      <c r="I37" s="438"/>
+      <c r="J37" s="439"/>
+      <c r="K37" s="437"/>
+      <c r="L37" s="438"/>
+      <c r="M37" s="438"/>
+      <c r="N37" s="439"/>
+      <c r="O37" s="437"/>
+      <c r="P37" s="438"/>
+      <c r="Q37" s="438"/>
+      <c r="R37" s="439"/>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="507"/>
-      <c r="C38" s="508"/>
-      <c r="D38" s="508"/>
-      <c r="E38" s="508"/>
-      <c r="F38" s="509"/>
-      <c r="G38" s="494"/>
-      <c r="H38" s="495"/>
-      <c r="I38" s="495"/>
-      <c r="J38" s="496"/>
-      <c r="K38" s="494"/>
-      <c r="L38" s="495"/>
-      <c r="M38" s="495"/>
-      <c r="N38" s="496"/>
-      <c r="O38" s="494"/>
-      <c r="P38" s="495"/>
-      <c r="Q38" s="495"/>
-      <c r="R38" s="496"/>
+    <row r="38" spans="2:18">
+      <c r="B38" s="526"/>
+      <c r="C38" s="527"/>
+      <c r="D38" s="527"/>
+      <c r="E38" s="527"/>
+      <c r="F38" s="528"/>
+      <c r="G38" s="437"/>
+      <c r="H38" s="438"/>
+      <c r="I38" s="438"/>
+      <c r="J38" s="439"/>
+      <c r="K38" s="437"/>
+      <c r="L38" s="438"/>
+      <c r="M38" s="438"/>
+      <c r="N38" s="439"/>
+      <c r="O38" s="437"/>
+      <c r="P38" s="438"/>
+      <c r="Q38" s="438"/>
+      <c r="R38" s="439"/>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="507"/>
-      <c r="C39" s="508"/>
-      <c r="D39" s="508"/>
-      <c r="E39" s="508"/>
-      <c r="F39" s="509"/>
-      <c r="G39" s="494"/>
-      <c r="H39" s="495"/>
-      <c r="I39" s="495"/>
-      <c r="J39" s="496"/>
-      <c r="K39" s="494"/>
-      <c r="L39" s="495"/>
-      <c r="M39" s="495"/>
-      <c r="N39" s="496"/>
-      <c r="O39" s="494"/>
-      <c r="P39" s="495"/>
-      <c r="Q39" s="495"/>
-      <c r="R39" s="496"/>
+    <row r="39" spans="2:18">
+      <c r="B39" s="526"/>
+      <c r="C39" s="527"/>
+      <c r="D39" s="527"/>
+      <c r="E39" s="527"/>
+      <c r="F39" s="528"/>
+      <c r="G39" s="437"/>
+      <c r="H39" s="438"/>
+      <c r="I39" s="438"/>
+      <c r="J39" s="439"/>
+      <c r="K39" s="437"/>
+      <c r="L39" s="438"/>
+      <c r="M39" s="438"/>
+      <c r="N39" s="439"/>
+      <c r="O39" s="437"/>
+      <c r="P39" s="438"/>
+      <c r="Q39" s="438"/>
+      <c r="R39" s="439"/>
     </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="507"/>
-      <c r="C40" s="508"/>
-      <c r="D40" s="508"/>
-      <c r="E40" s="508"/>
-      <c r="F40" s="509"/>
-      <c r="G40" s="494"/>
-      <c r="H40" s="495"/>
-      <c r="I40" s="495"/>
-      <c r="J40" s="496"/>
-      <c r="K40" s="494"/>
-      <c r="L40" s="495"/>
-      <c r="M40" s="495"/>
-      <c r="N40" s="496"/>
-      <c r="O40" s="494"/>
-      <c r="P40" s="495"/>
-      <c r="Q40" s="495"/>
-      <c r="R40" s="496"/>
+    <row r="40" spans="2:18">
+      <c r="B40" s="526"/>
+      <c r="C40" s="527"/>
+      <c r="D40" s="527"/>
+      <c r="E40" s="527"/>
+      <c r="F40" s="528"/>
+      <c r="G40" s="437"/>
+      <c r="H40" s="438"/>
+      <c r="I40" s="438"/>
+      <c r="J40" s="439"/>
+      <c r="K40" s="437"/>
+      <c r="L40" s="438"/>
+      <c r="M40" s="438"/>
+      <c r="N40" s="439"/>
+      <c r="O40" s="437"/>
+      <c r="P40" s="438"/>
+      <c r="Q40" s="438"/>
+      <c r="R40" s="439"/>
     </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="507"/>
-      <c r="C41" s="508"/>
-      <c r="D41" s="508"/>
-      <c r="E41" s="508"/>
-      <c r="F41" s="509"/>
-      <c r="G41" s="494"/>
-      <c r="H41" s="495"/>
-      <c r="I41" s="495"/>
-      <c r="J41" s="496"/>
-      <c r="K41" s="494"/>
-      <c r="L41" s="495"/>
-      <c r="M41" s="495"/>
-      <c r="N41" s="496"/>
-      <c r="O41" s="494"/>
-      <c r="P41" s="495"/>
-      <c r="Q41" s="495"/>
-      <c r="R41" s="496"/>
+    <row r="41" spans="2:18">
+      <c r="B41" s="526"/>
+      <c r="C41" s="527"/>
+      <c r="D41" s="527"/>
+      <c r="E41" s="527"/>
+      <c r="F41" s="528"/>
+      <c r="G41" s="437"/>
+      <c r="H41" s="438"/>
+      <c r="I41" s="438"/>
+      <c r="J41" s="439"/>
+      <c r="K41" s="437"/>
+      <c r="L41" s="438"/>
+      <c r="M41" s="438"/>
+      <c r="N41" s="439"/>
+      <c r="O41" s="437"/>
+      <c r="P41" s="438"/>
+      <c r="Q41" s="438"/>
+      <c r="R41" s="439"/>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="507"/>
-      <c r="C42" s="508"/>
-      <c r="D42" s="508"/>
-      <c r="E42" s="508"/>
-      <c r="F42" s="509"/>
-      <c r="G42" s="494"/>
-      <c r="H42" s="495"/>
-      <c r="I42" s="495"/>
-      <c r="J42" s="496"/>
-      <c r="K42" s="494"/>
-      <c r="L42" s="495"/>
-      <c r="M42" s="495"/>
-      <c r="N42" s="496"/>
-      <c r="O42" s="494"/>
-      <c r="P42" s="495"/>
-      <c r="Q42" s="495"/>
-      <c r="R42" s="496"/>
+    <row r="42" spans="2:18">
+      <c r="B42" s="526"/>
+      <c r="C42" s="527"/>
+      <c r="D42" s="527"/>
+      <c r="E42" s="527"/>
+      <c r="F42" s="528"/>
+      <c r="G42" s="437"/>
+      <c r="H42" s="438"/>
+      <c r="I42" s="438"/>
+      <c r="J42" s="439"/>
+      <c r="K42" s="437"/>
+      <c r="L42" s="438"/>
+      <c r="M42" s="438"/>
+      <c r="N42" s="439"/>
+      <c r="O42" s="437"/>
+      <c r="P42" s="438"/>
+      <c r="Q42" s="438"/>
+      <c r="R42" s="439"/>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="507"/>
-      <c r="C43" s="508"/>
-      <c r="D43" s="508"/>
-      <c r="E43" s="508"/>
-      <c r="F43" s="509"/>
-      <c r="G43" s="494"/>
-      <c r="H43" s="495"/>
-      <c r="I43" s="495"/>
-      <c r="J43" s="496"/>
-      <c r="K43" s="494"/>
-      <c r="L43" s="495"/>
-      <c r="M43" s="495"/>
-      <c r="N43" s="496"/>
-      <c r="O43" s="494"/>
-      <c r="P43" s="495"/>
-      <c r="Q43" s="495"/>
-      <c r="R43" s="496"/>
+    <row r="43" spans="2:18">
+      <c r="B43" s="526"/>
+      <c r="C43" s="527"/>
+      <c r="D43" s="527"/>
+      <c r="E43" s="527"/>
+      <c r="F43" s="528"/>
+      <c r="G43" s="437"/>
+      <c r="H43" s="438"/>
+      <c r="I43" s="438"/>
+      <c r="J43" s="439"/>
+      <c r="K43" s="437"/>
+      <c r="L43" s="438"/>
+      <c r="M43" s="438"/>
+      <c r="N43" s="439"/>
+      <c r="O43" s="437"/>
+      <c r="P43" s="438"/>
+      <c r="Q43" s="438"/>
+      <c r="R43" s="439"/>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="507"/>
-      <c r="C44" s="508"/>
-      <c r="D44" s="508"/>
-      <c r="E44" s="508"/>
-      <c r="F44" s="509"/>
-      <c r="G44" s="494"/>
-      <c r="H44" s="495"/>
-      <c r="I44" s="495"/>
-      <c r="J44" s="496"/>
-      <c r="K44" s="494"/>
-      <c r="L44" s="495"/>
-      <c r="M44" s="495"/>
-      <c r="N44" s="496"/>
-      <c r="O44" s="494"/>
-      <c r="P44" s="495"/>
-      <c r="Q44" s="495"/>
-      <c r="R44" s="496"/>
+    <row r="44" spans="2:18">
+      <c r="B44" s="526"/>
+      <c r="C44" s="527"/>
+      <c r="D44" s="527"/>
+      <c r="E44" s="527"/>
+      <c r="F44" s="528"/>
+      <c r="G44" s="437"/>
+      <c r="H44" s="438"/>
+      <c r="I44" s="438"/>
+      <c r="J44" s="439"/>
+      <c r="K44" s="437"/>
+      <c r="L44" s="438"/>
+      <c r="M44" s="438"/>
+      <c r="N44" s="439"/>
+      <c r="O44" s="437"/>
+      <c r="P44" s="438"/>
+      <c r="Q44" s="438"/>
+      <c r="R44" s="439"/>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="507"/>
-      <c r="C45" s="508"/>
-      <c r="D45" s="508"/>
-      <c r="E45" s="508"/>
-      <c r="F45" s="509"/>
-      <c r="G45" s="494"/>
-      <c r="H45" s="495"/>
-      <c r="I45" s="495"/>
-      <c r="J45" s="496"/>
-      <c r="K45" s="494"/>
-      <c r="L45" s="495"/>
-      <c r="M45" s="495"/>
-      <c r="N45" s="496"/>
-      <c r="O45" s="494"/>
-      <c r="P45" s="495"/>
-      <c r="Q45" s="495"/>
-      <c r="R45" s="496"/>
+    <row r="45" spans="2:18">
+      <c r="B45" s="526"/>
+      <c r="C45" s="527"/>
+      <c r="D45" s="527"/>
+      <c r="E45" s="527"/>
+      <c r="F45" s="528"/>
+      <c r="G45" s="437"/>
+      <c r="H45" s="438"/>
+      <c r="I45" s="438"/>
+      <c r="J45" s="439"/>
+      <c r="K45" s="437"/>
+      <c r="L45" s="438"/>
+      <c r="M45" s="438"/>
+      <c r="N45" s="439"/>
+      <c r="O45" s="437"/>
+      <c r="P45" s="438"/>
+      <c r="Q45" s="438"/>
+      <c r="R45" s="439"/>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="507"/>
-      <c r="C46" s="508"/>
-      <c r="D46" s="508"/>
-      <c r="E46" s="508"/>
-      <c r="F46" s="509"/>
-      <c r="G46" s="494"/>
-      <c r="H46" s="495"/>
-      <c r="I46" s="495"/>
-      <c r="J46" s="496"/>
-      <c r="K46" s="494"/>
-      <c r="L46" s="495"/>
-      <c r="M46" s="495"/>
-      <c r="N46" s="496"/>
-      <c r="O46" s="494"/>
-      <c r="P46" s="495"/>
-      <c r="Q46" s="495"/>
-      <c r="R46" s="496"/>
+    <row r="46" spans="2:18">
+      <c r="B46" s="526"/>
+      <c r="C46" s="527"/>
+      <c r="D46" s="527"/>
+      <c r="E46" s="527"/>
+      <c r="F46" s="528"/>
+      <c r="G46" s="437"/>
+      <c r="H46" s="438"/>
+      <c r="I46" s="438"/>
+      <c r="J46" s="439"/>
+      <c r="K46" s="437"/>
+      <c r="L46" s="438"/>
+      <c r="M46" s="438"/>
+      <c r="N46" s="439"/>
+      <c r="O46" s="437"/>
+      <c r="P46" s="438"/>
+      <c r="Q46" s="438"/>
+      <c r="R46" s="439"/>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="507"/>
-      <c r="C47" s="508"/>
-      <c r="D47" s="508"/>
-      <c r="E47" s="508"/>
-      <c r="F47" s="509"/>
-      <c r="G47" s="494"/>
-      <c r="H47" s="495"/>
-      <c r="I47" s="495"/>
-      <c r="J47" s="496"/>
-      <c r="K47" s="494"/>
-      <c r="L47" s="495"/>
-      <c r="M47" s="495"/>
-      <c r="N47" s="496"/>
-      <c r="O47" s="494"/>
-      <c r="P47" s="495"/>
-      <c r="Q47" s="495"/>
-      <c r="R47" s="496"/>
+    <row r="47" spans="2:18">
+      <c r="B47" s="526"/>
+      <c r="C47" s="527"/>
+      <c r="D47" s="527"/>
+      <c r="E47" s="527"/>
+      <c r="F47" s="528"/>
+      <c r="G47" s="437"/>
+      <c r="H47" s="438"/>
+      <c r="I47" s="438"/>
+      <c r="J47" s="439"/>
+      <c r="K47" s="437"/>
+      <c r="L47" s="438"/>
+      <c r="M47" s="438"/>
+      <c r="N47" s="439"/>
+      <c r="O47" s="437"/>
+      <c r="P47" s="438"/>
+      <c r="Q47" s="438"/>
+      <c r="R47" s="439"/>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="507"/>
-      <c r="C48" s="508"/>
-      <c r="D48" s="508"/>
-      <c r="E48" s="508"/>
-      <c r="F48" s="509"/>
-      <c r="G48" s="494"/>
-      <c r="H48" s="495"/>
-      <c r="I48" s="495"/>
-      <c r="J48" s="496"/>
-      <c r="K48" s="494"/>
-      <c r="L48" s="495"/>
-      <c r="M48" s="495"/>
-      <c r="N48" s="496"/>
-      <c r="O48" s="494"/>
-      <c r="P48" s="495"/>
-      <c r="Q48" s="495"/>
-      <c r="R48" s="496"/>
+    <row r="48" spans="2:18">
+      <c r="B48" s="526"/>
+      <c r="C48" s="527"/>
+      <c r="D48" s="527"/>
+      <c r="E48" s="527"/>
+      <c r="F48" s="528"/>
+      <c r="G48" s="437"/>
+      <c r="H48" s="438"/>
+      <c r="I48" s="438"/>
+      <c r="J48" s="439"/>
+      <c r="K48" s="437"/>
+      <c r="L48" s="438"/>
+      <c r="M48" s="438"/>
+      <c r="N48" s="439"/>
+      <c r="O48" s="437"/>
+      <c r="P48" s="438"/>
+      <c r="Q48" s="438"/>
+      <c r="R48" s="439"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="507"/>
-      <c r="C49" s="508"/>
-      <c r="D49" s="508"/>
-      <c r="E49" s="508"/>
-      <c r="F49" s="509"/>
-      <c r="G49" s="494"/>
-      <c r="H49" s="495"/>
-      <c r="I49" s="495"/>
-      <c r="J49" s="496"/>
-      <c r="K49" s="494"/>
-      <c r="L49" s="495"/>
-      <c r="M49" s="495"/>
-      <c r="N49" s="496"/>
-      <c r="O49" s="494"/>
-      <c r="P49" s="495"/>
-      <c r="Q49" s="495"/>
-      <c r="R49" s="496"/>
+    <row r="49" spans="2:18">
+      <c r="B49" s="526"/>
+      <c r="C49" s="527"/>
+      <c r="D49" s="527"/>
+      <c r="E49" s="527"/>
+      <c r="F49" s="528"/>
+      <c r="G49" s="437"/>
+      <c r="H49" s="438"/>
+      <c r="I49" s="438"/>
+      <c r="J49" s="439"/>
+      <c r="K49" s="437"/>
+      <c r="L49" s="438"/>
+      <c r="M49" s="438"/>
+      <c r="N49" s="439"/>
+      <c r="O49" s="437"/>
+      <c r="P49" s="438"/>
+      <c r="Q49" s="438"/>
+      <c r="R49" s="439"/>
     </row>
-    <row r="50" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="510"/>
-      <c r="C50" s="511"/>
-      <c r="D50" s="511"/>
-      <c r="E50" s="511"/>
-      <c r="F50" s="512"/>
-      <c r="G50" s="497"/>
-      <c r="H50" s="498"/>
-      <c r="I50" s="498"/>
-      <c r="J50" s="499"/>
-      <c r="K50" s="497"/>
-      <c r="L50" s="498"/>
-      <c r="M50" s="498"/>
-      <c r="N50" s="499"/>
-      <c r="O50" s="497"/>
-      <c r="P50" s="498"/>
-      <c r="Q50" s="498"/>
-      <c r="R50" s="499"/>
+    <row r="50" spans="2:18" ht="15.75" thickBot="1">
+      <c r="B50" s="529"/>
+      <c r="C50" s="530"/>
+      <c r="D50" s="530"/>
+      <c r="E50" s="530"/>
+      <c r="F50" s="531"/>
+      <c r="G50" s="440"/>
+      <c r="H50" s="441"/>
+      <c r="I50" s="441"/>
+      <c r="J50" s="442"/>
+      <c r="K50" s="440"/>
+      <c r="L50" s="441"/>
+      <c r="M50" s="441"/>
+      <c r="N50" s="442"/>
+      <c r="O50" s="440"/>
+      <c r="P50" s="441"/>
+      <c r="Q50" s="441"/>
+      <c r="R50" s="442"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -34328,7 +34416,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880F104-7035-43DA-B153-19B04B138594}">
   <dimension ref="D6:J15"/>
-  <sheetFormatPr defaultRowHeight="50.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="50.45" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="17.125" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
@@ -34338,12 +34426,12 @@
     <col min="10" max="10" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="E6" s="318" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D7" s="319" t="s">
         <v>168</v>
       </c>
@@ -34366,7 +34454,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D8" s="320" t="s">
         <v>175</v>
       </c>
@@ -34389,7 +34477,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D9" s="320" t="s">
         <v>182</v>
       </c>
@@ -34412,7 +34500,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D10" s="320" t="s">
         <v>187</v>
       </c>
@@ -34435,7 +34523,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D11" s="320" t="s">
         <v>193</v>
       </c>
@@ -34458,7 +34546,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D12" s="320" t="s">
         <v>198</v>
       </c>
@@ -34481,7 +34569,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="13" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D13" s="320" t="s">
         <v>205</v>
       </c>
@@ -34504,7 +34592,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D14" s="320" t="s">
         <v>210</v>
       </c>
@@ -34527,7 +34615,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
       <c r="D15" s="320" t="s">
         <v>217</v>
       </c>
@@ -34558,8 +34646,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
   <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:Y160"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y164"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="1" bestFit="1" customWidth="1"/>
@@ -34574,7 +34662,7 @@
     <col min="11" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="57" customHeight="1" thickBot="1">
       <c r="A1" s="257" t="s">
         <v>223</v>
       </c>
@@ -34606,7 +34694,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A2" s="236" t="s">
         <v>231</v>
       </c>
@@ -34640,7 +34728,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A3" s="237" t="s">
         <v>231</v>
       </c>
@@ -34674,7 +34762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A4" s="249" t="s">
         <v>231</v>
       </c>
@@ -34708,7 +34796,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A5" s="236" t="s">
         <v>231</v>
       </c>
@@ -34742,7 +34830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A6" s="236" t="s">
         <v>231</v>
       </c>
@@ -34776,7 +34864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A7" s="236" t="s">
         <v>231</v>
       </c>
@@ -34810,7 +34898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A8" s="250" t="s">
         <v>231</v>
       </c>
@@ -34844,7 +34932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A9" s="235" t="s">
         <v>231</v>
       </c>
@@ -34878,7 +34966,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A10" s="236" t="s">
         <v>231</v>
       </c>
@@ -34912,7 +35000,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A11" s="237" t="s">
         <v>231</v>
       </c>
@@ -34946,7 +35034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A12" s="249" t="s">
         <v>231</v>
       </c>
@@ -34980,7 +35068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="182" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A13" s="236" t="s">
         <v>231</v>
       </c>
@@ -35014,7 +35102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A14" s="236" t="s">
         <v>231</v>
       </c>
@@ -35048,7 +35136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A15" s="236" t="s">
         <v>231</v>
       </c>
@@ -35082,7 +35170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A16" s="236" t="s">
         <v>231</v>
       </c>
@@ -35116,7 +35204,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A17" s="236" t="s">
         <v>231</v>
       </c>
@@ -35150,7 +35238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A18" s="331" t="s">
         <v>231</v>
       </c>
@@ -35184,7 +35272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="262" t="s">
         <v>231</v>
       </c>
@@ -35218,7 +35306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A20" s="249" t="s">
         <v>231</v>
       </c>
@@ -35252,7 +35340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A21" s="236" t="s">
         <v>231</v>
       </c>
@@ -35286,7 +35374,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A22" s="236" t="s">
         <v>231</v>
       </c>
@@ -35320,7 +35408,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A23" s="236" t="s">
         <v>231</v>
       </c>
@@ -35354,7 +35442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A24" s="236" t="s">
         <v>231</v>
       </c>
@@ -35388,7 +35476,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A25" s="236" t="s">
         <v>231</v>
       </c>
@@ -35422,7 +35510,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="255" customFormat="1" ht="19.899999999999999" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" s="255" customFormat="1" ht="19.899999999999999" hidden="1" customHeight="1" thickBot="1">
       <c r="A26" s="237" t="s">
         <v>231</v>
       </c>
@@ -35456,7 +35544,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A27" s="235" t="s">
         <v>231</v>
       </c>
@@ -35490,7 +35578,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A28" s="236" t="s">
         <v>231</v>
       </c>
@@ -35524,7 +35612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A29" s="236" t="s">
         <v>231</v>
       </c>
@@ -35558,7 +35646,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A30" s="236" t="s">
         <v>231</v>
       </c>
@@ -35592,7 +35680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A31" s="236" t="s">
         <v>231</v>
       </c>
@@ -35626,7 +35714,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="13.9" hidden="1" customHeight="1">
       <c r="A32" s="236" t="s">
         <v>231</v>
       </c>
@@ -35660,7 +35748,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A33" s="236" t="s">
         <v>231</v>
       </c>
@@ -35694,7 +35782,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A34" s="237" t="s">
         <v>231</v>
       </c>
@@ -35728,7 +35816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="182" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A35" s="254" t="s">
         <v>231</v>
       </c>
@@ -35762,7 +35850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A36" s="246" t="s">
         <v>231</v>
       </c>
@@ -35796,7 +35884,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A37" s="246" t="s">
         <v>231</v>
       </c>
@@ -35830,7 +35918,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A38" s="212" t="s">
         <v>231</v>
       </c>
@@ -35864,7 +35952,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="255" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="255" customFormat="1">
       <c r="A39" s="262" t="s">
         <v>278</v>
       </c>
@@ -35898,7 +35986,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="182" customFormat="1">
       <c r="A40" s="379" t="s">
         <v>278</v>
       </c>
@@ -35932,7 +36020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="182" customFormat="1" ht="15.75" thickBot="1">
       <c r="A41" s="408" t="s">
         <v>278</v>
       </c>
@@ -35966,7 +36054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="262" t="s">
         <v>278</v>
       </c>
@@ -36000,7 +36088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="246" t="s">
         <v>278</v>
       </c>
@@ -36034,7 +36122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="246" t="s">
         <v>278</v>
       </c>
@@ -36068,7 +36156,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="246" t="s">
         <v>278</v>
       </c>
@@ -36102,7 +36190,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="246" t="s">
         <v>278</v>
       </c>
@@ -36136,7 +36224,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="246" t="s">
         <v>278</v>
       </c>
@@ -36170,7 +36258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="15.75" thickBot="1">
       <c r="A48" s="247" t="s">
         <v>278</v>
       </c>
@@ -36204,7 +36292,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" s="249" t="s">
         <v>231</v>
       </c>
@@ -36238,7 +36326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="249" t="s">
         <v>231</v>
       </c>
@@ -36272,7 +36360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="249" t="s">
         <v>231</v>
       </c>
@@ -36306,7 +36394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="249" t="s">
         <v>231</v>
       </c>
@@ -36340,7 +36428,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="249" t="s">
         <v>231</v>
       </c>
@@ -36374,7 +36462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="249" t="s">
         <v>231</v>
       </c>
@@ -36408,7 +36496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="249" t="s">
         <v>231</v>
       </c>
@@ -36442,7 +36530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="249" t="s">
         <v>231</v>
       </c>
@@ -36476,7 +36564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="249" t="s">
         <v>231</v>
       </c>
@@ -36510,7 +36598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="255" customFormat="1" hidden="1">
       <c r="A58" s="261" t="s">
         <v>231</v>
       </c>
@@ -36544,7 +36632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="235" t="s">
         <v>231</v>
       </c>
@@ -36578,7 +36666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="236" t="s">
         <v>231</v>
       </c>
@@ -36612,7 +36700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" s="236" t="s">
         <v>231</v>
       </c>
@@ -36646,7 +36734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" s="236" t="s">
         <v>231</v>
       </c>
@@ -36680,7 +36768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A63" s="237" t="s">
         <v>231</v>
       </c>
@@ -36714,7 +36802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="254" t="s">
         <v>231</v>
       </c>
@@ -36748,7 +36836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A65" s="247" t="s">
         <v>231</v>
       </c>
@@ -36782,7 +36870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="13.9" hidden="1" customHeight="1">
       <c r="A66" s="249" t="s">
         <v>231</v>
       </c>
@@ -36816,7 +36904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" s="236" t="s">
         <v>231</v>
       </c>
@@ -36850,7 +36938,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="236" t="s">
         <v>231</v>
       </c>
@@ -36884,7 +36972,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="236" t="s">
         <v>231</v>
       </c>
@@ -36918,7 +37006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="236" t="s">
         <v>231</v>
       </c>
@@ -36952,7 +37040,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="236" t="s">
         <v>231</v>
       </c>
@@ -36986,7 +37074,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="195" customFormat="1" ht="20.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="195" customFormat="1" ht="20.45" hidden="1" customHeight="1">
       <c r="A72" s="236" t="s">
         <v>231</v>
       </c>
@@ -37020,7 +37108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" s="255" customFormat="1" hidden="1">
       <c r="A73" s="250" t="s">
         <v>231</v>
       </c>
@@ -37054,7 +37142,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="235" t="s">
         <v>231</v>
       </c>
@@ -37088,7 +37176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="236" t="s">
         <v>231</v>
       </c>
@@ -37122,7 +37210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="236" t="s">
         <v>231</v>
       </c>
@@ -37156,7 +37244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="236" t="s">
         <v>231</v>
       </c>
@@ -37190,7 +37278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="236" t="s">
         <v>231</v>
       </c>
@@ -37224,7 +37312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="236" t="s">
         <v>231</v>
       </c>
@@ -37258,7 +37346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="236" t="s">
         <v>231</v>
       </c>
@@ -37292,7 +37380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="236" t="s">
         <v>231</v>
       </c>
@@ -37326,7 +37414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="236" t="s">
         <v>231</v>
       </c>
@@ -37360,7 +37448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="236" t="s">
         <v>231</v>
       </c>
@@ -37394,7 +37482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="236" t="s">
         <v>231</v>
       </c>
@@ -37428,7 +37516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="236" t="s">
         <v>231</v>
       </c>
@@ -37462,7 +37550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="236" t="s">
         <v>231</v>
       </c>
@@ -37496,7 +37584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="236" t="s">
         <v>231</v>
       </c>
@@ -37530,7 +37618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="236" t="s">
         <v>231</v>
       </c>
@@ -37564,7 +37652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="236" t="s">
         <v>231</v>
       </c>
@@ -37598,7 +37686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="250" t="s">
         <v>231</v>
       </c>
@@ -37632,7 +37720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="235" t="s">
         <v>231</v>
       </c>
@@ -37666,7 +37754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="255" customFormat="1" hidden="1">
       <c r="A92" s="235" t="s">
         <v>231</v>
       </c>
@@ -37700,7 +37788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="262" t="s">
         <v>231</v>
       </c>
@@ -37734,7 +37822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="246" t="s">
         <v>231</v>
       </c>
@@ -37768,7 +37856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="246" t="s">
         <v>231</v>
       </c>
@@ -37802,7 +37890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="246" t="s">
         <v>231</v>
       </c>
@@ -37836,7 +37924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="30.75" thickBot="1">
       <c r="A97" s="246" t="s">
         <v>278</v>
       </c>
@@ -37870,7 +37958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10">
       <c r="A98" s="262" t="s">
         <v>278</v>
       </c>
@@ -37904,7 +37992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="246" t="s">
         <v>278</v>
       </c>
@@ -37938,7 +38026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10">
       <c r="A100" s="246" t="s">
         <v>278</v>
       </c>
@@ -37958,7 +38046,7 @@
         <v>46208.864583333336</v>
       </c>
       <c r="G100" s="180">
-        <f t="shared" ref="G100:G125" si="6">F100+(H100/24)</f>
+        <f t="shared" ref="G100:G130" si="6">F100+(H100/24)</f>
         <v>46210.864583333336</v>
       </c>
       <c r="H100" s="32">
@@ -37972,7 +38060,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10">
       <c r="A101" s="246" t="s">
         <v>278</v>
       </c>
@@ -38006,7 +38094,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" ht="15.75" thickBot="1">
       <c r="A102" s="247" t="s">
         <v>278</v>
       </c>
@@ -38040,7 +38128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A103" s="249" t="s">
         <v>231</v>
       </c>
@@ -38074,7 +38162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A104" s="236" t="s">
         <v>231</v>
       </c>
@@ -38108,7 +38196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A105" s="236" t="s">
         <v>231</v>
       </c>
@@ -38142,7 +38230,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A106" s="237" t="s">
         <v>231</v>
       </c>
@@ -38176,7 +38264,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A107" s="235" t="s">
         <v>231</v>
       </c>
@@ -38210,7 +38298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A108" s="250" t="s">
         <v>231</v>
       </c>
@@ -38244,7 +38332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" ht="15.75" hidden="1" thickBot="1">
       <c r="A109" s="343" t="s">
         <v>231</v>
       </c>
@@ -38278,7 +38366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" ht="15.75" thickBot="1">
       <c r="A110" s="384" t="s">
         <v>278</v>
       </c>
@@ -38312,7 +38400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10">
       <c r="A111" s="262" t="s">
         <v>278</v>
       </c>
@@ -38346,7 +38434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10">
       <c r="A112" s="246" t="s">
         <v>278</v>
       </c>
@@ -38380,7 +38468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25">
       <c r="A113" s="246" t="s">
         <v>278</v>
       </c>
@@ -38417,7 +38505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25">
       <c r="A114" s="246" t="s">
         <v>278</v>
       </c>
@@ -38451,7 +38539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="15.75" thickBot="1">
       <c r="A115" s="331" t="s">
         <v>278</v>
       </c>
@@ -38485,7 +38573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25">
       <c r="A116" s="262" t="s">
         <v>278</v>
       </c>
@@ -38519,7 +38607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="15.75" thickBot="1">
       <c r="A117" s="331" t="s">
         <v>278</v>
       </c>
@@ -38553,7 +38641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="15.75" thickBot="1">
       <c r="A118" s="384" t="s">
         <v>278</v>
       </c>
@@ -38587,7 +38675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="15.75" hidden="1" thickBot="1">
       <c r="A119" s="262" t="s">
         <v>231</v>
       </c>
@@ -38621,7 +38709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:25" s="395" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" s="395" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A120" s="246" t="s">
         <v>231</v>
       </c>
@@ -38655,7 +38743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="15.75" hidden="1" thickBot="1">
       <c r="A121" s="246" t="s">
         <v>231</v>
       </c>
@@ -38688,7 +38776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="15.75" hidden="1" thickBot="1">
       <c r="A122" s="331" t="s">
         <v>231</v>
       </c>
@@ -38724,7 +38812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25">
       <c r="A123" s="262" t="s">
         <v>278</v>
       </c>
@@ -38751,21 +38839,21 @@
         <v>72</v>
       </c>
       <c r="I123" s="188">
-        <f t="shared" ref="I123:I160" si="8">G123+(J123/24)</f>
+        <f t="shared" ref="I123:I163" si="8">G123+(J123/24)</f>
         <v>46199.875</v>
       </c>
       <c r="J123" s="190">
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="400" t="s">
+    <row r="124" spans="1:25">
+      <c r="A124" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B124" s="401" t="s">
+      <c r="B124" s="189" t="s">
         <v>163</v>
       </c>
-      <c r="C124" s="402" t="s">
+      <c r="C124" s="122" t="s">
         <v>383</v>
       </c>
       <c r="D124" s="123" t="s">
@@ -38778,940 +38866,1450 @@
         <v>46197.375</v>
       </c>
       <c r="G124" s="205">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G124" si="9">F124+(H124/24)</f>
         <v>46200.375</v>
       </c>
       <c r="H124" s="184">
         <v>72</v>
       </c>
       <c r="I124" s="205">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I124" si="10">G124+(J124/24)</f>
         <v>46200.875</v>
       </c>
       <c r="J124" s="127">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="415" t="s">
+    <row r="125" spans="1:25">
+      <c r="A125" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C125" s="122" t="s">
+        <v>383</v>
+      </c>
+      <c r="D125" s="345" t="s">
+        <v>386</v>
+      </c>
+      <c r="E125" s="422">
+        <v>46200</v>
+      </c>
+      <c r="F125" s="423">
+        <v>46201.375</v>
+      </c>
+      <c r="G125" s="423">
+        <f>F125+(H125/24)</f>
+        <v>46204.875</v>
+      </c>
+      <c r="H125" s="344">
+        <v>84</v>
+      </c>
+      <c r="I125" s="423">
+        <f>G125+(J125/24)</f>
+        <v>46205.375</v>
+      </c>
+      <c r="J125" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25">
+      <c r="A126" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B126" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C126" s="122" t="s">
+        <v>387</v>
+      </c>
+      <c r="D126" s="421" t="s">
+        <v>388</v>
+      </c>
+      <c r="E126" s="406">
+        <v>46202</v>
+      </c>
+      <c r="F126" s="407">
+        <v>46203.5625</v>
+      </c>
+      <c r="G126" s="423">
+        <f t="shared" ref="G126:G129" si="11">F126+(H126/24)</f>
+        <v>46205.0625</v>
+      </c>
+      <c r="H126" s="404">
+        <v>36</v>
+      </c>
+      <c r="I126" s="423">
+        <f t="shared" ref="I126:I129" si="12">G126+(J126/24)</f>
+        <v>46205.5625</v>
+      </c>
+      <c r="J126" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" ht="30.75">
+      <c r="A127" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B127" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" s="122" t="s">
+        <v>387</v>
+      </c>
+      <c r="D127" s="458" t="s">
+        <v>389</v>
+      </c>
+      <c r="E127" s="239">
+        <v>46208</v>
+      </c>
+      <c r="F127" s="188">
+        <v>46209.791666666664</v>
+      </c>
+      <c r="G127" s="423">
+        <f t="shared" si="11"/>
+        <v>46211.291666666664</v>
+      </c>
+      <c r="H127" s="189">
+        <v>36</v>
+      </c>
+      <c r="I127" s="423">
+        <f t="shared" si="12"/>
+        <v>46211.791666666664</v>
+      </c>
+      <c r="J127" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25">
+      <c r="A128" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B128" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C128" s="122" t="s">
+        <v>387</v>
+      </c>
+      <c r="D128" s="122" t="s">
+        <v>390</v>
+      </c>
+      <c r="E128" s="239">
+        <v>46213</v>
+      </c>
+      <c r="F128" s="188">
+        <v>46214</v>
+      </c>
+      <c r="G128" s="423">
+        <f t="shared" si="11"/>
+        <v>46215.5</v>
+      </c>
+      <c r="H128" s="189">
+        <v>36</v>
+      </c>
+      <c r="I128" s="423">
+        <f t="shared" si="12"/>
+        <v>46216</v>
+      </c>
+      <c r="J128" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="30.75">
+      <c r="A129" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C129" s="122" t="s">
+        <v>387</v>
+      </c>
+      <c r="D129" s="458" t="s">
+        <v>391</v>
+      </c>
+      <c r="E129" s="239">
+        <v>46217</v>
+      </c>
+      <c r="F129" s="188">
+        <v>46218.875</v>
+      </c>
+      <c r="G129" s="423">
+        <f t="shared" si="11"/>
+        <v>46220.375</v>
+      </c>
+      <c r="H129" s="189">
+        <v>36</v>
+      </c>
+      <c r="I129" s="423">
+        <f t="shared" si="12"/>
+        <v>46220.875</v>
+      </c>
+      <c r="J129" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+      <c r="A130" s="415" t="s">
         <v>231</v>
       </c>
-      <c r="B125" s="416" t="s">
+      <c r="B130" s="416" t="s">
         <v>64</v>
       </c>
-      <c r="C125" s="417" t="s">
-        <v>386</v>
-      </c>
-      <c r="D125" s="417" t="s">
-        <v>387</v>
-      </c>
-      <c r="E125" s="418">
+      <c r="C130" s="417" t="s">
+        <v>392</v>
+      </c>
+      <c r="D130" s="417" t="s">
+        <v>393</v>
+      </c>
+      <c r="E130" s="418">
         <v>46162</v>
       </c>
-      <c r="F125" s="418">
+      <c r="F130" s="418">
         <v>46164</v>
       </c>
-      <c r="G125" s="419">
+      <c r="G130" s="419">
         <f t="shared" si="6"/>
         <v>46164.416666666664</v>
       </c>
-      <c r="H125" s="416">
+      <c r="H130" s="416">
         <v>10</v>
       </c>
-      <c r="I125" s="419">
+      <c r="I130" s="419">
         <f t="shared" si="8"/>
         <v>46164.833333333328</v>
       </c>
-      <c r="J125" s="420">
+      <c r="J130" s="420">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="380" t="s">
+    <row r="131" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+      <c r="A131" s="380" t="s">
         <v>231</v>
       </c>
-      <c r="B126" s="350" t="s">
+      <c r="B131" s="350" t="s">
         <v>64</v>
       </c>
-      <c r="C126" s="349" t="s">
-        <v>386</v>
-      </c>
-      <c r="D126" s="349" t="s">
-        <v>388</v>
-      </c>
-      <c r="E126" s="351">
+      <c r="C131" s="349" t="s">
+        <v>392</v>
+      </c>
+      <c r="D131" s="349" t="s">
+        <v>394</v>
+      </c>
+      <c r="E131" s="351">
         <v>46163</v>
       </c>
-      <c r="F126" s="351">
+      <c r="F131" s="351">
         <v>46165</v>
       </c>
-      <c r="G126" s="352">
-        <f>F125+(H125/24)</f>
+      <c r="G131" s="352">
+        <f>F130+(H130/24)</f>
         <v>46164.416666666664</v>
       </c>
-      <c r="H126" s="350">
+      <c r="H131" s="350">
         <v>5</v>
       </c>
-      <c r="I126" s="352">
+      <c r="I131" s="352">
         <f t="shared" si="8"/>
         <v>46164.625</v>
       </c>
-      <c r="J126" s="381">
+      <c r="J131" s="381">
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="380" t="s">
+    <row r="132" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+      <c r="A132" s="380" t="s">
         <v>231</v>
       </c>
-      <c r="B127" s="354" t="s">
+      <c r="B132" s="354" t="s">
         <v>64</v>
       </c>
-      <c r="C127" s="353" t="s">
-        <v>386</v>
-      </c>
-      <c r="D127" s="185" t="s">
-        <v>389</v>
-      </c>
-      <c r="E127" s="355">
+      <c r="C132" s="353" t="s">
+        <v>392</v>
+      </c>
+      <c r="D132" s="185" t="s">
+        <v>395</v>
+      </c>
+      <c r="E132" s="355">
         <v>46166</v>
       </c>
-      <c r="F127" s="355">
+      <c r="F132" s="355">
         <v>46168</v>
       </c>
-      <c r="G127" s="356">
-        <f t="shared" ref="G127:G160" si="9">F127+(H127/24)</f>
+      <c r="G132" s="356">
+        <f t="shared" ref="G132:G163" si="13">F132+(H132/24)</f>
         <v>46168.208333333336</v>
       </c>
-      <c r="H127" s="354">
+      <c r="H132" s="354">
         <v>5</v>
       </c>
-      <c r="I127" s="356">
+      <c r="I132" s="356">
         <f t="shared" si="8"/>
         <v>46168.416666666672</v>
       </c>
-      <c r="J127" s="382">
+      <c r="J132" s="382">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="380" t="s">
+    <row r="133" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+      <c r="A133" s="380" t="s">
         <v>231</v>
       </c>
-      <c r="B128" s="354" t="s">
+      <c r="B133" s="354" t="s">
         <v>64</v>
       </c>
-      <c r="C128" s="353" t="s">
-        <v>386</v>
-      </c>
-      <c r="D128" s="414" t="s">
-        <v>390</v>
-      </c>
-      <c r="E128" s="355">
+      <c r="C133" s="353" t="s">
+        <v>392</v>
+      </c>
+      <c r="D133" s="414" t="s">
+        <v>396</v>
+      </c>
+      <c r="E133" s="355">
         <v>46170</v>
       </c>
-      <c r="F128" s="355">
+      <c r="F133" s="355">
         <v>46172</v>
       </c>
-      <c r="G128" s="356">
-        <f t="shared" si="9"/>
+      <c r="G133" s="356">
+        <f t="shared" si="13"/>
         <v>46172.416666666664</v>
       </c>
-      <c r="H128" s="354">
+      <c r="H133" s="354">
         <v>10</v>
       </c>
-      <c r="I128" s="356">
+      <c r="I133" s="356">
         <f t="shared" si="8"/>
         <v>46172.833333333328</v>
       </c>
-      <c r="J128" s="382">
+      <c r="J133" s="382">
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="422" t="s">
+    <row r="134" spans="1:10">
+      <c r="A134" s="383" t="s">
         <v>278</v>
       </c>
-      <c r="B129" s="423" t="s">
-        <v>163</v>
-      </c>
-      <c r="C129" s="424" t="s">
-        <v>383</v>
-      </c>
-      <c r="D129" s="345" t="s">
-        <v>391</v>
-      </c>
-      <c r="E129" s="425">
-        <v>46200</v>
-      </c>
-      <c r="F129" s="426">
-        <v>46201.375</v>
-      </c>
-      <c r="G129" s="426">
-        <f>F129+(H129/24)</f>
-        <v>46204.875</v>
-      </c>
-      <c r="H129" s="344">
-        <v>84</v>
-      </c>
-      <c r="I129" s="426">
-        <f>G129+(J129/24)</f>
-        <v>46205.375</v>
-      </c>
-      <c r="J129" s="348">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="383" t="s">
-        <v>278</v>
-      </c>
-      <c r="B130" s="404" t="s">
-        <v>392</v>
-      </c>
-      <c r="C130" s="383" t="s">
-        <v>393</v>
-      </c>
-      <c r="D130" s="421" t="s">
-        <v>394</v>
-      </c>
-      <c r="E130" s="406">
+      <c r="B134" s="404" t="s">
+        <v>397</v>
+      </c>
+      <c r="C134" s="383" t="s">
+        <v>398</v>
+      </c>
+      <c r="D134" s="421" t="s">
+        <v>399</v>
+      </c>
+      <c r="E134" s="406">
         <v>46261</v>
       </c>
-      <c r="F130" s="407">
+      <c r="F134" s="407">
         <v>46266.25</v>
       </c>
-      <c r="G130" s="407">
-        <f t="shared" si="9"/>
+      <c r="G134" s="407">
+        <f t="shared" si="13"/>
         <v>46388.25</v>
       </c>
-      <c r="H130" s="404">
+      <c r="H134" s="404">
         <v>2928</v>
       </c>
-      <c r="I130" s="407">
+      <c r="I134" s="407">
         <f t="shared" si="8"/>
         <v>46388.583333333336</v>
       </c>
-      <c r="J130" s="404">
+      <c r="J134" s="404">
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="262" t="s">
+    <row r="135" spans="1:10">
+      <c r="A135" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B131" s="189" t="s">
+      <c r="B135" s="189" t="s">
         <v>232</v>
       </c>
-      <c r="C131" s="122" t="s">
-        <v>395</v>
-      </c>
-      <c r="D131" s="405" t="s">
-        <v>396</v>
-      </c>
-      <c r="E131" s="239">
+      <c r="C135" s="122" t="s">
+        <v>400</v>
+      </c>
+      <c r="D135" s="405" t="s">
+        <v>401</v>
+      </c>
+      <c r="E135" s="239">
         <v>46185</v>
       </c>
-      <c r="F131" s="188">
+      <c r="F135" s="188">
         <v>46187.635416666664</v>
       </c>
-      <c r="G131" s="188">
-        <f t="shared" si="9"/>
+      <c r="G135" s="188">
+        <f t="shared" si="13"/>
         <v>46189.135416666664</v>
       </c>
-      <c r="H131" s="189">
+      <c r="H135" s="189">
         <v>36</v>
       </c>
-      <c r="I131" s="188">
+      <c r="I135" s="188">
         <f t="shared" si="8"/>
         <v>46189.802083333328</v>
       </c>
-      <c r="J131" s="190">
+      <c r="J135" s="190">
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="246" t="s">
+    <row r="136" spans="1:10">
+      <c r="A136" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B132" s="32" t="s">
+      <c r="B136" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C132" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D132" s="397" t="s">
-        <v>397</v>
-      </c>
-      <c r="E132" s="54">
+      <c r="C136" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D136" s="397" t="s">
+        <v>402</v>
+      </c>
+      <c r="E136" s="54">
         <v>46187</v>
       </c>
-      <c r="F132" s="180">
+      <c r="F136" s="180">
         <v>46189.489583333336</v>
       </c>
-      <c r="G132" s="180">
-        <f t="shared" si="9"/>
+      <c r="G136" s="180">
+        <f t="shared" si="13"/>
         <v>46190.489583333336</v>
       </c>
-      <c r="H132" s="32">
+      <c r="H136" s="32">
         <v>24</v>
       </c>
-      <c r="I132" s="180">
+      <c r="I136" s="180">
         <f t="shared" si="8"/>
         <v>46191.15625</v>
       </c>
-      <c r="J132" s="126">
+      <c r="J136" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="246" t="s">
+    <row r="137" spans="1:10">
+      <c r="A137" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B133" s="32" t="s">
+      <c r="B137" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C133" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D133" s="392" t="s">
-        <v>398</v>
-      </c>
-      <c r="E133" s="393">
+      <c r="C137" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D137" s="392" t="s">
+        <v>403</v>
+      </c>
+      <c r="E137" s="393">
         <v>46191</v>
       </c>
-      <c r="F133" s="394">
+      <c r="F137" s="394">
         <v>46192.84375</v>
       </c>
-      <c r="G133" s="394">
-        <f t="shared" si="9"/>
+      <c r="G137" s="394">
+        <f t="shared" si="13"/>
         <v>46194.34375</v>
       </c>
-      <c r="H133" s="391">
+      <c r="H137" s="391">
         <v>36</v>
       </c>
-      <c r="I133" s="394">
+      <c r="I137" s="394">
         <f t="shared" si="8"/>
         <v>46195.010416666664</v>
       </c>
-      <c r="J133" s="126">
+      <c r="J137" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="246" t="s">
+    <row r="138" spans="1:10">
+      <c r="A138" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B134" s="32" t="s">
+      <c r="B138" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C134" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D134" s="392" t="s">
-        <v>399</v>
-      </c>
-      <c r="E134" s="54">
+      <c r="C138" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D138" s="392" t="s">
+        <v>404</v>
+      </c>
+      <c r="E138" s="54">
         <v>46191</v>
       </c>
-      <c r="F134" s="180">
+      <c r="F138" s="180">
         <v>46194.239583333336</v>
       </c>
-      <c r="G134" s="180">
-        <f t="shared" si="9"/>
+      <c r="G138" s="180">
+        <f t="shared" si="13"/>
         <v>46196.239583333336</v>
       </c>
-      <c r="H134" s="32">
+      <c r="H138" s="32">
         <v>48</v>
       </c>
-      <c r="I134" s="180">
+      <c r="I138" s="180">
         <f t="shared" si="8"/>
         <v>46196.90625</v>
       </c>
-      <c r="J134" s="126">
+      <c r="J138" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="246" t="s">
+    <row r="139" spans="1:10">
+      <c r="A139" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B135" s="32" t="s">
+      <c r="B139" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C135" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D135" s="392" t="s">
+      <c r="C139" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="E135" s="54">
+      <c r="D139" s="392" t="s">
+        <v>405</v>
+      </c>
+      <c r="E139" s="54">
         <v>46196</v>
       </c>
-      <c r="F135" s="180">
+      <c r="F139" s="180">
         <v>46198.552083333336</v>
       </c>
-      <c r="G135" s="180">
-        <f t="shared" si="9"/>
+      <c r="G139" s="180">
+        <f t="shared" si="13"/>
         <v>46199.552083333336</v>
       </c>
-      <c r="H135" s="32">
+      <c r="H139" s="32">
         <v>24</v>
       </c>
-      <c r="I135" s="180">
+      <c r="I139" s="180">
         <f t="shared" si="8"/>
         <v>46200.21875</v>
       </c>
-      <c r="J135" s="126">
+      <c r="J139" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="246" t="s">
+    <row r="140" spans="1:10">
+      <c r="A140" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B136" s="32" t="s">
+      <c r="B140" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C136" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D136" s="397" t="s">
-        <v>401</v>
-      </c>
-      <c r="E136" s="54">
+      <c r="C140" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D140" s="397" t="s">
+        <v>406</v>
+      </c>
+      <c r="E140" s="54">
         <v>46207</v>
       </c>
-      <c r="F136" s="180">
+      <c r="F140" s="180">
         <v>46209.181944444441</v>
       </c>
-      <c r="G136" s="180">
-        <f t="shared" si="9"/>
+      <c r="G140" s="180">
+        <f t="shared" si="13"/>
         <v>46210.181944444441</v>
       </c>
-      <c r="H136" s="32">
+      <c r="H140" s="32">
         <v>24</v>
       </c>
-      <c r="I136" s="180">
+      <c r="I140" s="180">
         <f t="shared" si="8"/>
         <v>46210.848611111105</v>
       </c>
-      <c r="J136" s="126">
+      <c r="J140" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="379" t="s">
+    <row r="141" spans="1:10">
+      <c r="A141" s="379" t="s">
         <v>278</v>
       </c>
-      <c r="B137" s="243" t="s">
+      <c r="B141" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="C137" s="244" t="s">
-        <v>395</v>
-      </c>
-      <c r="D137" s="397" t="s">
-        <v>402</v>
-      </c>
-      <c r="E137" s="54">
+      <c r="C141" s="244" t="s">
+        <v>400</v>
+      </c>
+      <c r="D141" s="397" t="s">
+        <v>407</v>
+      </c>
+      <c r="E141" s="54">
         <v>46209</v>
       </c>
-      <c r="F137" s="180">
+      <c r="F141" s="180">
         <v>46211.181944444441</v>
       </c>
-      <c r="G137" s="245">
-        <f>F137+(H137/24)</f>
+      <c r="G141" s="245">
+        <f>F141+(H141/24)</f>
         <v>46212.181944444441</v>
       </c>
-      <c r="H137" s="32">
+      <c r="H141" s="32">
         <v>24</v>
       </c>
-      <c r="I137" s="245">
-        <f>G137+(J137/24)</f>
+      <c r="I141" s="245">
+        <f>G141+(J141/24)</f>
         <v>46212.848611111105</v>
       </c>
-      <c r="J137" s="126">
+      <c r="J141" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="400" t="s">
+    <row r="142" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A142" s="400" t="s">
         <v>278</v>
       </c>
-      <c r="B138" s="401" t="s">
+      <c r="B142" s="401" t="s">
         <v>232</v>
       </c>
-      <c r="C138" s="402" t="s">
-        <v>395</v>
-      </c>
-      <c r="D138" s="403" t="s">
-        <v>403</v>
-      </c>
-      <c r="E138" s="240">
+      <c r="C142" s="402" t="s">
+        <v>400</v>
+      </c>
+      <c r="D142" s="403" t="s">
+        <v>408</v>
+      </c>
+      <c r="E142" s="240">
         <v>46217</v>
       </c>
-      <c r="F138" s="183">
+      <c r="F142" s="183">
         <v>46219.837500000001</v>
       </c>
-      <c r="G138" s="205">
-        <f>F138+(H138/24)</f>
+      <c r="G142" s="205">
+        <f>F142+(H142/24)</f>
         <v>46220.837500000001</v>
       </c>
-      <c r="H138" s="184">
+      <c r="H142" s="184">
         <v>24</v>
       </c>
-      <c r="I138" s="205">
-        <f>G138+(J138/24)</f>
+      <c r="I142" s="205">
+        <f>G142+(J142/24)</f>
         <v>46221.504166666666</v>
       </c>
-      <c r="J138" s="127">
+      <c r="J142" s="127">
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="187" t="s">
+    <row r="143" spans="1:10">
+      <c r="A143" s="187" t="s">
         <v>278</v>
       </c>
-      <c r="B139" s="170" t="s">
+      <c r="B143" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="C139" s="187" t="s">
-        <v>404</v>
-      </c>
-      <c r="D139" s="398" t="s">
-        <v>405</v>
-      </c>
-      <c r="E139" s="242">
+      <c r="C143" s="187" t="s">
+        <v>409</v>
+      </c>
+      <c r="D143" s="398" t="s">
+        <v>410</v>
+      </c>
+      <c r="E143" s="242">
         <v>46193</v>
       </c>
-      <c r="F139" s="181">
+      <c r="F143" s="181">
         <v>46195.25</v>
       </c>
-      <c r="G139" s="181">
-        <f>F139+(H139/24)</f>
+      <c r="G143" s="181">
+        <f>F143+(H143/24)</f>
         <v>46197.25</v>
       </c>
-      <c r="H139" s="399">
+      <c r="H143" s="399">
         <v>48</v>
       </c>
-      <c r="I139" s="181">
-        <f>G139+(J139/24)</f>
+      <c r="I143" s="181">
+        <f>G143+(J143/24)</f>
         <v>46197.75</v>
       </c>
-      <c r="J139" s="399">
+      <c r="J143" s="399">
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="335" t="s">
-        <v>278</v>
-      </c>
-      <c r="B140" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D140" s="390" t="s">
-        <v>440</v>
-      </c>
-      <c r="E140" s="54">
-        <v>46930</v>
-      </c>
-      <c r="F140" s="336">
-        <v>46201.854166666664</v>
-      </c>
-      <c r="G140" s="180">
-        <f t="shared" si="9"/>
-        <v>46207.229166666664</v>
-      </c>
-      <c r="H140" s="32">
-        <v>129</v>
-      </c>
-      <c r="I140" s="180">
-        <f t="shared" si="8"/>
-        <v>46207.229166666664</v>
-      </c>
-      <c r="J140" s="32"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="335" t="s">
-        <v>278</v>
-      </c>
-      <c r="B141" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="54"/>
-      <c r="F141" s="180"/>
-      <c r="G141" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H141" s="32"/>
-      <c r="I141" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J141" s="32"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="335" t="s">
-        <v>278</v>
-      </c>
-      <c r="B142" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="32"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H142" s="32"/>
-      <c r="I142" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J142" s="32"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="335" t="s">
-        <v>278</v>
-      </c>
-      <c r="B143" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="32"/>
-      <c r="F143" s="32"/>
-      <c r="G143" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H143" s="32"/>
-      <c r="I143" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J143" s="32"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10">
       <c r="A144" s="335" t="s">
         <v>278</v>
       </c>
       <c r="B144" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="32"/>
-      <c r="F144" s="32"/>
+      <c r="C144" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D144" s="424" t="s">
+        <v>412</v>
+      </c>
+      <c r="E144" s="54">
+        <v>46191</v>
+      </c>
+      <c r="F144" s="180">
+        <v>46194.833333333336</v>
+      </c>
       <c r="G144" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H144" s="32"/>
+        <f>F144+(H144/24)</f>
+        <v>46201.854166666672</v>
+      </c>
+      <c r="H144" s="32">
+        <v>168.5</v>
+      </c>
       <c r="I144" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J144" s="32"/>
+        <f>G144+(J144/24)</f>
+        <v>46203.354166666672</v>
+      </c>
+      <c r="J144" s="32">
+        <v>36</v>
+      </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="7"/>
-      <c r="B145" s="32"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="32"/>
-      <c r="F145" s="32"/>
+    <row r="145" spans="1:25">
+      <c r="A145" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B145" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D145" s="390" t="s">
+        <v>414</v>
+      </c>
+      <c r="E145" s="54">
+        <v>46930</v>
+      </c>
+      <c r="F145" s="336">
+        <v>46201.854166666664</v>
+      </c>
       <c r="G145" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H145" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46207.229166666664</v>
+      </c>
+      <c r="H145" s="32">
+        <v>129</v>
+      </c>
       <c r="I145" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J145" s="32"/>
+        <v>46208.729166666664</v>
+      </c>
+      <c r="J145" s="32">
+        <v>36</v>
+      </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="7"/>
-      <c r="B146" s="32"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="32"/>
-      <c r="F146" s="32"/>
+    <row r="146" spans="1:25">
+      <c r="A146" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B146" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D146" s="424" t="s">
+        <v>416</v>
+      </c>
+      <c r="E146" s="54">
+        <v>46186</v>
+      </c>
+      <c r="F146" s="336">
+        <v>46189.25</v>
+      </c>
       <c r="G146" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H146" s="32"/>
+        <f>F146+(H146/24)</f>
+        <v>46193.25</v>
+      </c>
+      <c r="H146" s="32">
+        <v>96</v>
+      </c>
       <c r="I146" s="180">
+        <f>G146+(J146/24)</f>
+        <v>46194.75</v>
+      </c>
+      <c r="J146" s="32">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25">
+      <c r="A147" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B147" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" s="244" t="s">
+        <v>415</v>
+      </c>
+      <c r="D147" s="424" t="s">
+        <v>417</v>
+      </c>
+      <c r="E147" s="425">
+        <v>46327</v>
+      </c>
+      <c r="F147" s="336">
+        <v>46330.25</v>
+      </c>
+      <c r="G147" s="245">
+        <f t="shared" si="13"/>
+        <v>46334.25</v>
+      </c>
+      <c r="H147" s="243">
+        <v>96</v>
+      </c>
+      <c r="I147" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J146" s="32"/>
+        <v>46335.75</v>
+      </c>
+      <c r="J147" s="243">
+        <v>36</v>
+      </c>
+      <c r="K147" s="426"/>
+      <c r="L147" s="426"/>
+      <c r="M147" s="426"/>
+      <c r="N147" s="426"/>
+      <c r="O147" s="426"/>
+      <c r="P147" s="426"/>
+      <c r="Q147" s="426"/>
+      <c r="R147" s="426"/>
+      <c r="S147" s="426"/>
+      <c r="T147" s="426"/>
+      <c r="U147" s="426"/>
+      <c r="V147" s="426"/>
+      <c r="W147" s="426"/>
+      <c r="X147" s="426"/>
+      <c r="Y147" s="426"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="7"/>
-      <c r="B147" s="32"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="32"/>
-      <c r="F147" s="32"/>
-      <c r="G147" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H147" s="32"/>
-      <c r="I147" s="180">
+    <row r="148" spans="1:25">
+      <c r="A148" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B148" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="244" t="s">
+        <v>415</v>
+      </c>
+      <c r="D148" s="424" t="s">
+        <v>418</v>
+      </c>
+      <c r="E148" s="425">
+        <v>46334</v>
+      </c>
+      <c r="F148" s="336">
+        <v>46334.25</v>
+      </c>
+      <c r="G148" s="245">
+        <f t="shared" si="13"/>
+        <v>46338.25</v>
+      </c>
+      <c r="H148" s="243">
+        <v>96</v>
+      </c>
+      <c r="I148" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J147" s="32"/>
+        <v>46339.75</v>
+      </c>
+      <c r="J148" s="243">
+        <v>36</v>
+      </c>
+      <c r="K148" s="426"/>
+      <c r="L148" s="426"/>
+      <c r="M148" s="426"/>
+      <c r="N148" s="426"/>
+      <c r="O148" s="426"/>
+      <c r="P148" s="426"/>
+      <c r="Q148" s="426"/>
+      <c r="R148" s="426"/>
+      <c r="S148" s="426"/>
+      <c r="T148" s="426"/>
+      <c r="U148" s="426"/>
+      <c r="V148" s="426"/>
+      <c r="W148" s="426"/>
+      <c r="X148" s="426"/>
+      <c r="Y148" s="426"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="7"/>
-      <c r="B148" s="32"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="32"/>
-      <c r="F148" s="32"/>
-      <c r="G148" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H148" s="32"/>
-      <c r="I148" s="180">
+    <row r="149" spans="1:25">
+      <c r="A149" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B149" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="244" t="s">
+        <v>415</v>
+      </c>
+      <c r="D149" s="424" t="s">
+        <v>419</v>
+      </c>
+      <c r="E149" s="425">
+        <v>46341</v>
+      </c>
+      <c r="F149" s="336">
+        <v>46344.25</v>
+      </c>
+      <c r="G149" s="245">
+        <f t="shared" si="13"/>
+        <v>46348.25</v>
+      </c>
+      <c r="H149" s="243">
+        <v>96</v>
+      </c>
+      <c r="I149" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J148" s="32"/>
+        <v>46349.75</v>
+      </c>
+      <c r="J149" s="243">
+        <v>36</v>
+      </c>
+      <c r="K149" s="426"/>
+      <c r="L149" s="426"/>
+      <c r="M149" s="426"/>
+      <c r="N149" s="426"/>
+      <c r="O149" s="426"/>
+      <c r="P149" s="426"/>
+      <c r="Q149" s="426"/>
+      <c r="R149" s="426"/>
+      <c r="S149" s="426"/>
+      <c r="T149" s="426"/>
+      <c r="U149" s="426"/>
+      <c r="V149" s="426"/>
+      <c r="W149" s="426"/>
+      <c r="X149" s="426"/>
+      <c r="Y149" s="426"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="7"/>
-      <c r="B149" s="32"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="32"/>
-      <c r="F149" s="32"/>
-      <c r="G149" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H149" s="32"/>
-      <c r="I149" s="180">
+    <row r="150" spans="1:25">
+      <c r="A150" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B150" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="244" t="s">
+        <v>415</v>
+      </c>
+      <c r="D150" s="424" t="s">
+        <v>420</v>
+      </c>
+      <c r="E150" s="425">
+        <v>46348</v>
+      </c>
+      <c r="F150" s="336">
+        <v>46351.25</v>
+      </c>
+      <c r="G150" s="245">
+        <f t="shared" si="13"/>
+        <v>46355.25</v>
+      </c>
+      <c r="H150" s="243">
+        <v>96</v>
+      </c>
+      <c r="I150" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J149" s="32"/>
+        <v>46356.75</v>
+      </c>
+      <c r="J150" s="243">
+        <v>36</v>
+      </c>
+      <c r="K150" s="426"/>
+      <c r="L150" s="426"/>
+      <c r="M150" s="426"/>
+      <c r="N150" s="426"/>
+      <c r="O150" s="426"/>
+      <c r="P150" s="426"/>
+      <c r="Q150" s="426"/>
+      <c r="R150" s="426"/>
+      <c r="S150" s="426"/>
+      <c r="T150" s="426"/>
+      <c r="U150" s="426"/>
+      <c r="V150" s="426"/>
+      <c r="W150" s="426"/>
+      <c r="X150" s="426"/>
+      <c r="Y150" s="426"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="7"/>
-      <c r="B150" s="32"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="32"/>
-      <c r="F150" s="32"/>
-      <c r="G150" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H150" s="32"/>
-      <c r="I150" s="180">
+    <row r="151" spans="1:25">
+      <c r="A151" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B151" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" s="244" t="s">
+        <v>415</v>
+      </c>
+      <c r="D151" s="424" t="s">
+        <v>421</v>
+      </c>
+      <c r="E151" s="425">
+        <v>46355</v>
+      </c>
+      <c r="F151" s="336">
+        <v>46358.25</v>
+      </c>
+      <c r="G151" s="245">
+        <f t="shared" si="13"/>
+        <v>46362.25</v>
+      </c>
+      <c r="H151" s="243">
+        <v>96</v>
+      </c>
+      <c r="I151" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J150" s="32"/>
+        <v>46363.75</v>
+      </c>
+      <c r="J151" s="243">
+        <v>36</v>
+      </c>
+      <c r="K151" s="426"/>
+      <c r="L151" s="426"/>
+      <c r="M151" s="426"/>
+      <c r="N151" s="426"/>
+      <c r="O151" s="426"/>
+      <c r="P151" s="426"/>
+      <c r="Q151" s="426"/>
+      <c r="R151" s="426"/>
+      <c r="S151" s="426"/>
+      <c r="T151" s="426"/>
+      <c r="U151" s="426"/>
+      <c r="V151" s="426"/>
+      <c r="W151" s="426"/>
+      <c r="X151" s="426"/>
+      <c r="Y151" s="426"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="7"/>
-      <c r="B151" s="32"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="32"/>
-      <c r="F151" s="32"/>
-      <c r="G151" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H151" s="32"/>
-      <c r="I151" s="180">
+    <row r="152" spans="1:25">
+      <c r="A152" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B152" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C152" s="244" t="s">
+        <v>422</v>
+      </c>
+      <c r="D152" s="424" t="s">
+        <v>423</v>
+      </c>
+      <c r="E152" s="425">
+        <v>46189</v>
+      </c>
+      <c r="F152" s="336">
+        <v>46191.583333333336</v>
+      </c>
+      <c r="G152" s="245">
+        <f t="shared" si="13"/>
+        <v>46193.083333333336</v>
+      </c>
+      <c r="H152" s="243">
+        <v>36</v>
+      </c>
+      <c r="I152" s="245">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J151" s="32"/>
+        <v>46193.583333333336</v>
+      </c>
+      <c r="J152" s="243">
+        <v>12</v>
+      </c>
+      <c r="K152" s="426"/>
+      <c r="L152" s="426"/>
+      <c r="M152" s="426"/>
+      <c r="N152" s="426"/>
+      <c r="O152" s="426"/>
+      <c r="P152" s="426"/>
+      <c r="Q152" s="426"/>
+      <c r="R152" s="426"/>
+      <c r="S152" s="426"/>
+      <c r="T152" s="426"/>
+      <c r="U152" s="426"/>
+      <c r="V152" s="426"/>
+      <c r="W152" s="426"/>
+      <c r="X152" s="426"/>
+      <c r="Y152" s="426"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="7"/>
-      <c r="B152" s="32"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="32"/>
-      <c r="F152" s="32"/>
-      <c r="G152" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H152" s="32"/>
-      <c r="I152" s="180">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J152" s="32"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="7"/>
-      <c r="B153" s="32"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="32"/>
-      <c r="F153" s="32"/>
+    <row r="153" spans="1:25">
+      <c r="A153" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B153" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C153" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D153" s="424" t="s">
+        <v>425</v>
+      </c>
+      <c r="E153" s="54">
+        <v>46192</v>
+      </c>
+      <c r="F153" s="180">
+        <v>46194.5625</v>
+      </c>
       <c r="G153" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H153" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46196.0625</v>
+      </c>
+      <c r="H153" s="243">
+        <v>36</v>
+      </c>
       <c r="I153" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J153" s="32"/>
+        <v>46196.5625</v>
+      </c>
+      <c r="J153" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="7"/>
-      <c r="B154" s="32"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="32"/>
-      <c r="F154" s="32"/>
+    <row r="154" spans="1:25">
+      <c r="A154" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B154" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C154" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D154" s="424" t="s">
+        <v>426</v>
+      </c>
+      <c r="E154" s="54">
+        <v>46197</v>
+      </c>
+      <c r="F154" s="180">
+        <v>46199.916666666664</v>
+      </c>
       <c r="G154" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H154" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46201.416666666664</v>
+      </c>
+      <c r="H154" s="243">
+        <v>36</v>
+      </c>
       <c r="I154" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J154" s="32"/>
+        <v>46201.916666666664</v>
+      </c>
+      <c r="J154" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="7"/>
-      <c r="B155" s="32"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="32"/>
-      <c r="F155" s="32"/>
+    <row r="155" spans="1:25">
+      <c r="A155" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B155" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C155" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D155" s="424" t="s">
+        <v>427</v>
+      </c>
+      <c r="E155" s="54">
+        <v>46203</v>
+      </c>
+      <c r="F155" s="180">
+        <v>46205.375</v>
+      </c>
       <c r="G155" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H155" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46206.875</v>
+      </c>
+      <c r="H155" s="243">
+        <v>36</v>
+      </c>
       <c r="I155" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J155" s="32"/>
+        <v>46207.375</v>
+      </c>
+      <c r="J155" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="7"/>
-      <c r="B156" s="32"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="32"/>
-      <c r="F156" s="32"/>
+    <row r="156" spans="1:25">
+      <c r="A156" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B156" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C156" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D156" s="424" t="s">
+        <v>428</v>
+      </c>
+      <c r="E156" s="54">
+        <v>46206</v>
+      </c>
+      <c r="F156" s="180">
+        <v>46217.229166666664</v>
+      </c>
       <c r="G156" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H156" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46218.729166666664</v>
+      </c>
+      <c r="H156" s="243">
+        <v>36</v>
+      </c>
       <c r="I156" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J156" s="32"/>
+        <v>46219.229166666664</v>
+      </c>
+      <c r="J156" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="7"/>
-      <c r="B157" s="32"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="32"/>
-      <c r="F157" s="32"/>
+    <row r="157" spans="1:25">
+      <c r="A157" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B157" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C157" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D157" s="424" t="s">
+        <v>429</v>
+      </c>
+      <c r="E157" s="54">
+        <v>46215</v>
+      </c>
+      <c r="F157" s="180">
+        <v>46217.229166666664</v>
+      </c>
       <c r="G157" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H157" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46218.729166666664</v>
+      </c>
+      <c r="H157" s="243">
+        <v>36</v>
+      </c>
       <c r="I157" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J157" s="32"/>
+        <v>46219.229166666664</v>
+      </c>
+      <c r="J157" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="7"/>
-      <c r="B158" s="32"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="32"/>
-      <c r="F158" s="32"/>
+    <row r="158" spans="1:25">
+      <c r="A158" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B158" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C158" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D158" s="424" t="s">
+        <v>430</v>
+      </c>
+      <c r="E158" s="54">
+        <v>46219</v>
+      </c>
+      <c r="F158" s="180">
+        <v>46221.1875</v>
+      </c>
       <c r="G158" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H158" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46222.6875</v>
+      </c>
+      <c r="H158" s="243">
+        <v>36</v>
+      </c>
       <c r="I158" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J158" s="32"/>
+        <v>46223.1875</v>
+      </c>
+      <c r="J158" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="7"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="32"/>
-      <c r="F159" s="32"/>
+    <row r="159" spans="1:25">
+      <c r="A159" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B159" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C159" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D159" s="424" t="s">
+        <v>431</v>
+      </c>
+      <c r="E159" s="54">
+        <v>46224</v>
+      </c>
+      <c r="F159" s="180">
+        <v>46226.729166666664</v>
+      </c>
       <c r="G159" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H159" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46228.229166666664</v>
+      </c>
+      <c r="H159" s="243">
+        <v>36</v>
+      </c>
       <c r="I159" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J159" s="32"/>
+        <v>46228.729166666664</v>
+      </c>
+      <c r="J159" s="243">
+        <v>12</v>
+      </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="7"/>
-      <c r="B160" s="32"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="32"/>
-      <c r="F160" s="32"/>
+    <row r="160" spans="1:25">
+      <c r="A160" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B160" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C160" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D160" s="424" t="s">
+        <v>432</v>
+      </c>
+      <c r="E160" s="54">
+        <v>46230</v>
+      </c>
+      <c r="F160" s="180">
+        <v>46232.645833333336</v>
+      </c>
       <c r="G160" s="180">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H160" s="32"/>
+        <f t="shared" si="13"/>
+        <v>46234.145833333336</v>
+      </c>
+      <c r="H160" s="243">
+        <v>36</v>
+      </c>
       <c r="I160" s="180">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J160" s="32"/>
+        <v>46234.645833333336</v>
+      </c>
+      <c r="J160" s="243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B161" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C161" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D161" s="424" t="s">
+        <v>433</v>
+      </c>
+      <c r="E161" s="54">
+        <v>46235</v>
+      </c>
+      <c r="F161" s="180">
+        <v>46237.833333333336</v>
+      </c>
+      <c r="G161" s="180">
+        <f t="shared" si="13"/>
+        <v>46239.333333333336</v>
+      </c>
+      <c r="H161" s="243">
+        <v>36</v>
+      </c>
+      <c r="I161" s="180">
+        <f t="shared" si="8"/>
+        <v>46239.833333333336</v>
+      </c>
+      <c r="J161" s="243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B162" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C162" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D162" s="424" t="s">
+        <v>434</v>
+      </c>
+      <c r="E162" s="54">
+        <v>46238</v>
+      </c>
+      <c r="F162" s="180">
+        <v>46240.75</v>
+      </c>
+      <c r="G162" s="180">
+        <f t="shared" si="13"/>
+        <v>46242.25</v>
+      </c>
+      <c r="H162" s="243">
+        <v>36</v>
+      </c>
+      <c r="I162" s="180">
+        <f t="shared" si="8"/>
+        <v>46242.75</v>
+      </c>
+      <c r="J162" s="243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" s="335" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" s="243" t="s">
+        <v>122</v>
+      </c>
+      <c r="C163" s="244" t="s">
+        <v>424</v>
+      </c>
+      <c r="D163" s="424" t="s">
+        <v>435</v>
+      </c>
+      <c r="E163" s="54">
+        <v>46245</v>
+      </c>
+      <c r="F163" s="180">
+        <v>46247.479166666664</v>
+      </c>
+      <c r="G163" s="180">
+        <f t="shared" si="13"/>
+        <v>46248.979166666664</v>
+      </c>
+      <c r="H163" s="243">
+        <v>36</v>
+      </c>
+      <c r="I163" s="180">
+        <f t="shared" si="8"/>
+        <v>46249.479166666664</v>
+      </c>
+      <c r="J163" s="243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" s="335"/>
+      <c r="B164" s="243"/>
+      <c r="C164" s="244"/>
+      <c r="D164" s="424"/>
+      <c r="E164" s="54"/>
+      <c r="F164" s="180"/>
+      <c r="G164" s="180"/>
+      <c r="H164" s="243"/>
+      <c r="I164" s="180"/>
+      <c r="J164" s="243"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J160" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
+  <autoFilter ref="A1:J163" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
     <filterColumn colId="0">
       <filters blank="1">
         <filter val="Planned"/>
@@ -39719,84 +40317,100 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="15" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D144" r:id="rId1" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:61104:" xr:uid="{D17E0007-350A-4606-AF8D-4F4113C58BAF}"/>
+    <hyperlink ref="D147" r:id="rId2" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60703:" xr:uid="{2CE69447-1583-4285-A3C6-E44253861F50}"/>
+    <hyperlink ref="D148" r:id="rId3" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60704:" xr:uid="{9B646115-87F0-4E9B-A26C-E8EDC2346D02}"/>
+    <hyperlink ref="D149" r:id="rId4" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60705:" xr:uid="{E88F1C80-86A4-402C-A7FA-01CE4B12C622}"/>
+    <hyperlink ref="D150" r:id="rId5" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60706:" xr:uid="{ED524307-DD66-4DB1-9398-118E3CD28160}"/>
+    <hyperlink ref="D151" r:id="rId6" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60707:" xr:uid="{2A3CDFC3-31C8-44B2-8428-4BB6443AB947}"/>
+    <hyperlink ref="D146" r:id="rId7" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60493:" xr:uid="{F26E0D90-75CF-4C75-BE7C-46BD69259230}"/>
+    <hyperlink ref="C152" r:id="rId8" xr:uid="{4BF92AC9-6F81-47D3-BADE-793677667278}"/>
+    <hyperlink ref="D153" r:id="rId9" xr:uid="{E005730F-31E3-4D24-9CAD-7F0A40A90785}"/>
+    <hyperlink ref="D154" r:id="rId10" xr:uid="{CD88DAD3-3FF4-4E5B-8E2B-399AE5F81F59}"/>
+    <hyperlink ref="D155" r:id="rId11" xr:uid="{E7B658C7-FFEB-4978-9A4E-D4E57D76FD92}"/>
+    <hyperlink ref="D156" r:id="rId12" xr:uid="{BB857F62-9EFB-4532-9E08-F51A99F5A052}"/>
+    <hyperlink ref="D157" r:id="rId13" xr:uid="{EC5EC0AC-3F5B-4A38-BEE4-5ABDE438163E}"/>
+    <hyperlink ref="D158" r:id="rId14" xr:uid="{42CF593B-3B32-4FD3-BF01-D92D8C273D20}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F4F7F26-D5D6-4844-933A-5AAFCB58CD1B}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="9" style="69"/>
     <col min="19" max="19" width="13" style="69" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="69"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="546" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
+      <c r="B1" s="452" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="547"/>
-      <c r="D1" s="547"/>
-      <c r="E1" s="548"/>
-      <c r="F1" s="546" t="s">
+      <c r="C1" s="453"/>
+      <c r="D1" s="453"/>
+      <c r="E1" s="454"/>
+      <c r="F1" s="452" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="547"/>
-      <c r="H1" s="547"/>
-      <c r="I1" s="548"/>
-      <c r="J1" s="546" t="s">
+      <c r="G1" s="453"/>
+      <c r="H1" s="453"/>
+      <c r="I1" s="454"/>
+      <c r="J1" s="452" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="547"/>
-      <c r="L1" s="547"/>
-      <c r="M1" s="548"/>
+      <c r="K1" s="453"/>
+      <c r="L1" s="453"/>
+      <c r="M1" s="454"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="70"/>
       <c r="B2" s="71" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="E2" s="73" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="F2" s="74" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="G2" s="72" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="H2" s="72" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="I2" s="73" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="J2" s="74" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="K2" s="72" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="M2" s="73" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3" s="75" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
@@ -39804,7 +40418,7 @@
       <c r="E3" s="76"/>
       <c r="F3" s="76"/>
       <c r="G3" s="76" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="H3" s="76"/>
       <c r="I3" s="76"/>
@@ -39813,9 +40427,9 @@
       <c r="L3" s="76"/>
       <c r="M3" s="76"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15">
       <c r="A4" s="75" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
@@ -39823,7 +40437,7 @@
       <c r="E4" s="76"/>
       <c r="F4" s="76"/>
       <c r="G4" s="76" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="H4" s="76"/>
       <c r="I4" s="76"/>
@@ -39832,9 +40446,9 @@
       <c r="L4" s="76"/>
       <c r="M4" s="76"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5" s="75" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
@@ -39842,7 +40456,7 @@
       <c r="E5" s="76"/>
       <c r="F5" s="76"/>
       <c r="G5" s="76" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="H5" s="76"/>
       <c r="I5" s="76"/>
@@ -39851,9 +40465,9 @@
       <c r="L5" s="76"/>
       <c r="M5" s="76"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" s="75" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="B6" s="77"/>
       <c r="C6" s="78"/>
@@ -39861,7 +40475,7 @@
       <c r="E6" s="79"/>
       <c r="F6" s="80"/>
       <c r="G6" s="81" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="H6" s="78"/>
       <c r="I6" s="79"/>
@@ -39870,9 +40484,9 @@
       <c r="L6" s="78"/>
       <c r="M6" s="79"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" s="75" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="B7" s="77"/>
       <c r="C7" s="78"/>
@@ -39880,7 +40494,7 @@
       <c r="E7" s="79"/>
       <c r="F7" s="80"/>
       <c r="G7" s="81" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="H7" s="78"/>
       <c r="I7" s="79"/>
@@ -39892,9 +40506,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" s="75" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="B8" s="77"/>
       <c r="C8" s="78"/>
@@ -39902,7 +40516,7 @@
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="81" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="H8" s="78"/>
       <c r="I8" s="79"/>
@@ -39911,9 +40525,9 @@
       <c r="L8" s="78"/>
       <c r="M8" s="79"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" s="75" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="B9" s="82"/>
       <c r="C9" s="83"/>
@@ -39921,7 +40535,7 @@
       <c r="E9" s="84"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="84"/>
@@ -39930,9 +40544,9 @@
       <c r="L9" s="83"/>
       <c r="M9" s="84"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" s="75" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="B10" s="87"/>
       <c r="C10" s="87"/>
@@ -39940,7 +40554,7 @@
       <c r="E10" s="87"/>
       <c r="F10" s="87"/>
       <c r="G10" s="87" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="H10" s="87"/>
       <c r="I10" s="87"/>
@@ -39949,9 +40563,9 @@
       <c r="L10" s="87"/>
       <c r="M10" s="87"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" s="75" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="B11" s="88"/>
       <c r="C11" s="89"/>
@@ -39959,7 +40573,7 @@
       <c r="E11" s="90"/>
       <c r="F11" s="91"/>
       <c r="G11" s="92" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="H11" s="89"/>
       <c r="I11" s="90"/>
@@ -39968,9 +40582,9 @@
       <c r="L11" s="89"/>
       <c r="M11" s="90"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="A12" s="75" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="B12" s="93"/>
       <c r="C12" s="94"/>
@@ -39978,7 +40592,7 @@
       <c r="E12" s="95"/>
       <c r="F12" s="96"/>
       <c r="G12" s="97" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="H12" s="94"/>
       <c r="I12" s="95"/>
@@ -39987,32 +40601,32 @@
       <c r="L12" s="94"/>
       <c r="M12" s="95"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13" s="75" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="B13" s="93"/>
       <c r="C13" s="94"/>
       <c r="D13" s="94"/>
       <c r="E13" s="95"/>
       <c r="F13" s="96"/>
-      <c r="G13" s="549" t="s">
+      <c r="G13" s="455" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="550"/>
-      <c r="I13" s="551"/>
+      <c r="H13" s="456"/>
+      <c r="I13" s="457"/>
       <c r="J13" s="98" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="K13" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="L13" s="99"/>
       <c r="M13" s="100"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="A14" s="75" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="B14" s="101"/>
       <c r="C14" s="101" t="s">
@@ -40021,36 +40635,36 @@
       <c r="D14" s="101"/>
       <c r="E14" s="101"/>
       <c r="F14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="G14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="H14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="I14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="J14" s="98" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="K14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="L14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="M14" s="86" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="O14" s="69" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15" s="75" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="B15" s="102"/>
       <c r="C15" s="103"/>
@@ -40083,9 +40697,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="A16" s="75" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="B16" s="102"/>
       <c r="C16" s="103"/>
@@ -40118,9 +40732,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13">
       <c r="A17" s="75" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>160</v>
@@ -40147,9 +40761,9 @@
       <c r="L17" s="103"/>
       <c r="M17" s="103"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13">
       <c r="A18" s="75" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>160</v>
@@ -40186,9 +40800,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13">
       <c r="A19" s="75" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="B19" s="102"/>
       <c r="C19" s="103"/>
@@ -40215,17 +40829,17 @@
       <c r="L19" s="103"/>
       <c r="M19" s="103"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15.75" thickBot="1">
       <c r="A20" s="111" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="B20" s="112"/>
       <c r="C20" s="113"/>
       <c r="D20" s="114" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="F20" s="103"/>
       <c r="G20" s="103"/>
@@ -40236,7 +40850,7 @@
       <c r="L20" s="103"/>
       <c r="M20" s="103"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13">
       <c r="J22" s="69" t="s">
         <v>18</v>
       </c>
@@ -40254,6 +40868,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
+      <Value>1</Value>
+    </TaxCatchAll>
+    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
+        </TermInfo>
+      </Terms>
+    </SAEFSecurityClassificationTaxHTField0>
+    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -40262,7 +40900,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Shell Document" ma:contentTypeID="0x0101006F0A470EEB1140E7AA14F4CE8A50B54C0001CB1477F4DD432AA86DD56CC3887AF4009BF70C544A1089499A02E2027F577943" ma:contentTypeVersion="21" ma:contentTypeDescription="Shell Document Content Type" ma:contentTypeScope="" ma:versionID="3b36c8c7df6bef78f4146e9643aced04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="b2778aaa-fd83-416e-8091-738aa96f6cd3" xmlns:ns3="91455a6e-8899-4f67-a6e4-e187ec74b863" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="619e014c6e05ed77e6b134c7f3fed7d8" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -40583,68 +41221,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
-      <Value>1</Value>
-    </TaxCatchAll>
-    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
-        </TermInfo>
-      </Terms>
-    </SAEFSecurityClassificationTaxHTField0>
-    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D682A838-9073-462C-9192-2FEB3851AAA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
-    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
-    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D682A838-9073-462C-9192-2FEB3851AAA4}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8618" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9346A013-6D14-43BE-AF65-3816727D0C86}"/>
+  <xr:revisionPtr revIDLastSave="8759" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F2D9E40-235E-410D-92E0-83EC1B2C95F6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="476">
   <si>
     <t xml:space="preserve">Top Hole </t>
   </si>
@@ -1321,10 +1321,6 @@
 GL 04a OSV (Shared) / 6 hrs: Class H CMT</t>
   </si>
   <si>
-    <t xml:space="preserve">	
-GL 04c OSV / 48 HRS: Items Riding the Boat</t>
-  </si>
-  <si>
     <t>Whale 10 Completion</t>
   </si>
   <si>
@@ -1824,6 +1820,21 @@
 GL 11 Run Upper Tieback</t>
   </si>
   <si>
+    <t xml:space="preserve">Vito VA-12 Drift/ CTCO/ Stim </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 02 Harvey America- Milk Run and Rig Fuel </t>
+  </si>
+  <si>
+    <t>Vito VA-11 Drift/ CTCO</t>
+  </si>
+  <si>
+    <t>Vito VA-10 Drift/ CTCO</t>
+  </si>
+  <si>
+    <t>GL 04 FSV/OSV Complete De-Mob (Groceries and Supplies)</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -1921,6 +1932,15 @@
   </si>
   <si>
     <t>Spot Hire 5</t>
+  </si>
+  <si>
+    <t>GL 03 OSV Pre-Mob OWIRS and Groceries</t>
+  </si>
+  <si>
+    <t>Vito VA-11 Drift/ CTCO to VA-10</t>
+  </si>
+  <si>
+    <t>Dark Vision for VA-10</t>
   </si>
 </sst>
 </file>
@@ -1930,7 +1950,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -3406,7 +3426,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="553">
+  <cellXfs count="566">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4545,9 +4565,6 @@
     <xf numFmtId="22" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4602,12 +4619,219 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="27" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4650,6 +4874,45 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4677,6 +4940,78 @@
     <xf numFmtId="0" fontId="10" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="29" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4695,290 +5030,14 @@
     <xf numFmtId="0" fontId="14" fillId="25" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="29" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -25790,6 +25849,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26023,7 +26086,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:DG60"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1"/>
     <col min="2" max="2" width="27.375" style="1" customWidth="1"/>
@@ -26046,7 +26109,7 @@
     <col min="112" max="16384" width="11.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111">
+    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A1" s="40"/>
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
@@ -26076,7 +26139,7 @@
       <c r="Y1" s="40"/>
       <c r="Z1" s="40"/>
     </row>
-    <row r="2" spans="1:111" ht="15.75">
+    <row r="2" spans="1:111" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
@@ -26108,7 +26171,7 @@
       <c r="Y2" s="40"/>
       <c r="Z2" s="40"/>
     </row>
-    <row r="3" spans="1:111">
+    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A3" s="40"/>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
@@ -26138,7 +26201,7 @@
       <c r="Y3" s="40"/>
       <c r="Z3" s="40"/>
     </row>
-    <row r="4" spans="1:111">
+    <row r="4" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -26168,7 +26231,7 @@
       <c r="Y4" s="40"/>
       <c r="Z4" s="40"/>
     </row>
-    <row r="5" spans="1:111">
+    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A5" s="40"/>
       <c r="B5" s="34"/>
       <c r="C5" s="6" t="s">
@@ -26197,7 +26260,7 @@
       <c r="Y5" s="40"/>
       <c r="Z5" s="40"/>
     </row>
-    <row r="6" spans="1:111" ht="15.75" thickBot="1">
+    <row r="6" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -26225,29 +26288,29 @@
       <c r="Y6" s="40"/>
       <c r="Z6" s="40"/>
     </row>
-    <row r="7" spans="1:111" ht="15.75" thickBot="1">
+    <row r="7" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="459">
+      <c r="G7" s="439">
         <v>2025</v>
       </c>
-      <c r="H7" s="460"/>
-      <c r="I7" s="460"/>
-      <c r="J7" s="460"/>
-      <c r="K7" s="460"/>
-      <c r="L7" s="460"/>
-      <c r="M7" s="460"/>
-      <c r="N7" s="461"/>
-      <c r="O7" s="462">
+      <c r="H7" s="440"/>
+      <c r="I7" s="440"/>
+      <c r="J7" s="440"/>
+      <c r="K7" s="440"/>
+      <c r="L7" s="440"/>
+      <c r="M7" s="440"/>
+      <c r="N7" s="441"/>
+      <c r="O7" s="442">
         <v>2026</v>
       </c>
-      <c r="P7" s="463"/>
-      <c r="Q7" s="463"/>
-      <c r="R7" s="464"/>
+      <c r="P7" s="443"/>
+      <c r="Q7" s="443"/>
+      <c r="R7" s="444"/>
       <c r="S7" s="40"/>
       <c r="T7" s="40"/>
       <c r="U7" s="40"/>
@@ -26257,31 +26320,31 @@
       <c r="Y7" s="40"/>
       <c r="Z7" s="40"/>
     </row>
-    <row r="8" spans="1:111">
+    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
       <c r="B8" s="40"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="465" t="s">
+      <c r="G8" s="447" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="466"/>
-      <c r="I8" s="466"/>
-      <c r="J8" s="466"/>
-      <c r="K8" s="467" t="s">
+      <c r="H8" s="448"/>
+      <c r="I8" s="448"/>
+      <c r="J8" s="448"/>
+      <c r="K8" s="449" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="467"/>
-      <c r="M8" s="467"/>
-      <c r="N8" s="467"/>
-      <c r="O8" s="468" t="s">
+      <c r="L8" s="449"/>
+      <c r="M8" s="449"/>
+      <c r="N8" s="449"/>
+      <c r="O8" s="458" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="468"/>
-      <c r="Q8" s="468"/>
-      <c r="R8" s="469"/>
+      <c r="P8" s="458"/>
+      <c r="Q8" s="458"/>
+      <c r="R8" s="459"/>
       <c r="S8" s="40"/>
       <c r="T8" s="40"/>
       <c r="U8" s="40"/>
@@ -26376,7 +26439,7 @@
       <c r="DF8" s="8"/>
       <c r="DG8" s="8"/>
     </row>
-    <row r="9" spans="1:111" ht="15.75" thickBot="1">
+    <row r="9" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40"/>
       <c r="B9" s="18" t="s">
         <v>9</v>
@@ -26499,9 +26562,9 @@
       <c r="DF9" s="9"/>
       <c r="DG9" s="9"/>
     </row>
-    <row r="10" spans="1:111">
+    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="40"/>
-      <c r="B10" s="428" t="s">
+      <c r="B10" s="450" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -26622,9 +26685,9 @@
       <c r="DF10" s="9"/>
       <c r="DG10" s="9"/>
     </row>
-    <row r="11" spans="1:111">
+    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="40"/>
-      <c r="B11" s="470"/>
+      <c r="B11" s="451"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
@@ -26745,9 +26808,9 @@
       <c r="DF11" s="9"/>
       <c r="DG11" s="9"/>
     </row>
-    <row r="12" spans="1:111">
+    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="40"/>
-      <c r="B12" s="470"/>
+      <c r="B12" s="451"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -26866,9 +26929,9 @@
       <c r="DF12" s="9"/>
       <c r="DG12" s="9"/>
     </row>
-    <row r="13" spans="1:111">
+    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A13" s="40"/>
-      <c r="B13" s="470"/>
+      <c r="B13" s="451"/>
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
@@ -26987,9 +27050,9 @@
       <c r="DF13" s="9"/>
       <c r="DG13" s="9"/>
     </row>
-    <row r="14" spans="1:111">
+    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="40"/>
-      <c r="B14" s="470"/>
+      <c r="B14" s="451"/>
       <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
@@ -27110,9 +27173,9 @@
       <c r="DF14" s="9"/>
       <c r="DG14" s="9"/>
     </row>
-    <row r="15" spans="1:111" ht="15.75" thickBot="1">
+    <row r="15" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40"/>
-      <c r="B15" s="471"/>
+      <c r="B15" s="452"/>
       <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
@@ -27231,9 +27294,9 @@
       <c r="DF15" s="9"/>
       <c r="DG15" s="9"/>
     </row>
-    <row r="16" spans="1:111">
+    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="40"/>
-      <c r="B16" s="427" t="s">
+      <c r="B16" s="445" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -27354,9 +27417,9 @@
       <c r="DF16" s="9"/>
       <c r="DG16" s="9"/>
     </row>
-    <row r="17" spans="1:111">
+    <row r="17" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A17" s="40"/>
-      <c r="B17" s="472"/>
+      <c r="B17" s="446"/>
       <c r="C17" s="7" t="s">
         <v>27</v>
       </c>
@@ -27475,9 +27538,9 @@
       <c r="DF17" s="9"/>
       <c r="DG17" s="9"/>
     </row>
-    <row r="18" spans="1:111" ht="15.75" thickBot="1">
+    <row r="18" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="40"/>
-      <c r="B18" s="472"/>
+      <c r="B18" s="446"/>
       <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
@@ -27596,9 +27659,9 @@
       <c r="DF18" s="9"/>
       <c r="DG18" s="9"/>
     </row>
-    <row r="19" spans="1:111">
+    <row r="19" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A19" s="40"/>
-      <c r="B19" s="427" t="s">
+      <c r="B19" s="445" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -27719,9 +27782,9 @@
       <c r="DF19" s="9"/>
       <c r="DG19" s="9"/>
     </row>
-    <row r="20" spans="1:111" ht="15.75" thickBot="1">
+    <row r="20" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="40"/>
-      <c r="B20" s="472"/>
+      <c r="B20" s="446"/>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
@@ -27840,9 +27903,9 @@
       <c r="DF20" s="9"/>
       <c r="DG20" s="9"/>
     </row>
-    <row r="21" spans="1:111">
+    <row r="21" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A21" s="40"/>
-      <c r="B21" s="427" t="s">
+      <c r="B21" s="445" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -27963,9 +28026,9 @@
       <c r="DF21" s="9"/>
       <c r="DG21" s="9"/>
     </row>
-    <row r="22" spans="1:111">
+    <row r="22" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
-      <c r="B22" s="472"/>
+      <c r="B22" s="446"/>
       <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
@@ -28084,9 +28147,9 @@
       <c r="DF22" s="9"/>
       <c r="DG22" s="9"/>
     </row>
-    <row r="23" spans="1:111" ht="15.75" thickBot="1">
+    <row r="23" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
-      <c r="B23" s="472"/>
+      <c r="B23" s="446"/>
       <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
@@ -28106,11 +28169,11 @@
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
-      <c r="N23" s="473"/>
-      <c r="O23" s="473"/>
-      <c r="P23" s="473"/>
-      <c r="Q23" s="473"/>
-      <c r="R23" s="474"/>
+      <c r="N23" s="455"/>
+      <c r="O23" s="455"/>
+      <c r="P23" s="455"/>
+      <c r="Q23" s="455"/>
+      <c r="R23" s="456"/>
       <c r="S23" s="40"/>
       <c r="T23" s="40"/>
       <c r="U23" s="40"/>
@@ -28120,9 +28183,9 @@
       <c r="Y23" s="40"/>
       <c r="Z23" s="40"/>
     </row>
-    <row r="24" spans="1:111">
+    <row r="24" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
-      <c r="B24" s="427" t="s">
+      <c r="B24" s="445" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -28140,12 +28203,12 @@
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
-      <c r="J24" s="475"/>
-      <c r="K24" s="475"/>
-      <c r="L24" s="475"/>
-      <c r="M24" s="475"/>
-      <c r="N24" s="475"/>
-      <c r="O24" s="475"/>
+      <c r="J24" s="457"/>
+      <c r="K24" s="457"/>
+      <c r="L24" s="457"/>
+      <c r="M24" s="457"/>
+      <c r="N24" s="457"/>
+      <c r="O24" s="457"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="14"/>
@@ -28158,9 +28221,9 @@
       <c r="Y24" s="40"/>
       <c r="Z24" s="40"/>
     </row>
-    <row r="25" spans="1:111" ht="15.75" thickBot="1">
+    <row r="25" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
-      <c r="B25" s="472"/>
+      <c r="B25" s="446"/>
       <c r="C25" s="7" t="s">
         <v>44</v>
       </c>
@@ -28181,10 +28244,10 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
-      <c r="O25" s="476"/>
-      <c r="P25" s="476"/>
-      <c r="Q25" s="476"/>
-      <c r="R25" s="477"/>
+      <c r="O25" s="453"/>
+      <c r="P25" s="453"/>
+      <c r="Q25" s="453"/>
+      <c r="R25" s="454"/>
       <c r="S25" s="40"/>
       <c r="T25" s="40"/>
       <c r="U25" s="40"/>
@@ -28194,7 +28257,7 @@
       <c r="Y25" s="40"/>
       <c r="Z25" s="40"/>
     </row>
-    <row r="26" spans="1:111" ht="15.75" thickBot="1">
+    <row r="26" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="40"/>
       <c r="B26" s="46" t="s">
         <v>20</v>
@@ -28234,7 +28297,7 @@
       <c r="Y26" s="40"/>
       <c r="Z26" s="40"/>
     </row>
-    <row r="27" spans="1:111" ht="15.75" thickBot="1">
+    <row r="27" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
       <c r="B27" s="32" t="s">
         <v>47</v>
@@ -28272,7 +28335,7 @@
       <c r="Y27" s="40"/>
       <c r="Z27" s="40"/>
     </row>
-    <row r="28" spans="1:111" ht="20.25" customHeight="1" thickBot="1">
+    <row r="28" spans="1:111" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="40"/>
       <c r="B28" s="39" t="s">
         <v>50</v>
@@ -28310,7 +28373,7 @@
       <c r="Y28" s="40"/>
       <c r="Z28" s="40"/>
     </row>
-    <row r="29" spans="1:111" ht="15.75" thickBot="1">
+    <row r="29" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="40"/>
       <c r="B29" s="46" t="s">
         <v>52</v>
@@ -28350,8 +28413,8 @@
       </c>
       <c r="Z29" s="40"/>
     </row>
-    <row r="30" spans="1:111" ht="15.75" thickBot="1">
-      <c r="B30" s="478" t="s">
+    <row r="30" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="438" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="33" t="s">
@@ -28387,9 +28450,9 @@
       <c r="Y30" s="40"/>
       <c r="Z30" s="40"/>
     </row>
-    <row r="31" spans="1:111" ht="15.75" thickBot="1">
+    <row r="31" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="40"/>
-      <c r="B31" s="478"/>
+      <c r="B31" s="438"/>
       <c r="C31" s="33" t="s">
         <v>48</v>
       </c>
@@ -28423,7 +28486,7 @@
       <c r="Y31" s="40"/>
       <c r="Z31" s="40"/>
     </row>
-    <row r="32" spans="1:111" ht="15.75" thickBot="1">
+    <row r="32" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="40"/>
       <c r="B32" s="46" t="s">
         <v>57</v>
@@ -28461,7 +28524,7 @@
       <c r="Y32" s="40"/>
       <c r="Z32" s="40"/>
     </row>
-    <row r="33" spans="1:26" ht="19.5" customHeight="1" thickBot="1">
+    <row r="33" spans="1:26" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="40"/>
       <c r="B33" s="62" t="s">
         <v>60</v>
@@ -28499,7 +28562,7 @@
       <c r="Y33" s="40"/>
       <c r="Z33" s="40"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" thickBot="1">
+    <row r="34" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="40"/>
       <c r="B34" s="46" t="s">
         <v>62</v>
@@ -28537,7 +28600,7 @@
       <c r="Y34" s="40"/>
       <c r="Z34" s="40"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" thickBot="1">
+    <row r="35" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40"/>
       <c r="B35" s="46" t="s">
         <v>64</v>
@@ -28577,7 +28640,7 @@
       <c r="Y35" s="40"/>
       <c r="Z35" s="40"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="40"/>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -28607,7 +28670,7 @@
       <c r="Y36" s="40"/>
       <c r="Z36" s="40"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="40"/>
       <c r="B37" s="40"/>
       <c r="C37" s="40"/>
@@ -28639,7 +28702,7 @@
       <c r="Y37" s="40"/>
       <c r="Z37" s="40"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="40"/>
       <c r="B38" s="40"/>
       <c r="C38" s="40"/>
@@ -28667,7 +28730,7 @@
       <c r="Y38" s="40"/>
       <c r="Z38" s="40"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="40"/>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -28695,7 +28758,7 @@
       <c r="Y39" s="40"/>
       <c r="Z39" s="40"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
       <c r="D40" s="40"/>
@@ -28722,7 +28785,7 @@
       <c r="Y40" s="40"/>
       <c r="Z40" s="40"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="40"/>
       <c r="B41" s="40"/>
       <c r="C41" s="40"/>
@@ -28750,7 +28813,7 @@
       <c r="Y41" s="40"/>
       <c r="Z41" s="40"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="40"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -28778,7 +28841,7 @@
       <c r="Y42" s="40"/>
       <c r="Z42" s="40"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="40"/>
       <c r="B43" s="40"/>
       <c r="C43" s="40"/>
@@ -28806,7 +28869,7 @@
       <c r="Y43" s="40"/>
       <c r="Z43" s="40"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="40"/>
       <c r="B44" s="40"/>
       <c r="C44" s="40"/>
@@ -28834,7 +28897,7 @@
       <c r="Y44" s="40"/>
       <c r="Z44" s="40"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="40"/>
       <c r="B45" s="40"/>
       <c r="C45" s="40"/>
@@ -28862,7 +28925,7 @@
       <c r="Y45" s="40"/>
       <c r="Z45" s="40"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="40"/>
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
@@ -28890,7 +28953,7 @@
       <c r="Y46" s="40"/>
       <c r="Z46" s="40"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="40"/>
       <c r="B47" s="40"/>
       <c r="C47" s="40"/>
@@ -28918,7 +28981,7 @@
       <c r="Y47" s="40"/>
       <c r="Z47" s="40"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="40"/>
       <c r="B48" s="40"/>
       <c r="C48" s="40"/>
@@ -28946,40 +29009,40 @@
       <c r="Y48" s="40"/>
       <c r="Z48" s="40"/>
     </row>
-    <row r="49" spans="21:21">
+    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="40"/>
     </row>
-    <row r="50" spans="21:21">
+    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U50" s="40"/>
     </row>
-    <row r="51" spans="21:21">
+    <row r="51" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U51" s="40"/>
     </row>
-    <row r="52" spans="21:21">
+    <row r="52" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U52" s="40"/>
     </row>
-    <row r="53" spans="21:21">
+    <row r="53" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U53" s="40"/>
     </row>
-    <row r="54" spans="21:21">
+    <row r="54" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U54" s="40"/>
     </row>
-    <row r="55" spans="21:21">
+    <row r="55" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U55" s="40"/>
     </row>
-    <row r="56" spans="21:21">
+    <row r="56" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U56" s="40"/>
     </row>
-    <row r="57" spans="21:21">
+    <row r="57" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U57" s="40"/>
     </row>
-    <row r="58" spans="21:21">
+    <row r="58" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U58" s="40"/>
     </row>
-    <row r="59" spans="21:21">
+    <row r="59" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U59" s="40"/>
     </row>
-    <row r="60" spans="21:21">
+    <row r="60" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U60" s="40"/>
     </row>
   </sheetData>
@@ -29008,7 +29071,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31789BA3-7E08-4BBD-8F4F-2CBDF359F836}">
   <dimension ref="A1:BS69"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="14.375" customWidth="1"/>
@@ -29030,7 +29093,7 @@
     <col min="44" max="44" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="1" customFormat="1">
+    <row r="1" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40"/>
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
@@ -29066,7 +29129,7 @@
       <c r="AO1" s="40"/>
       <c r="AP1" s="40"/>
     </row>
-    <row r="2" spans="1:71" s="1" customFormat="1">
+    <row r="2" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
@@ -29104,7 +29167,7 @@
       <c r="AO2" s="40"/>
       <c r="AP2" s="40"/>
     </row>
-    <row r="3" spans="1:71" s="1" customFormat="1">
+    <row r="3" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40"/>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
@@ -29140,7 +29203,7 @@
       <c r="AO3" s="40"/>
       <c r="AP3" s="40"/>
     </row>
-    <row r="4" spans="1:71" s="1" customFormat="1" ht="15.75">
+    <row r="4" spans="1:71" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -29178,7 +29241,7 @@
       <c r="AO4" s="40"/>
       <c r="AP4" s="40"/>
     </row>
-    <row r="5" spans="1:71" s="1" customFormat="1">
+    <row r="5" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="40"/>
       <c r="B5" s="162"/>
       <c r="C5" s="6" t="s">
@@ -29218,7 +29281,7 @@
       <c r="AO5" s="40"/>
       <c r="AP5" s="40"/>
     </row>
-    <row r="6" spans="1:71" s="1" customFormat="1">
+    <row r="6" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40"/>
       <c r="B6" s="128"/>
       <c r="C6" s="131" t="s">
@@ -29266,7 +29329,7 @@
       <c r="AO6" s="40"/>
       <c r="AP6" s="40"/>
     </row>
-    <row r="7" spans="1:71" s="1" customFormat="1">
+    <row r="7" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="40"/>
       <c r="B7" s="152"/>
       <c r="C7" s="131" t="s">
@@ -29275,58 +29338,58 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="479">
+      <c r="G7" s="472">
         <v>2026</v>
       </c>
-      <c r="H7" s="479"/>
-      <c r="I7" s="479"/>
-      <c r="J7" s="479"/>
-      <c r="K7" s="479"/>
-      <c r="L7" s="479"/>
-      <c r="M7" s="479"/>
-      <c r="N7" s="479"/>
-      <c r="O7" s="479"/>
-      <c r="P7" s="479"/>
-      <c r="Q7" s="479"/>
-      <c r="R7" s="479"/>
-      <c r="S7" s="479"/>
-      <c r="T7" s="479"/>
-      <c r="U7" s="479"/>
-      <c r="V7" s="479"/>
-      <c r="W7" s="479"/>
-      <c r="X7" s="479"/>
-      <c r="Y7" s="479"/>
-      <c r="Z7" s="479"/>
-      <c r="AA7" s="479"/>
-      <c r="AB7" s="479"/>
-      <c r="AC7" s="479"/>
-      <c r="AD7" s="479"/>
-      <c r="AE7" s="479"/>
-      <c r="AF7" s="479"/>
-      <c r="AG7" s="479"/>
-      <c r="AH7" s="479"/>
-      <c r="AI7" s="479"/>
-      <c r="AJ7" s="479"/>
-      <c r="AK7" s="479"/>
-      <c r="AL7" s="479"/>
-      <c r="AM7" s="479"/>
-      <c r="AN7" s="479"/>
-      <c r="AO7" s="479"/>
-      <c r="AP7" s="479"/>
-      <c r="AQ7" s="479"/>
-      <c r="AR7" s="479"/>
-      <c r="AS7" s="479"/>
-      <c r="AT7" s="479"/>
-      <c r="AU7" s="479"/>
-      <c r="AV7" s="479"/>
-      <c r="AW7" s="479"/>
-      <c r="AX7" s="479"/>
-      <c r="AY7" s="479"/>
-      <c r="AZ7" s="479"/>
-      <c r="BA7" s="479"/>
-      <c r="BB7" s="479"/>
+      <c r="H7" s="472"/>
+      <c r="I7" s="472"/>
+      <c r="J7" s="472"/>
+      <c r="K7" s="472"/>
+      <c r="L7" s="472"/>
+      <c r="M7" s="472"/>
+      <c r="N7" s="472"/>
+      <c r="O7" s="472"/>
+      <c r="P7" s="472"/>
+      <c r="Q7" s="472"/>
+      <c r="R7" s="472"/>
+      <c r="S7" s="472"/>
+      <c r="T7" s="472"/>
+      <c r="U7" s="472"/>
+      <c r="V7" s="472"/>
+      <c r="W7" s="472"/>
+      <c r="X7" s="472"/>
+      <c r="Y7" s="472"/>
+      <c r="Z7" s="472"/>
+      <c r="AA7" s="472"/>
+      <c r="AB7" s="472"/>
+      <c r="AC7" s="472"/>
+      <c r="AD7" s="472"/>
+      <c r="AE7" s="472"/>
+      <c r="AF7" s="472"/>
+      <c r="AG7" s="472"/>
+      <c r="AH7" s="472"/>
+      <c r="AI7" s="472"/>
+      <c r="AJ7" s="472"/>
+      <c r="AK7" s="472"/>
+      <c r="AL7" s="472"/>
+      <c r="AM7" s="472"/>
+      <c r="AN7" s="472"/>
+      <c r="AO7" s="472"/>
+      <c r="AP7" s="472"/>
+      <c r="AQ7" s="472"/>
+      <c r="AR7" s="472"/>
+      <c r="AS7" s="472"/>
+      <c r="AT7" s="472"/>
+      <c r="AU7" s="472"/>
+      <c r="AV7" s="472"/>
+      <c r="AW7" s="472"/>
+      <c r="AX7" s="472"/>
+      <c r="AY7" s="472"/>
+      <c r="AZ7" s="472"/>
+      <c r="BA7" s="472"/>
+      <c r="BB7" s="472"/>
     </row>
-    <row r="8" spans="1:71" s="1" customFormat="1">
+    <row r="8" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
       <c r="B8" s="167"/>
       <c r="C8" s="131" t="s">
@@ -29335,78 +29398,78 @@
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="480" t="s">
+      <c r="G8" s="484" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="480"/>
-      <c r="I8" s="480"/>
-      <c r="J8" s="480"/>
-      <c r="K8" s="481" t="s">
+      <c r="H8" s="484"/>
+      <c r="I8" s="484"/>
+      <c r="J8" s="484"/>
+      <c r="K8" s="479" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="481"/>
-      <c r="M8" s="481"/>
-      <c r="N8" s="481"/>
-      <c r="O8" s="482" t="s">
+      <c r="L8" s="479"/>
+      <c r="M8" s="479"/>
+      <c r="N8" s="479"/>
+      <c r="O8" s="480" t="s">
         <v>74</v>
       </c>
-      <c r="P8" s="482"/>
-      <c r="Q8" s="482"/>
-      <c r="R8" s="482"/>
-      <c r="S8" s="483" t="s">
+      <c r="P8" s="480"/>
+      <c r="Q8" s="480"/>
+      <c r="R8" s="480"/>
+      <c r="S8" s="478" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="483"/>
-      <c r="U8" s="483"/>
-      <c r="V8" s="483"/>
-      <c r="W8" s="481" t="s">
+      <c r="T8" s="478"/>
+      <c r="U8" s="478"/>
+      <c r="V8" s="478"/>
+      <c r="W8" s="479" t="s">
         <v>76</v>
       </c>
-      <c r="X8" s="481"/>
-      <c r="Y8" s="481"/>
-      <c r="Z8" s="481"/>
-      <c r="AA8" s="482" t="s">
+      <c r="X8" s="479"/>
+      <c r="Y8" s="479"/>
+      <c r="Z8" s="479"/>
+      <c r="AA8" s="480" t="s">
         <v>77</v>
       </c>
-      <c r="AB8" s="482"/>
-      <c r="AC8" s="482"/>
-      <c r="AD8" s="482"/>
-      <c r="AE8" s="484" t="s">
+      <c r="AB8" s="480"/>
+      <c r="AC8" s="480"/>
+      <c r="AD8" s="480"/>
+      <c r="AE8" s="477" t="s">
         <v>78</v>
       </c>
-      <c r="AF8" s="484"/>
-      <c r="AG8" s="484"/>
-      <c r="AH8" s="484"/>
-      <c r="AI8" s="485" t="s">
+      <c r="AF8" s="477"/>
+      <c r="AG8" s="477"/>
+      <c r="AH8" s="477"/>
+      <c r="AI8" s="473" t="s">
         <v>79</v>
       </c>
-      <c r="AJ8" s="485"/>
-      <c r="AK8" s="485"/>
-      <c r="AL8" s="485"/>
-      <c r="AM8" s="486" t="s">
+      <c r="AJ8" s="473"/>
+      <c r="AK8" s="473"/>
+      <c r="AL8" s="473"/>
+      <c r="AM8" s="474" t="s">
         <v>80</v>
       </c>
-      <c r="AN8" s="486"/>
-      <c r="AO8" s="486"/>
-      <c r="AP8" s="486"/>
-      <c r="AQ8" s="485" t="s">
+      <c r="AN8" s="474"/>
+      <c r="AO8" s="474"/>
+      <c r="AP8" s="474"/>
+      <c r="AQ8" s="473" t="s">
         <v>81</v>
       </c>
-      <c r="AR8" s="485"/>
-      <c r="AS8" s="485"/>
-      <c r="AT8" s="485"/>
-      <c r="AU8" s="486" t="s">
+      <c r="AR8" s="473"/>
+      <c r="AS8" s="473"/>
+      <c r="AT8" s="473"/>
+      <c r="AU8" s="474" t="s">
         <v>82</v>
       </c>
-      <c r="AV8" s="486"/>
-      <c r="AW8" s="486"/>
-      <c r="AX8" s="486"/>
-      <c r="AY8" s="485" t="s">
+      <c r="AV8" s="474"/>
+      <c r="AW8" s="474"/>
+      <c r="AX8" s="474"/>
+      <c r="AY8" s="473" t="s">
         <v>83</v>
       </c>
-      <c r="AZ8" s="485"/>
-      <c r="BA8" s="485"/>
-      <c r="BB8" s="485"/>
+      <c r="AZ8" s="473"/>
+      <c r="BA8" s="473"/>
+      <c r="BB8" s="473"/>
       <c r="BC8" s="8"/>
       <c r="BD8" s="8"/>
       <c r="BE8" s="8"/>
@@ -29425,7 +29488,7 @@
       <c r="BR8" s="8"/>
       <c r="BS8" s="8"/>
     </row>
-    <row r="9" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1">
+    <row r="9" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -29594,7 +29657,7 @@
       <c r="BR9" s="8"/>
       <c r="BS9" s="8"/>
     </row>
-    <row r="10" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1">
+    <row r="10" spans="1:71" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="40"/>
       <c r="B10" s="289" t="s">
         <v>9</v>
@@ -29623,42 +29686,42 @@
       <c r="P10" s="231"/>
       <c r="Q10" s="231"/>
       <c r="R10" s="378"/>
-      <c r="S10" s="487"/>
-      <c r="T10" s="488"/>
-      <c r="U10" s="488"/>
-      <c r="V10" s="488"/>
-      <c r="W10" s="488"/>
-      <c r="X10" s="488"/>
-      <c r="Y10" s="488"/>
-      <c r="Z10" s="488"/>
-      <c r="AA10" s="488"/>
-      <c r="AB10" s="488"/>
-      <c r="AC10" s="488"/>
-      <c r="AD10" s="489"/>
-      <c r="AE10" s="490"/>
-      <c r="AF10" s="491"/>
-      <c r="AG10" s="491"/>
-      <c r="AH10" s="491"/>
-      <c r="AI10" s="491"/>
-      <c r="AJ10" s="491"/>
-      <c r="AK10" s="491"/>
-      <c r="AL10" s="491"/>
-      <c r="AM10" s="491"/>
-      <c r="AN10" s="491"/>
-      <c r="AO10" s="491"/>
-      <c r="AP10" s="491"/>
-      <c r="AQ10" s="490"/>
-      <c r="AR10" s="491"/>
-      <c r="AS10" s="491"/>
-      <c r="AT10" s="491"/>
-      <c r="AU10" s="491"/>
-      <c r="AV10" s="491"/>
-      <c r="AW10" s="491"/>
-      <c r="AX10" s="491"/>
-      <c r="AY10" s="491"/>
-      <c r="AZ10" s="491"/>
-      <c r="BA10" s="491"/>
-      <c r="BB10" s="491"/>
+      <c r="S10" s="481"/>
+      <c r="T10" s="482"/>
+      <c r="U10" s="482"/>
+      <c r="V10" s="482"/>
+      <c r="W10" s="482"/>
+      <c r="X10" s="482"/>
+      <c r="Y10" s="482"/>
+      <c r="Z10" s="482"/>
+      <c r="AA10" s="482"/>
+      <c r="AB10" s="482"/>
+      <c r="AC10" s="482"/>
+      <c r="AD10" s="483"/>
+      <c r="AE10" s="475"/>
+      <c r="AF10" s="476"/>
+      <c r="AG10" s="476"/>
+      <c r="AH10" s="476"/>
+      <c r="AI10" s="476"/>
+      <c r="AJ10" s="476"/>
+      <c r="AK10" s="476"/>
+      <c r="AL10" s="476"/>
+      <c r="AM10" s="476"/>
+      <c r="AN10" s="476"/>
+      <c r="AO10" s="476"/>
+      <c r="AP10" s="476"/>
+      <c r="AQ10" s="475"/>
+      <c r="AR10" s="476"/>
+      <c r="AS10" s="476"/>
+      <c r="AT10" s="476"/>
+      <c r="AU10" s="476"/>
+      <c r="AV10" s="476"/>
+      <c r="AW10" s="476"/>
+      <c r="AX10" s="476"/>
+      <c r="AY10" s="476"/>
+      <c r="AZ10" s="476"/>
+      <c r="BA10" s="476"/>
+      <c r="BB10" s="476"/>
       <c r="BC10" s="9"/>
       <c r="BD10" s="9"/>
       <c r="BE10" s="9"/>
@@ -29677,7 +29740,7 @@
       <c r="BR10" s="9"/>
       <c r="BS10" s="9"/>
     </row>
-    <row r="11" spans="1:71" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="11" spans="1:71" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="150"/>
       <c r="B11" s="62" t="s">
         <v>84</v>
@@ -29743,7 +29806,7 @@
       <c r="BA11" s="38"/>
       <c r="BB11" s="42"/>
     </row>
-    <row r="12" spans="1:71" ht="30.75" thickBot="1">
+    <row r="12" spans="1:71" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="150"/>
       <c r="B12" s="62" t="s">
         <v>85</v>
@@ -29809,7 +29872,7 @@
       <c r="BA12" s="38"/>
       <c r="BB12" s="42"/>
     </row>
-    <row r="13" spans="1:71" ht="27" customHeight="1" thickBot="1">
+    <row r="13" spans="1:71" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="150"/>
       <c r="B13" s="62" t="s">
         <v>86</v>
@@ -29875,7 +29938,7 @@
       <c r="BA13" s="38"/>
       <c r="BB13" s="42"/>
     </row>
-    <row r="14" spans="1:71" ht="30.75" thickBot="1">
+    <row r="14" spans="1:71" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="150"/>
       <c r="B14" s="39" t="s">
         <v>87</v>
@@ -29941,9 +30004,9 @@
       <c r="BA14" s="150"/>
       <c r="BB14" s="177"/>
     </row>
-    <row r="15" spans="1:71" ht="15" customHeight="1">
+    <row r="15" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="150"/>
-      <c r="B15" s="427" t="s">
+      <c r="B15" s="445" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="116" t="s">
@@ -30013,9 +30076,9 @@
       <c r="BA15" s="150"/>
       <c r="BB15" s="177"/>
     </row>
-    <row r="16" spans="1:71">
+    <row r="16" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A16" s="150"/>
-      <c r="B16" s="427"/>
+      <c r="B16" s="445"/>
       <c r="C16" s="116" t="s">
         <v>42</v>
       </c>
@@ -30077,9 +30140,9 @@
       <c r="BA16" s="150"/>
       <c r="BB16" s="177"/>
     </row>
-    <row r="17" spans="1:54">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="150"/>
-      <c r="B17" s="427"/>
+      <c r="B17" s="445"/>
       <c r="C17" s="220" t="s">
         <v>23</v>
       </c>
@@ -30141,9 +30204,9 @@
       <c r="BA17" s="150"/>
       <c r="BB17" s="177"/>
     </row>
-    <row r="18" spans="1:54">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="150"/>
-      <c r="B18" s="427"/>
+      <c r="B18" s="445"/>
       <c r="C18" s="223" t="s">
         <v>91</v>
       </c>
@@ -30205,9 +30268,9 @@
       <c r="BA18" s="150"/>
       <c r="BB18" s="177"/>
     </row>
-    <row r="19" spans="1:54">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="150"/>
-      <c r="B19" s="427"/>
+      <c r="B19" s="445"/>
       <c r="C19" s="359" t="s">
         <v>93</v>
       </c>
@@ -30269,9 +30332,9 @@
       <c r="BA19" s="150"/>
       <c r="BB19" s="177"/>
     </row>
-    <row r="20" spans="1:54" ht="15.75" thickBot="1">
+    <row r="20" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="150"/>
-      <c r="B20" s="427"/>
+      <c r="B20" s="445"/>
       <c r="C20" s="359" t="s">
         <v>93</v>
       </c>
@@ -30333,9 +30396,9 @@
       <c r="BA20" s="150"/>
       <c r="BB20" s="177"/>
     </row>
-    <row r="21" spans="1:54" ht="15" customHeight="1">
+    <row r="21" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="150"/>
-      <c r="B21" s="427" t="s">
+      <c r="B21" s="445" t="s">
         <v>96</v>
       </c>
       <c r="C21" s="117" t="s">
@@ -30403,9 +30466,9 @@
       <c r="BA21" s="150"/>
       <c r="BB21" s="177"/>
     </row>
-    <row r="22" spans="1:54">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="150"/>
-      <c r="B22" s="427"/>
+      <c r="B22" s="445"/>
       <c r="C22" s="117" t="s">
         <v>27</v>
       </c>
@@ -30471,9 +30534,9 @@
       <c r="BA22" s="150"/>
       <c r="BB22" s="177"/>
     </row>
-    <row r="23" spans="1:54">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="150"/>
-      <c r="B23" s="427"/>
+      <c r="B23" s="445"/>
       <c r="C23" s="117" t="s">
         <v>27</v>
       </c>
@@ -30535,9 +30598,9 @@
       <c r="BA23" s="150"/>
       <c r="BB23" s="177"/>
     </row>
-    <row r="24" spans="1:54" s="164" customFormat="1">
+    <row r="24" spans="1:54" s="164" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="265"/>
-      <c r="B24" s="427"/>
+      <c r="B24" s="445"/>
       <c r="C24" s="117" t="s">
         <v>27</v>
       </c>
@@ -30602,9 +30665,9 @@
       <c r="BA24" s="265"/>
       <c r="BB24" s="177"/>
     </row>
-    <row r="25" spans="1:54" ht="15.75" thickBot="1">
+    <row r="25" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="150"/>
-      <c r="B25" s="427"/>
+      <c r="B25" s="445"/>
       <c r="C25" s="117" t="s">
         <v>27</v>
       </c>
@@ -30666,9 +30729,9 @@
       <c r="BA25" s="150"/>
       <c r="BB25" s="177"/>
     </row>
-    <row r="26" spans="1:54">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="150"/>
-      <c r="B26" s="427" t="s">
+      <c r="B26" s="445" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -30736,9 +30799,9 @@
       <c r="BA26" s="150"/>
       <c r="BB26" s="177"/>
     </row>
-    <row r="27" spans="1:54">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="150"/>
-      <c r="B27" s="427"/>
+      <c r="B27" s="445"/>
       <c r="C27" s="7" t="s">
         <v>38</v>
       </c>
@@ -30800,9 +30863,9 @@
       <c r="BA27" s="150"/>
       <c r="BB27" s="177"/>
     </row>
-    <row r="28" spans="1:54">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="150"/>
-      <c r="B28" s="427"/>
+      <c r="B28" s="445"/>
       <c r="C28" s="7" t="s">
         <v>38</v>
       </c>
@@ -30864,9 +30927,9 @@
       <c r="BA28" s="150"/>
       <c r="BB28" s="177"/>
     </row>
-    <row r="29" spans="1:54" ht="15.75" thickBot="1">
+    <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="150"/>
-      <c r="B29" s="472"/>
+      <c r="B29" s="446"/>
       <c r="C29" s="7" t="s">
         <v>38</v>
       </c>
@@ -30930,9 +30993,9 @@
       <c r="BA29" s="150"/>
       <c r="BB29" s="177"/>
     </row>
-    <row r="30" spans="1:54" ht="15" customHeight="1">
+    <row r="30" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="150"/>
-      <c r="B30" s="428" t="s">
+      <c r="B30" s="450" t="s">
         <v>106</v>
       </c>
       <c r="C30" s="116" t="s">
@@ -30996,9 +31059,9 @@
       <c r="BA30" s="150"/>
       <c r="BB30" s="177"/>
     </row>
-    <row r="31" spans="1:54">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="150"/>
-      <c r="B31" s="432"/>
+      <c r="B31" s="500"/>
       <c r="C31" s="116" t="s">
         <v>44</v>
       </c>
@@ -31060,9 +31123,9 @@
       <c r="BA31" s="150"/>
       <c r="BB31" s="177"/>
     </row>
-    <row r="32" spans="1:54" ht="15.75" thickBot="1">
+    <row r="32" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="150"/>
-      <c r="B32" s="432"/>
+      <c r="B32" s="500"/>
       <c r="C32" s="363" t="s">
         <v>44</v>
       </c>
@@ -31124,9 +31187,9 @@
       <c r="BA32" s="150"/>
       <c r="BB32" s="177"/>
     </row>
-    <row r="33" spans="1:54">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="150"/>
-      <c r="B33" s="433"/>
+      <c r="B33" s="501"/>
       <c r="C33" s="363" t="s">
         <v>44</v>
       </c>
@@ -31187,9 +31250,9 @@
       <c r="BA33" s="150"/>
       <c r="BB33" s="177"/>
     </row>
-    <row r="34" spans="1:54">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="150"/>
-      <c r="B34" s="472" t="s">
+      <c r="B34" s="446" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="116" t="s">
@@ -31255,9 +31318,9 @@
       <c r="BA34" s="150"/>
       <c r="BB34" s="177"/>
     </row>
-    <row r="35" spans="1:54" ht="15.75" thickBot="1">
+    <row r="35" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="150"/>
-      <c r="B35" s="472"/>
+      <c r="B35" s="446"/>
       <c r="C35" s="116" t="s">
         <v>27</v>
       </c>
@@ -31319,7 +31382,7 @@
       <c r="BA35" s="150"/>
       <c r="BB35" s="177"/>
     </row>
-    <row r="36" spans="1:54" ht="15.75" thickBot="1">
+    <row r="36" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="150"/>
       <c r="B36" s="32" t="s">
         <v>112</v>
@@ -31387,9 +31450,9 @@
       <c r="BA36" s="150"/>
       <c r="BB36" s="177"/>
     </row>
-    <row r="37" spans="1:54">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="150"/>
-      <c r="B37" s="472" t="s">
+      <c r="B37" s="446" t="s">
         <v>115</v>
       </c>
       <c r="C37" s="116" t="s">
@@ -31453,9 +31516,9 @@
       <c r="BA37" s="150"/>
       <c r="BB37" s="177"/>
     </row>
-    <row r="38" spans="1:54" ht="15.75" thickBot="1">
+    <row r="38" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="150"/>
-      <c r="B38" s="472"/>
+      <c r="B38" s="446"/>
       <c r="C38" s="116" t="s">
         <v>20</v>
       </c>
@@ -31517,9 +31580,9 @@
       <c r="BA38" s="150"/>
       <c r="BB38" s="177"/>
     </row>
-    <row r="39" spans="1:54">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="150"/>
-      <c r="B39" s="492" t="s">
+      <c r="B39" s="533" t="s">
         <v>118</v>
       </c>
       <c r="C39" s="116" t="s">
@@ -31583,9 +31646,9 @@
       <c r="BA39" s="150"/>
       <c r="BB39" s="177"/>
     </row>
-    <row r="40" spans="1:54">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="150"/>
-      <c r="B40" s="492"/>
+      <c r="B40" s="533"/>
       <c r="C40" s="116" t="s">
         <v>113</v>
       </c>
@@ -31647,9 +31710,9 @@
       <c r="BA40" s="150"/>
       <c r="BB40" s="177"/>
     </row>
-    <row r="41" spans="1:54" ht="15.75" thickBot="1">
+    <row r="41" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="150"/>
-      <c r="B41" s="492"/>
+      <c r="B41" s="533"/>
       <c r="C41" s="116" t="s">
         <v>113</v>
       </c>
@@ -31711,9 +31774,9 @@
       <c r="BA41" s="150"/>
       <c r="BB41" s="177"/>
     </row>
-    <row r="42" spans="1:54">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="150"/>
-      <c r="B42" s="493" t="s">
+      <c r="B42" s="511" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="223" t="s">
@@ -31777,9 +31840,9 @@
       <c r="BA42" s="150"/>
       <c r="BB42" s="177"/>
     </row>
-    <row r="43" spans="1:54">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="150"/>
-      <c r="B43" s="493"/>
+      <c r="B43" s="511"/>
       <c r="C43" s="223" t="s">
         <v>113</v>
       </c>
@@ -31841,9 +31904,9 @@
       <c r="BA43" s="150"/>
       <c r="BB43" s="177"/>
     </row>
-    <row r="44" spans="1:54" ht="15.75" thickBot="1">
+    <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="150"/>
-      <c r="B44" s="493"/>
+      <c r="B44" s="511"/>
       <c r="C44" s="223" t="s">
         <v>113</v>
       </c>
@@ -31905,7 +31968,7 @@
       <c r="BA44" s="150"/>
       <c r="BB44" s="177"/>
     </row>
-    <row r="45" spans="1:54" ht="15.75" thickBot="1">
+    <row r="45" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="150"/>
       <c r="B45" s="121" t="s">
         <v>64</v>
@@ -31971,7 +32034,7 @@
       <c r="BA45" s="150"/>
       <c r="BB45" s="177"/>
     </row>
-    <row r="46" spans="1:54" ht="15.75" thickBot="1">
+    <row r="46" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="150"/>
       <c r="B46" s="121" t="s">
         <v>27</v>
@@ -32037,7 +32100,7 @@
       <c r="BA46" s="150"/>
       <c r="BB46" s="177"/>
     </row>
-    <row r="47" spans="1:54" ht="15.75" thickBot="1">
+    <row r="47" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="150"/>
       <c r="B47" s="121" t="s">
         <v>128</v>
@@ -32103,7 +32166,7 @@
       <c r="BA47" s="314"/>
       <c r="BB47" s="315"/>
     </row>
-    <row r="48" spans="1:54" ht="15.75" thickBot="1">
+    <row r="48" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="150" t="s">
         <v>18</v>
       </c>
@@ -32164,51 +32227,51 @@
       <c r="BA48" s="314"/>
       <c r="BB48" s="315"/>
     </row>
-    <row r="49" spans="1:54" ht="19.5" thickBot="1">
+    <row r="49" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="150"/>
-      <c r="B49" s="494" t="s">
+      <c r="B49" s="512" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="495"/>
-      <c r="D49" s="495"/>
-      <c r="E49" s="495"/>
-      <c r="F49" s="496"/>
-      <c r="G49" s="497" t="s">
+      <c r="C49" s="513"/>
+      <c r="D49" s="513"/>
+      <c r="E49" s="513"/>
+      <c r="F49" s="514"/>
+      <c r="G49" s="488" t="s">
         <v>132</v>
       </c>
-      <c r="H49" s="498"/>
-      <c r="I49" s="498"/>
-      <c r="J49" s="499"/>
-      <c r="K49" s="497" t="s">
+      <c r="H49" s="489"/>
+      <c r="I49" s="489"/>
+      <c r="J49" s="490"/>
+      <c r="K49" s="488" t="s">
         <v>133</v>
       </c>
-      <c r="L49" s="498"/>
-      <c r="M49" s="498"/>
-      <c r="N49" s="499"/>
-      <c r="O49" s="497" t="s">
+      <c r="L49" s="489"/>
+      <c r="M49" s="489"/>
+      <c r="N49" s="490"/>
+      <c r="O49" s="488" t="s">
         <v>134</v>
       </c>
-      <c r="P49" s="498"/>
-      <c r="Q49" s="498"/>
-      <c r="R49" s="499"/>
-      <c r="S49" s="497" t="s">
+      <c r="P49" s="489"/>
+      <c r="Q49" s="489"/>
+      <c r="R49" s="490"/>
+      <c r="S49" s="488" t="s">
         <v>135</v>
       </c>
-      <c r="T49" s="498"/>
-      <c r="U49" s="498"/>
-      <c r="V49" s="499"/>
-      <c r="W49" s="497" t="s">
+      <c r="T49" s="489"/>
+      <c r="U49" s="489"/>
+      <c r="V49" s="490"/>
+      <c r="W49" s="488" t="s">
         <v>133</v>
       </c>
-      <c r="X49" s="498"/>
-      <c r="Y49" s="498"/>
-      <c r="Z49" s="499"/>
-      <c r="AA49" s="497" t="s">
+      <c r="X49" s="489"/>
+      <c r="Y49" s="489"/>
+      <c r="Z49" s="490"/>
+      <c r="AA49" s="488" t="s">
         <v>136</v>
       </c>
-      <c r="AB49" s="498"/>
-      <c r="AC49" s="498"/>
-      <c r="AD49" s="499"/>
+      <c r="AB49" s="489"/>
+      <c r="AC49" s="489"/>
+      <c r="AD49" s="490"/>
       <c r="AE49" s="192"/>
       <c r="AF49" s="192"/>
       <c r="AG49" s="192"/>
@@ -32234,51 +32297,51 @@
       <c r="BA49" s="192"/>
       <c r="BB49" s="193"/>
     </row>
-    <row r="50" spans="1:54" ht="19.5" thickBot="1">
+    <row r="50" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="150"/>
-      <c r="B50" s="500" t="s">
+      <c r="B50" s="485" t="s">
         <v>137</v>
       </c>
-      <c r="C50" s="501"/>
-      <c r="D50" s="501"/>
-      <c r="E50" s="501"/>
-      <c r="F50" s="502"/>
-      <c r="G50" s="503" t="s">
+      <c r="C50" s="486"/>
+      <c r="D50" s="486"/>
+      <c r="E50" s="486"/>
+      <c r="F50" s="487"/>
+      <c r="G50" s="466" t="s">
         <v>136</v>
       </c>
-      <c r="H50" s="504"/>
-      <c r="I50" s="504"/>
-      <c r="J50" s="505"/>
-      <c r="K50" s="503" t="s">
+      <c r="H50" s="467"/>
+      <c r="I50" s="467"/>
+      <c r="J50" s="468"/>
+      <c r="K50" s="466" t="s">
         <v>138</v>
       </c>
-      <c r="L50" s="504"/>
-      <c r="M50" s="504"/>
-      <c r="N50" s="505"/>
-      <c r="O50" s="500" t="s">
+      <c r="L50" s="467"/>
+      <c r="M50" s="467"/>
+      <c r="N50" s="468"/>
+      <c r="O50" s="485" t="s">
         <v>139</v>
       </c>
-      <c r="P50" s="501"/>
-      <c r="Q50" s="501"/>
-      <c r="R50" s="502"/>
-      <c r="S50" s="500" t="s">
+      <c r="P50" s="486"/>
+      <c r="Q50" s="486"/>
+      <c r="R50" s="487"/>
+      <c r="S50" s="485" t="s">
         <v>138</v>
       </c>
-      <c r="T50" s="501"/>
-      <c r="U50" s="501"/>
-      <c r="V50" s="502"/>
-      <c r="W50" s="500" t="s">
+      <c r="T50" s="486"/>
+      <c r="U50" s="486"/>
+      <c r="V50" s="487"/>
+      <c r="W50" s="485" t="s">
         <v>138</v>
       </c>
-      <c r="X50" s="501"/>
-      <c r="Y50" s="501"/>
-      <c r="Z50" s="502"/>
-      <c r="AA50" s="500" t="s">
+      <c r="X50" s="486"/>
+      <c r="Y50" s="486"/>
+      <c r="Z50" s="487"/>
+      <c r="AA50" s="485" t="s">
         <v>138</v>
       </c>
-      <c r="AB50" s="501"/>
-      <c r="AC50" s="501"/>
-      <c r="AD50" s="502"/>
+      <c r="AB50" s="486"/>
+      <c r="AC50" s="486"/>
+      <c r="AD50" s="487"/>
       <c r="AE50" s="192"/>
       <c r="AF50" s="192"/>
       <c r="AG50" s="192"/>
@@ -32304,47 +32367,47 @@
       <c r="BA50" s="192"/>
       <c r="BB50" s="193"/>
     </row>
-    <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1">
+    <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="150"/>
-      <c r="B51" s="506" t="s">
+      <c r="B51" s="460" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="507"/>
-      <c r="D51" s="507"/>
-      <c r="E51" s="507"/>
-      <c r="F51" s="508"/>
-      <c r="G51" s="509" t="s">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="462"/>
+      <c r="G51" s="469" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="510"/>
-      <c r="I51" s="510"/>
-      <c r="J51" s="511"/>
-      <c r="K51" s="512" t="s">
+      <c r="H51" s="470"/>
+      <c r="I51" s="470"/>
+      <c r="J51" s="471"/>
+      <c r="K51" s="494" t="s">
         <v>142</v>
       </c>
-      <c r="L51" s="513"/>
-      <c r="M51" s="513"/>
-      <c r="N51" s="514"/>
-      <c r="O51" s="506" t="s">
+      <c r="L51" s="495"/>
+      <c r="M51" s="495"/>
+      <c r="N51" s="496"/>
+      <c r="O51" s="460" t="s">
         <v>143</v>
       </c>
-      <c r="P51" s="507"/>
-      <c r="Q51" s="507"/>
-      <c r="R51" s="508"/>
-      <c r="S51" s="506"/>
-      <c r="T51" s="507"/>
-      <c r="U51" s="507"/>
-      <c r="V51" s="508"/>
-      <c r="W51" s="506" t="s">
+      <c r="P51" s="461"/>
+      <c r="Q51" s="461"/>
+      <c r="R51" s="462"/>
+      <c r="S51" s="460"/>
+      <c r="T51" s="461"/>
+      <c r="U51" s="461"/>
+      <c r="V51" s="462"/>
+      <c r="W51" s="460" t="s">
         <v>143</v>
       </c>
-      <c r="X51" s="507"/>
-      <c r="Y51" s="507"/>
-      <c r="Z51" s="508"/>
-      <c r="AA51" s="506"/>
-      <c r="AB51" s="507"/>
-      <c r="AC51" s="507"/>
-      <c r="AD51" s="515"/>
+      <c r="X51" s="461"/>
+      <c r="Y51" s="461"/>
+      <c r="Z51" s="462"/>
+      <c r="AA51" s="460"/>
+      <c r="AB51" s="461"/>
+      <c r="AC51" s="461"/>
+      <c r="AD51" s="535"/>
       <c r="AE51" s="192"/>
       <c r="AF51" s="192"/>
       <c r="AG51" s="192"/>
@@ -32370,45 +32433,45 @@
       <c r="BA51" s="192"/>
       <c r="BB51" s="193"/>
     </row>
-    <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1">
+    <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="150"/>
-      <c r="B52" s="516" t="s">
+      <c r="B52" s="463" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="517"/>
-      <c r="D52" s="517"/>
-      <c r="E52" s="517"/>
-      <c r="F52" s="518"/>
-      <c r="G52" s="519" t="s">
+      <c r="C52" s="464"/>
+      <c r="D52" s="464"/>
+      <c r="E52" s="464"/>
+      <c r="F52" s="465"/>
+      <c r="G52" s="491" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="520"/>
-      <c r="I52" s="520"/>
-      <c r="J52" s="521"/>
-      <c r="K52" s="429" t="s">
+      <c r="H52" s="492"/>
+      <c r="I52" s="492"/>
+      <c r="J52" s="493"/>
+      <c r="K52" s="497" t="s">
         <v>146</v>
       </c>
-      <c r="L52" s="430"/>
-      <c r="M52" s="430"/>
-      <c r="N52" s="431"/>
-      <c r="O52" s="429" t="s">
+      <c r="L52" s="498"/>
+      <c r="M52" s="498"/>
+      <c r="N52" s="499"/>
+      <c r="O52" s="497" t="s">
         <v>147</v>
       </c>
-      <c r="P52" s="430"/>
-      <c r="Q52" s="430"/>
-      <c r="R52" s="431"/>
-      <c r="S52" s="516"/>
-      <c r="T52" s="517"/>
-      <c r="U52" s="517"/>
-      <c r="V52" s="518"/>
-      <c r="W52" s="516"/>
-      <c r="X52" s="517"/>
-      <c r="Y52" s="517"/>
-      <c r="Z52" s="518"/>
-      <c r="AA52" s="516"/>
-      <c r="AB52" s="517"/>
-      <c r="AC52" s="517"/>
-      <c r="AD52" s="522"/>
+      <c r="P52" s="498"/>
+      <c r="Q52" s="498"/>
+      <c r="R52" s="499"/>
+      <c r="S52" s="463"/>
+      <c r="T52" s="464"/>
+      <c r="U52" s="464"/>
+      <c r="V52" s="465"/>
+      <c r="W52" s="463"/>
+      <c r="X52" s="464"/>
+      <c r="Y52" s="464"/>
+      <c r="Z52" s="465"/>
+      <c r="AA52" s="463"/>
+      <c r="AB52" s="464"/>
+      <c r="AC52" s="464"/>
+      <c r="AD52" s="534"/>
       <c r="AE52" s="192"/>
       <c r="AF52" s="192"/>
       <c r="AG52" s="192"/>
@@ -32434,51 +32497,51 @@
       <c r="BA52" s="192"/>
       <c r="BB52" s="193"/>
     </row>
-    <row r="53" spans="1:54" ht="15" customHeight="1">
+    <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="150"/>
-      <c r="B53" s="523" t="s">
+      <c r="B53" s="515" t="s">
         <v>148</v>
       </c>
-      <c r="C53" s="524"/>
-      <c r="D53" s="524"/>
-      <c r="E53" s="524"/>
-      <c r="F53" s="525"/>
-      <c r="G53" s="443" t="s">
+      <c r="C53" s="516"/>
+      <c r="D53" s="516"/>
+      <c r="E53" s="516"/>
+      <c r="F53" s="517"/>
+      <c r="G53" s="524" t="s">
         <v>149</v>
       </c>
-      <c r="H53" s="444"/>
-      <c r="I53" s="444"/>
-      <c r="J53" s="445"/>
-      <c r="K53" s="443" t="s">
+      <c r="H53" s="525"/>
+      <c r="I53" s="525"/>
+      <c r="J53" s="526"/>
+      <c r="K53" s="524" t="s">
         <v>150</v>
       </c>
-      <c r="L53" s="444"/>
-      <c r="M53" s="444"/>
-      <c r="N53" s="445"/>
-      <c r="O53" s="434" t="s">
+      <c r="L53" s="525"/>
+      <c r="M53" s="525"/>
+      <c r="N53" s="526"/>
+      <c r="O53" s="502" t="s">
         <v>151</v>
       </c>
-      <c r="P53" s="435"/>
-      <c r="Q53" s="435"/>
-      <c r="R53" s="436"/>
-      <c r="S53" s="434" t="s">
+      <c r="P53" s="503"/>
+      <c r="Q53" s="503"/>
+      <c r="R53" s="504"/>
+      <c r="S53" s="502" t="s">
         <v>152</v>
       </c>
-      <c r="T53" s="435"/>
-      <c r="U53" s="435"/>
-      <c r="V53" s="436"/>
-      <c r="W53" s="434" t="s">
+      <c r="T53" s="503"/>
+      <c r="U53" s="503"/>
+      <c r="V53" s="504"/>
+      <c r="W53" s="502" t="s">
         <v>153</v>
       </c>
-      <c r="X53" s="435"/>
-      <c r="Y53" s="435"/>
-      <c r="Z53" s="436"/>
-      <c r="AA53" s="434" t="s">
+      <c r="X53" s="503"/>
+      <c r="Y53" s="503"/>
+      <c r="Z53" s="504"/>
+      <c r="AA53" s="502" t="s">
         <v>154</v>
       </c>
-      <c r="AB53" s="435"/>
-      <c r="AC53" s="435"/>
-      <c r="AD53" s="436"/>
+      <c r="AB53" s="503"/>
+      <c r="AC53" s="503"/>
+      <c r="AD53" s="504"/>
       <c r="AE53" s="150"/>
       <c r="AF53" s="150"/>
       <c r="AG53" s="150"/>
@@ -32506,37 +32569,37 @@
       <c r="BA53" s="150"/>
       <c r="BB53" s="150"/>
     </row>
-    <row r="54" spans="1:54" ht="15" customHeight="1">
+    <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="150"/>
-      <c r="B54" s="526"/>
-      <c r="C54" s="527"/>
-      <c r="D54" s="527"/>
-      <c r="E54" s="527"/>
-      <c r="F54" s="528"/>
-      <c r="G54" s="446"/>
-      <c r="H54" s="447"/>
-      <c r="I54" s="447"/>
-      <c r="J54" s="448"/>
-      <c r="K54" s="446"/>
-      <c r="L54" s="447"/>
-      <c r="M54" s="447"/>
-      <c r="N54" s="448"/>
-      <c r="O54" s="437"/>
-      <c r="P54" s="438"/>
-      <c r="Q54" s="438"/>
-      <c r="R54" s="439"/>
-      <c r="S54" s="437"/>
-      <c r="T54" s="438"/>
-      <c r="U54" s="438"/>
-      <c r="V54" s="439"/>
-      <c r="W54" s="437"/>
-      <c r="X54" s="438"/>
-      <c r="Y54" s="438"/>
-      <c r="Z54" s="439"/>
-      <c r="AA54" s="437"/>
-      <c r="AB54" s="438"/>
-      <c r="AC54" s="438"/>
-      <c r="AD54" s="439"/>
+      <c r="B54" s="518"/>
+      <c r="C54" s="519"/>
+      <c r="D54" s="519"/>
+      <c r="E54" s="519"/>
+      <c r="F54" s="520"/>
+      <c r="G54" s="527"/>
+      <c r="H54" s="528"/>
+      <c r="I54" s="528"/>
+      <c r="J54" s="529"/>
+      <c r="K54" s="527"/>
+      <c r="L54" s="528"/>
+      <c r="M54" s="528"/>
+      <c r="N54" s="529"/>
+      <c r="O54" s="505"/>
+      <c r="P54" s="506"/>
+      <c r="Q54" s="506"/>
+      <c r="R54" s="507"/>
+      <c r="S54" s="505"/>
+      <c r="T54" s="506"/>
+      <c r="U54" s="506"/>
+      <c r="V54" s="507"/>
+      <c r="W54" s="505"/>
+      <c r="X54" s="506"/>
+      <c r="Y54" s="506"/>
+      <c r="Z54" s="507"/>
+      <c r="AA54" s="505"/>
+      <c r="AB54" s="506"/>
+      <c r="AC54" s="506"/>
+      <c r="AD54" s="507"/>
       <c r="AE54" s="150"/>
       <c r="AF54" s="150"/>
       <c r="AG54" s="150"/>
@@ -32562,36 +32625,36 @@
       <c r="BA54" s="150"/>
       <c r="BB54" s="150"/>
     </row>
-    <row r="55" spans="1:54" ht="15" customHeight="1">
-      <c r="B55" s="526"/>
-      <c r="C55" s="527"/>
-      <c r="D55" s="527"/>
-      <c r="E55" s="527"/>
-      <c r="F55" s="528"/>
-      <c r="G55" s="446"/>
-      <c r="H55" s="447"/>
-      <c r="I55" s="447"/>
-      <c r="J55" s="448"/>
-      <c r="K55" s="446"/>
-      <c r="L55" s="447"/>
-      <c r="M55" s="447"/>
-      <c r="N55" s="448"/>
-      <c r="O55" s="437"/>
-      <c r="P55" s="438"/>
-      <c r="Q55" s="438"/>
-      <c r="R55" s="439"/>
-      <c r="S55" s="437"/>
-      <c r="T55" s="438"/>
-      <c r="U55" s="438"/>
-      <c r="V55" s="439"/>
-      <c r="W55" s="437"/>
-      <c r="X55" s="438"/>
-      <c r="Y55" s="438"/>
-      <c r="Z55" s="439"/>
-      <c r="AA55" s="437"/>
-      <c r="AB55" s="438"/>
-      <c r="AC55" s="438"/>
-      <c r="AD55" s="439"/>
+    <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="518"/>
+      <c r="C55" s="519"/>
+      <c r="D55" s="519"/>
+      <c r="E55" s="519"/>
+      <c r="F55" s="520"/>
+      <c r="G55" s="527"/>
+      <c r="H55" s="528"/>
+      <c r="I55" s="528"/>
+      <c r="J55" s="529"/>
+      <c r="K55" s="527"/>
+      <c r="L55" s="528"/>
+      <c r="M55" s="528"/>
+      <c r="N55" s="529"/>
+      <c r="O55" s="505"/>
+      <c r="P55" s="506"/>
+      <c r="Q55" s="506"/>
+      <c r="R55" s="507"/>
+      <c r="S55" s="505"/>
+      <c r="T55" s="506"/>
+      <c r="U55" s="506"/>
+      <c r="V55" s="507"/>
+      <c r="W55" s="505"/>
+      <c r="X55" s="506"/>
+      <c r="Y55" s="506"/>
+      <c r="Z55" s="507"/>
+      <c r="AA55" s="505"/>
+      <c r="AB55" s="506"/>
+      <c r="AC55" s="506"/>
+      <c r="AD55" s="507"/>
       <c r="AE55" s="150"/>
       <c r="AF55" s="150"/>
       <c r="AG55" s="150"/>
@@ -32617,439 +32680,439 @@
       <c r="BA55" s="150"/>
       <c r="BB55" s="150"/>
     </row>
-    <row r="56" spans="1:54" ht="15" customHeight="1">
-      <c r="B56" s="526"/>
-      <c r="C56" s="527"/>
-      <c r="D56" s="527"/>
-      <c r="E56" s="527"/>
-      <c r="F56" s="528"/>
-      <c r="G56" s="446"/>
-      <c r="H56" s="447"/>
-      <c r="I56" s="447"/>
-      <c r="J56" s="448"/>
-      <c r="K56" s="446"/>
-      <c r="L56" s="447"/>
-      <c r="M56" s="447"/>
-      <c r="N56" s="448"/>
-      <c r="O56" s="437"/>
-      <c r="P56" s="438"/>
-      <c r="Q56" s="438"/>
-      <c r="R56" s="439"/>
-      <c r="S56" s="437"/>
-      <c r="T56" s="438"/>
-      <c r="U56" s="438"/>
-      <c r="V56" s="439"/>
-      <c r="W56" s="437"/>
-      <c r="X56" s="438"/>
-      <c r="Y56" s="438"/>
-      <c r="Z56" s="439"/>
-      <c r="AA56" s="437"/>
-      <c r="AB56" s="438"/>
-      <c r="AC56" s="438"/>
-      <c r="AD56" s="439"/>
+    <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="518"/>
+      <c r="C56" s="519"/>
+      <c r="D56" s="519"/>
+      <c r="E56" s="519"/>
+      <c r="F56" s="520"/>
+      <c r="G56" s="527"/>
+      <c r="H56" s="528"/>
+      <c r="I56" s="528"/>
+      <c r="J56" s="529"/>
+      <c r="K56" s="527"/>
+      <c r="L56" s="528"/>
+      <c r="M56" s="528"/>
+      <c r="N56" s="529"/>
+      <c r="O56" s="505"/>
+      <c r="P56" s="506"/>
+      <c r="Q56" s="506"/>
+      <c r="R56" s="507"/>
+      <c r="S56" s="505"/>
+      <c r="T56" s="506"/>
+      <c r="U56" s="506"/>
+      <c r="V56" s="507"/>
+      <c r="W56" s="505"/>
+      <c r="X56" s="506"/>
+      <c r="Y56" s="506"/>
+      <c r="Z56" s="507"/>
+      <c r="AA56" s="505"/>
+      <c r="AB56" s="506"/>
+      <c r="AC56" s="506"/>
+      <c r="AD56" s="507"/>
     </row>
-    <row r="57" spans="1:54" ht="15" customHeight="1">
-      <c r="B57" s="526"/>
-      <c r="C57" s="527"/>
-      <c r="D57" s="527"/>
-      <c r="E57" s="527"/>
-      <c r="F57" s="528"/>
-      <c r="G57" s="446"/>
-      <c r="H57" s="447"/>
-      <c r="I57" s="447"/>
-      <c r="J57" s="448"/>
-      <c r="K57" s="446"/>
-      <c r="L57" s="447"/>
-      <c r="M57" s="447"/>
-      <c r="N57" s="448"/>
-      <c r="O57" s="437"/>
-      <c r="P57" s="438"/>
-      <c r="Q57" s="438"/>
-      <c r="R57" s="439"/>
-      <c r="S57" s="437"/>
-      <c r="T57" s="438"/>
-      <c r="U57" s="438"/>
-      <c r="V57" s="439"/>
-      <c r="W57" s="437"/>
-      <c r="X57" s="438"/>
-      <c r="Y57" s="438"/>
-      <c r="Z57" s="439"/>
-      <c r="AA57" s="437"/>
-      <c r="AB57" s="438"/>
-      <c r="AC57" s="438"/>
-      <c r="AD57" s="439"/>
+    <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="518"/>
+      <c r="C57" s="519"/>
+      <c r="D57" s="519"/>
+      <c r="E57" s="519"/>
+      <c r="F57" s="520"/>
+      <c r="G57" s="527"/>
+      <c r="H57" s="528"/>
+      <c r="I57" s="528"/>
+      <c r="J57" s="529"/>
+      <c r="K57" s="527"/>
+      <c r="L57" s="528"/>
+      <c r="M57" s="528"/>
+      <c r="N57" s="529"/>
+      <c r="O57" s="505"/>
+      <c r="P57" s="506"/>
+      <c r="Q57" s="506"/>
+      <c r="R57" s="507"/>
+      <c r="S57" s="505"/>
+      <c r="T57" s="506"/>
+      <c r="U57" s="506"/>
+      <c r="V57" s="507"/>
+      <c r="W57" s="505"/>
+      <c r="X57" s="506"/>
+      <c r="Y57" s="506"/>
+      <c r="Z57" s="507"/>
+      <c r="AA57" s="505"/>
+      <c r="AB57" s="506"/>
+      <c r="AC57" s="506"/>
+      <c r="AD57" s="507"/>
     </row>
-    <row r="58" spans="1:54" ht="15" customHeight="1">
-      <c r="B58" s="526"/>
-      <c r="C58" s="527"/>
-      <c r="D58" s="527"/>
-      <c r="E58" s="527"/>
-      <c r="F58" s="528"/>
-      <c r="G58" s="446"/>
-      <c r="H58" s="447"/>
-      <c r="I58" s="447"/>
-      <c r="J58" s="448"/>
-      <c r="K58" s="446"/>
-      <c r="L58" s="447"/>
-      <c r="M58" s="447"/>
-      <c r="N58" s="448"/>
-      <c r="O58" s="437"/>
-      <c r="P58" s="438"/>
-      <c r="Q58" s="438"/>
-      <c r="R58" s="439"/>
-      <c r="S58" s="437"/>
-      <c r="T58" s="438"/>
-      <c r="U58" s="438"/>
-      <c r="V58" s="439"/>
-      <c r="W58" s="437"/>
-      <c r="X58" s="438"/>
-      <c r="Y58" s="438"/>
-      <c r="Z58" s="439"/>
-      <c r="AA58" s="437"/>
-      <c r="AB58" s="438"/>
-      <c r="AC58" s="438"/>
-      <c r="AD58" s="439"/>
+    <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="518"/>
+      <c r="C58" s="519"/>
+      <c r="D58" s="519"/>
+      <c r="E58" s="519"/>
+      <c r="F58" s="520"/>
+      <c r="G58" s="527"/>
+      <c r="H58" s="528"/>
+      <c r="I58" s="528"/>
+      <c r="J58" s="529"/>
+      <c r="K58" s="527"/>
+      <c r="L58" s="528"/>
+      <c r="M58" s="528"/>
+      <c r="N58" s="529"/>
+      <c r="O58" s="505"/>
+      <c r="P58" s="506"/>
+      <c r="Q58" s="506"/>
+      <c r="R58" s="507"/>
+      <c r="S58" s="505"/>
+      <c r="T58" s="506"/>
+      <c r="U58" s="506"/>
+      <c r="V58" s="507"/>
+      <c r="W58" s="505"/>
+      <c r="X58" s="506"/>
+      <c r="Y58" s="506"/>
+      <c r="Z58" s="507"/>
+      <c r="AA58" s="505"/>
+      <c r="AB58" s="506"/>
+      <c r="AC58" s="506"/>
+      <c r="AD58" s="507"/>
     </row>
-    <row r="59" spans="1:54" ht="15" customHeight="1">
-      <c r="B59" s="526"/>
-      <c r="C59" s="527"/>
-      <c r="D59" s="527"/>
-      <c r="E59" s="527"/>
-      <c r="F59" s="528"/>
-      <c r="G59" s="446"/>
-      <c r="H59" s="447"/>
-      <c r="I59" s="447"/>
-      <c r="J59" s="448"/>
-      <c r="K59" s="446"/>
-      <c r="L59" s="447"/>
-      <c r="M59" s="447"/>
-      <c r="N59" s="448"/>
-      <c r="O59" s="437"/>
-      <c r="P59" s="438"/>
-      <c r="Q59" s="438"/>
-      <c r="R59" s="439"/>
-      <c r="S59" s="437"/>
-      <c r="T59" s="438"/>
-      <c r="U59" s="438"/>
-      <c r="V59" s="439"/>
-      <c r="W59" s="437"/>
-      <c r="X59" s="438"/>
-      <c r="Y59" s="438"/>
-      <c r="Z59" s="439"/>
-      <c r="AA59" s="437"/>
-      <c r="AB59" s="438"/>
-      <c r="AC59" s="438"/>
-      <c r="AD59" s="439"/>
+    <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="518"/>
+      <c r="C59" s="519"/>
+      <c r="D59" s="519"/>
+      <c r="E59" s="519"/>
+      <c r="F59" s="520"/>
+      <c r="G59" s="527"/>
+      <c r="H59" s="528"/>
+      <c r="I59" s="528"/>
+      <c r="J59" s="529"/>
+      <c r="K59" s="527"/>
+      <c r="L59" s="528"/>
+      <c r="M59" s="528"/>
+      <c r="N59" s="529"/>
+      <c r="O59" s="505"/>
+      <c r="P59" s="506"/>
+      <c r="Q59" s="506"/>
+      <c r="R59" s="507"/>
+      <c r="S59" s="505"/>
+      <c r="T59" s="506"/>
+      <c r="U59" s="506"/>
+      <c r="V59" s="507"/>
+      <c r="W59" s="505"/>
+      <c r="X59" s="506"/>
+      <c r="Y59" s="506"/>
+      <c r="Z59" s="507"/>
+      <c r="AA59" s="505"/>
+      <c r="AB59" s="506"/>
+      <c r="AC59" s="506"/>
+      <c r="AD59" s="507"/>
     </row>
-    <row r="60" spans="1:54" ht="15" customHeight="1">
-      <c r="B60" s="526"/>
-      <c r="C60" s="527"/>
-      <c r="D60" s="527"/>
-      <c r="E60" s="527"/>
-      <c r="F60" s="528"/>
-      <c r="G60" s="446"/>
-      <c r="H60" s="447"/>
-      <c r="I60" s="447"/>
-      <c r="J60" s="448"/>
-      <c r="K60" s="446"/>
-      <c r="L60" s="447"/>
-      <c r="M60" s="447"/>
-      <c r="N60" s="448"/>
-      <c r="O60" s="437"/>
-      <c r="P60" s="438"/>
-      <c r="Q60" s="438"/>
-      <c r="R60" s="439"/>
-      <c r="S60" s="437"/>
-      <c r="T60" s="438"/>
-      <c r="U60" s="438"/>
-      <c r="V60" s="439"/>
-      <c r="W60" s="437"/>
-      <c r="X60" s="438"/>
-      <c r="Y60" s="438"/>
-      <c r="Z60" s="439"/>
-      <c r="AA60" s="437"/>
-      <c r="AB60" s="438"/>
-      <c r="AC60" s="438"/>
-      <c r="AD60" s="439"/>
+    <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="518"/>
+      <c r="C60" s="519"/>
+      <c r="D60" s="519"/>
+      <c r="E60" s="519"/>
+      <c r="F60" s="520"/>
+      <c r="G60" s="527"/>
+      <c r="H60" s="528"/>
+      <c r="I60" s="528"/>
+      <c r="J60" s="529"/>
+      <c r="K60" s="527"/>
+      <c r="L60" s="528"/>
+      <c r="M60" s="528"/>
+      <c r="N60" s="529"/>
+      <c r="O60" s="505"/>
+      <c r="P60" s="506"/>
+      <c r="Q60" s="506"/>
+      <c r="R60" s="507"/>
+      <c r="S60" s="505"/>
+      <c r="T60" s="506"/>
+      <c r="U60" s="506"/>
+      <c r="V60" s="507"/>
+      <c r="W60" s="505"/>
+      <c r="X60" s="506"/>
+      <c r="Y60" s="506"/>
+      <c r="Z60" s="507"/>
+      <c r="AA60" s="505"/>
+      <c r="AB60" s="506"/>
+      <c r="AC60" s="506"/>
+      <c r="AD60" s="507"/>
     </row>
-    <row r="61" spans="1:54" ht="15" customHeight="1">
-      <c r="B61" s="526"/>
-      <c r="C61" s="527"/>
-      <c r="D61" s="527"/>
-      <c r="E61" s="527"/>
-      <c r="F61" s="528"/>
-      <c r="G61" s="446"/>
-      <c r="H61" s="447"/>
-      <c r="I61" s="447"/>
-      <c r="J61" s="448"/>
-      <c r="K61" s="446"/>
-      <c r="L61" s="447"/>
-      <c r="M61" s="447"/>
-      <c r="N61" s="448"/>
-      <c r="O61" s="437"/>
-      <c r="P61" s="438"/>
-      <c r="Q61" s="438"/>
-      <c r="R61" s="439"/>
-      <c r="S61" s="437"/>
-      <c r="T61" s="438"/>
-      <c r="U61" s="438"/>
-      <c r="V61" s="439"/>
-      <c r="W61" s="437"/>
-      <c r="X61" s="438"/>
-      <c r="Y61" s="438"/>
-      <c r="Z61" s="439"/>
-      <c r="AA61" s="437"/>
-      <c r="AB61" s="438"/>
-      <c r="AC61" s="438"/>
-      <c r="AD61" s="439"/>
+    <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="518"/>
+      <c r="C61" s="519"/>
+      <c r="D61" s="519"/>
+      <c r="E61" s="519"/>
+      <c r="F61" s="520"/>
+      <c r="G61" s="527"/>
+      <c r="H61" s="528"/>
+      <c r="I61" s="528"/>
+      <c r="J61" s="529"/>
+      <c r="K61" s="527"/>
+      <c r="L61" s="528"/>
+      <c r="M61" s="528"/>
+      <c r="N61" s="529"/>
+      <c r="O61" s="505"/>
+      <c r="P61" s="506"/>
+      <c r="Q61" s="506"/>
+      <c r="R61" s="507"/>
+      <c r="S61" s="505"/>
+      <c r="T61" s="506"/>
+      <c r="U61" s="506"/>
+      <c r="V61" s="507"/>
+      <c r="W61" s="505"/>
+      <c r="X61" s="506"/>
+      <c r="Y61" s="506"/>
+      <c r="Z61" s="507"/>
+      <c r="AA61" s="505"/>
+      <c r="AB61" s="506"/>
+      <c r="AC61" s="506"/>
+      <c r="AD61" s="507"/>
     </row>
-    <row r="62" spans="1:54" ht="52.5" customHeight="1">
-      <c r="B62" s="526"/>
-      <c r="C62" s="527"/>
-      <c r="D62" s="527"/>
-      <c r="E62" s="527"/>
-      <c r="F62" s="528"/>
-      <c r="G62" s="446"/>
-      <c r="H62" s="447"/>
-      <c r="I62" s="447"/>
-      <c r="J62" s="448"/>
-      <c r="K62" s="446"/>
-      <c r="L62" s="447"/>
-      <c r="M62" s="447"/>
-      <c r="N62" s="448"/>
-      <c r="O62" s="437"/>
-      <c r="P62" s="438"/>
-      <c r="Q62" s="438"/>
-      <c r="R62" s="439"/>
-      <c r="S62" s="437"/>
-      <c r="T62" s="438"/>
-      <c r="U62" s="438"/>
-      <c r="V62" s="439"/>
-      <c r="W62" s="437"/>
-      <c r="X62" s="438"/>
-      <c r="Y62" s="438"/>
-      <c r="Z62" s="439"/>
-      <c r="AA62" s="437"/>
-      <c r="AB62" s="438"/>
-      <c r="AC62" s="438"/>
-      <c r="AD62" s="439"/>
+    <row r="62" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="518"/>
+      <c r="C62" s="519"/>
+      <c r="D62" s="519"/>
+      <c r="E62" s="519"/>
+      <c r="F62" s="520"/>
+      <c r="G62" s="527"/>
+      <c r="H62" s="528"/>
+      <c r="I62" s="528"/>
+      <c r="J62" s="529"/>
+      <c r="K62" s="527"/>
+      <c r="L62" s="528"/>
+      <c r="M62" s="528"/>
+      <c r="N62" s="529"/>
+      <c r="O62" s="505"/>
+      <c r="P62" s="506"/>
+      <c r="Q62" s="506"/>
+      <c r="R62" s="507"/>
+      <c r="S62" s="505"/>
+      <c r="T62" s="506"/>
+      <c r="U62" s="506"/>
+      <c r="V62" s="507"/>
+      <c r="W62" s="505"/>
+      <c r="X62" s="506"/>
+      <c r="Y62" s="506"/>
+      <c r="Z62" s="507"/>
+      <c r="AA62" s="505"/>
+      <c r="AB62" s="506"/>
+      <c r="AC62" s="506"/>
+      <c r="AD62" s="507"/>
     </row>
-    <row r="63" spans="1:54" ht="15" customHeight="1">
-      <c r="B63" s="526"/>
-      <c r="C63" s="527"/>
-      <c r="D63" s="527"/>
-      <c r="E63" s="527"/>
-      <c r="F63" s="528"/>
-      <c r="G63" s="446"/>
-      <c r="H63" s="447"/>
-      <c r="I63" s="447"/>
-      <c r="J63" s="448"/>
-      <c r="K63" s="446"/>
-      <c r="L63" s="447"/>
-      <c r="M63" s="447"/>
-      <c r="N63" s="448"/>
-      <c r="O63" s="437"/>
-      <c r="P63" s="438"/>
-      <c r="Q63" s="438"/>
-      <c r="R63" s="439"/>
-      <c r="S63" s="437"/>
-      <c r="T63" s="438"/>
-      <c r="U63" s="438"/>
-      <c r="V63" s="439"/>
-      <c r="W63" s="437"/>
-      <c r="X63" s="438"/>
-      <c r="Y63" s="438"/>
-      <c r="Z63" s="439"/>
-      <c r="AA63" s="437"/>
-      <c r="AB63" s="438"/>
-      <c r="AC63" s="438"/>
-      <c r="AD63" s="439"/>
+    <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="518"/>
+      <c r="C63" s="519"/>
+      <c r="D63" s="519"/>
+      <c r="E63" s="519"/>
+      <c r="F63" s="520"/>
+      <c r="G63" s="527"/>
+      <c r="H63" s="528"/>
+      <c r="I63" s="528"/>
+      <c r="J63" s="529"/>
+      <c r="K63" s="527"/>
+      <c r="L63" s="528"/>
+      <c r="M63" s="528"/>
+      <c r="N63" s="529"/>
+      <c r="O63" s="505"/>
+      <c r="P63" s="506"/>
+      <c r="Q63" s="506"/>
+      <c r="R63" s="507"/>
+      <c r="S63" s="505"/>
+      <c r="T63" s="506"/>
+      <c r="U63" s="506"/>
+      <c r="V63" s="507"/>
+      <c r="W63" s="505"/>
+      <c r="X63" s="506"/>
+      <c r="Y63" s="506"/>
+      <c r="Z63" s="507"/>
+      <c r="AA63" s="505"/>
+      <c r="AB63" s="506"/>
+      <c r="AC63" s="506"/>
+      <c r="AD63" s="507"/>
     </row>
-    <row r="64" spans="1:54" ht="15" customHeight="1">
-      <c r="B64" s="526"/>
-      <c r="C64" s="527"/>
-      <c r="D64" s="527"/>
-      <c r="E64" s="527"/>
-      <c r="F64" s="528"/>
-      <c r="G64" s="446"/>
-      <c r="H64" s="447"/>
-      <c r="I64" s="447"/>
-      <c r="J64" s="448"/>
-      <c r="K64" s="446"/>
-      <c r="L64" s="447"/>
-      <c r="M64" s="447"/>
-      <c r="N64" s="448"/>
-      <c r="O64" s="437"/>
-      <c r="P64" s="438"/>
-      <c r="Q64" s="438"/>
-      <c r="R64" s="439"/>
-      <c r="S64" s="437"/>
-      <c r="T64" s="438"/>
-      <c r="U64" s="438"/>
-      <c r="V64" s="439"/>
-      <c r="W64" s="437"/>
-      <c r="X64" s="438"/>
-      <c r="Y64" s="438"/>
-      <c r="Z64" s="439"/>
-      <c r="AA64" s="437"/>
-      <c r="AB64" s="438"/>
-      <c r="AC64" s="438"/>
-      <c r="AD64" s="439"/>
+    <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="518"/>
+      <c r="C64" s="519"/>
+      <c r="D64" s="519"/>
+      <c r="E64" s="519"/>
+      <c r="F64" s="520"/>
+      <c r="G64" s="527"/>
+      <c r="H64" s="528"/>
+      <c r="I64" s="528"/>
+      <c r="J64" s="529"/>
+      <c r="K64" s="527"/>
+      <c r="L64" s="528"/>
+      <c r="M64" s="528"/>
+      <c r="N64" s="529"/>
+      <c r="O64" s="505"/>
+      <c r="P64" s="506"/>
+      <c r="Q64" s="506"/>
+      <c r="R64" s="507"/>
+      <c r="S64" s="505"/>
+      <c r="T64" s="506"/>
+      <c r="U64" s="506"/>
+      <c r="V64" s="507"/>
+      <c r="W64" s="505"/>
+      <c r="X64" s="506"/>
+      <c r="Y64" s="506"/>
+      <c r="Z64" s="507"/>
+      <c r="AA64" s="505"/>
+      <c r="AB64" s="506"/>
+      <c r="AC64" s="506"/>
+      <c r="AD64" s="507"/>
     </row>
-    <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1">
-      <c r="B65" s="526"/>
-      <c r="C65" s="527"/>
-      <c r="D65" s="527"/>
-      <c r="E65" s="527"/>
-      <c r="F65" s="528"/>
-      <c r="G65" s="446"/>
-      <c r="H65" s="447"/>
-      <c r="I65" s="447"/>
-      <c r="J65" s="448"/>
-      <c r="K65" s="446"/>
-      <c r="L65" s="447"/>
-      <c r="M65" s="447"/>
-      <c r="N65" s="448"/>
-      <c r="O65" s="437"/>
-      <c r="P65" s="438"/>
-      <c r="Q65" s="438"/>
-      <c r="R65" s="439"/>
-      <c r="S65" s="437"/>
-      <c r="T65" s="438"/>
-      <c r="U65" s="438"/>
-      <c r="V65" s="439"/>
-      <c r="W65" s="437"/>
-      <c r="X65" s="438"/>
-      <c r="Y65" s="438"/>
-      <c r="Z65" s="439"/>
-      <c r="AA65" s="437"/>
-      <c r="AB65" s="438"/>
-      <c r="AC65" s="438"/>
-      <c r="AD65" s="439"/>
+    <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="518"/>
+      <c r="C65" s="519"/>
+      <c r="D65" s="519"/>
+      <c r="E65" s="519"/>
+      <c r="F65" s="520"/>
+      <c r="G65" s="527"/>
+      <c r="H65" s="528"/>
+      <c r="I65" s="528"/>
+      <c r="J65" s="529"/>
+      <c r="K65" s="527"/>
+      <c r="L65" s="528"/>
+      <c r="M65" s="528"/>
+      <c r="N65" s="529"/>
+      <c r="O65" s="505"/>
+      <c r="P65" s="506"/>
+      <c r="Q65" s="506"/>
+      <c r="R65" s="507"/>
+      <c r="S65" s="505"/>
+      <c r="T65" s="506"/>
+      <c r="U65" s="506"/>
+      <c r="V65" s="507"/>
+      <c r="W65" s="505"/>
+      <c r="X65" s="506"/>
+      <c r="Y65" s="506"/>
+      <c r="Z65" s="507"/>
+      <c r="AA65" s="505"/>
+      <c r="AB65" s="506"/>
+      <c r="AC65" s="506"/>
+      <c r="AD65" s="507"/>
     </row>
-    <row r="66" spans="2:30" ht="15" customHeight="1">
-      <c r="B66" s="526"/>
-      <c r="C66" s="527"/>
-      <c r="D66" s="527"/>
-      <c r="E66" s="527"/>
-      <c r="F66" s="528"/>
-      <c r="G66" s="446"/>
-      <c r="H66" s="447"/>
-      <c r="I66" s="447"/>
-      <c r="J66" s="448"/>
-      <c r="K66" s="446"/>
-      <c r="L66" s="447"/>
-      <c r="M66" s="447"/>
-      <c r="N66" s="448"/>
-      <c r="O66" s="437"/>
-      <c r="P66" s="438"/>
-      <c r="Q66" s="438"/>
-      <c r="R66" s="439"/>
-      <c r="S66" s="437"/>
-      <c r="T66" s="438"/>
-      <c r="U66" s="438"/>
-      <c r="V66" s="439"/>
-      <c r="W66" s="437"/>
-      <c r="X66" s="438"/>
-      <c r="Y66" s="438"/>
-      <c r="Z66" s="439"/>
-      <c r="AA66" s="437"/>
-      <c r="AB66" s="438"/>
-      <c r="AC66" s="438"/>
-      <c r="AD66" s="439"/>
+    <row r="66" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="518"/>
+      <c r="C66" s="519"/>
+      <c r="D66" s="519"/>
+      <c r="E66" s="519"/>
+      <c r="F66" s="520"/>
+      <c r="G66" s="527"/>
+      <c r="H66" s="528"/>
+      <c r="I66" s="528"/>
+      <c r="J66" s="529"/>
+      <c r="K66" s="527"/>
+      <c r="L66" s="528"/>
+      <c r="M66" s="528"/>
+      <c r="N66" s="529"/>
+      <c r="O66" s="505"/>
+      <c r="P66" s="506"/>
+      <c r="Q66" s="506"/>
+      <c r="R66" s="507"/>
+      <c r="S66" s="505"/>
+      <c r="T66" s="506"/>
+      <c r="U66" s="506"/>
+      <c r="V66" s="507"/>
+      <c r="W66" s="505"/>
+      <c r="X66" s="506"/>
+      <c r="Y66" s="506"/>
+      <c r="Z66" s="507"/>
+      <c r="AA66" s="505"/>
+      <c r="AB66" s="506"/>
+      <c r="AC66" s="506"/>
+      <c r="AD66" s="507"/>
     </row>
-    <row r="67" spans="2:30" ht="15" customHeight="1">
-      <c r="B67" s="526"/>
-      <c r="C67" s="527"/>
-      <c r="D67" s="527"/>
-      <c r="E67" s="527"/>
-      <c r="F67" s="528"/>
-      <c r="G67" s="446"/>
-      <c r="H67" s="447"/>
-      <c r="I67" s="447"/>
-      <c r="J67" s="448"/>
-      <c r="K67" s="446"/>
-      <c r="L67" s="447"/>
-      <c r="M67" s="447"/>
-      <c r="N67" s="448"/>
-      <c r="O67" s="437"/>
-      <c r="P67" s="438"/>
-      <c r="Q67" s="438"/>
-      <c r="R67" s="439"/>
-      <c r="S67" s="437"/>
-      <c r="T67" s="438"/>
-      <c r="U67" s="438"/>
-      <c r="V67" s="439"/>
-      <c r="W67" s="437"/>
-      <c r="X67" s="438"/>
-      <c r="Y67" s="438"/>
-      <c r="Z67" s="439"/>
-      <c r="AA67" s="437"/>
-      <c r="AB67" s="438"/>
-      <c r="AC67" s="438"/>
-      <c r="AD67" s="439"/>
+    <row r="67" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="518"/>
+      <c r="C67" s="519"/>
+      <c r="D67" s="519"/>
+      <c r="E67" s="519"/>
+      <c r="F67" s="520"/>
+      <c r="G67" s="527"/>
+      <c r="H67" s="528"/>
+      <c r="I67" s="528"/>
+      <c r="J67" s="529"/>
+      <c r="K67" s="527"/>
+      <c r="L67" s="528"/>
+      <c r="M67" s="528"/>
+      <c r="N67" s="529"/>
+      <c r="O67" s="505"/>
+      <c r="P67" s="506"/>
+      <c r="Q67" s="506"/>
+      <c r="R67" s="507"/>
+      <c r="S67" s="505"/>
+      <c r="T67" s="506"/>
+      <c r="U67" s="506"/>
+      <c r="V67" s="507"/>
+      <c r="W67" s="505"/>
+      <c r="X67" s="506"/>
+      <c r="Y67" s="506"/>
+      <c r="Z67" s="507"/>
+      <c r="AA67" s="505"/>
+      <c r="AB67" s="506"/>
+      <c r="AC67" s="506"/>
+      <c r="AD67" s="507"/>
     </row>
-    <row r="68" spans="2:30" ht="15.75" customHeight="1">
-      <c r="B68" s="526"/>
-      <c r="C68" s="527"/>
-      <c r="D68" s="527"/>
-      <c r="E68" s="527"/>
-      <c r="F68" s="528"/>
-      <c r="G68" s="446"/>
-      <c r="H68" s="447"/>
-      <c r="I68" s="447"/>
-      <c r="J68" s="448"/>
-      <c r="K68" s="446"/>
-      <c r="L68" s="447"/>
-      <c r="M68" s="447"/>
-      <c r="N68" s="448"/>
-      <c r="O68" s="437"/>
-      <c r="P68" s="438"/>
-      <c r="Q68" s="438"/>
-      <c r="R68" s="439"/>
-      <c r="S68" s="437"/>
-      <c r="T68" s="438"/>
-      <c r="U68" s="438"/>
-      <c r="V68" s="439"/>
-      <c r="W68" s="437"/>
-      <c r="X68" s="438"/>
-      <c r="Y68" s="438"/>
-      <c r="Z68" s="439"/>
-      <c r="AA68" s="437"/>
-      <c r="AB68" s="438"/>
-      <c r="AC68" s="438"/>
-      <c r="AD68" s="439"/>
+    <row r="68" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="518"/>
+      <c r="C68" s="519"/>
+      <c r="D68" s="519"/>
+      <c r="E68" s="519"/>
+      <c r="F68" s="520"/>
+      <c r="G68" s="527"/>
+      <c r="H68" s="528"/>
+      <c r="I68" s="528"/>
+      <c r="J68" s="529"/>
+      <c r="K68" s="527"/>
+      <c r="L68" s="528"/>
+      <c r="M68" s="528"/>
+      <c r="N68" s="529"/>
+      <c r="O68" s="505"/>
+      <c r="P68" s="506"/>
+      <c r="Q68" s="506"/>
+      <c r="R68" s="507"/>
+      <c r="S68" s="505"/>
+      <c r="T68" s="506"/>
+      <c r="U68" s="506"/>
+      <c r="V68" s="507"/>
+      <c r="W68" s="505"/>
+      <c r="X68" s="506"/>
+      <c r="Y68" s="506"/>
+      <c r="Z68" s="507"/>
+      <c r="AA68" s="505"/>
+      <c r="AB68" s="506"/>
+      <c r="AC68" s="506"/>
+      <c r="AD68" s="507"/>
     </row>
-    <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B69" s="529"/>
-      <c r="C69" s="530"/>
-      <c r="D69" s="530"/>
-      <c r="E69" s="530"/>
-      <c r="F69" s="531"/>
-      <c r="G69" s="449"/>
-      <c r="H69" s="450"/>
-      <c r="I69" s="450"/>
-      <c r="J69" s="451"/>
-      <c r="K69" s="449"/>
-      <c r="L69" s="450"/>
-      <c r="M69" s="450"/>
-      <c r="N69" s="451"/>
-      <c r="O69" s="440"/>
-      <c r="P69" s="441"/>
-      <c r="Q69" s="441"/>
-      <c r="R69" s="442"/>
-      <c r="S69" s="440"/>
-      <c r="T69" s="441"/>
-      <c r="U69" s="441"/>
-      <c r="V69" s="442"/>
-      <c r="W69" s="440"/>
-      <c r="X69" s="441"/>
-      <c r="Y69" s="441"/>
-      <c r="Z69" s="442"/>
-      <c r="AA69" s="440"/>
-      <c r="AB69" s="441"/>
-      <c r="AC69" s="441"/>
-      <c r="AD69" s="442"/>
+    <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="521"/>
+      <c r="C69" s="522"/>
+      <c r="D69" s="522"/>
+      <c r="E69" s="522"/>
+      <c r="F69" s="523"/>
+      <c r="G69" s="530"/>
+      <c r="H69" s="531"/>
+      <c r="I69" s="531"/>
+      <c r="J69" s="532"/>
+      <c r="K69" s="530"/>
+      <c r="L69" s="531"/>
+      <c r="M69" s="531"/>
+      <c r="N69" s="532"/>
+      <c r="O69" s="508"/>
+      <c r="P69" s="509"/>
+      <c r="Q69" s="509"/>
+      <c r="R69" s="510"/>
+      <c r="S69" s="508"/>
+      <c r="T69" s="509"/>
+      <c r="U69" s="509"/>
+      <c r="V69" s="510"/>
+      <c r="W69" s="508"/>
+      <c r="X69" s="509"/>
+      <c r="Y69" s="509"/>
+      <c r="Z69" s="510"/>
+      <c r="AA69" s="508"/>
+      <c r="AB69" s="509"/>
+      <c r="AC69" s="509"/>
+      <c r="AD69" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -33123,7 +33186,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C108CD-255B-4DDA-A6DD-9C6B6781DBDE}">
   <dimension ref="B1:R50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
@@ -33131,7 +33194,7 @@
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B1" s="2"/>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -33154,7 +33217,7 @@
       <c r="Q1" s="40"/>
       <c r="R1" s="40"/>
     </row>
-    <row r="2" spans="2:18">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
         <v>1</v>
@@ -33174,7 +33237,7 @@
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
     </row>
-    <row r="3" spans="2:18">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -33195,7 +33258,7 @@
       <c r="Q3" s="40"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="2:18" ht="15.75">
+    <row r="4" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -33218,7 +33281,7 @@
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="2:18">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="162"/>
       <c r="C5" s="6" t="s">
         <v>5</v>
@@ -33241,7 +33304,7 @@
       <c r="Q5" s="40"/>
       <c r="R5" s="40"/>
     </row>
-    <row r="6" spans="2:18">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6" s="128"/>
       <c r="C6" s="131" t="s">
         <v>69</v>
@@ -33264,7 +33327,7 @@
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
     </row>
-    <row r="7" spans="2:18">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="152"/>
       <c r="C7" s="131" t="s">
         <v>70</v>
@@ -33272,26 +33335,26 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="532" t="s">
+      <c r="G7" s="542" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="533"/>
-      <c r="I7" s="533"/>
-      <c r="J7" s="534"/>
-      <c r="K7" s="535" t="s">
+      <c r="H7" s="543"/>
+      <c r="I7" s="543"/>
+      <c r="J7" s="544"/>
+      <c r="K7" s="539" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="536"/>
-      <c r="M7" s="536"/>
-      <c r="N7" s="537"/>
-      <c r="O7" s="538" t="s">
+      <c r="L7" s="540"/>
+      <c r="M7" s="540"/>
+      <c r="N7" s="541"/>
+      <c r="O7" s="536" t="s">
         <v>76</v>
       </c>
-      <c r="P7" s="539"/>
-      <c r="Q7" s="539"/>
-      <c r="R7" s="540"/>
+      <c r="P7" s="537"/>
+      <c r="Q7" s="537"/>
+      <c r="R7" s="538"/>
     </row>
-    <row r="8" spans="2:18" ht="15.75" thickBot="1">
+    <row r="8" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="167"/>
       <c r="C8" s="131" t="s">
         <v>71</v>
@@ -33336,7 +33399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="15.75" thickBot="1">
+    <row r="9" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="289" t="s">
         <v>9</v>
       </c>
@@ -33365,7 +33428,7 @@
       <c r="Q9" s="231"/>
       <c r="R9" s="231"/>
     </row>
-    <row r="10" spans="2:18" ht="15.75" thickBot="1">
+    <row r="10" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="141" t="s">
         <v>157</v>
       </c>
@@ -33394,7 +33457,7 @@
       <c r="Q10" s="52"/>
       <c r="R10" s="230"/>
     </row>
-    <row r="11" spans="2:18" ht="45.75" thickBot="1">
+    <row r="11" spans="2:18" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="141" t="s">
         <v>85</v>
       </c>
@@ -33423,7 +33486,7 @@
       <c r="Q11" s="38"/>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="2:18" ht="30.75" thickBot="1">
+    <row r="12" spans="2:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="141" t="s">
         <v>158</v>
       </c>
@@ -33452,7 +33515,7 @@
       <c r="Q12" s="38"/>
       <c r="R12" s="42"/>
     </row>
-    <row r="13" spans="2:18" ht="30.75" thickBot="1">
+    <row r="13" spans="2:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="134" t="s">
         <v>87</v>
       </c>
@@ -33481,8 +33544,8 @@
       <c r="Q13" s="139"/>
       <c r="R13" s="224"/>
     </row>
-    <row r="14" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B14" s="541" t="s">
+    <row r="14" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="549" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="146" t="s">
@@ -33510,8 +33573,8 @@
       <c r="Q14" s="265"/>
       <c r="R14" s="266"/>
     </row>
-    <row r="15" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B15" s="542"/>
+    <row r="15" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="550"/>
       <c r="C15" s="228" t="s">
         <v>93</v>
       </c>
@@ -33537,8 +33600,8 @@
       <c r="Q15" s="149"/>
       <c r="R15" s="267"/>
     </row>
-    <row r="16" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B16" s="541" t="s">
+    <row r="16" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="549" t="s">
         <v>160</v>
       </c>
       <c r="C16" s="263" t="s">
@@ -33566,8 +33629,8 @@
       <c r="Q16" s="148"/>
       <c r="R16" s="264"/>
     </row>
-    <row r="17" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B17" s="543"/>
+    <row r="17" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="551"/>
       <c r="C17" s="296" t="s">
         <v>27</v>
       </c>
@@ -33597,8 +33660,8 @@
       </c>
       <c r="R17" s="271"/>
     </row>
-    <row r="18" spans="2:18">
-      <c r="B18" s="544" t="s">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="552" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="122" t="s">
@@ -33626,8 +33689,8 @@
       <c r="Q18" s="265"/>
       <c r="R18" s="266"/>
     </row>
-    <row r="19" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B19" s="545"/>
+    <row r="19" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="553"/>
       <c r="C19" s="123" t="s">
         <v>38</v>
       </c>
@@ -33655,8 +33718,8 @@
       <c r="Q19" s="265"/>
       <c r="R19" s="266"/>
     </row>
-    <row r="20" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B20" s="544" t="s">
+    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="552" t="s">
         <v>162</v>
       </c>
       <c r="C20" s="119" t="s">
@@ -33684,8 +33747,8 @@
       <c r="Q20" s="148"/>
       <c r="R20" s="264"/>
     </row>
-    <row r="21" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B21" s="545"/>
+    <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="553"/>
       <c r="C21" s="284" t="s">
         <v>44</v>
       </c>
@@ -33711,7 +33774,7 @@
       <c r="Q21" s="274"/>
       <c r="R21" s="275"/>
     </row>
-    <row r="22" spans="2:18" ht="15.75" thickBot="1">
+    <row r="22" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="135" t="s">
         <v>112</v>
       </c>
@@ -33742,8 +33805,8 @@
       <c r="Q22" s="265"/>
       <c r="R22" s="266"/>
     </row>
-    <row r="23" spans="2:18">
-      <c r="B23" s="546" t="s">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23" s="554" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="119" t="s">
@@ -33771,8 +33834,8 @@
       <c r="Q23" s="148"/>
       <c r="R23" s="264"/>
     </row>
-    <row r="24" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B24" s="547"/>
+    <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="555"/>
       <c r="C24" s="124" t="s">
         <v>20</v>
       </c>
@@ -33798,8 +33861,8 @@
       <c r="Q24" s="219"/>
       <c r="R24" s="281"/>
     </row>
-    <row r="25" spans="2:18">
-      <c r="B25" s="541" t="s">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="549" t="s">
         <v>163</v>
       </c>
       <c r="C25" s="119" t="s">
@@ -33827,8 +33890,8 @@
       <c r="Q25" s="22"/>
       <c r="R25" s="23"/>
     </row>
-    <row r="26" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B26" s="542"/>
+    <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="550"/>
       <c r="C26" s="124" t="s">
         <v>113</v>
       </c>
@@ -33854,7 +33917,7 @@
       <c r="Q26" s="16"/>
       <c r="R26" s="24"/>
     </row>
-    <row r="27" spans="2:18" ht="15.75" thickBot="1">
+    <row r="27" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="305" t="s">
         <v>122</v>
       </c>
@@ -33883,7 +33946,7 @@
       <c r="Q27" s="160"/>
       <c r="R27" s="278"/>
     </row>
-    <row r="28" spans="2:18" ht="15.75" thickBot="1">
+    <row r="28" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="307" t="s">
         <v>64</v>
       </c>
@@ -33912,7 +33975,7 @@
       <c r="Q28" s="197"/>
       <c r="R28" s="198"/>
     </row>
-    <row r="29" spans="2:18" ht="15.75" thickBot="1">
+    <row r="29" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="171" t="s">
         <v>27</v>
       </c>
@@ -33941,440 +34004,440 @@
       <c r="Q29" s="173"/>
       <c r="R29" s="312"/>
     </row>
-    <row r="30" spans="2:18" ht="19.5" thickBot="1">
-      <c r="B30" s="494" t="s">
+    <row r="30" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="512" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="495"/>
-      <c r="D30" s="495"/>
-      <c r="E30" s="495"/>
-      <c r="F30" s="495"/>
-      <c r="G30" s="494" t="s">
+      <c r="C30" s="513"/>
+      <c r="D30" s="513"/>
+      <c r="E30" s="513"/>
+      <c r="F30" s="513"/>
+      <c r="G30" s="512" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="495"/>
-      <c r="I30" s="495"/>
+      <c r="H30" s="513"/>
+      <c r="I30" s="513"/>
       <c r="J30" s="548"/>
-      <c r="K30" s="497" t="s">
+      <c r="K30" s="488" t="s">
         <v>135</v>
       </c>
-      <c r="L30" s="498"/>
-      <c r="M30" s="498"/>
-      <c r="N30" s="499"/>
-      <c r="O30" s="497"/>
-      <c r="P30" s="498"/>
-      <c r="Q30" s="498"/>
-      <c r="R30" s="499"/>
+      <c r="L30" s="489"/>
+      <c r="M30" s="489"/>
+      <c r="N30" s="490"/>
+      <c r="O30" s="488"/>
+      <c r="P30" s="489"/>
+      <c r="Q30" s="489"/>
+      <c r="R30" s="490"/>
     </row>
-    <row r="31" spans="2:18" ht="19.5" thickBot="1">
-      <c r="B31" s="500" t="s">
+    <row r="31" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="485" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="501"/>
-      <c r="D31" s="501"/>
-      <c r="E31" s="501"/>
-      <c r="F31" s="501"/>
-      <c r="G31" s="500" t="s">
+      <c r="C31" s="486"/>
+      <c r="D31" s="486"/>
+      <c r="E31" s="486"/>
+      <c r="F31" s="486"/>
+      <c r="G31" s="485" t="s">
         <v>139</v>
       </c>
-      <c r="H31" s="501"/>
-      <c r="I31" s="501"/>
-      <c r="J31" s="549"/>
-      <c r="K31" s="500" t="s">
+      <c r="H31" s="486"/>
+      <c r="I31" s="486"/>
+      <c r="J31" s="556"/>
+      <c r="K31" s="485" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="501"/>
-      <c r="M31" s="501"/>
-      <c r="N31" s="549"/>
-      <c r="O31" s="500" t="s">
+      <c r="L31" s="486"/>
+      <c r="M31" s="486"/>
+      <c r="N31" s="556"/>
+      <c r="O31" s="485" t="s">
         <v>138</v>
       </c>
-      <c r="P31" s="501"/>
-      <c r="Q31" s="501"/>
-      <c r="R31" s="549"/>
+      <c r="P31" s="486"/>
+      <c r="Q31" s="486"/>
+      <c r="R31" s="556"/>
     </row>
-    <row r="32" spans="2:18" ht="19.5" thickBot="1">
-      <c r="B32" s="506" t="s">
+    <row r="32" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="460" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="507"/>
-      <c r="D32" s="507"/>
-      <c r="E32" s="507"/>
-      <c r="F32" s="507"/>
-      <c r="G32" s="506" t="s">
+      <c r="C32" s="461"/>
+      <c r="D32" s="461"/>
+      <c r="E32" s="461"/>
+      <c r="F32" s="461"/>
+      <c r="G32" s="460" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="507"/>
-      <c r="I32" s="507"/>
-      <c r="J32" s="515"/>
-      <c r="K32" s="506" t="s">
+      <c r="H32" s="461"/>
+      <c r="I32" s="461"/>
+      <c r="J32" s="535"/>
+      <c r="K32" s="460" t="s">
         <v>142</v>
       </c>
-      <c r="L32" s="507"/>
-      <c r="M32" s="507"/>
-      <c r="N32" s="515"/>
-      <c r="O32" s="506" t="s">
+      <c r="L32" s="461"/>
+      <c r="M32" s="461"/>
+      <c r="N32" s="535"/>
+      <c r="O32" s="460" t="s">
         <v>142</v>
       </c>
-      <c r="P32" s="507"/>
-      <c r="Q32" s="507"/>
-      <c r="R32" s="515"/>
+      <c r="P32" s="461"/>
+      <c r="Q32" s="461"/>
+      <c r="R32" s="535"/>
     </row>
-    <row r="33" spans="2:18" ht="19.5" thickBot="1">
-      <c r="B33" s="550" t="s">
+    <row r="33" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="545" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="551"/>
-      <c r="D33" s="551"/>
-      <c r="E33" s="551"/>
-      <c r="F33" s="552"/>
-      <c r="G33" s="516" t="s">
+      <c r="C33" s="546"/>
+      <c r="D33" s="546"/>
+      <c r="E33" s="546"/>
+      <c r="F33" s="547"/>
+      <c r="G33" s="463" t="s">
         <v>147</v>
       </c>
-      <c r="H33" s="517"/>
-      <c r="I33" s="517"/>
-      <c r="J33" s="522"/>
-      <c r="K33" s="516" t="s">
+      <c r="H33" s="464"/>
+      <c r="I33" s="464"/>
+      <c r="J33" s="534"/>
+      <c r="K33" s="463" t="s">
         <v>165</v>
       </c>
-      <c r="L33" s="517"/>
-      <c r="M33" s="517"/>
-      <c r="N33" s="522"/>
-      <c r="O33" s="516"/>
-      <c r="P33" s="517"/>
-      <c r="Q33" s="517"/>
-      <c r="R33" s="522"/>
+      <c r="L33" s="464"/>
+      <c r="M33" s="464"/>
+      <c r="N33" s="534"/>
+      <c r="O33" s="463"/>
+      <c r="P33" s="464"/>
+      <c r="Q33" s="464"/>
+      <c r="R33" s="534"/>
     </row>
-    <row r="34" spans="2:18">
-      <c r="B34" s="523" t="s">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B34" s="515" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="524"/>
-      <c r="D34" s="524"/>
-      <c r="E34" s="524"/>
-      <c r="F34" s="525"/>
-      <c r="G34" s="434" t="s">
+      <c r="C34" s="516"/>
+      <c r="D34" s="516"/>
+      <c r="E34" s="516"/>
+      <c r="F34" s="517"/>
+      <c r="G34" s="502" t="s">
         <v>151</v>
       </c>
-      <c r="H34" s="435"/>
-      <c r="I34" s="435"/>
-      <c r="J34" s="436"/>
-      <c r="K34" s="434" t="s">
+      <c r="H34" s="503"/>
+      <c r="I34" s="503"/>
+      <c r="J34" s="504"/>
+      <c r="K34" s="502" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="435"/>
-      <c r="M34" s="435"/>
-      <c r="N34" s="436"/>
-      <c r="O34" s="434" t="s">
+      <c r="L34" s="503"/>
+      <c r="M34" s="503"/>
+      <c r="N34" s="504"/>
+      <c r="O34" s="502" t="s">
         <v>166</v>
       </c>
-      <c r="P34" s="435"/>
-      <c r="Q34" s="435"/>
-      <c r="R34" s="436"/>
+      <c r="P34" s="503"/>
+      <c r="Q34" s="503"/>
+      <c r="R34" s="504"/>
     </row>
-    <row r="35" spans="2:18">
-      <c r="B35" s="526"/>
-      <c r="C35" s="527"/>
-      <c r="D35" s="527"/>
-      <c r="E35" s="527"/>
-      <c r="F35" s="528"/>
-      <c r="G35" s="437"/>
-      <c r="H35" s="438"/>
-      <c r="I35" s="438"/>
-      <c r="J35" s="439"/>
-      <c r="K35" s="437"/>
-      <c r="L35" s="438"/>
-      <c r="M35" s="438"/>
-      <c r="N35" s="439"/>
-      <c r="O35" s="437"/>
-      <c r="P35" s="438"/>
-      <c r="Q35" s="438"/>
-      <c r="R35" s="439"/>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B35" s="518"/>
+      <c r="C35" s="519"/>
+      <c r="D35" s="519"/>
+      <c r="E35" s="519"/>
+      <c r="F35" s="520"/>
+      <c r="G35" s="505"/>
+      <c r="H35" s="506"/>
+      <c r="I35" s="506"/>
+      <c r="J35" s="507"/>
+      <c r="K35" s="505"/>
+      <c r="L35" s="506"/>
+      <c r="M35" s="506"/>
+      <c r="N35" s="507"/>
+      <c r="O35" s="505"/>
+      <c r="P35" s="506"/>
+      <c r="Q35" s="506"/>
+      <c r="R35" s="507"/>
     </row>
-    <row r="36" spans="2:18">
-      <c r="B36" s="526"/>
-      <c r="C36" s="527"/>
-      <c r="D36" s="527"/>
-      <c r="E36" s="527"/>
-      <c r="F36" s="528"/>
-      <c r="G36" s="437"/>
-      <c r="H36" s="438"/>
-      <c r="I36" s="438"/>
-      <c r="J36" s="439"/>
-      <c r="K36" s="437"/>
-      <c r="L36" s="438"/>
-      <c r="M36" s="438"/>
-      <c r="N36" s="439"/>
-      <c r="O36" s="437"/>
-      <c r="P36" s="438"/>
-      <c r="Q36" s="438"/>
-      <c r="R36" s="439"/>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B36" s="518"/>
+      <c r="C36" s="519"/>
+      <c r="D36" s="519"/>
+      <c r="E36" s="519"/>
+      <c r="F36" s="520"/>
+      <c r="G36" s="505"/>
+      <c r="H36" s="506"/>
+      <c r="I36" s="506"/>
+      <c r="J36" s="507"/>
+      <c r="K36" s="505"/>
+      <c r="L36" s="506"/>
+      <c r="M36" s="506"/>
+      <c r="N36" s="507"/>
+      <c r="O36" s="505"/>
+      <c r="P36" s="506"/>
+      <c r="Q36" s="506"/>
+      <c r="R36" s="507"/>
     </row>
-    <row r="37" spans="2:18">
-      <c r="B37" s="526"/>
-      <c r="C37" s="527"/>
-      <c r="D37" s="527"/>
-      <c r="E37" s="527"/>
-      <c r="F37" s="528"/>
-      <c r="G37" s="437"/>
-      <c r="H37" s="438"/>
-      <c r="I37" s="438"/>
-      <c r="J37" s="439"/>
-      <c r="K37" s="437"/>
-      <c r="L37" s="438"/>
-      <c r="M37" s="438"/>
-      <c r="N37" s="439"/>
-      <c r="O37" s="437"/>
-      <c r="P37" s="438"/>
-      <c r="Q37" s="438"/>
-      <c r="R37" s="439"/>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37" s="518"/>
+      <c r="C37" s="519"/>
+      <c r="D37" s="519"/>
+      <c r="E37" s="519"/>
+      <c r="F37" s="520"/>
+      <c r="G37" s="505"/>
+      <c r="H37" s="506"/>
+      <c r="I37" s="506"/>
+      <c r="J37" s="507"/>
+      <c r="K37" s="505"/>
+      <c r="L37" s="506"/>
+      <c r="M37" s="506"/>
+      <c r="N37" s="507"/>
+      <c r="O37" s="505"/>
+      <c r="P37" s="506"/>
+      <c r="Q37" s="506"/>
+      <c r="R37" s="507"/>
     </row>
-    <row r="38" spans="2:18">
-      <c r="B38" s="526"/>
-      <c r="C38" s="527"/>
-      <c r="D38" s="527"/>
-      <c r="E38" s="527"/>
-      <c r="F38" s="528"/>
-      <c r="G38" s="437"/>
-      <c r="H38" s="438"/>
-      <c r="I38" s="438"/>
-      <c r="J38" s="439"/>
-      <c r="K38" s="437"/>
-      <c r="L38" s="438"/>
-      <c r="M38" s="438"/>
-      <c r="N38" s="439"/>
-      <c r="O38" s="437"/>
-      <c r="P38" s="438"/>
-      <c r="Q38" s="438"/>
-      <c r="R38" s="439"/>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B38" s="518"/>
+      <c r="C38" s="519"/>
+      <c r="D38" s="519"/>
+      <c r="E38" s="519"/>
+      <c r="F38" s="520"/>
+      <c r="G38" s="505"/>
+      <c r="H38" s="506"/>
+      <c r="I38" s="506"/>
+      <c r="J38" s="507"/>
+      <c r="K38" s="505"/>
+      <c r="L38" s="506"/>
+      <c r="M38" s="506"/>
+      <c r="N38" s="507"/>
+      <c r="O38" s="505"/>
+      <c r="P38" s="506"/>
+      <c r="Q38" s="506"/>
+      <c r="R38" s="507"/>
     </row>
-    <row r="39" spans="2:18">
-      <c r="B39" s="526"/>
-      <c r="C39" s="527"/>
-      <c r="D39" s="527"/>
-      <c r="E39" s="527"/>
-      <c r="F39" s="528"/>
-      <c r="G39" s="437"/>
-      <c r="H39" s="438"/>
-      <c r="I39" s="438"/>
-      <c r="J39" s="439"/>
-      <c r="K39" s="437"/>
-      <c r="L39" s="438"/>
-      <c r="M39" s="438"/>
-      <c r="N39" s="439"/>
-      <c r="O39" s="437"/>
-      <c r="P39" s="438"/>
-      <c r="Q39" s="438"/>
-      <c r="R39" s="439"/>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B39" s="518"/>
+      <c r="C39" s="519"/>
+      <c r="D39" s="519"/>
+      <c r="E39" s="519"/>
+      <c r="F39" s="520"/>
+      <c r="G39" s="505"/>
+      <c r="H39" s="506"/>
+      <c r="I39" s="506"/>
+      <c r="J39" s="507"/>
+      <c r="K39" s="505"/>
+      <c r="L39" s="506"/>
+      <c r="M39" s="506"/>
+      <c r="N39" s="507"/>
+      <c r="O39" s="505"/>
+      <c r="P39" s="506"/>
+      <c r="Q39" s="506"/>
+      <c r="R39" s="507"/>
     </row>
-    <row r="40" spans="2:18">
-      <c r="B40" s="526"/>
-      <c r="C40" s="527"/>
-      <c r="D40" s="527"/>
-      <c r="E40" s="527"/>
-      <c r="F40" s="528"/>
-      <c r="G40" s="437"/>
-      <c r="H40" s="438"/>
-      <c r="I40" s="438"/>
-      <c r="J40" s="439"/>
-      <c r="K40" s="437"/>
-      <c r="L40" s="438"/>
-      <c r="M40" s="438"/>
-      <c r="N40" s="439"/>
-      <c r="O40" s="437"/>
-      <c r="P40" s="438"/>
-      <c r="Q40" s="438"/>
-      <c r="R40" s="439"/>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B40" s="518"/>
+      <c r="C40" s="519"/>
+      <c r="D40" s="519"/>
+      <c r="E40" s="519"/>
+      <c r="F40" s="520"/>
+      <c r="G40" s="505"/>
+      <c r="H40" s="506"/>
+      <c r="I40" s="506"/>
+      <c r="J40" s="507"/>
+      <c r="K40" s="505"/>
+      <c r="L40" s="506"/>
+      <c r="M40" s="506"/>
+      <c r="N40" s="507"/>
+      <c r="O40" s="505"/>
+      <c r="P40" s="506"/>
+      <c r="Q40" s="506"/>
+      <c r="R40" s="507"/>
     </row>
-    <row r="41" spans="2:18">
-      <c r="B41" s="526"/>
-      <c r="C41" s="527"/>
-      <c r="D41" s="527"/>
-      <c r="E41" s="527"/>
-      <c r="F41" s="528"/>
-      <c r="G41" s="437"/>
-      <c r="H41" s="438"/>
-      <c r="I41" s="438"/>
-      <c r="J41" s="439"/>
-      <c r="K41" s="437"/>
-      <c r="L41" s="438"/>
-      <c r="M41" s="438"/>
-      <c r="N41" s="439"/>
-      <c r="O41" s="437"/>
-      <c r="P41" s="438"/>
-      <c r="Q41" s="438"/>
-      <c r="R41" s="439"/>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B41" s="518"/>
+      <c r="C41" s="519"/>
+      <c r="D41" s="519"/>
+      <c r="E41" s="519"/>
+      <c r="F41" s="520"/>
+      <c r="G41" s="505"/>
+      <c r="H41" s="506"/>
+      <c r="I41" s="506"/>
+      <c r="J41" s="507"/>
+      <c r="K41" s="505"/>
+      <c r="L41" s="506"/>
+      <c r="M41" s="506"/>
+      <c r="N41" s="507"/>
+      <c r="O41" s="505"/>
+      <c r="P41" s="506"/>
+      <c r="Q41" s="506"/>
+      <c r="R41" s="507"/>
     </row>
-    <row r="42" spans="2:18">
-      <c r="B42" s="526"/>
-      <c r="C42" s="527"/>
-      <c r="D42" s="527"/>
-      <c r="E42" s="527"/>
-      <c r="F42" s="528"/>
-      <c r="G42" s="437"/>
-      <c r="H42" s="438"/>
-      <c r="I42" s="438"/>
-      <c r="J42" s="439"/>
-      <c r="K42" s="437"/>
-      <c r="L42" s="438"/>
-      <c r="M42" s="438"/>
-      <c r="N42" s="439"/>
-      <c r="O42" s="437"/>
-      <c r="P42" s="438"/>
-      <c r="Q42" s="438"/>
-      <c r="R42" s="439"/>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B42" s="518"/>
+      <c r="C42" s="519"/>
+      <c r="D42" s="519"/>
+      <c r="E42" s="519"/>
+      <c r="F42" s="520"/>
+      <c r="G42" s="505"/>
+      <c r="H42" s="506"/>
+      <c r="I42" s="506"/>
+      <c r="J42" s="507"/>
+      <c r="K42" s="505"/>
+      <c r="L42" s="506"/>
+      <c r="M42" s="506"/>
+      <c r="N42" s="507"/>
+      <c r="O42" s="505"/>
+      <c r="P42" s="506"/>
+      <c r="Q42" s="506"/>
+      <c r="R42" s="507"/>
     </row>
-    <row r="43" spans="2:18">
-      <c r="B43" s="526"/>
-      <c r="C43" s="527"/>
-      <c r="D43" s="527"/>
-      <c r="E43" s="527"/>
-      <c r="F43" s="528"/>
-      <c r="G43" s="437"/>
-      <c r="H43" s="438"/>
-      <c r="I43" s="438"/>
-      <c r="J43" s="439"/>
-      <c r="K43" s="437"/>
-      <c r="L43" s="438"/>
-      <c r="M43" s="438"/>
-      <c r="N43" s="439"/>
-      <c r="O43" s="437"/>
-      <c r="P43" s="438"/>
-      <c r="Q43" s="438"/>
-      <c r="R43" s="439"/>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B43" s="518"/>
+      <c r="C43" s="519"/>
+      <c r="D43" s="519"/>
+      <c r="E43" s="519"/>
+      <c r="F43" s="520"/>
+      <c r="G43" s="505"/>
+      <c r="H43" s="506"/>
+      <c r="I43" s="506"/>
+      <c r="J43" s="507"/>
+      <c r="K43" s="505"/>
+      <c r="L43" s="506"/>
+      <c r="M43" s="506"/>
+      <c r="N43" s="507"/>
+      <c r="O43" s="505"/>
+      <c r="P43" s="506"/>
+      <c r="Q43" s="506"/>
+      <c r="R43" s="507"/>
     </row>
-    <row r="44" spans="2:18">
-      <c r="B44" s="526"/>
-      <c r="C44" s="527"/>
-      <c r="D44" s="527"/>
-      <c r="E44" s="527"/>
-      <c r="F44" s="528"/>
-      <c r="G44" s="437"/>
-      <c r="H44" s="438"/>
-      <c r="I44" s="438"/>
-      <c r="J44" s="439"/>
-      <c r="K44" s="437"/>
-      <c r="L44" s="438"/>
-      <c r="M44" s="438"/>
-      <c r="N44" s="439"/>
-      <c r="O44" s="437"/>
-      <c r="P44" s="438"/>
-      <c r="Q44" s="438"/>
-      <c r="R44" s="439"/>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B44" s="518"/>
+      <c r="C44" s="519"/>
+      <c r="D44" s="519"/>
+      <c r="E44" s="519"/>
+      <c r="F44" s="520"/>
+      <c r="G44" s="505"/>
+      <c r="H44" s="506"/>
+      <c r="I44" s="506"/>
+      <c r="J44" s="507"/>
+      <c r="K44" s="505"/>
+      <c r="L44" s="506"/>
+      <c r="M44" s="506"/>
+      <c r="N44" s="507"/>
+      <c r="O44" s="505"/>
+      <c r="P44" s="506"/>
+      <c r="Q44" s="506"/>
+      <c r="R44" s="507"/>
     </row>
-    <row r="45" spans="2:18">
-      <c r="B45" s="526"/>
-      <c r="C45" s="527"/>
-      <c r="D45" s="527"/>
-      <c r="E45" s="527"/>
-      <c r="F45" s="528"/>
-      <c r="G45" s="437"/>
-      <c r="H45" s="438"/>
-      <c r="I45" s="438"/>
-      <c r="J45" s="439"/>
-      <c r="K45" s="437"/>
-      <c r="L45" s="438"/>
-      <c r="M45" s="438"/>
-      <c r="N45" s="439"/>
-      <c r="O45" s="437"/>
-      <c r="P45" s="438"/>
-      <c r="Q45" s="438"/>
-      <c r="R45" s="439"/>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B45" s="518"/>
+      <c r="C45" s="519"/>
+      <c r="D45" s="519"/>
+      <c r="E45" s="519"/>
+      <c r="F45" s="520"/>
+      <c r="G45" s="505"/>
+      <c r="H45" s="506"/>
+      <c r="I45" s="506"/>
+      <c r="J45" s="507"/>
+      <c r="K45" s="505"/>
+      <c r="L45" s="506"/>
+      <c r="M45" s="506"/>
+      <c r="N45" s="507"/>
+      <c r="O45" s="505"/>
+      <c r="P45" s="506"/>
+      <c r="Q45" s="506"/>
+      <c r="R45" s="507"/>
     </row>
-    <row r="46" spans="2:18">
-      <c r="B46" s="526"/>
-      <c r="C46" s="527"/>
-      <c r="D46" s="527"/>
-      <c r="E46" s="527"/>
-      <c r="F46" s="528"/>
-      <c r="G46" s="437"/>
-      <c r="H46" s="438"/>
-      <c r="I46" s="438"/>
-      <c r="J46" s="439"/>
-      <c r="K46" s="437"/>
-      <c r="L46" s="438"/>
-      <c r="M46" s="438"/>
-      <c r="N46" s="439"/>
-      <c r="O46" s="437"/>
-      <c r="P46" s="438"/>
-      <c r="Q46" s="438"/>
-      <c r="R46" s="439"/>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B46" s="518"/>
+      <c r="C46" s="519"/>
+      <c r="D46" s="519"/>
+      <c r="E46" s="519"/>
+      <c r="F46" s="520"/>
+      <c r="G46" s="505"/>
+      <c r="H46" s="506"/>
+      <c r="I46" s="506"/>
+      <c r="J46" s="507"/>
+      <c r="K46" s="505"/>
+      <c r="L46" s="506"/>
+      <c r="M46" s="506"/>
+      <c r="N46" s="507"/>
+      <c r="O46" s="505"/>
+      <c r="P46" s="506"/>
+      <c r="Q46" s="506"/>
+      <c r="R46" s="507"/>
     </row>
-    <row r="47" spans="2:18">
-      <c r="B47" s="526"/>
-      <c r="C47" s="527"/>
-      <c r="D47" s="527"/>
-      <c r="E47" s="527"/>
-      <c r="F47" s="528"/>
-      <c r="G47" s="437"/>
-      <c r="H47" s="438"/>
-      <c r="I47" s="438"/>
-      <c r="J47" s="439"/>
-      <c r="K47" s="437"/>
-      <c r="L47" s="438"/>
-      <c r="M47" s="438"/>
-      <c r="N47" s="439"/>
-      <c r="O47" s="437"/>
-      <c r="P47" s="438"/>
-      <c r="Q47" s="438"/>
-      <c r="R47" s="439"/>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="518"/>
+      <c r="C47" s="519"/>
+      <c r="D47" s="519"/>
+      <c r="E47" s="519"/>
+      <c r="F47" s="520"/>
+      <c r="G47" s="505"/>
+      <c r="H47" s="506"/>
+      <c r="I47" s="506"/>
+      <c r="J47" s="507"/>
+      <c r="K47" s="505"/>
+      <c r="L47" s="506"/>
+      <c r="M47" s="506"/>
+      <c r="N47" s="507"/>
+      <c r="O47" s="505"/>
+      <c r="P47" s="506"/>
+      <c r="Q47" s="506"/>
+      <c r="R47" s="507"/>
     </row>
-    <row r="48" spans="2:18">
-      <c r="B48" s="526"/>
-      <c r="C48" s="527"/>
-      <c r="D48" s="527"/>
-      <c r="E48" s="527"/>
-      <c r="F48" s="528"/>
-      <c r="G48" s="437"/>
-      <c r="H48" s="438"/>
-      <c r="I48" s="438"/>
-      <c r="J48" s="439"/>
-      <c r="K48" s="437"/>
-      <c r="L48" s="438"/>
-      <c r="M48" s="438"/>
-      <c r="N48" s="439"/>
-      <c r="O48" s="437"/>
-      <c r="P48" s="438"/>
-      <c r="Q48" s="438"/>
-      <c r="R48" s="439"/>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B48" s="518"/>
+      <c r="C48" s="519"/>
+      <c r="D48" s="519"/>
+      <c r="E48" s="519"/>
+      <c r="F48" s="520"/>
+      <c r="G48" s="505"/>
+      <c r="H48" s="506"/>
+      <c r="I48" s="506"/>
+      <c r="J48" s="507"/>
+      <c r="K48" s="505"/>
+      <c r="L48" s="506"/>
+      <c r="M48" s="506"/>
+      <c r="N48" s="507"/>
+      <c r="O48" s="505"/>
+      <c r="P48" s="506"/>
+      <c r="Q48" s="506"/>
+      <c r="R48" s="507"/>
     </row>
-    <row r="49" spans="2:18">
-      <c r="B49" s="526"/>
-      <c r="C49" s="527"/>
-      <c r="D49" s="527"/>
-      <c r="E49" s="527"/>
-      <c r="F49" s="528"/>
-      <c r="G49" s="437"/>
-      <c r="H49" s="438"/>
-      <c r="I49" s="438"/>
-      <c r="J49" s="439"/>
-      <c r="K49" s="437"/>
-      <c r="L49" s="438"/>
-      <c r="M49" s="438"/>
-      <c r="N49" s="439"/>
-      <c r="O49" s="437"/>
-      <c r="P49" s="438"/>
-      <c r="Q49" s="438"/>
-      <c r="R49" s="439"/>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B49" s="518"/>
+      <c r="C49" s="519"/>
+      <c r="D49" s="519"/>
+      <c r="E49" s="519"/>
+      <c r="F49" s="520"/>
+      <c r="G49" s="505"/>
+      <c r="H49" s="506"/>
+      <c r="I49" s="506"/>
+      <c r="J49" s="507"/>
+      <c r="K49" s="505"/>
+      <c r="L49" s="506"/>
+      <c r="M49" s="506"/>
+      <c r="N49" s="507"/>
+      <c r="O49" s="505"/>
+      <c r="P49" s="506"/>
+      <c r="Q49" s="506"/>
+      <c r="R49" s="507"/>
     </row>
-    <row r="50" spans="2:18" ht="15.75" thickBot="1">
-      <c r="B50" s="529"/>
-      <c r="C50" s="530"/>
-      <c r="D50" s="530"/>
-      <c r="E50" s="530"/>
-      <c r="F50" s="531"/>
-      <c r="G50" s="440"/>
-      <c r="H50" s="441"/>
-      <c r="I50" s="441"/>
-      <c r="J50" s="442"/>
-      <c r="K50" s="440"/>
-      <c r="L50" s="441"/>
-      <c r="M50" s="441"/>
-      <c r="N50" s="442"/>
-      <c r="O50" s="440"/>
-      <c r="P50" s="441"/>
-      <c r="Q50" s="441"/>
-      <c r="R50" s="442"/>
+    <row r="50" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="521"/>
+      <c r="C50" s="522"/>
+      <c r="D50" s="522"/>
+      <c r="E50" s="522"/>
+      <c r="F50" s="523"/>
+      <c r="G50" s="508"/>
+      <c r="H50" s="509"/>
+      <c r="I50" s="509"/>
+      <c r="J50" s="510"/>
+      <c r="K50" s="508"/>
+      <c r="L50" s="509"/>
+      <c r="M50" s="509"/>
+      <c r="N50" s="510"/>
+      <c r="O50" s="508"/>
+      <c r="P50" s="509"/>
+      <c r="Q50" s="509"/>
+      <c r="R50" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -34416,7 +34479,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9880F104-7035-43DA-B153-19B04B138594}">
   <dimension ref="D6:J15"/>
-  <sheetFormatPr defaultRowHeight="50.45" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="50.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17.125" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
@@ -34426,12 +34489,12 @@
     <col min="10" max="10" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="6" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E6" s="318" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="7" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="319" t="s">
         <v>168</v>
       </c>
@@ -34454,7 +34517,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="8" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="320" t="s">
         <v>175</v>
       </c>
@@ -34477,7 +34540,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="9" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="320" t="s">
         <v>182</v>
       </c>
@@ -34500,7 +34563,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="10" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D10" s="320" t="s">
         <v>187</v>
       </c>
@@ -34523,7 +34586,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="11" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="320" t="s">
         <v>193</v>
       </c>
@@ -34546,7 +34609,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="12" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="320" t="s">
         <v>198</v>
       </c>
@@ -34569,7 +34632,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="13" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="13" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="320" t="s">
         <v>205</v>
       </c>
@@ -34592,7 +34655,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="14" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D14" s="320" t="s">
         <v>210</v>
       </c>
@@ -34615,7 +34678,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="4:10" ht="50.45" customHeight="1" thickBot="1">
+    <row r="15" spans="4:10" ht="50.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D15" s="320" t="s">
         <v>217</v>
       </c>
@@ -34646,8 +34709,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
   <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:Y164"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15"/>
+  <dimension ref="A1:Y167"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="1" bestFit="1" customWidth="1"/>
@@ -34662,7 +34725,7 @@
     <col min="11" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57" customHeight="1" thickBot="1">
+    <row r="1" spans="1:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="257" t="s">
         <v>223</v>
       </c>
@@ -34694,7 +34757,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="2" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="236" t="s">
         <v>231</v>
       </c>
@@ -34728,7 +34791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="3" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="237" t="s">
         <v>231</v>
       </c>
@@ -34762,7 +34825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="4" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="249" t="s">
         <v>231</v>
       </c>
@@ -34796,7 +34859,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="5" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="236" t="s">
         <v>231</v>
       </c>
@@ -34830,7 +34893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="6" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="236" t="s">
         <v>231</v>
       </c>
@@ -34864,7 +34927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="7" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="236" t="s">
         <v>231</v>
       </c>
@@ -34898,7 +34961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="8" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="250" t="s">
         <v>231</v>
       </c>
@@ -34932,7 +34995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="9" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="235" t="s">
         <v>231</v>
       </c>
@@ -34966,7 +35029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="10" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="236" t="s">
         <v>231</v>
       </c>
@@ -35000,7 +35063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="11" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="237" t="s">
         <v>231</v>
       </c>
@@ -35034,7 +35097,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="249" t="s">
         <v>231</v>
       </c>
@@ -35068,7 +35131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="13" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="236" t="s">
         <v>231</v>
       </c>
@@ -35102,7 +35165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="236" t="s">
         <v>231</v>
       </c>
@@ -35136,7 +35199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="15" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="236" t="s">
         <v>231</v>
       </c>
@@ -35170,7 +35233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="236" t="s">
         <v>231</v>
       </c>
@@ -35204,7 +35267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="17" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="236" t="s">
         <v>231</v>
       </c>
@@ -35238,7 +35301,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="18" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="331" t="s">
         <v>231</v>
       </c>
@@ -35272,7 +35335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="19" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="262" t="s">
         <v>231</v>
       </c>
@@ -35306,7 +35369,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="20" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="249" t="s">
         <v>231</v>
       </c>
@@ -35340,7 +35403,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="21" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="236" t="s">
         <v>231</v>
       </c>
@@ -35374,7 +35437,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="236" t="s">
         <v>231</v>
       </c>
@@ -35408,7 +35471,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="23" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="236" t="s">
         <v>231</v>
       </c>
@@ -35442,7 +35505,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="24" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="236" t="s">
         <v>231</v>
       </c>
@@ -35476,7 +35539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="25" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="236" t="s">
         <v>231</v>
       </c>
@@ -35510,7 +35573,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="255" customFormat="1" ht="19.899999999999999" hidden="1" customHeight="1" thickBot="1">
+    <row r="26" spans="1:10" s="255" customFormat="1" ht="19.899999999999999" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="237" t="s">
         <v>231</v>
       </c>
@@ -35544,7 +35607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="27" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="235" t="s">
         <v>231</v>
       </c>
@@ -35578,7 +35641,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="28" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="236" t="s">
         <v>231</v>
       </c>
@@ -35612,7 +35675,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="29" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="236" t="s">
         <v>231</v>
       </c>
@@ -35646,7 +35709,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="30" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="236" t="s">
         <v>231</v>
       </c>
@@ -35680,7 +35743,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="31" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="236" t="s">
         <v>231</v>
       </c>
@@ -35714,7 +35777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.9" hidden="1" customHeight="1">
+    <row r="32" spans="1:10" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="236" t="s">
         <v>231</v>
       </c>
@@ -35748,7 +35811,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="33" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="236" t="s">
         <v>231</v>
       </c>
@@ -35782,7 +35845,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="34" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="237" t="s">
         <v>231</v>
       </c>
@@ -35816,7 +35879,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="35" spans="1:10" s="182" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="254" t="s">
         <v>231</v>
       </c>
@@ -35850,7 +35913,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="36" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="246" t="s">
         <v>231</v>
       </c>
@@ -35884,7 +35947,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="37" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="246" t="s">
         <v>231</v>
       </c>
@@ -35918,7 +35981,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="38" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="212" t="s">
         <v>231</v>
       </c>
@@ -35952,109 +36015,109 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="255" customFormat="1">
-      <c r="A39" s="262" t="s">
+    <row r="39" spans="1:10" s="255" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="427" t="s">
         <v>278</v>
       </c>
-      <c r="B39" s="189" t="s">
+      <c r="B39" s="428" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="122" t="s">
+      <c r="C39" s="409" t="s">
         <v>273</v>
       </c>
-      <c r="D39" s="410" t="s">
+      <c r="D39" s="409" t="s">
         <v>279</v>
       </c>
-      <c r="E39" s="239">
-        <v>46185</v>
-      </c>
-      <c r="F39" s="188">
-        <v>46187.125</v>
-      </c>
-      <c r="G39" s="188">
-        <f t="shared" si="2"/>
-        <v>46189.125</v>
-      </c>
-      <c r="H39" s="189">
+      <c r="E39" s="429">
+        <v>46194</v>
+      </c>
+      <c r="F39" s="430">
+        <v>46196.6875</v>
+      </c>
+      <c r="G39" s="430">
+        <f>F39+(H39/24)</f>
+        <v>46198.6875</v>
+      </c>
+      <c r="H39" s="428">
         <v>48</v>
       </c>
-      <c r="I39" s="188">
-        <f t="shared" si="3"/>
-        <v>46191.125</v>
-      </c>
-      <c r="J39" s="190">
+      <c r="I39" s="430">
+        <f>G39+(J39/24)</f>
+        <v>46200.6875</v>
+      </c>
+      <c r="J39" s="431">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="182" customFormat="1">
+    <row r="40" spans="1:10" s="182" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="379" t="s">
         <v>278</v>
       </c>
       <c r="B40" s="243" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="244" t="s">
         <v>273</v>
       </c>
       <c r="D40" s="244" t="s">
         <v>280</v>
       </c>
-      <c r="E40" s="54">
-        <v>46189</v>
-      </c>
-      <c r="F40" s="180">
-        <v>46190.25</v>
+      <c r="E40" s="424">
+        <v>46182</v>
+      </c>
+      <c r="F40" s="245">
+        <v>46185</v>
       </c>
       <c r="G40" s="245">
         <f>F40+(H40/24)</f>
-        <v>46190.5</v>
-      </c>
-      <c r="H40" s="32">
+        <v>46185.25</v>
+      </c>
+      <c r="H40" s="243">
         <v>6</v>
       </c>
       <c r="I40" s="245">
         <f>G40+(J40/24)</f>
-        <v>46192.5</v>
-      </c>
-      <c r="J40" s="126">
+        <v>46187.25</v>
+      </c>
+      <c r="J40" s="432">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="182" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A41" s="408" t="s">
+    <row r="41" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="409" t="s">
+      <c r="B41" s="189" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="212" t="s">
+      <c r="C41" s="122" t="s">
         <v>273</v>
       </c>
-      <c r="D41" s="411" t="s">
-        <v>281</v>
-      </c>
-      <c r="E41" s="241">
-        <v>46187</v>
-      </c>
-      <c r="F41" s="213">
-        <v>46190.375</v>
-      </c>
-      <c r="G41" s="339">
+      <c r="D41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="239">
+        <v>46191</v>
+      </c>
+      <c r="F41" s="188">
+        <v>46193.708333333336</v>
+      </c>
+      <c r="G41" s="188">
         <f>F41+(H41/24)</f>
-        <v>46192.375</v>
-      </c>
-      <c r="H41" s="214">
+        <v>46196.708333333336</v>
+      </c>
+      <c r="H41" s="189">
+        <v>72</v>
+      </c>
+      <c r="I41" s="188">
+        <f>G41+(J41/24)</f>
+        <v>46198.708333333336</v>
+      </c>
+      <c r="J41" s="190">
         <v>48</v>
       </c>
-      <c r="I41" s="339">
-        <f>G41+(J41/24)</f>
-        <v>46194.375</v>
-      </c>
-      <c r="J41" s="215">
-        <v>48</v>
-      </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="262" t="s">
         <v>278</v>
       </c>
@@ -36062,33 +36125,33 @@
         <v>160</v>
       </c>
       <c r="C42" s="122" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" s="122" t="s">
         <v>282</v>
       </c>
-      <c r="D42" s="122" t="s">
-        <v>283</v>
-      </c>
       <c r="E42" s="239">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="F42" s="188">
-        <v>46198.3125</v>
+        <v>46207.875</v>
       </c>
       <c r="G42" s="188">
         <f t="shared" si="2"/>
-        <v>46201.3125</v>
+        <v>46210.875</v>
       </c>
       <c r="H42" s="189">
         <v>72</v>
       </c>
       <c r="I42" s="188">
         <f t="shared" si="3"/>
-        <v>46203.3125</v>
+        <v>46212.875</v>
       </c>
       <c r="J42" s="190">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="246" t="s">
         <v>278</v>
       </c>
@@ -36096,33 +36159,33 @@
         <v>160</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E43" s="54">
-        <v>46198</v>
+        <v>46208</v>
       </c>
       <c r="F43" s="180">
-        <v>46200.947916666664</v>
+        <v>46210.510416666664</v>
       </c>
       <c r="G43" s="180">
         <f t="shared" si="2"/>
-        <v>46202.947916666664</v>
+        <v>46212.510416666664</v>
       </c>
       <c r="H43" s="32">
         <v>48</v>
       </c>
       <c r="I43" s="180">
         <f t="shared" si="3"/>
-        <v>46204.947916666664</v>
+        <v>46214.510416666664</v>
       </c>
       <c r="J43" s="126">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="246" t="s">
         <v>278</v>
       </c>
@@ -36130,33 +36193,33 @@
         <v>160</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E44" s="54">
-        <v>46204</v>
+        <v>46214</v>
       </c>
       <c r="F44" s="180">
-        <v>46207.572916666664</v>
+        <v>46217.135416666664</v>
       </c>
       <c r="G44" s="180">
         <f t="shared" si="2"/>
-        <v>46210.572916666664</v>
+        <v>46220.135416666664</v>
       </c>
       <c r="H44" s="32">
         <v>72</v>
       </c>
       <c r="I44" s="180">
         <f t="shared" si="3"/>
-        <v>46212.572916666664</v>
+        <v>46222.135416666664</v>
       </c>
       <c r="J44" s="126">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="246" t="s">
         <v>278</v>
       </c>
@@ -36164,33 +36227,33 @@
         <v>160</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D45" s="244" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E45" s="54">
-        <v>46208</v>
+        <v>46218</v>
       </c>
       <c r="F45" s="180">
-        <v>46212.229166666664</v>
+        <v>46221.791666666664</v>
       </c>
       <c r="G45" s="180">
         <f t="shared" si="2"/>
-        <v>46213.229166666664</v>
+        <v>46222.791666666664</v>
       </c>
       <c r="H45" s="32">
         <v>24</v>
       </c>
       <c r="I45" s="180">
         <f t="shared" si="3"/>
-        <v>46215.229166666664</v>
+        <v>46224.791666666664</v>
       </c>
       <c r="J45" s="126">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="246" t="s">
         <v>278</v>
       </c>
@@ -36198,33 +36261,33 @@
         <v>160</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E46" s="54">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="F46" s="180">
-        <v>46216.927083333336</v>
+        <v>46226.489583333336</v>
       </c>
       <c r="G46" s="180">
         <f t="shared" si="2"/>
-        <v>46221.927083333336</v>
+        <v>46231.489583333336</v>
       </c>
       <c r="H46" s="32">
         <v>120</v>
       </c>
       <c r="I46" s="180">
         <f t="shared" si="3"/>
-        <v>46223.927083333336</v>
+        <v>46233.489583333336</v>
       </c>
       <c r="J46" s="126">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="246" t="s">
         <v>278</v>
       </c>
@@ -36232,33 +36295,33 @@
         <v>160</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E47" s="54">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="F47" s="180">
-        <v>46219.927083333336</v>
+        <v>46229.489583333336</v>
       </c>
       <c r="G47" s="180">
         <f t="shared" si="2"/>
-        <v>46221.927083333336</v>
+        <v>46231.489583333336</v>
       </c>
       <c r="H47" s="32">
         <v>48</v>
       </c>
       <c r="I47" s="180">
         <f t="shared" si="3"/>
-        <v>46223.927083333336</v>
+        <v>46233.489583333336</v>
       </c>
       <c r="J47" s="126">
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1">
+    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="247" t="s">
         <v>278</v>
       </c>
@@ -36266,33 +36329,33 @@
         <v>160</v>
       </c>
       <c r="C48" s="123" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D48" s="402" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E48" s="240">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="F48" s="183">
-        <v>46223.927083333336</v>
+        <v>46233.489583333336</v>
       </c>
       <c r="G48" s="183">
         <f t="shared" si="2"/>
-        <v>46225.927083333336</v>
+        <v>46235.489583333336</v>
       </c>
       <c r="H48" s="184">
         <v>48</v>
       </c>
       <c r="I48" s="183">
         <f t="shared" si="3"/>
-        <v>46227.927083333336</v>
+        <v>46237.489583333336</v>
       </c>
       <c r="J48" s="127">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="249" t="s">
         <v>231</v>
       </c>
@@ -36300,10 +36363,10 @@
         <v>161</v>
       </c>
       <c r="C49" s="187" t="s">
+        <v>289</v>
+      </c>
+      <c r="D49" s="187" t="s">
         <v>290</v>
-      </c>
-      <c r="D49" s="187" t="s">
-        <v>291</v>
       </c>
       <c r="E49" s="242">
         <v>46046</v>
@@ -36326,7 +36389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="249" t="s">
         <v>231</v>
       </c>
@@ -36334,10 +36397,10 @@
         <v>161</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E50" s="54">
         <v>46052</v>
@@ -36360,7 +36423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="249" t="s">
         <v>231</v>
       </c>
@@ -36368,10 +36431,10 @@
         <v>161</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E51" s="54">
         <v>46053</v>
@@ -36394,7 +36457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="249" t="s">
         <v>231</v>
       </c>
@@ -36402,10 +36465,10 @@
         <v>161</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E52" s="54">
         <v>46057</v>
@@ -36428,7 +36491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="249" t="s">
         <v>231</v>
       </c>
@@ -36436,10 +36499,10 @@
         <v>161</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E53" s="54">
         <v>46062</v>
@@ -36462,7 +36525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="249" t="s">
         <v>231</v>
       </c>
@@ -36470,10 +36533,10 @@
         <v>161</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E54" s="8">
         <v>46068</v>
@@ -36496,7 +36559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="249" t="s">
         <v>231</v>
       </c>
@@ -36504,10 +36567,10 @@
         <v>161</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E55" s="54">
         <v>46072</v>
@@ -36530,7 +36593,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="249" t="s">
         <v>231</v>
       </c>
@@ -36538,10 +36601,10 @@
         <v>161</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E56" s="54">
         <v>46074</v>
@@ -36564,7 +36627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="249" t="s">
         <v>231</v>
       </c>
@@ -36572,10 +36635,10 @@
         <v>161</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E57" s="54">
         <v>46079</v>
@@ -36598,7 +36661,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="255" customFormat="1" hidden="1">
+    <row r="58" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="261" t="s">
         <v>231</v>
       </c>
@@ -36606,10 +36669,10 @@
         <v>161</v>
       </c>
       <c r="C58" s="212" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D58" s="212" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E58" s="241">
         <v>46081</v>
@@ -36632,7 +36695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="235" t="s">
         <v>231</v>
       </c>
@@ -36640,10 +36703,10 @@
         <v>161</v>
       </c>
       <c r="C59" s="122" t="s">
+        <v>300</v>
+      </c>
+      <c r="D59" s="122" t="s">
         <v>301</v>
-      </c>
-      <c r="D59" s="122" t="s">
-        <v>302</v>
       </c>
       <c r="E59" s="239">
         <v>46084</v>
@@ -36666,7 +36729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="236" t="s">
         <v>231</v>
       </c>
@@ -36674,10 +36737,10 @@
         <v>161</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E60" s="54">
         <v>46089</v>
@@ -36700,7 +36763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="236" t="s">
         <v>231</v>
       </c>
@@ -36708,10 +36771,10 @@
         <v>161</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E61" s="54">
         <v>46092</v>
@@ -36734,7 +36797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="236" t="s">
         <v>231</v>
       </c>
@@ -36742,10 +36805,10 @@
         <v>161</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D62" s="251" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E62" s="54">
         <v>46099</v>
@@ -36768,7 +36831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="63" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="237" t="s">
         <v>231</v>
       </c>
@@ -36776,10 +36839,10 @@
         <v>161</v>
       </c>
       <c r="C63" s="123" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D63" s="123" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E63" s="240">
         <v>46103</v>
@@ -36802,7 +36865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="254" t="s">
         <v>231</v>
       </c>
@@ -36810,10 +36873,10 @@
         <v>161</v>
       </c>
       <c r="C64" s="187" t="s">
+        <v>306</v>
+      </c>
+      <c r="D64" s="187" t="s">
         <v>307</v>
-      </c>
-      <c r="D64" s="187" t="s">
-        <v>308</v>
       </c>
       <c r="E64" s="242">
         <v>46109</v>
@@ -36836,7 +36899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="65" spans="1:10" s="255" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="247" t="s">
         <v>231</v>
       </c>
@@ -36844,10 +36907,10 @@
         <v>161</v>
       </c>
       <c r="C65" s="123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D65" s="123" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E65" s="240">
         <v>46112</v>
@@ -36870,18 +36933,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.9" hidden="1" customHeight="1">
+    <row r="66" spans="1:10" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="249" t="s">
         <v>231</v>
       </c>
       <c r="B66" s="209" t="s">
+        <v>309</v>
+      </c>
+      <c r="C66" s="187" t="s">
         <v>310</v>
       </c>
-      <c r="C66" s="187" t="s">
+      <c r="D66" s="187" t="s">
         <v>311</v>
-      </c>
-      <c r="D66" s="187" t="s">
-        <v>312</v>
       </c>
       <c r="E66" s="242">
         <v>46045</v>
@@ -36904,18 +36967,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B67" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D67" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E67" s="54">
         <v>46060</v>
@@ -36938,18 +37001,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B68" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D68" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E68" s="54">
         <v>46068</v>
@@ -36972,18 +37035,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B69" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D69" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E69" s="54">
         <v>46052</v>
@@ -37006,18 +37069,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B70" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D70" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E70" s="54">
         <v>46055</v>
@@ -37040,18 +37103,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B71" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D71" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E71" s="54">
         <v>46059</v>
@@ -37074,18 +37137,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="195" customFormat="1" ht="20.45" hidden="1" customHeight="1">
+    <row r="72" spans="1:10" s="195" customFormat="1" ht="20.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B72" s="208" t="s">
+        <v>309</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="D72" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E72" s="54">
         <v>46072</v>
@@ -37108,18 +37171,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="255" customFormat="1" hidden="1">
+    <row r="73" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="250" t="s">
         <v>231</v>
       </c>
       <c r="B73" s="252" t="s">
+        <v>309</v>
+      </c>
+      <c r="C73" s="253" t="s">
         <v>310</v>
       </c>
-      <c r="C73" s="253" t="s">
-        <v>311</v>
-      </c>
       <c r="D73" s="212" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E73" s="241">
         <v>46073</v>
@@ -37142,18 +37205,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="235" t="s">
         <v>231</v>
       </c>
       <c r="B74" s="189" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C74" s="122" t="s">
+        <v>319</v>
+      </c>
+      <c r="D74" s="122" t="s">
         <v>320</v>
-      </c>
-      <c r="D74" s="122" t="s">
-        <v>321</v>
       </c>
       <c r="E74" s="239">
         <v>46065</v>
@@ -37176,18 +37239,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E75" s="54">
         <v>46066</v>
@@ -37210,18 +37273,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E76" s="54">
         <v>46069</v>
@@ -37244,18 +37307,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E77" s="54">
         <v>46070</v>
@@ -37278,18 +37341,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E78" s="54">
         <v>46071</v>
@@ -37312,18 +37375,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E79" s="54">
         <v>46077</v>
@@ -37346,18 +37409,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E80" s="54">
         <v>46085</v>
@@ -37380,18 +37443,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E81" s="54">
         <v>46085</v>
@@ -37414,18 +37477,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E82" s="54">
         <v>46088</v>
@@ -37448,18 +37511,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E83" s="54">
         <v>46095</v>
@@ -37482,18 +37545,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E84" s="54">
         <v>46099</v>
@@ -37516,18 +37579,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E85" s="54">
         <v>46099</v>
@@ -37550,18 +37613,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E86" s="54">
         <v>46112</v>
@@ -37584,18 +37647,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E87" s="54">
         <v>46120</v>
@@ -37618,18 +37681,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E88" s="54">
         <v>46125</v>
@@ -37652,18 +37715,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="236" t="s">
         <v>231</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D89" s="185" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E89" s="8">
         <v>46131</v>
@@ -37686,18 +37749,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="250" t="s">
         <v>231</v>
       </c>
       <c r="B90" s="214" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C90" s="212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D90" s="212" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E90" s="241">
         <v>46139</v>
@@ -37720,18 +37783,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="235" t="s">
         <v>231</v>
       </c>
       <c r="B91" s="189" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C91" s="122" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D91" s="122" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E91" s="239">
         <v>46142</v>
@@ -37754,18 +37817,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="255" customFormat="1" hidden="1">
+    <row r="92" spans="1:10" s="255" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="235" t="s">
         <v>231</v>
       </c>
       <c r="B92" s="214" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C92" s="212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D92" s="212" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E92" s="241">
         <v>46151</v>
@@ -37788,18 +37851,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="262" t="s">
         <v>231</v>
       </c>
       <c r="B93" s="189" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C93" s="122" t="s">
+        <v>339</v>
+      </c>
+      <c r="D93" s="122" t="s">
         <v>340</v>
-      </c>
-      <c r="D93" s="122" t="s">
-        <v>341</v>
       </c>
       <c r="E93" s="239">
         <v>46154</v>
@@ -37822,18 +37885,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="246" t="s">
         <v>231</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E94" s="54">
         <v>46162</v>
@@ -37856,18 +37919,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="246" t="s">
         <v>231</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E95" s="54">
         <v>46163</v>
@@ -37890,18 +37953,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="246" t="s">
         <v>231</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E96" s="54">
         <v>46173</v>
@@ -37924,211 +37987,211 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="30.75" thickBot="1">
+    <row r="97" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D97" s="396" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E97" s="54">
         <v>46183</v>
       </c>
       <c r="F97" s="180">
-        <v>46185.479166666664</v>
+        <v>46185.729166666664</v>
       </c>
       <c r="G97" s="180">
         <f t="shared" si="4"/>
-        <v>46187.479166666664</v>
+        <v>46187.729166666664</v>
       </c>
       <c r="H97" s="32">
         <v>48</v>
       </c>
       <c r="I97" s="180">
         <f t="shared" si="5"/>
-        <v>46187.854166666664</v>
+        <v>46188.104166666664</v>
       </c>
       <c r="J97" s="126">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="262" t="s">
         <v>278</v>
       </c>
       <c r="B98" s="189" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C98" s="122" t="s">
+        <v>345</v>
+      </c>
+      <c r="D98" s="122" t="s">
         <v>346</v>
-      </c>
-      <c r="D98" s="122" t="s">
-        <v>347</v>
       </c>
       <c r="E98" s="239">
         <v>46190</v>
       </c>
       <c r="F98" s="188">
-        <v>46192.364583333336</v>
+        <v>46192.791666666664</v>
       </c>
       <c r="G98" s="188">
         <f t="shared" si="4"/>
-        <v>46193.864583333336</v>
+        <v>46194.291666666664</v>
       </c>
       <c r="H98" s="189">
         <v>36</v>
       </c>
       <c r="I98" s="188">
         <f t="shared" si="5"/>
-        <v>46194.65625</v>
+        <v>46195.083333333328</v>
       </c>
       <c r="J98" s="190">
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E99" s="54">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="F99" s="180">
-        <v>46203.28125</v>
+        <v>46203.708333333336</v>
       </c>
       <c r="G99" s="180">
         <f t="shared" si="4"/>
-        <v>46205.78125</v>
+        <v>46206.208333333336</v>
       </c>
       <c r="H99" s="32">
         <v>60</v>
       </c>
       <c r="I99" s="180">
         <f t="shared" si="5"/>
-        <v>46206.572916666664</v>
+        <v>46207</v>
       </c>
       <c r="J99" s="126">
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E100" s="54">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F100" s="180">
-        <v>46208.864583333336</v>
+        <v>46209.291666666664</v>
       </c>
       <c r="G100" s="180">
         <f t="shared" ref="G100:G130" si="6">F100+(H100/24)</f>
-        <v>46210.864583333336</v>
+        <v>46211.291666666664</v>
       </c>
       <c r="H100" s="32">
         <v>48</v>
       </c>
       <c r="I100" s="180">
         <f t="shared" ref="I100:I120" si="7">G100+(J100/24)</f>
-        <v>46211.65625</v>
+        <v>46212.083333333328</v>
       </c>
       <c r="J100" s="126">
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E101" s="54">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="F101" s="213">
-        <v>46212.864583333336</v>
+        <v>46213.291666666664</v>
       </c>
       <c r="G101" s="180">
         <f t="shared" si="6"/>
-        <v>46214.114583333336</v>
+        <v>46214.541666666664</v>
       </c>
       <c r="H101" s="214">
         <v>30</v>
       </c>
       <c r="I101" s="180">
         <f t="shared" si="7"/>
-        <v>46214.90625</v>
+        <v>46215.333333333328</v>
       </c>
       <c r="J101" s="215">
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15.75" thickBot="1">
+    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="247" t="s">
         <v>278</v>
       </c>
       <c r="B102" s="184" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C102" s="123" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D102" s="123" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E102" s="240">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F102" s="183">
-        <v>46220.677083333336</v>
+        <v>46221.104166666664</v>
       </c>
       <c r="G102" s="183">
         <f t="shared" si="6"/>
-        <v>46222.177083333336</v>
+        <v>46222.604166666664</v>
       </c>
       <c r="H102" s="184">
         <v>36</v>
       </c>
       <c r="I102" s="183">
         <f t="shared" si="7"/>
-        <v>46222.96875</v>
+        <v>46223.395833333328</v>
       </c>
       <c r="J102" s="127">
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="103" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="249" t="s">
         <v>231</v>
       </c>
@@ -38136,10 +38199,10 @@
         <v>64</v>
       </c>
       <c r="C103" s="335" t="s">
+        <v>351</v>
+      </c>
+      <c r="D103" s="187" t="s">
         <v>352</v>
-      </c>
-      <c r="D103" s="187" t="s">
-        <v>353</v>
       </c>
       <c r="E103" s="242">
         <v>46095</v>
@@ -38162,7 +38225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="104" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="236" t="s">
         <v>231</v>
       </c>
@@ -38170,10 +38233,10 @@
         <v>64</v>
       </c>
       <c r="C104" s="244" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E104" s="54">
         <v>46097</v>
@@ -38196,7 +38259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="105" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="236" t="s">
         <v>231</v>
       </c>
@@ -38204,10 +38267,10 @@
         <v>64</v>
       </c>
       <c r="C105" s="244" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E105" s="54">
         <v>46101</v>
@@ -38230,7 +38293,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="106" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="237" t="s">
         <v>231</v>
       </c>
@@ -38238,10 +38301,10 @@
         <v>64</v>
       </c>
       <c r="C106" s="204" t="s">
+        <v>355</v>
+      </c>
+      <c r="D106" s="123" t="s">
         <v>356</v>
-      </c>
-      <c r="D106" s="123" t="s">
-        <v>357</v>
       </c>
       <c r="E106" s="240">
         <v>46112</v>
@@ -38264,7 +38327,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="107" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="235" t="s">
         <v>231</v>
       </c>
@@ -38272,10 +38335,10 @@
         <v>64</v>
       </c>
       <c r="C107" s="202" t="s">
+        <v>357</v>
+      </c>
+      <c r="D107" s="122" t="s">
         <v>358</v>
-      </c>
-      <c r="D107" s="122" t="s">
-        <v>359</v>
       </c>
       <c r="E107" s="239">
         <v>46124</v>
@@ -38298,7 +38361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="108" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="250" t="s">
         <v>231</v>
       </c>
@@ -38306,10 +38369,10 @@
         <v>64</v>
       </c>
       <c r="C108" s="338" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D108" s="212" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E108" s="241">
         <v>46108</v>
@@ -38332,7 +38395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="109" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="343" t="s">
         <v>231</v>
       </c>
@@ -38340,10 +38403,10 @@
         <v>64</v>
       </c>
       <c r="C109" s="345" t="s">
+        <v>360</v>
+      </c>
+      <c r="D109" s="345" t="s">
         <v>361</v>
-      </c>
-      <c r="D109" s="345" t="s">
-        <v>362</v>
       </c>
       <c r="E109" s="346">
         <v>46142</v>
@@ -38366,18 +38429,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.75" thickBot="1">
+    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="384" t="s">
         <v>278</v>
       </c>
       <c r="B110" s="385" t="s">
+        <v>362</v>
+      </c>
+      <c r="C110" s="386" t="s">
         <v>363</v>
       </c>
-      <c r="C110" s="386" t="s">
+      <c r="D110" s="386" t="s">
         <v>364</v>
-      </c>
-      <c r="D110" s="386" t="s">
-        <v>365</v>
       </c>
       <c r="E110" s="387">
         <v>46216</v>
@@ -38400,18 +38463,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="262" t="s">
         <v>278</v>
       </c>
       <c r="B111" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C111" s="122" t="s">
+        <v>365</v>
+      </c>
+      <c r="D111" s="122" t="s">
         <v>366</v>
-      </c>
-      <c r="D111" s="122" t="s">
-        <v>367</v>
       </c>
       <c r="E111" s="239">
         <v>46220</v>
@@ -38434,18 +38497,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E112" s="54">
         <v>46224</v>
@@ -38468,18 +38531,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E113" s="54">
         <v>46226</v>
@@ -38505,18 +38568,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="246" t="s">
         <v>278</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E114" s="54">
         <v>46228</v>
@@ -38539,18 +38602,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="15.75" thickBot="1">
+    <row r="115" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="331" t="s">
         <v>278</v>
       </c>
       <c r="B115" s="214" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C115" s="212" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D115" s="212" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E115" s="241">
         <v>46229</v>
@@ -38573,18 +38636,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="262" t="s">
         <v>278</v>
       </c>
       <c r="B116" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C116" s="122" t="s">
+        <v>371</v>
+      </c>
+      <c r="D116" s="122" t="s">
         <v>372</v>
-      </c>
-      <c r="D116" s="122" t="s">
-        <v>373</v>
       </c>
       <c r="E116" s="239">
         <v>46232</v>
@@ -38607,18 +38670,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="15.75" thickBot="1">
+    <row r="117" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="331" t="s">
         <v>278</v>
       </c>
       <c r="B117" s="214" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C117" s="212" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D117" s="212" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E117" s="241">
         <v>46241</v>
@@ -38641,18 +38704,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="15.75" thickBot="1">
+    <row r="118" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="384" t="s">
         <v>278</v>
       </c>
       <c r="B118" s="385" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C118" s="386" t="s">
+        <v>374</v>
+      </c>
+      <c r="D118" s="386" t="s">
         <v>375</v>
-      </c>
-      <c r="D118" s="386" t="s">
-        <v>376</v>
       </c>
       <c r="E118" s="387">
         <v>46246</v>
@@ -38675,7 +38738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="15.75" hidden="1" thickBot="1">
+    <row r="119" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="262" t="s">
         <v>231</v>
       </c>
@@ -38683,10 +38746,10 @@
         <v>122</v>
       </c>
       <c r="C119" s="122" t="s">
+        <v>376</v>
+      </c>
+      <c r="D119" s="411" t="s">
         <v>377</v>
-      </c>
-      <c r="D119" s="412" t="s">
-        <v>378</v>
       </c>
       <c r="E119" s="239">
         <v>46159</v>
@@ -38709,7 +38772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:25" s="395" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="120" spans="1:25" s="395" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="246" t="s">
         <v>231</v>
       </c>
@@ -38717,10 +38780,10 @@
         <v>122</v>
       </c>
       <c r="C120" s="392" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D120" s="392" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E120" s="393">
         <v>46162</v>
@@ -38739,11 +38802,11 @@
         <f t="shared" si="7"/>
         <v>46167.666666666664</v>
       </c>
-      <c r="J120" s="413">
+      <c r="J120" s="412">
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="15.75" hidden="1" thickBot="1">
+    <row r="121" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="246" t="s">
         <v>231</v>
       </c>
@@ -38751,10 +38814,10 @@
         <v>122</v>
       </c>
       <c r="C121" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D121" s="390" t="s">
         <v>380</v>
-      </c>
-      <c r="D121" s="390" t="s">
-        <v>381</v>
       </c>
       <c r="E121" s="54">
         <v>46168</v>
@@ -38776,7 +38839,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="15.75" hidden="1" thickBot="1">
+    <row r="122" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="331" t="s">
         <v>231</v>
       </c>
@@ -38784,10 +38847,10 @@
         <v>122</v>
       </c>
       <c r="C122" s="212" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D122" s="253" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E122" s="241">
         <v>46170</v>
@@ -38812,7 +38875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="262" t="s">
         <v>278</v>
       </c>
@@ -38820,10 +38883,10 @@
         <v>163</v>
       </c>
       <c r="C123" s="122" t="s">
+        <v>382</v>
+      </c>
+      <c r="D123" s="122" t="s">
         <v>383</v>
-      </c>
-      <c r="D123" s="122" t="s">
-        <v>384</v>
       </c>
       <c r="E123" s="239">
         <v>46193</v>
@@ -38846,7 +38909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="262" t="s">
         <v>278</v>
       </c>
@@ -38854,10 +38917,10 @@
         <v>163</v>
       </c>
       <c r="C124" s="122" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D124" s="123" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E124" s="240">
         <v>46195</v>
@@ -38880,7 +38943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="262" t="s">
         <v>278</v>
       </c>
@@ -38888,25 +38951,25 @@
         <v>163</v>
       </c>
       <c r="C125" s="122" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D125" s="345" t="s">
-        <v>386</v>
-      </c>
-      <c r="E125" s="422">
+        <v>385</v>
+      </c>
+      <c r="E125" s="421">
         <v>46200</v>
       </c>
-      <c r="F125" s="423">
+      <c r="F125" s="422">
         <v>46201.375</v>
       </c>
-      <c r="G125" s="423">
+      <c r="G125" s="422">
         <f>F125+(H125/24)</f>
         <v>46204.875</v>
       </c>
       <c r="H125" s="344">
         <v>84</v>
       </c>
-      <c r="I125" s="423">
+      <c r="I125" s="422">
         <f>G125+(J125/24)</f>
         <v>46205.375</v>
       </c>
@@ -38914,7 +38977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="262" t="s">
         <v>278</v>
       </c>
@@ -38922,10 +38985,10 @@
         <v>163</v>
       </c>
       <c r="C126" s="122" t="s">
+        <v>386</v>
+      </c>
+      <c r="D126" s="420" t="s">
         <v>387</v>
-      </c>
-      <c r="D126" s="421" t="s">
-        <v>388</v>
       </c>
       <c r="E126" s="406">
         <v>46202</v>
@@ -38933,14 +38996,14 @@
       <c r="F126" s="407">
         <v>46203.5625</v>
       </c>
-      <c r="G126" s="423">
+      <c r="G126" s="422">
         <f t="shared" ref="G126:G129" si="11">F126+(H126/24)</f>
         <v>46205.0625</v>
       </c>
       <c r="H126" s="404">
         <v>36</v>
       </c>
-      <c r="I126" s="423">
+      <c r="I126" s="422">
         <f t="shared" ref="I126:I129" si="12">G126+(J126/24)</f>
         <v>46205.5625</v>
       </c>
@@ -38948,7 +39011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="30.75">
+    <row r="127" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="262" t="s">
         <v>278</v>
       </c>
@@ -38956,10 +39019,10 @@
         <v>163</v>
       </c>
       <c r="C127" s="122" t="s">
-        <v>387</v>
-      </c>
-      <c r="D127" s="458" t="s">
-        <v>389</v>
+        <v>386</v>
+      </c>
+      <c r="D127" s="426" t="s">
+        <v>388</v>
       </c>
       <c r="E127" s="239">
         <v>46208</v>
@@ -38967,14 +39030,14 @@
       <c r="F127" s="188">
         <v>46209.791666666664</v>
       </c>
-      <c r="G127" s="423">
+      <c r="G127" s="422">
         <f t="shared" si="11"/>
         <v>46211.291666666664</v>
       </c>
       <c r="H127" s="189">
         <v>36</v>
       </c>
-      <c r="I127" s="423">
+      <c r="I127" s="422">
         <f t="shared" si="12"/>
         <v>46211.791666666664</v>
       </c>
@@ -38982,7 +39045,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="262" t="s">
         <v>278</v>
       </c>
@@ -38990,10 +39053,10 @@
         <v>163</v>
       </c>
       <c r="C128" s="122" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D128" s="122" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E128" s="239">
         <v>46213</v>
@@ -39001,14 +39064,14 @@
       <c r="F128" s="188">
         <v>46214</v>
       </c>
-      <c r="G128" s="423">
+      <c r="G128" s="422">
         <f t="shared" si="11"/>
         <v>46215.5</v>
       </c>
       <c r="H128" s="189">
         <v>36</v>
       </c>
-      <c r="I128" s="423">
+      <c r="I128" s="422">
         <f t="shared" si="12"/>
         <v>46216</v>
       </c>
@@ -39016,7 +39079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="30.75">
+    <row r="129" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="262" t="s">
         <v>278</v>
       </c>
@@ -39024,10 +39087,10 @@
         <v>163</v>
       </c>
       <c r="C129" s="122" t="s">
-        <v>387</v>
-      </c>
-      <c r="D129" s="458" t="s">
-        <v>391</v>
+        <v>386</v>
+      </c>
+      <c r="D129" s="426" t="s">
+        <v>390</v>
       </c>
       <c r="E129" s="239">
         <v>46217</v>
@@ -39035,14 +39098,14 @@
       <c r="F129" s="188">
         <v>46218.875</v>
       </c>
-      <c r="G129" s="423">
+      <c r="G129" s="422">
         <f t="shared" si="11"/>
         <v>46220.375</v>
       </c>
       <c r="H129" s="189">
         <v>36</v>
       </c>
-      <c r="I129" s="423">
+      <c r="I129" s="422">
         <f t="shared" si="12"/>
         <v>46220.875</v>
       </c>
@@ -39050,41 +39113,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" hidden="1" thickBot="1">
-      <c r="A130" s="415" t="s">
+    <row r="130" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="414" t="s">
         <v>231</v>
       </c>
-      <c r="B130" s="416" t="s">
+      <c r="B130" s="415" t="s">
         <v>64</v>
       </c>
-      <c r="C130" s="417" t="s">
+      <c r="C130" s="416" t="s">
+        <v>391</v>
+      </c>
+      <c r="D130" s="416" t="s">
         <v>392</v>
       </c>
-      <c r="D130" s="417" t="s">
-        <v>393</v>
-      </c>
-      <c r="E130" s="418">
+      <c r="E130" s="417">
         <v>46162</v>
       </c>
-      <c r="F130" s="418">
+      <c r="F130" s="417">
         <v>46164</v>
       </c>
-      <c r="G130" s="419">
+      <c r="G130" s="418">
         <f t="shared" si="6"/>
         <v>46164.416666666664</v>
       </c>
-      <c r="H130" s="416">
+      <c r="H130" s="415">
         <v>10</v>
       </c>
-      <c r="I130" s="419">
+      <c r="I130" s="418">
         <f t="shared" si="8"/>
         <v>46164.833333333328</v>
       </c>
-      <c r="J130" s="420">
+      <c r="J130" s="419">
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="131" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="380" t="s">
         <v>231</v>
       </c>
@@ -39092,10 +39155,10 @@
         <v>64</v>
       </c>
       <c r="C131" s="349" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D131" s="349" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E131" s="351">
         <v>46163</v>
@@ -39118,7 +39181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="132" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="380" t="s">
         <v>231</v>
       </c>
@@ -39126,10 +39189,10 @@
         <v>64</v>
       </c>
       <c r="C132" s="353" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D132" s="185" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E132" s="355">
         <v>46166</v>
@@ -39152,7 +39215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.75" hidden="1" thickBot="1">
+    <row r="133" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="380" t="s">
         <v>231</v>
       </c>
@@ -39160,10 +39223,10 @@
         <v>64</v>
       </c>
       <c r="C133" s="353" t="s">
-        <v>392</v>
-      </c>
-      <c r="D133" s="414" t="s">
-        <v>396</v>
+        <v>391</v>
+      </c>
+      <c r="D133" s="413" t="s">
+        <v>395</v>
       </c>
       <c r="E133" s="355">
         <v>46170</v>
@@ -39186,18 +39249,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="383" t="s">
         <v>278</v>
       </c>
       <c r="B134" s="404" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" s="383" t="s">
         <v>397</v>
       </c>
-      <c r="C134" s="383" t="s">
+      <c r="D134" s="420" t="s">
         <v>398</v>
-      </c>
-      <c r="D134" s="421" t="s">
-        <v>399</v>
       </c>
       <c r="E134" s="406">
         <v>46261</v>
@@ -39220,7 +39283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="262" t="s">
         <v>278</v>
       </c>
@@ -39228,33 +39291,33 @@
         <v>232</v>
       </c>
       <c r="C135" s="122" t="s">
+        <v>399</v>
+      </c>
+      <c r="D135" s="405" t="s">
         <v>400</v>
       </c>
-      <c r="D135" s="405" t="s">
-        <v>401</v>
-      </c>
       <c r="E135" s="239">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="F135" s="188">
-        <v>46187.635416666664</v>
+        <v>46188.739583333336</v>
       </c>
       <c r="G135" s="188">
         <f t="shared" si="13"/>
-        <v>46189.135416666664</v>
+        <v>46190.239583333336</v>
       </c>
       <c r="H135" s="189">
         <v>36</v>
       </c>
       <c r="I135" s="188">
         <f t="shared" si="8"/>
-        <v>46189.802083333328</v>
+        <v>46190.90625</v>
       </c>
       <c r="J135" s="190">
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="246" t="s">
         <v>278</v>
       </c>
@@ -39262,33 +39325,33 @@
         <v>232</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D136" s="397" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E136" s="54">
         <v>46187</v>
       </c>
       <c r="F136" s="180">
-        <v>46189.489583333336</v>
+        <v>46189.34375</v>
       </c>
       <c r="G136" s="180">
         <f t="shared" si="13"/>
-        <v>46190.489583333336</v>
+        <v>46190.34375</v>
       </c>
       <c r="H136" s="32">
         <v>24</v>
       </c>
       <c r="I136" s="180">
         <f t="shared" si="8"/>
-        <v>46191.15625</v>
+        <v>46191.010416666664</v>
       </c>
       <c r="J136" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="246" t="s">
         <v>278</v>
       </c>
@@ -39296,33 +39359,33 @@
         <v>232</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D137" s="392" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E137" s="393">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="F137" s="394">
-        <v>46192.84375</v>
+        <v>46192.697916666664</v>
       </c>
       <c r="G137" s="394">
         <f t="shared" si="13"/>
-        <v>46194.34375</v>
+        <v>46194.197916666664</v>
       </c>
       <c r="H137" s="391">
         <v>36</v>
       </c>
       <c r="I137" s="394">
         <f t="shared" si="8"/>
-        <v>46195.010416666664</v>
+        <v>46194.864583333328</v>
       </c>
       <c r="J137" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="246" t="s">
         <v>278</v>
       </c>
@@ -39330,33 +39393,33 @@
         <v>232</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D138" s="392" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E138" s="54">
         <v>46191</v>
       </c>
       <c r="F138" s="180">
-        <v>46194.239583333336</v>
+        <v>46194.09375</v>
       </c>
       <c r="G138" s="180">
         <f t="shared" si="13"/>
-        <v>46196.239583333336</v>
+        <v>46196.09375</v>
       </c>
       <c r="H138" s="32">
         <v>48</v>
       </c>
       <c r="I138" s="180">
         <f t="shared" si="8"/>
-        <v>46196.90625</v>
+        <v>46196.760416666664</v>
       </c>
       <c r="J138" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="246" t="s">
         <v>278</v>
       </c>
@@ -39364,33 +39427,33 @@
         <v>232</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D139" s="392" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E139" s="54">
         <v>46196</v>
       </c>
       <c r="F139" s="180">
-        <v>46198.552083333336</v>
+        <v>46198.40625</v>
       </c>
       <c r="G139" s="180">
         <f t="shared" si="13"/>
-        <v>46199.552083333336</v>
+        <v>46199.40625</v>
       </c>
       <c r="H139" s="32">
         <v>24</v>
       </c>
       <c r="I139" s="180">
         <f t="shared" si="8"/>
-        <v>46200.21875</v>
+        <v>46200.072916666664</v>
       </c>
       <c r="J139" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="246" t="s">
         <v>278</v>
       </c>
@@ -39398,33 +39461,33 @@
         <v>232</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D140" s="397" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E140" s="54">
         <v>46207</v>
       </c>
       <c r="F140" s="180">
-        <v>46209.181944444441</v>
+        <v>46209.036111111112</v>
       </c>
       <c r="G140" s="180">
         <f t="shared" si="13"/>
-        <v>46210.181944444441</v>
+        <v>46210.036111111112</v>
       </c>
       <c r="H140" s="32">
         <v>24</v>
       </c>
       <c r="I140" s="180">
         <f t="shared" si="8"/>
-        <v>46210.848611111105</v>
+        <v>46210.702777777777</v>
       </c>
       <c r="J140" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="379" t="s">
         <v>278</v>
       </c>
@@ -39432,33 +39495,33 @@
         <v>232</v>
       </c>
       <c r="C141" s="244" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D141" s="397" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E141" s="54">
         <v>46209</v>
       </c>
       <c r="F141" s="180">
-        <v>46211.181944444441</v>
+        <v>46211.036111111112</v>
       </c>
       <c r="G141" s="245">
         <f>F141+(H141/24)</f>
-        <v>46212.181944444441</v>
+        <v>46212.036111111112</v>
       </c>
       <c r="H141" s="32">
         <v>24</v>
       </c>
       <c r="I141" s="245">
         <f>G141+(J141/24)</f>
-        <v>46212.848611111105</v>
+        <v>46212.702777777777</v>
       </c>
       <c r="J141" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.75" thickBot="1">
+    <row r="142" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="400" t="s">
         <v>278</v>
       </c>
@@ -39466,33 +39529,33 @@
         <v>232</v>
       </c>
       <c r="C142" s="402" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D142" s="403" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E142" s="240">
         <v>46217</v>
       </c>
       <c r="F142" s="183">
-        <v>46219.837500000001</v>
+        <v>46219.691666666666</v>
       </c>
       <c r="G142" s="205">
         <f>F142+(H142/24)</f>
-        <v>46220.837500000001</v>
+        <v>46220.691666666666</v>
       </c>
       <c r="H142" s="184">
         <v>24</v>
       </c>
       <c r="I142" s="205">
         <f>G142+(J142/24)</f>
-        <v>46221.504166666666</v>
+        <v>46221.35833333333</v>
       </c>
       <c r="J142" s="127">
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="187" t="s">
         <v>278</v>
       </c>
@@ -39500,10 +39563,10 @@
         <v>64</v>
       </c>
       <c r="C143" s="187" t="s">
+        <v>408</v>
+      </c>
+      <c r="D143" s="398" t="s">
         <v>409</v>
-      </c>
-      <c r="D143" s="398" t="s">
-        <v>410</v>
       </c>
       <c r="E143" s="242">
         <v>46193</v>
@@ -39520,13 +39583,13 @@
       </c>
       <c r="I143" s="181">
         <f>G143+(J143/24)</f>
-        <v>46197.75</v>
+        <v>46197.5</v>
       </c>
       <c r="J143" s="399">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="335" t="s">
         <v>278</v>
       </c>
@@ -39534,10 +39597,10 @@
         <v>20</v>
       </c>
       <c r="C144" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D144" s="423" t="s">
         <v>411</v>
-      </c>
-      <c r="D144" s="424" t="s">
-        <v>412</v>
       </c>
       <c r="E144" s="54">
         <v>46191</v>
@@ -39560,7 +39623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="335" t="s">
         <v>278</v>
       </c>
@@ -39568,10 +39631,10 @@
         <v>20</v>
       </c>
       <c r="C145" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D145" s="390" t="s">
         <v>413</v>
-      </c>
-      <c r="D145" s="390" t="s">
-        <v>414</v>
       </c>
       <c r="E145" s="54">
         <v>46930</v>
@@ -39594,7 +39657,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="335" t="s">
         <v>278</v>
       </c>
@@ -39602,10 +39665,10 @@
         <v>20</v>
       </c>
       <c r="C146" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D146" s="423" t="s">
         <v>415</v>
-      </c>
-      <c r="D146" s="424" t="s">
-        <v>416</v>
       </c>
       <c r="E146" s="54">
         <v>46186</v>
@@ -39628,7 +39691,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="335" t="s">
         <v>278</v>
       </c>
@@ -39636,12 +39699,12 @@
         <v>20</v>
       </c>
       <c r="C147" s="244" t="s">
-        <v>415</v>
-      </c>
-      <c r="D147" s="424" t="s">
-        <v>417</v>
-      </c>
-      <c r="E147" s="425">
+        <v>414</v>
+      </c>
+      <c r="D147" s="423" t="s">
+        <v>416</v>
+      </c>
+      <c r="E147" s="424">
         <v>46327</v>
       </c>
       <c r="F147" s="336">
@@ -39661,23 +39724,23 @@
       <c r="J147" s="243">
         <v>36</v>
       </c>
-      <c r="K147" s="426"/>
-      <c r="L147" s="426"/>
-      <c r="M147" s="426"/>
-      <c r="N147" s="426"/>
-      <c r="O147" s="426"/>
-      <c r="P147" s="426"/>
-      <c r="Q147" s="426"/>
-      <c r="R147" s="426"/>
-      <c r="S147" s="426"/>
-      <c r="T147" s="426"/>
-      <c r="U147" s="426"/>
-      <c r="V147" s="426"/>
-      <c r="W147" s="426"/>
-      <c r="X147" s="426"/>
-      <c r="Y147" s="426"/>
+      <c r="K147" s="425"/>
+      <c r="L147" s="425"/>
+      <c r="M147" s="425"/>
+      <c r="N147" s="425"/>
+      <c r="O147" s="425"/>
+      <c r="P147" s="425"/>
+      <c r="Q147" s="425"/>
+      <c r="R147" s="425"/>
+      <c r="S147" s="425"/>
+      <c r="T147" s="425"/>
+      <c r="U147" s="425"/>
+      <c r="V147" s="425"/>
+      <c r="W147" s="425"/>
+      <c r="X147" s="425"/>
+      <c r="Y147" s="425"/>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="335" t="s">
         <v>278</v>
       </c>
@@ -39685,12 +39748,12 @@
         <v>20</v>
       </c>
       <c r="C148" s="244" t="s">
-        <v>415</v>
-      </c>
-      <c r="D148" s="424" t="s">
-        <v>418</v>
-      </c>
-      <c r="E148" s="425">
+        <v>414</v>
+      </c>
+      <c r="D148" s="423" t="s">
+        <v>417</v>
+      </c>
+      <c r="E148" s="424">
         <v>46334</v>
       </c>
       <c r="F148" s="336">
@@ -39710,23 +39773,23 @@
       <c r="J148" s="243">
         <v>36</v>
       </c>
-      <c r="K148" s="426"/>
-      <c r="L148" s="426"/>
-      <c r="M148" s="426"/>
-      <c r="N148" s="426"/>
-      <c r="O148" s="426"/>
-      <c r="P148" s="426"/>
-      <c r="Q148" s="426"/>
-      <c r="R148" s="426"/>
-      <c r="S148" s="426"/>
-      <c r="T148" s="426"/>
-      <c r="U148" s="426"/>
-      <c r="V148" s="426"/>
-      <c r="W148" s="426"/>
-      <c r="X148" s="426"/>
-      <c r="Y148" s="426"/>
+      <c r="K148" s="425"/>
+      <c r="L148" s="425"/>
+      <c r="M148" s="425"/>
+      <c r="N148" s="425"/>
+      <c r="O148" s="425"/>
+      <c r="P148" s="425"/>
+      <c r="Q148" s="425"/>
+      <c r="R148" s="425"/>
+      <c r="S148" s="425"/>
+      <c r="T148" s="425"/>
+      <c r="U148" s="425"/>
+      <c r="V148" s="425"/>
+      <c r="W148" s="425"/>
+      <c r="X148" s="425"/>
+      <c r="Y148" s="425"/>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="335" t="s">
         <v>278</v>
       </c>
@@ -39734,12 +39797,12 @@
         <v>20</v>
       </c>
       <c r="C149" s="244" t="s">
-        <v>415</v>
-      </c>
-      <c r="D149" s="424" t="s">
-        <v>419</v>
-      </c>
-      <c r="E149" s="425">
+        <v>414</v>
+      </c>
+      <c r="D149" s="423" t="s">
+        <v>418</v>
+      </c>
+      <c r="E149" s="424">
         <v>46341</v>
       </c>
       <c r="F149" s="336">
@@ -39759,23 +39822,23 @@
       <c r="J149" s="243">
         <v>36</v>
       </c>
-      <c r="K149" s="426"/>
-      <c r="L149" s="426"/>
-      <c r="M149" s="426"/>
-      <c r="N149" s="426"/>
-      <c r="O149" s="426"/>
-      <c r="P149" s="426"/>
-      <c r="Q149" s="426"/>
-      <c r="R149" s="426"/>
-      <c r="S149" s="426"/>
-      <c r="T149" s="426"/>
-      <c r="U149" s="426"/>
-      <c r="V149" s="426"/>
-      <c r="W149" s="426"/>
-      <c r="X149" s="426"/>
-      <c r="Y149" s="426"/>
+      <c r="K149" s="425"/>
+      <c r="L149" s="425"/>
+      <c r="M149" s="425"/>
+      <c r="N149" s="425"/>
+      <c r="O149" s="425"/>
+      <c r="P149" s="425"/>
+      <c r="Q149" s="425"/>
+      <c r="R149" s="425"/>
+      <c r="S149" s="425"/>
+      <c r="T149" s="425"/>
+      <c r="U149" s="425"/>
+      <c r="V149" s="425"/>
+      <c r="W149" s="425"/>
+      <c r="X149" s="425"/>
+      <c r="Y149" s="425"/>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="335" t="s">
         <v>278</v>
       </c>
@@ -39783,12 +39846,12 @@
         <v>20</v>
       </c>
       <c r="C150" s="244" t="s">
-        <v>415</v>
-      </c>
-      <c r="D150" s="424" t="s">
-        <v>420</v>
-      </c>
-      <c r="E150" s="425">
+        <v>414</v>
+      </c>
+      <c r="D150" s="423" t="s">
+        <v>419</v>
+      </c>
+      <c r="E150" s="424">
         <v>46348</v>
       </c>
       <c r="F150" s="336">
@@ -39808,23 +39871,23 @@
       <c r="J150" s="243">
         <v>36</v>
       </c>
-      <c r="K150" s="426"/>
-      <c r="L150" s="426"/>
-      <c r="M150" s="426"/>
-      <c r="N150" s="426"/>
-      <c r="O150" s="426"/>
-      <c r="P150" s="426"/>
-      <c r="Q150" s="426"/>
-      <c r="R150" s="426"/>
-      <c r="S150" s="426"/>
-      <c r="T150" s="426"/>
-      <c r="U150" s="426"/>
-      <c r="V150" s="426"/>
-      <c r="W150" s="426"/>
-      <c r="X150" s="426"/>
-      <c r="Y150" s="426"/>
+      <c r="K150" s="425"/>
+      <c r="L150" s="425"/>
+      <c r="M150" s="425"/>
+      <c r="N150" s="425"/>
+      <c r="O150" s="425"/>
+      <c r="P150" s="425"/>
+      <c r="Q150" s="425"/>
+      <c r="R150" s="425"/>
+      <c r="S150" s="425"/>
+      <c r="T150" s="425"/>
+      <c r="U150" s="425"/>
+      <c r="V150" s="425"/>
+      <c r="W150" s="425"/>
+      <c r="X150" s="425"/>
+      <c r="Y150" s="425"/>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="335" t="s">
         <v>278</v>
       </c>
@@ -39832,12 +39895,12 @@
         <v>20</v>
       </c>
       <c r="C151" s="244" t="s">
-        <v>415</v>
-      </c>
-      <c r="D151" s="424" t="s">
-        <v>421</v>
-      </c>
-      <c r="E151" s="425">
+        <v>414</v>
+      </c>
+      <c r="D151" s="423" t="s">
+        <v>420</v>
+      </c>
+      <c r="E151" s="424">
         <v>46355</v>
       </c>
       <c r="F151" s="336">
@@ -39857,23 +39920,23 @@
       <c r="J151" s="243">
         <v>36</v>
       </c>
-      <c r="K151" s="426"/>
-      <c r="L151" s="426"/>
-      <c r="M151" s="426"/>
-      <c r="N151" s="426"/>
-      <c r="O151" s="426"/>
-      <c r="P151" s="426"/>
-      <c r="Q151" s="426"/>
-      <c r="R151" s="426"/>
-      <c r="S151" s="426"/>
-      <c r="T151" s="426"/>
-      <c r="U151" s="426"/>
-      <c r="V151" s="426"/>
-      <c r="W151" s="426"/>
-      <c r="X151" s="426"/>
-      <c r="Y151" s="426"/>
+      <c r="K151" s="425"/>
+      <c r="L151" s="425"/>
+      <c r="M151" s="425"/>
+      <c r="N151" s="425"/>
+      <c r="O151" s="425"/>
+      <c r="P151" s="425"/>
+      <c r="Q151" s="425"/>
+      <c r="R151" s="425"/>
+      <c r="S151" s="425"/>
+      <c r="T151" s="425"/>
+      <c r="U151" s="425"/>
+      <c r="V151" s="425"/>
+      <c r="W151" s="425"/>
+      <c r="X151" s="425"/>
+      <c r="Y151" s="425"/>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="335" t="s">
         <v>278</v>
       </c>
@@ -39881,12 +39944,12 @@
         <v>122</v>
       </c>
       <c r="C152" s="244" t="s">
+        <v>421</v>
+      </c>
+      <c r="D152" s="423" t="s">
         <v>422</v>
       </c>
-      <c r="D152" s="424" t="s">
-        <v>423</v>
-      </c>
-      <c r="E152" s="425">
+      <c r="E152" s="424">
         <v>46189</v>
       </c>
       <c r="F152" s="336">
@@ -39906,23 +39969,23 @@
       <c r="J152" s="243">
         <v>12</v>
       </c>
-      <c r="K152" s="426"/>
-      <c r="L152" s="426"/>
-      <c r="M152" s="426"/>
-      <c r="N152" s="426"/>
-      <c r="O152" s="426"/>
-      <c r="P152" s="426"/>
-      <c r="Q152" s="426"/>
-      <c r="R152" s="426"/>
-      <c r="S152" s="426"/>
-      <c r="T152" s="426"/>
-      <c r="U152" s="426"/>
-      <c r="V152" s="426"/>
-      <c r="W152" s="426"/>
-      <c r="X152" s="426"/>
-      <c r="Y152" s="426"/>
+      <c r="K152" s="425"/>
+      <c r="L152" s="425"/>
+      <c r="M152" s="425"/>
+      <c r="N152" s="425"/>
+      <c r="O152" s="425"/>
+      <c r="P152" s="425"/>
+      <c r="Q152" s="425"/>
+      <c r="R152" s="425"/>
+      <c r="S152" s="425"/>
+      <c r="T152" s="425"/>
+      <c r="U152" s="425"/>
+      <c r="V152" s="425"/>
+      <c r="W152" s="425"/>
+      <c r="X152" s="425"/>
+      <c r="Y152" s="425"/>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="335" t="s">
         <v>278</v>
       </c>
@@ -39930,10 +39993,10 @@
         <v>122</v>
       </c>
       <c r="C153" s="244" t="s">
+        <v>423</v>
+      </c>
+      <c r="D153" s="423" t="s">
         <v>424</v>
-      </c>
-      <c r="D153" s="424" t="s">
-        <v>425</v>
       </c>
       <c r="E153" s="54">
         <v>46192</v>
@@ -39956,7 +40019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="335" t="s">
         <v>278</v>
       </c>
@@ -39964,10 +40027,10 @@
         <v>122</v>
       </c>
       <c r="C154" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D154" s="424" t="s">
-        <v>426</v>
+        <v>423</v>
+      </c>
+      <c r="D154" s="423" t="s">
+        <v>425</v>
       </c>
       <c r="E154" s="54">
         <v>46197</v>
@@ -39990,7 +40053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="335" t="s">
         <v>278</v>
       </c>
@@ -39998,10 +40061,10 @@
         <v>122</v>
       </c>
       <c r="C155" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D155" s="424" t="s">
-        <v>427</v>
+        <v>423</v>
+      </c>
+      <c r="D155" s="423" t="s">
+        <v>426</v>
       </c>
       <c r="E155" s="54">
         <v>46203</v>
@@ -40024,7 +40087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="335" t="s">
         <v>278</v>
       </c>
@@ -40032,10 +40095,10 @@
         <v>122</v>
       </c>
       <c r="C156" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D156" s="424" t="s">
-        <v>428</v>
+        <v>423</v>
+      </c>
+      <c r="D156" s="423" t="s">
+        <v>427</v>
       </c>
       <c r="E156" s="54">
         <v>46206</v>
@@ -40058,7 +40121,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="335" t="s">
         <v>278</v>
       </c>
@@ -40066,10 +40129,10 @@
         <v>122</v>
       </c>
       <c r="C157" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D157" s="424" t="s">
-        <v>429</v>
+        <v>423</v>
+      </c>
+      <c r="D157" s="423" t="s">
+        <v>428</v>
       </c>
       <c r="E157" s="54">
         <v>46215</v>
@@ -40092,7 +40155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="335" t="s">
         <v>278</v>
       </c>
@@ -40100,10 +40163,10 @@
         <v>122</v>
       </c>
       <c r="C158" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D158" s="424" t="s">
-        <v>430</v>
+        <v>423</v>
+      </c>
+      <c r="D158" s="423" t="s">
+        <v>429</v>
       </c>
       <c r="E158" s="54">
         <v>46219</v>
@@ -40126,7 +40189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="335" t="s">
         <v>278</v>
       </c>
@@ -40134,10 +40197,10 @@
         <v>122</v>
       </c>
       <c r="C159" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D159" s="424" t="s">
-        <v>431</v>
+        <v>423</v>
+      </c>
+      <c r="D159" s="423" t="s">
+        <v>430</v>
       </c>
       <c r="E159" s="54">
         <v>46224</v>
@@ -40160,7 +40223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="335" t="s">
         <v>278</v>
       </c>
@@ -40168,10 +40231,10 @@
         <v>122</v>
       </c>
       <c r="C160" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D160" s="424" t="s">
-        <v>432</v>
+        <v>423</v>
+      </c>
+      <c r="D160" s="423" t="s">
+        <v>431</v>
       </c>
       <c r="E160" s="54">
         <v>46230</v>
@@ -40194,7 +40257,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="335" t="s">
         <v>278</v>
       </c>
@@ -40202,10 +40265,10 @@
         <v>122</v>
       </c>
       <c r="C161" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D161" s="424" t="s">
-        <v>433</v>
+        <v>423</v>
+      </c>
+      <c r="D161" s="423" t="s">
+        <v>432</v>
       </c>
       <c r="E161" s="54">
         <v>46235</v>
@@ -40228,7 +40291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="335" t="s">
         <v>278</v>
       </c>
@@ -40236,10 +40299,10 @@
         <v>122</v>
       </c>
       <c r="C162" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D162" s="424" t="s">
-        <v>434</v>
+        <v>423</v>
+      </c>
+      <c r="D162" s="423" t="s">
+        <v>433</v>
       </c>
       <c r="E162" s="54">
         <v>46238</v>
@@ -40262,51 +40325,175 @@
         <v>12</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
-      <c r="A163" s="335" t="s">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="433" t="s">
         <v>278</v>
       </c>
-      <c r="B163" s="243" t="s">
+      <c r="B163" s="408" t="s">
         <v>122</v>
       </c>
-      <c r="C163" s="244" t="s">
-        <v>424</v>
-      </c>
-      <c r="D163" s="424" t="s">
-        <v>435</v>
-      </c>
-      <c r="E163" s="54">
+      <c r="C163" s="410" t="s">
+        <v>423</v>
+      </c>
+      <c r="D163" s="434" t="s">
+        <v>434</v>
+      </c>
+      <c r="E163" s="241">
         <v>46245</v>
       </c>
-      <c r="F163" s="180">
+      <c r="F163" s="213">
         <v>46247.479166666664</v>
       </c>
-      <c r="G163" s="180">
+      <c r="G163" s="213">
         <f t="shared" si="13"/>
         <v>46248.979166666664</v>
       </c>
-      <c r="H163" s="243">
+      <c r="H163" s="408">
         <v>36</v>
       </c>
-      <c r="I163" s="180">
+      <c r="I163" s="213">
         <f t="shared" si="8"/>
         <v>46249.479166666664</v>
       </c>
-      <c r="J163" s="243">
+      <c r="J163" s="408">
         <v>12</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
-      <c r="A164" s="335"/>
-      <c r="B164" s="243"/>
-      <c r="C164" s="244"/>
-      <c r="D164" s="424"/>
-      <c r="E164" s="54"/>
-      <c r="F164" s="180"/>
-      <c r="G164" s="180"/>
-      <c r="H164" s="243"/>
-      <c r="I164" s="180"/>
-      <c r="J164" s="243"/>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="435" t="s">
+        <v>278</v>
+      </c>
+      <c r="B164" s="354" t="s">
+        <v>64</v>
+      </c>
+      <c r="C164" s="435" t="s">
+        <v>435</v>
+      </c>
+      <c r="D164" s="436" t="s">
+        <v>436</v>
+      </c>
+      <c r="E164" s="355">
+        <v>46184</v>
+      </c>
+      <c r="F164" s="356">
+        <v>46185</v>
+      </c>
+      <c r="G164" s="181">
+        <f>F164+(H164/24)</f>
+        <v>46187</v>
+      </c>
+      <c r="H164" s="399">
+        <v>48</v>
+      </c>
+      <c r="I164" s="181">
+        <f>G164+(J164/24)</f>
+        <v>46187.25</v>
+      </c>
+      <c r="J164" s="437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="435" t="s">
+        <v>278</v>
+      </c>
+      <c r="B165" s="354" t="s">
+        <v>64</v>
+      </c>
+      <c r="C165" s="349" t="s">
+        <v>437</v>
+      </c>
+      <c r="D165" s="435" t="s">
+        <v>473</v>
+      </c>
+      <c r="E165" s="355">
+        <v>46191</v>
+      </c>
+      <c r="F165" s="356">
+        <v>46192</v>
+      </c>
+      <c r="G165" s="336">
+        <f>F165+(H165/24)</f>
+        <v>46194</v>
+      </c>
+      <c r="H165" s="399">
+        <v>48</v>
+      </c>
+      <c r="I165" s="336">
+        <f>G165+(J165/24)</f>
+        <v>46194.25</v>
+      </c>
+      <c r="J165" s="437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="349" t="s">
+        <v>278</v>
+      </c>
+      <c r="B166" s="350" t="s">
+        <v>64</v>
+      </c>
+      <c r="C166" s="349" t="s">
+        <v>474</v>
+      </c>
+      <c r="D166" s="349" t="s">
+        <v>475</v>
+      </c>
+      <c r="E166" s="564">
+        <v>46191</v>
+      </c>
+      <c r="F166" s="563">
+        <v>46192</v>
+      </c>
+      <c r="G166" s="336">
+        <f>F166+(H166/24)</f>
+        <v>46194</v>
+      </c>
+      <c r="H166" s="565">
+        <v>48</v>
+      </c>
+      <c r="I166" s="336">
+        <f>G166+(J166/24)</f>
+        <v>46194.25</v>
+      </c>
+      <c r="J166" s="437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="349" t="s">
+        <v>278</v>
+      </c>
+      <c r="B167" s="350" t="s">
+        <v>64</v>
+      </c>
+      <c r="C167" s="349" t="s">
+        <v>438</v>
+      </c>
+      <c r="D167" s="349" t="s">
+        <v>439</v>
+      </c>
+      <c r="E167" s="351">
+        <v>46198</v>
+      </c>
+      <c r="F167" s="352">
+        <v>46199.25</v>
+      </c>
+      <c r="G167" s="336">
+        <f>F167+(H167/24)</f>
+        <v>46201.25</v>
+      </c>
+      <c r="H167" s="565">
+        <v>48</v>
+      </c>
+      <c r="I167" s="336">
+        <f>G167+(J167/24)</f>
+        <v>46201.5</v>
+      </c>
+      <c r="J167" s="437">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J163" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
@@ -40342,75 +40529,75 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F4F7F26-D5D6-4844-933A-5AAFCB58CD1B}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="18" width="9" style="69"/>
     <col min="19" max="19" width="13" style="69" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="69"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B1" s="452" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="557" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="453"/>
-      <c r="D1" s="453"/>
-      <c r="E1" s="454"/>
-      <c r="F1" s="452" t="s">
+      <c r="C1" s="558"/>
+      <c r="D1" s="558"/>
+      <c r="E1" s="559"/>
+      <c r="F1" s="557" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="453"/>
-      <c r="H1" s="453"/>
-      <c r="I1" s="454"/>
-      <c r="J1" s="452" t="s">
+      <c r="G1" s="558"/>
+      <c r="H1" s="558"/>
+      <c r="I1" s="559"/>
+      <c r="J1" s="557" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="453"/>
-      <c r="L1" s="453"/>
-      <c r="M1" s="454"/>
+      <c r="K1" s="558"/>
+      <c r="L1" s="558"/>
+      <c r="M1" s="559"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="70"/>
       <c r="B2" s="71" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E2" s="73" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F2" s="74" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G2" s="72" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H2" s="72" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="I2" s="73" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J2" s="74" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K2" s="72" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M2" s="73" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="75" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
@@ -40418,7 +40605,7 @@
       <c r="E3" s="76"/>
       <c r="F3" s="76"/>
       <c r="G3" s="76" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H3" s="76"/>
       <c r="I3" s="76"/>
@@ -40427,9 +40614,9 @@
       <c r="L3" s="76"/>
       <c r="M3" s="76"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="75" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
@@ -40437,7 +40624,7 @@
       <c r="E4" s="76"/>
       <c r="F4" s="76"/>
       <c r="G4" s="76" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H4" s="76"/>
       <c r="I4" s="76"/>
@@ -40446,9 +40633,9 @@
       <c r="L4" s="76"/>
       <c r="M4" s="76"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="75" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
@@ -40456,7 +40643,7 @@
       <c r="E5" s="76"/>
       <c r="F5" s="76"/>
       <c r="G5" s="76" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H5" s="76"/>
       <c r="I5" s="76"/>
@@ -40465,9 +40652,9 @@
       <c r="L5" s="76"/>
       <c r="M5" s="76"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="75" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B6" s="77"/>
       <c r="C6" s="78"/>
@@ -40475,7 +40662,7 @@
       <c r="E6" s="79"/>
       <c r="F6" s="80"/>
       <c r="G6" s="81" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H6" s="78"/>
       <c r="I6" s="79"/>
@@ -40484,9 +40671,9 @@
       <c r="L6" s="78"/>
       <c r="M6" s="79"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="75" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B7" s="77"/>
       <c r="C7" s="78"/>
@@ -40494,7 +40681,7 @@
       <c r="E7" s="79"/>
       <c r="F7" s="80"/>
       <c r="G7" s="81" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H7" s="78"/>
       <c r="I7" s="79"/>
@@ -40506,9 +40693,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="75" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B8" s="77"/>
       <c r="C8" s="78"/>
@@ -40516,7 +40703,7 @@
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="81" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H8" s="78"/>
       <c r="I8" s="79"/>
@@ -40525,9 +40712,9 @@
       <c r="L8" s="78"/>
       <c r="M8" s="79"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B9" s="82"/>
       <c r="C9" s="83"/>
@@ -40535,7 +40722,7 @@
       <c r="E9" s="84"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="84"/>
@@ -40544,9 +40731,9 @@
       <c r="L9" s="83"/>
       <c r="M9" s="84"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="75" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B10" s="87"/>
       <c r="C10" s="87"/>
@@ -40554,7 +40741,7 @@
       <c r="E10" s="87"/>
       <c r="F10" s="87"/>
       <c r="G10" s="87" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H10" s="87"/>
       <c r="I10" s="87"/>
@@ -40563,9 +40750,9 @@
       <c r="L10" s="87"/>
       <c r="M10" s="87"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="75" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B11" s="88"/>
       <c r="C11" s="89"/>
@@ -40573,7 +40760,7 @@
       <c r="E11" s="90"/>
       <c r="F11" s="91"/>
       <c r="G11" s="92" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H11" s="89"/>
       <c r="I11" s="90"/>
@@ -40582,9 +40769,9 @@
       <c r="L11" s="89"/>
       <c r="M11" s="90"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B12" s="93"/>
       <c r="C12" s="94"/>
@@ -40592,7 +40779,7 @@
       <c r="E12" s="95"/>
       <c r="F12" s="96"/>
       <c r="G12" s="97" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H12" s="94"/>
       <c r="I12" s="95"/>
@@ -40601,32 +40788,32 @@
       <c r="L12" s="94"/>
       <c r="M12" s="95"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="75" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B13" s="93"/>
       <c r="C13" s="94"/>
       <c r="D13" s="94"/>
       <c r="E13" s="95"/>
       <c r="F13" s="96"/>
-      <c r="G13" s="455" t="s">
+      <c r="G13" s="560" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="456"/>
-      <c r="I13" s="457"/>
+      <c r="H13" s="561"/>
+      <c r="I13" s="562"/>
       <c r="J13" s="98" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="K13" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L13" s="99"/>
       <c r="M13" s="100"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="75" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B14" s="101"/>
       <c r="C14" s="101" t="s">
@@ -40635,36 +40822,36 @@
       <c r="D14" s="101"/>
       <c r="E14" s="101"/>
       <c r="F14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J14" s="98" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="K14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="M14" s="86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="O14" s="69" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="75" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B15" s="102"/>
       <c r="C15" s="103"/>
@@ -40697,9 +40884,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="75" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B16" s="102"/>
       <c r="C16" s="103"/>
@@ -40732,9 +40919,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>160</v>
@@ -40761,9 +40948,9 @@
       <c r="L17" s="103"/>
       <c r="M17" s="103"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="75" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>160</v>
@@ -40800,9 +40987,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B19" s="102"/>
       <c r="C19" s="103"/>
@@ -40829,17 +41016,17 @@
       <c r="L19" s="103"/>
       <c r="M19" s="103"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75" thickBot="1">
+    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="111" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B20" s="112"/>
       <c r="C20" s="113"/>
       <c r="D20" s="114" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F20" s="103"/>
       <c r="G20" s="103"/>
@@ -40850,7 +41037,7 @@
       <c r="L20" s="103"/>
       <c r="M20" s="103"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J22" s="69" t="s">
         <v>18</v>
       </c>
@@ -40868,30 +41055,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
-      <Value>1</Value>
-    </TaxCatchAll>
-    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
-        </TermInfo>
-      </Terms>
-    </SAEFSecurityClassificationTaxHTField0>
-    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -40900,7 +41063,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Shell Document" ma:contentTypeID="0x0101006F0A470EEB1140E7AA14F4CE8A50B54C0001CB1477F4DD432AA86DD56CC3887AF4009BF70C544A1089499A02E2027F577943" ma:contentTypeVersion="21" ma:contentTypeDescription="Shell Document Content Type" ma:contentTypeScope="" ma:versionID="3b36c8c7df6bef78f4146e9643aced04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="b2778aaa-fd83-416e-8091-738aa96f6cd3" xmlns:ns3="91455a6e-8899-4f67-a6e4-e187ec74b863" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="619e014c6e05ed77e6b134c7f3fed7d8" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -41221,16 +41384,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
+      <Value>1</Value>
+    </TaxCatchAll>
+    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
+        </TermInfo>
+      </Terms>
+    </SAEFSecurityClassificationTaxHTField0>
+    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D682A838-9073-462C-9192-2FEB3851AAA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
+    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D682A838-9073-462C-9192-2FEB3851AAA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
+    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8759" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F2D9E40-235E-410D-92E0-83EC1B2C95F6}"/>
+  <xr:revisionPtr revIDLastSave="8828" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B711C60B-ECB9-4E9D-B31F-35C84BC9D311}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Vessel Schedule" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$164</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="ActualBeyond">PeriodInActual*(#REF!&gt;0)</definedName>
     <definedName name="PercentComplete">PercentCompleteBeyond*PeriodInPlan</definedName>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="478">
   <si>
     <t xml:space="preserve">Top Hole </t>
   </si>
@@ -1941,6 +1941,12 @@
   </si>
   <si>
     <t>Dark Vision for VA-10</t>
+  </si>
+  <si>
+    <t>NVOY Dummy Well - Rig Acceptance </t>
+  </si>
+  <si>
+    <t>GL 02 OSV - Backload Marine Riser 50jts</t>
   </si>
 </sst>
 </file>
@@ -4655,6 +4661,15 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5028,15 +5043,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -25849,10 +25855,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26295,22 +26297,22 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="439">
+      <c r="G7" s="442">
         <v>2025</v>
       </c>
-      <c r="H7" s="440"/>
-      <c r="I7" s="440"/>
-      <c r="J7" s="440"/>
-      <c r="K7" s="440"/>
-      <c r="L7" s="440"/>
-      <c r="M7" s="440"/>
-      <c r="N7" s="441"/>
-      <c r="O7" s="442">
+      <c r="H7" s="443"/>
+      <c r="I7" s="443"/>
+      <c r="J7" s="443"/>
+      <c r="K7" s="443"/>
+      <c r="L7" s="443"/>
+      <c r="M7" s="443"/>
+      <c r="N7" s="444"/>
+      <c r="O7" s="445">
         <v>2026</v>
       </c>
-      <c r="P7" s="443"/>
-      <c r="Q7" s="443"/>
-      <c r="R7" s="444"/>
+      <c r="P7" s="446"/>
+      <c r="Q7" s="446"/>
+      <c r="R7" s="447"/>
       <c r="S7" s="40"/>
       <c r="T7" s="40"/>
       <c r="U7" s="40"/>
@@ -26327,24 +26329,24 @@
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="447" t="s">
+      <c r="G8" s="450" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="448"/>
-      <c r="I8" s="448"/>
-      <c r="J8" s="448"/>
-      <c r="K8" s="449" t="s">
+      <c r="H8" s="451"/>
+      <c r="I8" s="451"/>
+      <c r="J8" s="451"/>
+      <c r="K8" s="452" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="449"/>
-      <c r="M8" s="449"/>
-      <c r="N8" s="449"/>
-      <c r="O8" s="458" t="s">
+      <c r="L8" s="452"/>
+      <c r="M8" s="452"/>
+      <c r="N8" s="452"/>
+      <c r="O8" s="461" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="458"/>
-      <c r="Q8" s="458"/>
-      <c r="R8" s="459"/>
+      <c r="P8" s="461"/>
+      <c r="Q8" s="461"/>
+      <c r="R8" s="462"/>
       <c r="S8" s="40"/>
       <c r="T8" s="40"/>
       <c r="U8" s="40"/>
@@ -26564,7 +26566,7 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="40"/>
-      <c r="B10" s="450" t="s">
+      <c r="B10" s="453" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -26687,7 +26689,7 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="40"/>
-      <c r="B11" s="451"/>
+      <c r="B11" s="454"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
@@ -26810,7 +26812,7 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="40"/>
-      <c r="B12" s="451"/>
+      <c r="B12" s="454"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -26931,7 +26933,7 @@
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A13" s="40"/>
-      <c r="B13" s="451"/>
+      <c r="B13" s="454"/>
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
@@ -27052,7 +27054,7 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="40"/>
-      <c r="B14" s="451"/>
+      <c r="B14" s="454"/>
       <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
@@ -27175,7 +27177,7 @@
     </row>
     <row r="15" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40"/>
-      <c r="B15" s="452"/>
+      <c r="B15" s="455"/>
       <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
@@ -27296,7 +27298,7 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="40"/>
-      <c r="B16" s="445" t="s">
+      <c r="B16" s="448" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -27419,7 +27421,7 @@
     </row>
     <row r="17" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A17" s="40"/>
-      <c r="B17" s="446"/>
+      <c r="B17" s="449"/>
       <c r="C17" s="7" t="s">
         <v>27</v>
       </c>
@@ -27540,7 +27542,7 @@
     </row>
     <row r="18" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="40"/>
-      <c r="B18" s="446"/>
+      <c r="B18" s="449"/>
       <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
@@ -27661,7 +27663,7 @@
     </row>
     <row r="19" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A19" s="40"/>
-      <c r="B19" s="445" t="s">
+      <c r="B19" s="448" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -27784,7 +27786,7 @@
     </row>
     <row r="20" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="40"/>
-      <c r="B20" s="446"/>
+      <c r="B20" s="449"/>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
@@ -27905,7 +27907,7 @@
     </row>
     <row r="21" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A21" s="40"/>
-      <c r="B21" s="445" t="s">
+      <c r="B21" s="448" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -28028,7 +28030,7 @@
     </row>
     <row r="22" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
-      <c r="B22" s="446"/>
+      <c r="B22" s="449"/>
       <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
@@ -28149,7 +28151,7 @@
     </row>
     <row r="23" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
-      <c r="B23" s="446"/>
+      <c r="B23" s="449"/>
       <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
@@ -28169,11 +28171,11 @@
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
-      <c r="N23" s="455"/>
-      <c r="O23" s="455"/>
-      <c r="P23" s="455"/>
-      <c r="Q23" s="455"/>
-      <c r="R23" s="456"/>
+      <c r="N23" s="458"/>
+      <c r="O23" s="458"/>
+      <c r="P23" s="458"/>
+      <c r="Q23" s="458"/>
+      <c r="R23" s="459"/>
       <c r="S23" s="40"/>
       <c r="T23" s="40"/>
       <c r="U23" s="40"/>
@@ -28185,7 +28187,7 @@
     </row>
     <row r="24" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
-      <c r="B24" s="445" t="s">
+      <c r="B24" s="448" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -28203,12 +28205,12 @@
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
-      <c r="J24" s="457"/>
-      <c r="K24" s="457"/>
-      <c r="L24" s="457"/>
-      <c r="M24" s="457"/>
-      <c r="N24" s="457"/>
-      <c r="O24" s="457"/>
+      <c r="J24" s="460"/>
+      <c r="K24" s="460"/>
+      <c r="L24" s="460"/>
+      <c r="M24" s="460"/>
+      <c r="N24" s="460"/>
+      <c r="O24" s="460"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="14"/>
@@ -28223,7 +28225,7 @@
     </row>
     <row r="25" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40"/>
-      <c r="B25" s="446"/>
+      <c r="B25" s="449"/>
       <c r="C25" s="7" t="s">
         <v>44</v>
       </c>
@@ -28244,10 +28246,10 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
-      <c r="O25" s="453"/>
-      <c r="P25" s="453"/>
-      <c r="Q25" s="453"/>
-      <c r="R25" s="454"/>
+      <c r="O25" s="456"/>
+      <c r="P25" s="456"/>
+      <c r="Q25" s="456"/>
+      <c r="R25" s="457"/>
       <c r="S25" s="40"/>
       <c r="T25" s="40"/>
       <c r="U25" s="40"/>
@@ -28414,7 +28416,7 @@
       <c r="Z29" s="40"/>
     </row>
     <row r="30" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="438" t="s">
+      <c r="B30" s="441" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="33" t="s">
@@ -28452,7 +28454,7 @@
     </row>
     <row r="31" spans="1:111" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="40"/>
-      <c r="B31" s="438"/>
+      <c r="B31" s="441"/>
       <c r="C31" s="33" t="s">
         <v>48</v>
       </c>
@@ -29338,56 +29340,56 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="472">
+      <c r="G7" s="475">
         <v>2026</v>
       </c>
-      <c r="H7" s="472"/>
-      <c r="I7" s="472"/>
-      <c r="J7" s="472"/>
-      <c r="K7" s="472"/>
-      <c r="L7" s="472"/>
-      <c r="M7" s="472"/>
-      <c r="N7" s="472"/>
-      <c r="O7" s="472"/>
-      <c r="P7" s="472"/>
-      <c r="Q7" s="472"/>
-      <c r="R7" s="472"/>
-      <c r="S7" s="472"/>
-      <c r="T7" s="472"/>
-      <c r="U7" s="472"/>
-      <c r="V7" s="472"/>
-      <c r="W7" s="472"/>
-      <c r="X7" s="472"/>
-      <c r="Y7" s="472"/>
-      <c r="Z7" s="472"/>
-      <c r="AA7" s="472"/>
-      <c r="AB7" s="472"/>
-      <c r="AC7" s="472"/>
-      <c r="AD7" s="472"/>
-      <c r="AE7" s="472"/>
-      <c r="AF7" s="472"/>
-      <c r="AG7" s="472"/>
-      <c r="AH7" s="472"/>
-      <c r="AI7" s="472"/>
-      <c r="AJ7" s="472"/>
-      <c r="AK7" s="472"/>
-      <c r="AL7" s="472"/>
-      <c r="AM7" s="472"/>
-      <c r="AN7" s="472"/>
-      <c r="AO7" s="472"/>
-      <c r="AP7" s="472"/>
-      <c r="AQ7" s="472"/>
-      <c r="AR7" s="472"/>
-      <c r="AS7" s="472"/>
-      <c r="AT7" s="472"/>
-      <c r="AU7" s="472"/>
-      <c r="AV7" s="472"/>
-      <c r="AW7" s="472"/>
-      <c r="AX7" s="472"/>
-      <c r="AY7" s="472"/>
-      <c r="AZ7" s="472"/>
-      <c r="BA7" s="472"/>
-      <c r="BB7" s="472"/>
+      <c r="H7" s="475"/>
+      <c r="I7" s="475"/>
+      <c r="J7" s="475"/>
+      <c r="K7" s="475"/>
+      <c r="L7" s="475"/>
+      <c r="M7" s="475"/>
+      <c r="N7" s="475"/>
+      <c r="O7" s="475"/>
+      <c r="P7" s="475"/>
+      <c r="Q7" s="475"/>
+      <c r="R7" s="475"/>
+      <c r="S7" s="475"/>
+      <c r="T7" s="475"/>
+      <c r="U7" s="475"/>
+      <c r="V7" s="475"/>
+      <c r="W7" s="475"/>
+      <c r="X7" s="475"/>
+      <c r="Y7" s="475"/>
+      <c r="Z7" s="475"/>
+      <c r="AA7" s="475"/>
+      <c r="AB7" s="475"/>
+      <c r="AC7" s="475"/>
+      <c r="AD7" s="475"/>
+      <c r="AE7" s="475"/>
+      <c r="AF7" s="475"/>
+      <c r="AG7" s="475"/>
+      <c r="AH7" s="475"/>
+      <c r="AI7" s="475"/>
+      <c r="AJ7" s="475"/>
+      <c r="AK7" s="475"/>
+      <c r="AL7" s="475"/>
+      <c r="AM7" s="475"/>
+      <c r="AN7" s="475"/>
+      <c r="AO7" s="475"/>
+      <c r="AP7" s="475"/>
+      <c r="AQ7" s="475"/>
+      <c r="AR7" s="475"/>
+      <c r="AS7" s="475"/>
+      <c r="AT7" s="475"/>
+      <c r="AU7" s="475"/>
+      <c r="AV7" s="475"/>
+      <c r="AW7" s="475"/>
+      <c r="AX7" s="475"/>
+      <c r="AY7" s="475"/>
+      <c r="AZ7" s="475"/>
+      <c r="BA7" s="475"/>
+      <c r="BB7" s="475"/>
     </row>
     <row r="8" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
@@ -29398,78 +29400,78 @@
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="484" t="s">
+      <c r="G8" s="487" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="484"/>
-      <c r="I8" s="484"/>
-      <c r="J8" s="484"/>
-      <c r="K8" s="479" t="s">
+      <c r="H8" s="487"/>
+      <c r="I8" s="487"/>
+      <c r="J8" s="487"/>
+      <c r="K8" s="482" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="479"/>
-      <c r="M8" s="479"/>
-      <c r="N8" s="479"/>
-      <c r="O8" s="480" t="s">
+      <c r="L8" s="482"/>
+      <c r="M8" s="482"/>
+      <c r="N8" s="482"/>
+      <c r="O8" s="483" t="s">
         <v>74</v>
       </c>
-      <c r="P8" s="480"/>
-      <c r="Q8" s="480"/>
-      <c r="R8" s="480"/>
-      <c r="S8" s="478" t="s">
+      <c r="P8" s="483"/>
+      <c r="Q8" s="483"/>
+      <c r="R8" s="483"/>
+      <c r="S8" s="481" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="478"/>
-      <c r="U8" s="478"/>
-      <c r="V8" s="478"/>
-      <c r="W8" s="479" t="s">
+      <c r="T8" s="481"/>
+      <c r="U8" s="481"/>
+      <c r="V8" s="481"/>
+      <c r="W8" s="482" t="s">
         <v>76</v>
       </c>
-      <c r="X8" s="479"/>
-      <c r="Y8" s="479"/>
-      <c r="Z8" s="479"/>
-      <c r="AA8" s="480" t="s">
+      <c r="X8" s="482"/>
+      <c r="Y8" s="482"/>
+      <c r="Z8" s="482"/>
+      <c r="AA8" s="483" t="s">
         <v>77</v>
       </c>
-      <c r="AB8" s="480"/>
-      <c r="AC8" s="480"/>
-      <c r="AD8" s="480"/>
-      <c r="AE8" s="477" t="s">
+      <c r="AB8" s="483"/>
+      <c r="AC8" s="483"/>
+      <c r="AD8" s="483"/>
+      <c r="AE8" s="480" t="s">
         <v>78</v>
       </c>
-      <c r="AF8" s="477"/>
-      <c r="AG8" s="477"/>
-      <c r="AH8" s="477"/>
-      <c r="AI8" s="473" t="s">
+      <c r="AF8" s="480"/>
+      <c r="AG8" s="480"/>
+      <c r="AH8" s="480"/>
+      <c r="AI8" s="476" t="s">
         <v>79</v>
       </c>
-      <c r="AJ8" s="473"/>
-      <c r="AK8" s="473"/>
-      <c r="AL8" s="473"/>
-      <c r="AM8" s="474" t="s">
+      <c r="AJ8" s="476"/>
+      <c r="AK8" s="476"/>
+      <c r="AL8" s="476"/>
+      <c r="AM8" s="477" t="s">
         <v>80</v>
       </c>
-      <c r="AN8" s="474"/>
-      <c r="AO8" s="474"/>
-      <c r="AP8" s="474"/>
-      <c r="AQ8" s="473" t="s">
+      <c r="AN8" s="477"/>
+      <c r="AO8" s="477"/>
+      <c r="AP8" s="477"/>
+      <c r="AQ8" s="476" t="s">
         <v>81</v>
       </c>
-      <c r="AR8" s="473"/>
-      <c r="AS8" s="473"/>
-      <c r="AT8" s="473"/>
-      <c r="AU8" s="474" t="s">
+      <c r="AR8" s="476"/>
+      <c r="AS8" s="476"/>
+      <c r="AT8" s="476"/>
+      <c r="AU8" s="477" t="s">
         <v>82</v>
       </c>
-      <c r="AV8" s="474"/>
-      <c r="AW8" s="474"/>
-      <c r="AX8" s="474"/>
-      <c r="AY8" s="473" t="s">
+      <c r="AV8" s="477"/>
+      <c r="AW8" s="477"/>
+      <c r="AX8" s="477"/>
+      <c r="AY8" s="476" t="s">
         <v>83</v>
       </c>
-      <c r="AZ8" s="473"/>
-      <c r="BA8" s="473"/>
-      <c r="BB8" s="473"/>
+      <c r="AZ8" s="476"/>
+      <c r="BA8" s="476"/>
+      <c r="BB8" s="476"/>
       <c r="BC8" s="8"/>
       <c r="BD8" s="8"/>
       <c r="BE8" s="8"/>
@@ -29686,42 +29688,42 @@
       <c r="P10" s="231"/>
       <c r="Q10" s="231"/>
       <c r="R10" s="378"/>
-      <c r="S10" s="481"/>
-      <c r="T10" s="482"/>
-      <c r="U10" s="482"/>
-      <c r="V10" s="482"/>
-      <c r="W10" s="482"/>
-      <c r="X10" s="482"/>
-      <c r="Y10" s="482"/>
-      <c r="Z10" s="482"/>
-      <c r="AA10" s="482"/>
-      <c r="AB10" s="482"/>
-      <c r="AC10" s="482"/>
-      <c r="AD10" s="483"/>
-      <c r="AE10" s="475"/>
-      <c r="AF10" s="476"/>
-      <c r="AG10" s="476"/>
-      <c r="AH10" s="476"/>
-      <c r="AI10" s="476"/>
-      <c r="AJ10" s="476"/>
-      <c r="AK10" s="476"/>
-      <c r="AL10" s="476"/>
-      <c r="AM10" s="476"/>
-      <c r="AN10" s="476"/>
-      <c r="AO10" s="476"/>
-      <c r="AP10" s="476"/>
-      <c r="AQ10" s="475"/>
-      <c r="AR10" s="476"/>
-      <c r="AS10" s="476"/>
-      <c r="AT10" s="476"/>
-      <c r="AU10" s="476"/>
-      <c r="AV10" s="476"/>
-      <c r="AW10" s="476"/>
-      <c r="AX10" s="476"/>
-      <c r="AY10" s="476"/>
-      <c r="AZ10" s="476"/>
-      <c r="BA10" s="476"/>
-      <c r="BB10" s="476"/>
+      <c r="S10" s="484"/>
+      <c r="T10" s="485"/>
+      <c r="U10" s="485"/>
+      <c r="V10" s="485"/>
+      <c r="W10" s="485"/>
+      <c r="X10" s="485"/>
+      <c r="Y10" s="485"/>
+      <c r="Z10" s="485"/>
+      <c r="AA10" s="485"/>
+      <c r="AB10" s="485"/>
+      <c r="AC10" s="485"/>
+      <c r="AD10" s="486"/>
+      <c r="AE10" s="478"/>
+      <c r="AF10" s="479"/>
+      <c r="AG10" s="479"/>
+      <c r="AH10" s="479"/>
+      <c r="AI10" s="479"/>
+      <c r="AJ10" s="479"/>
+      <c r="AK10" s="479"/>
+      <c r="AL10" s="479"/>
+      <c r="AM10" s="479"/>
+      <c r="AN10" s="479"/>
+      <c r="AO10" s="479"/>
+      <c r="AP10" s="479"/>
+      <c r="AQ10" s="478"/>
+      <c r="AR10" s="479"/>
+      <c r="AS10" s="479"/>
+      <c r="AT10" s="479"/>
+      <c r="AU10" s="479"/>
+      <c r="AV10" s="479"/>
+      <c r="AW10" s="479"/>
+      <c r="AX10" s="479"/>
+      <c r="AY10" s="479"/>
+      <c r="AZ10" s="479"/>
+      <c r="BA10" s="479"/>
+      <c r="BB10" s="479"/>
       <c r="BC10" s="9"/>
       <c r="BD10" s="9"/>
       <c r="BE10" s="9"/>
@@ -30006,7 +30008,7 @@
     </row>
     <row r="15" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="150"/>
-      <c r="B15" s="445" t="s">
+      <c r="B15" s="448" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="116" t="s">
@@ -30078,7 +30080,7 @@
     </row>
     <row r="16" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A16" s="150"/>
-      <c r="B16" s="445"/>
+      <c r="B16" s="448"/>
       <c r="C16" s="116" t="s">
         <v>42</v>
       </c>
@@ -30142,7 +30144,7 @@
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="150"/>
-      <c r="B17" s="445"/>
+      <c r="B17" s="448"/>
       <c r="C17" s="220" t="s">
         <v>23</v>
       </c>
@@ -30206,7 +30208,7 @@
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="150"/>
-      <c r="B18" s="445"/>
+      <c r="B18" s="448"/>
       <c r="C18" s="223" t="s">
         <v>91</v>
       </c>
@@ -30270,7 +30272,7 @@
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="150"/>
-      <c r="B19" s="445"/>
+      <c r="B19" s="448"/>
       <c r="C19" s="359" t="s">
         <v>93</v>
       </c>
@@ -30334,7 +30336,7 @@
     </row>
     <row r="20" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="150"/>
-      <c r="B20" s="445"/>
+      <c r="B20" s="448"/>
       <c r="C20" s="359" t="s">
         <v>93</v>
       </c>
@@ -30398,7 +30400,7 @@
     </row>
     <row r="21" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="150"/>
-      <c r="B21" s="445" t="s">
+      <c r="B21" s="448" t="s">
         <v>96</v>
       </c>
       <c r="C21" s="117" t="s">
@@ -30468,7 +30470,7 @@
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="150"/>
-      <c r="B22" s="445"/>
+      <c r="B22" s="448"/>
       <c r="C22" s="117" t="s">
         <v>27</v>
       </c>
@@ -30536,7 +30538,7 @@
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="150"/>
-      <c r="B23" s="445"/>
+      <c r="B23" s="448"/>
       <c r="C23" s="117" t="s">
         <v>27</v>
       </c>
@@ -30600,7 +30602,7 @@
     </row>
     <row r="24" spans="1:54" s="164" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="265"/>
-      <c r="B24" s="445"/>
+      <c r="B24" s="448"/>
       <c r="C24" s="117" t="s">
         <v>27</v>
       </c>
@@ -30667,7 +30669,7 @@
     </row>
     <row r="25" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="150"/>
-      <c r="B25" s="445"/>
+      <c r="B25" s="448"/>
       <c r="C25" s="117" t="s">
         <v>27</v>
       </c>
@@ -30731,7 +30733,7 @@
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="150"/>
-      <c r="B26" s="445" t="s">
+      <c r="B26" s="448" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -30801,7 +30803,7 @@
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="150"/>
-      <c r="B27" s="445"/>
+      <c r="B27" s="448"/>
       <c r="C27" s="7" t="s">
         <v>38</v>
       </c>
@@ -30865,7 +30867,7 @@
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="150"/>
-      <c r="B28" s="445"/>
+      <c r="B28" s="448"/>
       <c r="C28" s="7" t="s">
         <v>38</v>
       </c>
@@ -30929,7 +30931,7 @@
     </row>
     <row r="29" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="150"/>
-      <c r="B29" s="446"/>
+      <c r="B29" s="449"/>
       <c r="C29" s="7" t="s">
         <v>38</v>
       </c>
@@ -30995,7 +30997,7 @@
     </row>
     <row r="30" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="150"/>
-      <c r="B30" s="450" t="s">
+      <c r="B30" s="453" t="s">
         <v>106</v>
       </c>
       <c r="C30" s="116" t="s">
@@ -31061,7 +31063,7 @@
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="150"/>
-      <c r="B31" s="500"/>
+      <c r="B31" s="503"/>
       <c r="C31" s="116" t="s">
         <v>44</v>
       </c>
@@ -31125,7 +31127,7 @@
     </row>
     <row r="32" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="150"/>
-      <c r="B32" s="500"/>
+      <c r="B32" s="503"/>
       <c r="C32" s="363" t="s">
         <v>44</v>
       </c>
@@ -31189,7 +31191,7 @@
     </row>
     <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="150"/>
-      <c r="B33" s="501"/>
+      <c r="B33" s="504"/>
       <c r="C33" s="363" t="s">
         <v>44</v>
       </c>
@@ -31252,7 +31254,7 @@
     </row>
     <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="150"/>
-      <c r="B34" s="446" t="s">
+      <c r="B34" s="449" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="116" t="s">
@@ -31320,7 +31322,7 @@
     </row>
     <row r="35" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="150"/>
-      <c r="B35" s="446"/>
+      <c r="B35" s="449"/>
       <c r="C35" s="116" t="s">
         <v>27</v>
       </c>
@@ -31452,7 +31454,7 @@
     </row>
     <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="150"/>
-      <c r="B37" s="446" t="s">
+      <c r="B37" s="449" t="s">
         <v>115</v>
       </c>
       <c r="C37" s="116" t="s">
@@ -31518,7 +31520,7 @@
     </row>
     <row r="38" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="150"/>
-      <c r="B38" s="446"/>
+      <c r="B38" s="449"/>
       <c r="C38" s="116" t="s">
         <v>20</v>
       </c>
@@ -31582,7 +31584,7 @@
     </row>
     <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="150"/>
-      <c r="B39" s="533" t="s">
+      <c r="B39" s="536" t="s">
         <v>118</v>
       </c>
       <c r="C39" s="116" t="s">
@@ -31648,7 +31650,7 @@
     </row>
     <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="150"/>
-      <c r="B40" s="533"/>
+      <c r="B40" s="536"/>
       <c r="C40" s="116" t="s">
         <v>113</v>
       </c>
@@ -31712,7 +31714,7 @@
     </row>
     <row r="41" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="150"/>
-      <c r="B41" s="533"/>
+      <c r="B41" s="536"/>
       <c r="C41" s="116" t="s">
         <v>113</v>
       </c>
@@ -31776,7 +31778,7 @@
     </row>
     <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="150"/>
-      <c r="B42" s="511" t="s">
+      <c r="B42" s="514" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="223" t="s">
@@ -31842,7 +31844,7 @@
     </row>
     <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="150"/>
-      <c r="B43" s="511"/>
+      <c r="B43" s="514"/>
       <c r="C43" s="223" t="s">
         <v>113</v>
       </c>
@@ -31906,7 +31908,7 @@
     </row>
     <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="150"/>
-      <c r="B44" s="511"/>
+      <c r="B44" s="514"/>
       <c r="C44" s="223" t="s">
         <v>113</v>
       </c>
@@ -32229,49 +32231,49 @@
     </row>
     <row r="49" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="150"/>
-      <c r="B49" s="512" t="s">
+      <c r="B49" s="515" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="513"/>
-      <c r="D49" s="513"/>
-      <c r="E49" s="513"/>
-      <c r="F49" s="514"/>
-      <c r="G49" s="488" t="s">
+      <c r="C49" s="516"/>
+      <c r="D49" s="516"/>
+      <c r="E49" s="516"/>
+      <c r="F49" s="517"/>
+      <c r="G49" s="491" t="s">
         <v>132</v>
       </c>
-      <c r="H49" s="489"/>
-      <c r="I49" s="489"/>
-      <c r="J49" s="490"/>
-      <c r="K49" s="488" t="s">
+      <c r="H49" s="492"/>
+      <c r="I49" s="492"/>
+      <c r="J49" s="493"/>
+      <c r="K49" s="491" t="s">
         <v>133</v>
       </c>
-      <c r="L49" s="489"/>
-      <c r="M49" s="489"/>
-      <c r="N49" s="490"/>
-      <c r="O49" s="488" t="s">
+      <c r="L49" s="492"/>
+      <c r="M49" s="492"/>
+      <c r="N49" s="493"/>
+      <c r="O49" s="491" t="s">
         <v>134</v>
       </c>
-      <c r="P49" s="489"/>
-      <c r="Q49" s="489"/>
-      <c r="R49" s="490"/>
-      <c r="S49" s="488" t="s">
+      <c r="P49" s="492"/>
+      <c r="Q49" s="492"/>
+      <c r="R49" s="493"/>
+      <c r="S49" s="491" t="s">
         <v>135</v>
       </c>
-      <c r="T49" s="489"/>
-      <c r="U49" s="489"/>
-      <c r="V49" s="490"/>
-      <c r="W49" s="488" t="s">
+      <c r="T49" s="492"/>
+      <c r="U49" s="492"/>
+      <c r="V49" s="493"/>
+      <c r="W49" s="491" t="s">
         <v>133</v>
       </c>
-      <c r="X49" s="489"/>
-      <c r="Y49" s="489"/>
-      <c r="Z49" s="490"/>
-      <c r="AA49" s="488" t="s">
+      <c r="X49" s="492"/>
+      <c r="Y49" s="492"/>
+      <c r="Z49" s="493"/>
+      <c r="AA49" s="491" t="s">
         <v>136</v>
       </c>
-      <c r="AB49" s="489"/>
-      <c r="AC49" s="489"/>
-      <c r="AD49" s="490"/>
+      <c r="AB49" s="492"/>
+      <c r="AC49" s="492"/>
+      <c r="AD49" s="493"/>
       <c r="AE49" s="192"/>
       <c r="AF49" s="192"/>
       <c r="AG49" s="192"/>
@@ -32299,49 +32301,49 @@
     </row>
     <row r="50" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="150"/>
-      <c r="B50" s="485" t="s">
+      <c r="B50" s="488" t="s">
         <v>137</v>
       </c>
-      <c r="C50" s="486"/>
-      <c r="D50" s="486"/>
-      <c r="E50" s="486"/>
-      <c r="F50" s="487"/>
-      <c r="G50" s="466" t="s">
+      <c r="C50" s="489"/>
+      <c r="D50" s="489"/>
+      <c r="E50" s="489"/>
+      <c r="F50" s="490"/>
+      <c r="G50" s="469" t="s">
         <v>136</v>
       </c>
-      <c r="H50" s="467"/>
-      <c r="I50" s="467"/>
-      <c r="J50" s="468"/>
-      <c r="K50" s="466" t="s">
+      <c r="H50" s="470"/>
+      <c r="I50" s="470"/>
+      <c r="J50" s="471"/>
+      <c r="K50" s="469" t="s">
         <v>138</v>
       </c>
-      <c r="L50" s="467"/>
-      <c r="M50" s="467"/>
-      <c r="N50" s="468"/>
-      <c r="O50" s="485" t="s">
+      <c r="L50" s="470"/>
+      <c r="M50" s="470"/>
+      <c r="N50" s="471"/>
+      <c r="O50" s="488" t="s">
         <v>139</v>
       </c>
-      <c r="P50" s="486"/>
-      <c r="Q50" s="486"/>
-      <c r="R50" s="487"/>
-      <c r="S50" s="485" t="s">
+      <c r="P50" s="489"/>
+      <c r="Q50" s="489"/>
+      <c r="R50" s="490"/>
+      <c r="S50" s="488" t="s">
         <v>138</v>
       </c>
-      <c r="T50" s="486"/>
-      <c r="U50" s="486"/>
-      <c r="V50" s="487"/>
-      <c r="W50" s="485" t="s">
+      <c r="T50" s="489"/>
+      <c r="U50" s="489"/>
+      <c r="V50" s="490"/>
+      <c r="W50" s="488" t="s">
         <v>138</v>
       </c>
-      <c r="X50" s="486"/>
-      <c r="Y50" s="486"/>
-      <c r="Z50" s="487"/>
-      <c r="AA50" s="485" t="s">
+      <c r="X50" s="489"/>
+      <c r="Y50" s="489"/>
+      <c r="Z50" s="490"/>
+      <c r="AA50" s="488" t="s">
         <v>138</v>
       </c>
-      <c r="AB50" s="486"/>
-      <c r="AC50" s="486"/>
-      <c r="AD50" s="487"/>
+      <c r="AB50" s="489"/>
+      <c r="AC50" s="489"/>
+      <c r="AD50" s="490"/>
       <c r="AE50" s="192"/>
       <c r="AF50" s="192"/>
       <c r="AG50" s="192"/>
@@ -32369,45 +32371,45 @@
     </row>
     <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="150"/>
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="463" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="462"/>
-      <c r="G51" s="469" t="s">
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="465"/>
+      <c r="G51" s="472" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="470"/>
-      <c r="I51" s="470"/>
-      <c r="J51" s="471"/>
-      <c r="K51" s="494" t="s">
+      <c r="H51" s="473"/>
+      <c r="I51" s="473"/>
+      <c r="J51" s="474"/>
+      <c r="K51" s="497" t="s">
         <v>142</v>
       </c>
-      <c r="L51" s="495"/>
-      <c r="M51" s="495"/>
-      <c r="N51" s="496"/>
-      <c r="O51" s="460" t="s">
+      <c r="L51" s="498"/>
+      <c r="M51" s="498"/>
+      <c r="N51" s="499"/>
+      <c r="O51" s="463" t="s">
         <v>143</v>
       </c>
-      <c r="P51" s="461"/>
-      <c r="Q51" s="461"/>
-      <c r="R51" s="462"/>
-      <c r="S51" s="460"/>
-      <c r="T51" s="461"/>
-      <c r="U51" s="461"/>
-      <c r="V51" s="462"/>
-      <c r="W51" s="460" t="s">
+      <c r="P51" s="464"/>
+      <c r="Q51" s="464"/>
+      <c r="R51" s="465"/>
+      <c r="S51" s="463"/>
+      <c r="T51" s="464"/>
+      <c r="U51" s="464"/>
+      <c r="V51" s="465"/>
+      <c r="W51" s="463" t="s">
         <v>143</v>
       </c>
-      <c r="X51" s="461"/>
-      <c r="Y51" s="461"/>
-      <c r="Z51" s="462"/>
-      <c r="AA51" s="460"/>
-      <c r="AB51" s="461"/>
-      <c r="AC51" s="461"/>
-      <c r="AD51" s="535"/>
+      <c r="X51" s="464"/>
+      <c r="Y51" s="464"/>
+      <c r="Z51" s="465"/>
+      <c r="AA51" s="463"/>
+      <c r="AB51" s="464"/>
+      <c r="AC51" s="464"/>
+      <c r="AD51" s="538"/>
       <c r="AE51" s="192"/>
       <c r="AF51" s="192"/>
       <c r="AG51" s="192"/>
@@ -32435,43 +32437,43 @@
     </row>
     <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="150"/>
-      <c r="B52" s="463" t="s">
+      <c r="B52" s="466" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="464"/>
-      <c r="D52" s="464"/>
-      <c r="E52" s="464"/>
-      <c r="F52" s="465"/>
-      <c r="G52" s="491" t="s">
+      <c r="C52" s="467"/>
+      <c r="D52" s="467"/>
+      <c r="E52" s="467"/>
+      <c r="F52" s="468"/>
+      <c r="G52" s="494" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="492"/>
-      <c r="I52" s="492"/>
-      <c r="J52" s="493"/>
-      <c r="K52" s="497" t="s">
+      <c r="H52" s="495"/>
+      <c r="I52" s="495"/>
+      <c r="J52" s="496"/>
+      <c r="K52" s="500" t="s">
         <v>146</v>
       </c>
-      <c r="L52" s="498"/>
-      <c r="M52" s="498"/>
-      <c r="N52" s="499"/>
-      <c r="O52" s="497" t="s">
+      <c r="L52" s="501"/>
+      <c r="M52" s="501"/>
+      <c r="N52" s="502"/>
+      <c r="O52" s="500" t="s">
         <v>147</v>
       </c>
-      <c r="P52" s="498"/>
-      <c r="Q52" s="498"/>
-      <c r="R52" s="499"/>
-      <c r="S52" s="463"/>
-      <c r="T52" s="464"/>
-      <c r="U52" s="464"/>
-      <c r="V52" s="465"/>
-      <c r="W52" s="463"/>
-      <c r="X52" s="464"/>
-      <c r="Y52" s="464"/>
-      <c r="Z52" s="465"/>
-      <c r="AA52" s="463"/>
-      <c r="AB52" s="464"/>
-      <c r="AC52" s="464"/>
-      <c r="AD52" s="534"/>
+      <c r="P52" s="501"/>
+      <c r="Q52" s="501"/>
+      <c r="R52" s="502"/>
+      <c r="S52" s="466"/>
+      <c r="T52" s="467"/>
+      <c r="U52" s="467"/>
+      <c r="V52" s="468"/>
+      <c r="W52" s="466"/>
+      <c r="X52" s="467"/>
+      <c r="Y52" s="467"/>
+      <c r="Z52" s="468"/>
+      <c r="AA52" s="466"/>
+      <c r="AB52" s="467"/>
+      <c r="AC52" s="467"/>
+      <c r="AD52" s="537"/>
       <c r="AE52" s="192"/>
       <c r="AF52" s="192"/>
       <c r="AG52" s="192"/>
@@ -32499,49 +32501,49 @@
     </row>
     <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="150"/>
-      <c r="B53" s="515" t="s">
+      <c r="B53" s="518" t="s">
         <v>148</v>
       </c>
-      <c r="C53" s="516"/>
-      <c r="D53" s="516"/>
-      <c r="E53" s="516"/>
-      <c r="F53" s="517"/>
-      <c r="G53" s="524" t="s">
+      <c r="C53" s="519"/>
+      <c r="D53" s="519"/>
+      <c r="E53" s="519"/>
+      <c r="F53" s="520"/>
+      <c r="G53" s="527" t="s">
         <v>149</v>
       </c>
-      <c r="H53" s="525"/>
-      <c r="I53" s="525"/>
-      <c r="J53" s="526"/>
-      <c r="K53" s="524" t="s">
+      <c r="H53" s="528"/>
+      <c r="I53" s="528"/>
+      <c r="J53" s="529"/>
+      <c r="K53" s="527" t="s">
         <v>150</v>
       </c>
-      <c r="L53" s="525"/>
-      <c r="M53" s="525"/>
-      <c r="N53" s="526"/>
-      <c r="O53" s="502" t="s">
+      <c r="L53" s="528"/>
+      <c r="M53" s="528"/>
+      <c r="N53" s="529"/>
+      <c r="O53" s="505" t="s">
         <v>151</v>
       </c>
-      <c r="P53" s="503"/>
-      <c r="Q53" s="503"/>
-      <c r="R53" s="504"/>
-      <c r="S53" s="502" t="s">
+      <c r="P53" s="506"/>
+      <c r="Q53" s="506"/>
+      <c r="R53" s="507"/>
+      <c r="S53" s="505" t="s">
         <v>152</v>
       </c>
-      <c r="T53" s="503"/>
-      <c r="U53" s="503"/>
-      <c r="V53" s="504"/>
-      <c r="W53" s="502" t="s">
+      <c r="T53" s="506"/>
+      <c r="U53" s="506"/>
+      <c r="V53" s="507"/>
+      <c r="W53" s="505" t="s">
         <v>153</v>
       </c>
-      <c r="X53" s="503"/>
-      <c r="Y53" s="503"/>
-      <c r="Z53" s="504"/>
-      <c r="AA53" s="502" t="s">
+      <c r="X53" s="506"/>
+      <c r="Y53" s="506"/>
+      <c r="Z53" s="507"/>
+      <c r="AA53" s="505" t="s">
         <v>154</v>
       </c>
-      <c r="AB53" s="503"/>
-      <c r="AC53" s="503"/>
-      <c r="AD53" s="504"/>
+      <c r="AB53" s="506"/>
+      <c r="AC53" s="506"/>
+      <c r="AD53" s="507"/>
       <c r="AE53" s="150"/>
       <c r="AF53" s="150"/>
       <c r="AG53" s="150"/>
@@ -32571,35 +32573,35 @@
     </row>
     <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="150"/>
-      <c r="B54" s="518"/>
-      <c r="C54" s="519"/>
-      <c r="D54" s="519"/>
-      <c r="E54" s="519"/>
-      <c r="F54" s="520"/>
-      <c r="G54" s="527"/>
-      <c r="H54" s="528"/>
-      <c r="I54" s="528"/>
-      <c r="J54" s="529"/>
-      <c r="K54" s="527"/>
-      <c r="L54" s="528"/>
-      <c r="M54" s="528"/>
-      <c r="N54" s="529"/>
-      <c r="O54" s="505"/>
-      <c r="P54" s="506"/>
-      <c r="Q54" s="506"/>
-      <c r="R54" s="507"/>
-      <c r="S54" s="505"/>
-      <c r="T54" s="506"/>
-      <c r="U54" s="506"/>
-      <c r="V54" s="507"/>
-      <c r="W54" s="505"/>
-      <c r="X54" s="506"/>
-      <c r="Y54" s="506"/>
-      <c r="Z54" s="507"/>
-      <c r="AA54" s="505"/>
-      <c r="AB54" s="506"/>
-      <c r="AC54" s="506"/>
-      <c r="AD54" s="507"/>
+      <c r="B54" s="521"/>
+      <c r="C54" s="522"/>
+      <c r="D54" s="522"/>
+      <c r="E54" s="522"/>
+      <c r="F54" s="523"/>
+      <c r="G54" s="530"/>
+      <c r="H54" s="531"/>
+      <c r="I54" s="531"/>
+      <c r="J54" s="532"/>
+      <c r="K54" s="530"/>
+      <c r="L54" s="531"/>
+      <c r="M54" s="531"/>
+      <c r="N54" s="532"/>
+      <c r="O54" s="508"/>
+      <c r="P54" s="509"/>
+      <c r="Q54" s="509"/>
+      <c r="R54" s="510"/>
+      <c r="S54" s="508"/>
+      <c r="T54" s="509"/>
+      <c r="U54" s="509"/>
+      <c r="V54" s="510"/>
+      <c r="W54" s="508"/>
+      <c r="X54" s="509"/>
+      <c r="Y54" s="509"/>
+      <c r="Z54" s="510"/>
+      <c r="AA54" s="508"/>
+      <c r="AB54" s="509"/>
+      <c r="AC54" s="509"/>
+      <c r="AD54" s="510"/>
       <c r="AE54" s="150"/>
       <c r="AF54" s="150"/>
       <c r="AG54" s="150"/>
@@ -32626,35 +32628,35 @@
       <c r="BB54" s="150"/>
     </row>
     <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="518"/>
-      <c r="C55" s="519"/>
-      <c r="D55" s="519"/>
-      <c r="E55" s="519"/>
-      <c r="F55" s="520"/>
-      <c r="G55" s="527"/>
-      <c r="H55" s="528"/>
-      <c r="I55" s="528"/>
-      <c r="J55" s="529"/>
-      <c r="K55" s="527"/>
-      <c r="L55" s="528"/>
-      <c r="M55" s="528"/>
-      <c r="N55" s="529"/>
-      <c r="O55" s="505"/>
-      <c r="P55" s="506"/>
-      <c r="Q55" s="506"/>
-      <c r="R55" s="507"/>
-      <c r="S55" s="505"/>
-      <c r="T55" s="506"/>
-      <c r="U55" s="506"/>
-      <c r="V55" s="507"/>
-      <c r="W55" s="505"/>
-      <c r="X55" s="506"/>
-      <c r="Y55" s="506"/>
-      <c r="Z55" s="507"/>
-      <c r="AA55" s="505"/>
-      <c r="AB55" s="506"/>
-      <c r="AC55" s="506"/>
-      <c r="AD55" s="507"/>
+      <c r="B55" s="521"/>
+      <c r="C55" s="522"/>
+      <c r="D55" s="522"/>
+      <c r="E55" s="522"/>
+      <c r="F55" s="523"/>
+      <c r="G55" s="530"/>
+      <c r="H55" s="531"/>
+      <c r="I55" s="531"/>
+      <c r="J55" s="532"/>
+      <c r="K55" s="530"/>
+      <c r="L55" s="531"/>
+      <c r="M55" s="531"/>
+      <c r="N55" s="532"/>
+      <c r="O55" s="508"/>
+      <c r="P55" s="509"/>
+      <c r="Q55" s="509"/>
+      <c r="R55" s="510"/>
+      <c r="S55" s="508"/>
+      <c r="T55" s="509"/>
+      <c r="U55" s="509"/>
+      <c r="V55" s="510"/>
+      <c r="W55" s="508"/>
+      <c r="X55" s="509"/>
+      <c r="Y55" s="509"/>
+      <c r="Z55" s="510"/>
+      <c r="AA55" s="508"/>
+      <c r="AB55" s="509"/>
+      <c r="AC55" s="509"/>
+      <c r="AD55" s="510"/>
       <c r="AE55" s="150"/>
       <c r="AF55" s="150"/>
       <c r="AG55" s="150"/>
@@ -32681,438 +32683,438 @@
       <c r="BB55" s="150"/>
     </row>
     <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="518"/>
-      <c r="C56" s="519"/>
-      <c r="D56" s="519"/>
-      <c r="E56" s="519"/>
-      <c r="F56" s="520"/>
-      <c r="G56" s="527"/>
-      <c r="H56" s="528"/>
-      <c r="I56" s="528"/>
-      <c r="J56" s="529"/>
-      <c r="K56" s="527"/>
-      <c r="L56" s="528"/>
-      <c r="M56" s="528"/>
-      <c r="N56" s="529"/>
-      <c r="O56" s="505"/>
-      <c r="P56" s="506"/>
-      <c r="Q56" s="506"/>
-      <c r="R56" s="507"/>
-      <c r="S56" s="505"/>
-      <c r="T56" s="506"/>
-      <c r="U56" s="506"/>
-      <c r="V56" s="507"/>
-      <c r="W56" s="505"/>
-      <c r="X56" s="506"/>
-      <c r="Y56" s="506"/>
-      <c r="Z56" s="507"/>
-      <c r="AA56" s="505"/>
-      <c r="AB56" s="506"/>
-      <c r="AC56" s="506"/>
-      <c r="AD56" s="507"/>
+      <c r="B56" s="521"/>
+      <c r="C56" s="522"/>
+      <c r="D56" s="522"/>
+      <c r="E56" s="522"/>
+      <c r="F56" s="523"/>
+      <c r="G56" s="530"/>
+      <c r="H56" s="531"/>
+      <c r="I56" s="531"/>
+      <c r="J56" s="532"/>
+      <c r="K56" s="530"/>
+      <c r="L56" s="531"/>
+      <c r="M56" s="531"/>
+      <c r="N56" s="532"/>
+      <c r="O56" s="508"/>
+      <c r="P56" s="509"/>
+      <c r="Q56" s="509"/>
+      <c r="R56" s="510"/>
+      <c r="S56" s="508"/>
+      <c r="T56" s="509"/>
+      <c r="U56" s="509"/>
+      <c r="V56" s="510"/>
+      <c r="W56" s="508"/>
+      <c r="X56" s="509"/>
+      <c r="Y56" s="509"/>
+      <c r="Z56" s="510"/>
+      <c r="AA56" s="508"/>
+      <c r="AB56" s="509"/>
+      <c r="AC56" s="509"/>
+      <c r="AD56" s="510"/>
     </row>
     <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="518"/>
-      <c r="C57" s="519"/>
-      <c r="D57" s="519"/>
-      <c r="E57" s="519"/>
-      <c r="F57" s="520"/>
-      <c r="G57" s="527"/>
-      <c r="H57" s="528"/>
-      <c r="I57" s="528"/>
-      <c r="J57" s="529"/>
-      <c r="K57" s="527"/>
-      <c r="L57" s="528"/>
-      <c r="M57" s="528"/>
-      <c r="N57" s="529"/>
-      <c r="O57" s="505"/>
-      <c r="P57" s="506"/>
-      <c r="Q57" s="506"/>
-      <c r="R57" s="507"/>
-      <c r="S57" s="505"/>
-      <c r="T57" s="506"/>
-      <c r="U57" s="506"/>
-      <c r="V57" s="507"/>
-      <c r="W57" s="505"/>
-      <c r="X57" s="506"/>
-      <c r="Y57" s="506"/>
-      <c r="Z57" s="507"/>
-      <c r="AA57" s="505"/>
-      <c r="AB57" s="506"/>
-      <c r="AC57" s="506"/>
-      <c r="AD57" s="507"/>
+      <c r="B57" s="521"/>
+      <c r="C57" s="522"/>
+      <c r="D57" s="522"/>
+      <c r="E57" s="522"/>
+      <c r="F57" s="523"/>
+      <c r="G57" s="530"/>
+      <c r="H57" s="531"/>
+      <c r="I57" s="531"/>
+      <c r="J57" s="532"/>
+      <c r="K57" s="530"/>
+      <c r="L57" s="531"/>
+      <c r="M57" s="531"/>
+      <c r="N57" s="532"/>
+      <c r="O57" s="508"/>
+      <c r="P57" s="509"/>
+      <c r="Q57" s="509"/>
+      <c r="R57" s="510"/>
+      <c r="S57" s="508"/>
+      <c r="T57" s="509"/>
+      <c r="U57" s="509"/>
+      <c r="V57" s="510"/>
+      <c r="W57" s="508"/>
+      <c r="X57" s="509"/>
+      <c r="Y57" s="509"/>
+      <c r="Z57" s="510"/>
+      <c r="AA57" s="508"/>
+      <c r="AB57" s="509"/>
+      <c r="AC57" s="509"/>
+      <c r="AD57" s="510"/>
     </row>
     <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="518"/>
-      <c r="C58" s="519"/>
-      <c r="D58" s="519"/>
-      <c r="E58" s="519"/>
-      <c r="F58" s="520"/>
-      <c r="G58" s="527"/>
-      <c r="H58" s="528"/>
-      <c r="I58" s="528"/>
-      <c r="J58" s="529"/>
-      <c r="K58" s="527"/>
-      <c r="L58" s="528"/>
-      <c r="M58" s="528"/>
-      <c r="N58" s="529"/>
-      <c r="O58" s="505"/>
-      <c r="P58" s="506"/>
-      <c r="Q58" s="506"/>
-      <c r="R58" s="507"/>
-      <c r="S58" s="505"/>
-      <c r="T58" s="506"/>
-      <c r="U58" s="506"/>
-      <c r="V58" s="507"/>
-      <c r="W58" s="505"/>
-      <c r="X58" s="506"/>
-      <c r="Y58" s="506"/>
-      <c r="Z58" s="507"/>
-      <c r="AA58" s="505"/>
-      <c r="AB58" s="506"/>
-      <c r="AC58" s="506"/>
-      <c r="AD58" s="507"/>
+      <c r="B58" s="521"/>
+      <c r="C58" s="522"/>
+      <c r="D58" s="522"/>
+      <c r="E58" s="522"/>
+      <c r="F58" s="523"/>
+      <c r="G58" s="530"/>
+      <c r="H58" s="531"/>
+      <c r="I58" s="531"/>
+      <c r="J58" s="532"/>
+      <c r="K58" s="530"/>
+      <c r="L58" s="531"/>
+      <c r="M58" s="531"/>
+      <c r="N58" s="532"/>
+      <c r="O58" s="508"/>
+      <c r="P58" s="509"/>
+      <c r="Q58" s="509"/>
+      <c r="R58" s="510"/>
+      <c r="S58" s="508"/>
+      <c r="T58" s="509"/>
+      <c r="U58" s="509"/>
+      <c r="V58" s="510"/>
+      <c r="W58" s="508"/>
+      <c r="X58" s="509"/>
+      <c r="Y58" s="509"/>
+      <c r="Z58" s="510"/>
+      <c r="AA58" s="508"/>
+      <c r="AB58" s="509"/>
+      <c r="AC58" s="509"/>
+      <c r="AD58" s="510"/>
     </row>
     <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="518"/>
-      <c r="C59" s="519"/>
-      <c r="D59" s="519"/>
-      <c r="E59" s="519"/>
-      <c r="F59" s="520"/>
-      <c r="G59" s="527"/>
-      <c r="H59" s="528"/>
-      <c r="I59" s="528"/>
-      <c r="J59" s="529"/>
-      <c r="K59" s="527"/>
-      <c r="L59" s="528"/>
-      <c r="M59" s="528"/>
-      <c r="N59" s="529"/>
-      <c r="O59" s="505"/>
-      <c r="P59" s="506"/>
-      <c r="Q59" s="506"/>
-      <c r="R59" s="507"/>
-      <c r="S59" s="505"/>
-      <c r="T59" s="506"/>
-      <c r="U59" s="506"/>
-      <c r="V59" s="507"/>
-      <c r="W59" s="505"/>
-      <c r="X59" s="506"/>
-      <c r="Y59" s="506"/>
-      <c r="Z59" s="507"/>
-      <c r="AA59" s="505"/>
-      <c r="AB59" s="506"/>
-      <c r="AC59" s="506"/>
-      <c r="AD59" s="507"/>
+      <c r="B59" s="521"/>
+      <c r="C59" s="522"/>
+      <c r="D59" s="522"/>
+      <c r="E59" s="522"/>
+      <c r="F59" s="523"/>
+      <c r="G59" s="530"/>
+      <c r="H59" s="531"/>
+      <c r="I59" s="531"/>
+      <c r="J59" s="532"/>
+      <c r="K59" s="530"/>
+      <c r="L59" s="531"/>
+      <c r="M59" s="531"/>
+      <c r="N59" s="532"/>
+      <c r="O59" s="508"/>
+      <c r="P59" s="509"/>
+      <c r="Q59" s="509"/>
+      <c r="R59" s="510"/>
+      <c r="S59" s="508"/>
+      <c r="T59" s="509"/>
+      <c r="U59" s="509"/>
+      <c r="V59" s="510"/>
+      <c r="W59" s="508"/>
+      <c r="X59" s="509"/>
+      <c r="Y59" s="509"/>
+      <c r="Z59" s="510"/>
+      <c r="AA59" s="508"/>
+      <c r="AB59" s="509"/>
+      <c r="AC59" s="509"/>
+      <c r="AD59" s="510"/>
     </row>
     <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="518"/>
-      <c r="C60" s="519"/>
-      <c r="D60" s="519"/>
-      <c r="E60" s="519"/>
-      <c r="F60" s="520"/>
-      <c r="G60" s="527"/>
-      <c r="H60" s="528"/>
-      <c r="I60" s="528"/>
-      <c r="J60" s="529"/>
-      <c r="K60" s="527"/>
-      <c r="L60" s="528"/>
-      <c r="M60" s="528"/>
-      <c r="N60" s="529"/>
-      <c r="O60" s="505"/>
-      <c r="P60" s="506"/>
-      <c r="Q60" s="506"/>
-      <c r="R60" s="507"/>
-      <c r="S60" s="505"/>
-      <c r="T60" s="506"/>
-      <c r="U60" s="506"/>
-      <c r="V60" s="507"/>
-      <c r="W60" s="505"/>
-      <c r="X60" s="506"/>
-      <c r="Y60" s="506"/>
-      <c r="Z60" s="507"/>
-      <c r="AA60" s="505"/>
-      <c r="AB60" s="506"/>
-      <c r="AC60" s="506"/>
-      <c r="AD60" s="507"/>
+      <c r="B60" s="521"/>
+      <c r="C60" s="522"/>
+      <c r="D60" s="522"/>
+      <c r="E60" s="522"/>
+      <c r="F60" s="523"/>
+      <c r="G60" s="530"/>
+      <c r="H60" s="531"/>
+      <c r="I60" s="531"/>
+      <c r="J60" s="532"/>
+      <c r="K60" s="530"/>
+      <c r="L60" s="531"/>
+      <c r="M60" s="531"/>
+      <c r="N60" s="532"/>
+      <c r="O60" s="508"/>
+      <c r="P60" s="509"/>
+      <c r="Q60" s="509"/>
+      <c r="R60" s="510"/>
+      <c r="S60" s="508"/>
+      <c r="T60" s="509"/>
+      <c r="U60" s="509"/>
+      <c r="V60" s="510"/>
+      <c r="W60" s="508"/>
+      <c r="X60" s="509"/>
+      <c r="Y60" s="509"/>
+      <c r="Z60" s="510"/>
+      <c r="AA60" s="508"/>
+      <c r="AB60" s="509"/>
+      <c r="AC60" s="509"/>
+      <c r="AD60" s="510"/>
     </row>
     <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="518"/>
-      <c r="C61" s="519"/>
-      <c r="D61" s="519"/>
-      <c r="E61" s="519"/>
-      <c r="F61" s="520"/>
-      <c r="G61" s="527"/>
-      <c r="H61" s="528"/>
-      <c r="I61" s="528"/>
-      <c r="J61" s="529"/>
-      <c r="K61" s="527"/>
-      <c r="L61" s="528"/>
-      <c r="M61" s="528"/>
-      <c r="N61" s="529"/>
-      <c r="O61" s="505"/>
-      <c r="P61" s="506"/>
-      <c r="Q61" s="506"/>
-      <c r="R61" s="507"/>
-      <c r="S61" s="505"/>
-      <c r="T61" s="506"/>
-      <c r="U61" s="506"/>
-      <c r="V61" s="507"/>
-      <c r="W61" s="505"/>
-      <c r="X61" s="506"/>
-      <c r="Y61" s="506"/>
-      <c r="Z61" s="507"/>
-      <c r="AA61" s="505"/>
-      <c r="AB61" s="506"/>
-      <c r="AC61" s="506"/>
-      <c r="AD61" s="507"/>
+      <c r="B61" s="521"/>
+      <c r="C61" s="522"/>
+      <c r="D61" s="522"/>
+      <c r="E61" s="522"/>
+      <c r="F61" s="523"/>
+      <c r="G61" s="530"/>
+      <c r="H61" s="531"/>
+      <c r="I61" s="531"/>
+      <c r="J61" s="532"/>
+      <c r="K61" s="530"/>
+      <c r="L61" s="531"/>
+      <c r="M61" s="531"/>
+      <c r="N61" s="532"/>
+      <c r="O61" s="508"/>
+      <c r="P61" s="509"/>
+      <c r="Q61" s="509"/>
+      <c r="R61" s="510"/>
+      <c r="S61" s="508"/>
+      <c r="T61" s="509"/>
+      <c r="U61" s="509"/>
+      <c r="V61" s="510"/>
+      <c r="W61" s="508"/>
+      <c r="X61" s="509"/>
+      <c r="Y61" s="509"/>
+      <c r="Z61" s="510"/>
+      <c r="AA61" s="508"/>
+      <c r="AB61" s="509"/>
+      <c r="AC61" s="509"/>
+      <c r="AD61" s="510"/>
     </row>
     <row r="62" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="518"/>
-      <c r="C62" s="519"/>
-      <c r="D62" s="519"/>
-      <c r="E62" s="519"/>
-      <c r="F62" s="520"/>
-      <c r="G62" s="527"/>
-      <c r="H62" s="528"/>
-      <c r="I62" s="528"/>
-      <c r="J62" s="529"/>
-      <c r="K62" s="527"/>
-      <c r="L62" s="528"/>
-      <c r="M62" s="528"/>
-      <c r="N62" s="529"/>
-      <c r="O62" s="505"/>
-      <c r="P62" s="506"/>
-      <c r="Q62" s="506"/>
-      <c r="R62" s="507"/>
-      <c r="S62" s="505"/>
-      <c r="T62" s="506"/>
-      <c r="U62" s="506"/>
-      <c r="V62" s="507"/>
-      <c r="W62" s="505"/>
-      <c r="X62" s="506"/>
-      <c r="Y62" s="506"/>
-      <c r="Z62" s="507"/>
-      <c r="AA62" s="505"/>
-      <c r="AB62" s="506"/>
-      <c r="AC62" s="506"/>
-      <c r="AD62" s="507"/>
+      <c r="B62" s="521"/>
+      <c r="C62" s="522"/>
+      <c r="D62" s="522"/>
+      <c r="E62" s="522"/>
+      <c r="F62" s="523"/>
+      <c r="G62" s="530"/>
+      <c r="H62" s="531"/>
+      <c r="I62" s="531"/>
+      <c r="J62" s="532"/>
+      <c r="K62" s="530"/>
+      <c r="L62" s="531"/>
+      <c r="M62" s="531"/>
+      <c r="N62" s="532"/>
+      <c r="O62" s="508"/>
+      <c r="P62" s="509"/>
+      <c r="Q62" s="509"/>
+      <c r="R62" s="510"/>
+      <c r="S62" s="508"/>
+      <c r="T62" s="509"/>
+      <c r="U62" s="509"/>
+      <c r="V62" s="510"/>
+      <c r="W62" s="508"/>
+      <c r="X62" s="509"/>
+      <c r="Y62" s="509"/>
+      <c r="Z62" s="510"/>
+      <c r="AA62" s="508"/>
+      <c r="AB62" s="509"/>
+      <c r="AC62" s="509"/>
+      <c r="AD62" s="510"/>
     </row>
     <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="518"/>
-      <c r="C63" s="519"/>
-      <c r="D63" s="519"/>
-      <c r="E63" s="519"/>
-      <c r="F63" s="520"/>
-      <c r="G63" s="527"/>
-      <c r="H63" s="528"/>
-      <c r="I63" s="528"/>
-      <c r="J63" s="529"/>
-      <c r="K63" s="527"/>
-      <c r="L63" s="528"/>
-      <c r="M63" s="528"/>
-      <c r="N63" s="529"/>
-      <c r="O63" s="505"/>
-      <c r="P63" s="506"/>
-      <c r="Q63" s="506"/>
-      <c r="R63" s="507"/>
-      <c r="S63" s="505"/>
-      <c r="T63" s="506"/>
-      <c r="U63" s="506"/>
-      <c r="V63" s="507"/>
-      <c r="W63" s="505"/>
-      <c r="X63" s="506"/>
-      <c r="Y63" s="506"/>
-      <c r="Z63" s="507"/>
-      <c r="AA63" s="505"/>
-      <c r="AB63" s="506"/>
-      <c r="AC63" s="506"/>
-      <c r="AD63" s="507"/>
+      <c r="B63" s="521"/>
+      <c r="C63" s="522"/>
+      <c r="D63" s="522"/>
+      <c r="E63" s="522"/>
+      <c r="F63" s="523"/>
+      <c r="G63" s="530"/>
+      <c r="H63" s="531"/>
+      <c r="I63" s="531"/>
+      <c r="J63" s="532"/>
+      <c r="K63" s="530"/>
+      <c r="L63" s="531"/>
+      <c r="M63" s="531"/>
+      <c r="N63" s="532"/>
+      <c r="O63" s="508"/>
+      <c r="P63" s="509"/>
+      <c r="Q63" s="509"/>
+      <c r="R63" s="510"/>
+      <c r="S63" s="508"/>
+      <c r="T63" s="509"/>
+      <c r="U63" s="509"/>
+      <c r="V63" s="510"/>
+      <c r="W63" s="508"/>
+      <c r="X63" s="509"/>
+      <c r="Y63" s="509"/>
+      <c r="Z63" s="510"/>
+      <c r="AA63" s="508"/>
+      <c r="AB63" s="509"/>
+      <c r="AC63" s="509"/>
+      <c r="AD63" s="510"/>
     </row>
     <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="518"/>
-      <c r="C64" s="519"/>
-      <c r="D64" s="519"/>
-      <c r="E64" s="519"/>
-      <c r="F64" s="520"/>
-      <c r="G64" s="527"/>
-      <c r="H64" s="528"/>
-      <c r="I64" s="528"/>
-      <c r="J64" s="529"/>
-      <c r="K64" s="527"/>
-      <c r="L64" s="528"/>
-      <c r="M64" s="528"/>
-      <c r="N64" s="529"/>
-      <c r="O64" s="505"/>
-      <c r="P64" s="506"/>
-      <c r="Q64" s="506"/>
-      <c r="R64" s="507"/>
-      <c r="S64" s="505"/>
-      <c r="T64" s="506"/>
-      <c r="U64" s="506"/>
-      <c r="V64" s="507"/>
-      <c r="W64" s="505"/>
-      <c r="X64" s="506"/>
-      <c r="Y64" s="506"/>
-      <c r="Z64" s="507"/>
-      <c r="AA64" s="505"/>
-      <c r="AB64" s="506"/>
-      <c r="AC64" s="506"/>
-      <c r="AD64" s="507"/>
+      <c r="B64" s="521"/>
+      <c r="C64" s="522"/>
+      <c r="D64" s="522"/>
+      <c r="E64" s="522"/>
+      <c r="F64" s="523"/>
+      <c r="G64" s="530"/>
+      <c r="H64" s="531"/>
+      <c r="I64" s="531"/>
+      <c r="J64" s="532"/>
+      <c r="K64" s="530"/>
+      <c r="L64" s="531"/>
+      <c r="M64" s="531"/>
+      <c r="N64" s="532"/>
+      <c r="O64" s="508"/>
+      <c r="P64" s="509"/>
+      <c r="Q64" s="509"/>
+      <c r="R64" s="510"/>
+      <c r="S64" s="508"/>
+      <c r="T64" s="509"/>
+      <c r="U64" s="509"/>
+      <c r="V64" s="510"/>
+      <c r="W64" s="508"/>
+      <c r="X64" s="509"/>
+      <c r="Y64" s="509"/>
+      <c r="Z64" s="510"/>
+      <c r="AA64" s="508"/>
+      <c r="AB64" s="509"/>
+      <c r="AC64" s="509"/>
+      <c r="AD64" s="510"/>
     </row>
     <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="518"/>
-      <c r="C65" s="519"/>
-      <c r="D65" s="519"/>
-      <c r="E65" s="519"/>
-      <c r="F65" s="520"/>
-      <c r="G65" s="527"/>
-      <c r="H65" s="528"/>
-      <c r="I65" s="528"/>
-      <c r="J65" s="529"/>
-      <c r="K65" s="527"/>
-      <c r="L65" s="528"/>
-      <c r="M65" s="528"/>
-      <c r="N65" s="529"/>
-      <c r="O65" s="505"/>
-      <c r="P65" s="506"/>
-      <c r="Q65" s="506"/>
-      <c r="R65" s="507"/>
-      <c r="S65" s="505"/>
-      <c r="T65" s="506"/>
-      <c r="U65" s="506"/>
-      <c r="V65" s="507"/>
-      <c r="W65" s="505"/>
-      <c r="X65" s="506"/>
-      <c r="Y65" s="506"/>
-      <c r="Z65" s="507"/>
-      <c r="AA65" s="505"/>
-      <c r="AB65" s="506"/>
-      <c r="AC65" s="506"/>
-      <c r="AD65" s="507"/>
+      <c r="B65" s="521"/>
+      <c r="C65" s="522"/>
+      <c r="D65" s="522"/>
+      <c r="E65" s="522"/>
+      <c r="F65" s="523"/>
+      <c r="G65" s="530"/>
+      <c r="H65" s="531"/>
+      <c r="I65" s="531"/>
+      <c r="J65" s="532"/>
+      <c r="K65" s="530"/>
+      <c r="L65" s="531"/>
+      <c r="M65" s="531"/>
+      <c r="N65" s="532"/>
+      <c r="O65" s="508"/>
+      <c r="P65" s="509"/>
+      <c r="Q65" s="509"/>
+      <c r="R65" s="510"/>
+      <c r="S65" s="508"/>
+      <c r="T65" s="509"/>
+      <c r="U65" s="509"/>
+      <c r="V65" s="510"/>
+      <c r="W65" s="508"/>
+      <c r="X65" s="509"/>
+      <c r="Y65" s="509"/>
+      <c r="Z65" s="510"/>
+      <c r="AA65" s="508"/>
+      <c r="AB65" s="509"/>
+      <c r="AC65" s="509"/>
+      <c r="AD65" s="510"/>
     </row>
     <row r="66" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="518"/>
-      <c r="C66" s="519"/>
-      <c r="D66" s="519"/>
-      <c r="E66" s="519"/>
-      <c r="F66" s="520"/>
-      <c r="G66" s="527"/>
-      <c r="H66" s="528"/>
-      <c r="I66" s="528"/>
-      <c r="J66" s="529"/>
-      <c r="K66" s="527"/>
-      <c r="L66" s="528"/>
-      <c r="M66" s="528"/>
-      <c r="N66" s="529"/>
-      <c r="O66" s="505"/>
-      <c r="P66" s="506"/>
-      <c r="Q66" s="506"/>
-      <c r="R66" s="507"/>
-      <c r="S66" s="505"/>
-      <c r="T66" s="506"/>
-      <c r="U66" s="506"/>
-      <c r="V66" s="507"/>
-      <c r="W66" s="505"/>
-      <c r="X66" s="506"/>
-      <c r="Y66" s="506"/>
-      <c r="Z66" s="507"/>
-      <c r="AA66" s="505"/>
-      <c r="AB66" s="506"/>
-      <c r="AC66" s="506"/>
-      <c r="AD66" s="507"/>
+      <c r="B66" s="521"/>
+      <c r="C66" s="522"/>
+      <c r="D66" s="522"/>
+      <c r="E66" s="522"/>
+      <c r="F66" s="523"/>
+      <c r="G66" s="530"/>
+      <c r="H66" s="531"/>
+      <c r="I66" s="531"/>
+      <c r="J66" s="532"/>
+      <c r="K66" s="530"/>
+      <c r="L66" s="531"/>
+      <c r="M66" s="531"/>
+      <c r="N66" s="532"/>
+      <c r="O66" s="508"/>
+      <c r="P66" s="509"/>
+      <c r="Q66" s="509"/>
+      <c r="R66" s="510"/>
+      <c r="S66" s="508"/>
+      <c r="T66" s="509"/>
+      <c r="U66" s="509"/>
+      <c r="V66" s="510"/>
+      <c r="W66" s="508"/>
+      <c r="X66" s="509"/>
+      <c r="Y66" s="509"/>
+      <c r="Z66" s="510"/>
+      <c r="AA66" s="508"/>
+      <c r="AB66" s="509"/>
+      <c r="AC66" s="509"/>
+      <c r="AD66" s="510"/>
     </row>
     <row r="67" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="518"/>
-      <c r="C67" s="519"/>
-      <c r="D67" s="519"/>
-      <c r="E67" s="519"/>
-      <c r="F67" s="520"/>
-      <c r="G67" s="527"/>
-      <c r="H67" s="528"/>
-      <c r="I67" s="528"/>
-      <c r="J67" s="529"/>
-      <c r="K67" s="527"/>
-      <c r="L67" s="528"/>
-      <c r="M67" s="528"/>
-      <c r="N67" s="529"/>
-      <c r="O67" s="505"/>
-      <c r="P67" s="506"/>
-      <c r="Q67" s="506"/>
-      <c r="R67" s="507"/>
-      <c r="S67" s="505"/>
-      <c r="T67" s="506"/>
-      <c r="U67" s="506"/>
-      <c r="V67" s="507"/>
-      <c r="W67" s="505"/>
-      <c r="X67" s="506"/>
-      <c r="Y67" s="506"/>
-      <c r="Z67" s="507"/>
-      <c r="AA67" s="505"/>
-      <c r="AB67" s="506"/>
-      <c r="AC67" s="506"/>
-      <c r="AD67" s="507"/>
+      <c r="B67" s="521"/>
+      <c r="C67" s="522"/>
+      <c r="D67" s="522"/>
+      <c r="E67" s="522"/>
+      <c r="F67" s="523"/>
+      <c r="G67" s="530"/>
+      <c r="H67" s="531"/>
+      <c r="I67" s="531"/>
+      <c r="J67" s="532"/>
+      <c r="K67" s="530"/>
+      <c r="L67" s="531"/>
+      <c r="M67" s="531"/>
+      <c r="N67" s="532"/>
+      <c r="O67" s="508"/>
+      <c r="P67" s="509"/>
+      <c r="Q67" s="509"/>
+      <c r="R67" s="510"/>
+      <c r="S67" s="508"/>
+      <c r="T67" s="509"/>
+      <c r="U67" s="509"/>
+      <c r="V67" s="510"/>
+      <c r="W67" s="508"/>
+      <c r="X67" s="509"/>
+      <c r="Y67" s="509"/>
+      <c r="Z67" s="510"/>
+      <c r="AA67" s="508"/>
+      <c r="AB67" s="509"/>
+      <c r="AC67" s="509"/>
+      <c r="AD67" s="510"/>
     </row>
     <row r="68" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="518"/>
-      <c r="C68" s="519"/>
-      <c r="D68" s="519"/>
-      <c r="E68" s="519"/>
-      <c r="F68" s="520"/>
-      <c r="G68" s="527"/>
-      <c r="H68" s="528"/>
-      <c r="I68" s="528"/>
-      <c r="J68" s="529"/>
-      <c r="K68" s="527"/>
-      <c r="L68" s="528"/>
-      <c r="M68" s="528"/>
-      <c r="N68" s="529"/>
-      <c r="O68" s="505"/>
-      <c r="P68" s="506"/>
-      <c r="Q68" s="506"/>
-      <c r="R68" s="507"/>
-      <c r="S68" s="505"/>
-      <c r="T68" s="506"/>
-      <c r="U68" s="506"/>
-      <c r="V68" s="507"/>
-      <c r="W68" s="505"/>
-      <c r="X68" s="506"/>
-      <c r="Y68" s="506"/>
-      <c r="Z68" s="507"/>
-      <c r="AA68" s="505"/>
-      <c r="AB68" s="506"/>
-      <c r="AC68" s="506"/>
-      <c r="AD68" s="507"/>
+      <c r="B68" s="521"/>
+      <c r="C68" s="522"/>
+      <c r="D68" s="522"/>
+      <c r="E68" s="522"/>
+      <c r="F68" s="523"/>
+      <c r="G68" s="530"/>
+      <c r="H68" s="531"/>
+      <c r="I68" s="531"/>
+      <c r="J68" s="532"/>
+      <c r="K68" s="530"/>
+      <c r="L68" s="531"/>
+      <c r="M68" s="531"/>
+      <c r="N68" s="532"/>
+      <c r="O68" s="508"/>
+      <c r="P68" s="509"/>
+      <c r="Q68" s="509"/>
+      <c r="R68" s="510"/>
+      <c r="S68" s="508"/>
+      <c r="T68" s="509"/>
+      <c r="U68" s="509"/>
+      <c r="V68" s="510"/>
+      <c r="W68" s="508"/>
+      <c r="X68" s="509"/>
+      <c r="Y68" s="509"/>
+      <c r="Z68" s="510"/>
+      <c r="AA68" s="508"/>
+      <c r="AB68" s="509"/>
+      <c r="AC68" s="509"/>
+      <c r="AD68" s="510"/>
     </row>
     <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="521"/>
-      <c r="C69" s="522"/>
-      <c r="D69" s="522"/>
-      <c r="E69" s="522"/>
-      <c r="F69" s="523"/>
-      <c r="G69" s="530"/>
-      <c r="H69" s="531"/>
-      <c r="I69" s="531"/>
-      <c r="J69" s="532"/>
-      <c r="K69" s="530"/>
-      <c r="L69" s="531"/>
-      <c r="M69" s="531"/>
-      <c r="N69" s="532"/>
-      <c r="O69" s="508"/>
-      <c r="P69" s="509"/>
-      <c r="Q69" s="509"/>
-      <c r="R69" s="510"/>
-      <c r="S69" s="508"/>
-      <c r="T69" s="509"/>
-      <c r="U69" s="509"/>
-      <c r="V69" s="510"/>
-      <c r="W69" s="508"/>
-      <c r="X69" s="509"/>
-      <c r="Y69" s="509"/>
-      <c r="Z69" s="510"/>
-      <c r="AA69" s="508"/>
-      <c r="AB69" s="509"/>
-      <c r="AC69" s="509"/>
-      <c r="AD69" s="510"/>
+      <c r="B69" s="524"/>
+      <c r="C69" s="525"/>
+      <c r="D69" s="525"/>
+      <c r="E69" s="525"/>
+      <c r="F69" s="526"/>
+      <c r="G69" s="533"/>
+      <c r="H69" s="534"/>
+      <c r="I69" s="534"/>
+      <c r="J69" s="535"/>
+      <c r="K69" s="533"/>
+      <c r="L69" s="534"/>
+      <c r="M69" s="534"/>
+      <c r="N69" s="535"/>
+      <c r="O69" s="511"/>
+      <c r="P69" s="512"/>
+      <c r="Q69" s="512"/>
+      <c r="R69" s="513"/>
+      <c r="S69" s="511"/>
+      <c r="T69" s="512"/>
+      <c r="U69" s="512"/>
+      <c r="V69" s="513"/>
+      <c r="W69" s="511"/>
+      <c r="X69" s="512"/>
+      <c r="Y69" s="512"/>
+      <c r="Z69" s="513"/>
+      <c r="AA69" s="511"/>
+      <c r="AB69" s="512"/>
+      <c r="AC69" s="512"/>
+      <c r="AD69" s="513"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -33335,24 +33337,24 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="542" t="s">
+      <c r="G7" s="545" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="543"/>
-      <c r="I7" s="543"/>
-      <c r="J7" s="544"/>
-      <c r="K7" s="539" t="s">
+      <c r="H7" s="546"/>
+      <c r="I7" s="546"/>
+      <c r="J7" s="547"/>
+      <c r="K7" s="542" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="540"/>
-      <c r="M7" s="540"/>
-      <c r="N7" s="541"/>
-      <c r="O7" s="536" t="s">
+      <c r="L7" s="543"/>
+      <c r="M7" s="543"/>
+      <c r="N7" s="544"/>
+      <c r="O7" s="539" t="s">
         <v>76</v>
       </c>
-      <c r="P7" s="537"/>
-      <c r="Q7" s="537"/>
-      <c r="R7" s="538"/>
+      <c r="P7" s="540"/>
+      <c r="Q7" s="540"/>
+      <c r="R7" s="541"/>
     </row>
     <row r="8" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="167"/>
@@ -33545,7 +33547,7 @@
       <c r="R13" s="224"/>
     </row>
     <row r="14" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="549" t="s">
+      <c r="B14" s="552" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="146" t="s">
@@ -33574,7 +33576,7 @@
       <c r="R14" s="266"/>
     </row>
     <row r="15" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="550"/>
+      <c r="B15" s="553"/>
       <c r="C15" s="228" t="s">
         <v>93</v>
       </c>
@@ -33601,7 +33603,7 @@
       <c r="R15" s="267"/>
     </row>
     <row r="16" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="549" t="s">
+      <c r="B16" s="552" t="s">
         <v>160</v>
       </c>
       <c r="C16" s="263" t="s">
@@ -33630,7 +33632,7 @@
       <c r="R16" s="264"/>
     </row>
     <row r="17" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="551"/>
+      <c r="B17" s="554"/>
       <c r="C17" s="296" t="s">
         <v>27</v>
       </c>
@@ -33661,7 +33663,7 @@
       <c r="R17" s="271"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="552" t="s">
+      <c r="B18" s="555" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="122" t="s">
@@ -33690,7 +33692,7 @@
       <c r="R18" s="266"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="553"/>
+      <c r="B19" s="556"/>
       <c r="C19" s="123" t="s">
         <v>38</v>
       </c>
@@ -33719,7 +33721,7 @@
       <c r="R19" s="266"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="552" t="s">
+      <c r="B20" s="555" t="s">
         <v>162</v>
       </c>
       <c r="C20" s="119" t="s">
@@ -33748,7 +33750,7 @@
       <c r="R20" s="264"/>
     </row>
     <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="553"/>
+      <c r="B21" s="556"/>
       <c r="C21" s="284" t="s">
         <v>44</v>
       </c>
@@ -33806,7 +33808,7 @@
       <c r="R22" s="266"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="554" t="s">
+      <c r="B23" s="557" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="119" t="s">
@@ -33835,7 +33837,7 @@
       <c r="R23" s="264"/>
     </row>
     <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="555"/>
+      <c r="B24" s="558"/>
       <c r="C24" s="124" t="s">
         <v>20</v>
       </c>
@@ -33862,7 +33864,7 @@
       <c r="R24" s="281"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="549" t="s">
+      <c r="B25" s="552" t="s">
         <v>163</v>
       </c>
       <c r="C25" s="119" t="s">
@@ -33891,7 +33893,7 @@
       <c r="R25" s="23"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="550"/>
+      <c r="B26" s="553"/>
       <c r="C26" s="124" t="s">
         <v>113</v>
       </c>
@@ -34005,439 +34007,439 @@
       <c r="R29" s="312"/>
     </row>
     <row r="30" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="512" t="s">
+      <c r="B30" s="515" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="513"/>
-      <c r="D30" s="513"/>
-      <c r="E30" s="513"/>
-      <c r="F30" s="513"/>
-      <c r="G30" s="512" t="s">
+      <c r="C30" s="516"/>
+      <c r="D30" s="516"/>
+      <c r="E30" s="516"/>
+      <c r="F30" s="516"/>
+      <c r="G30" s="515" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="513"/>
-      <c r="I30" s="513"/>
-      <c r="J30" s="548"/>
-      <c r="K30" s="488" t="s">
+      <c r="H30" s="516"/>
+      <c r="I30" s="516"/>
+      <c r="J30" s="551"/>
+      <c r="K30" s="491" t="s">
         <v>135</v>
       </c>
-      <c r="L30" s="489"/>
-      <c r="M30" s="489"/>
-      <c r="N30" s="490"/>
-      <c r="O30" s="488"/>
-      <c r="P30" s="489"/>
-      <c r="Q30" s="489"/>
-      <c r="R30" s="490"/>
+      <c r="L30" s="492"/>
+      <c r="M30" s="492"/>
+      <c r="N30" s="493"/>
+      <c r="O30" s="491"/>
+      <c r="P30" s="492"/>
+      <c r="Q30" s="492"/>
+      <c r="R30" s="493"/>
     </row>
     <row r="31" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="485" t="s">
+      <c r="B31" s="488" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="486"/>
-      <c r="D31" s="486"/>
-      <c r="E31" s="486"/>
-      <c r="F31" s="486"/>
-      <c r="G31" s="485" t="s">
+      <c r="C31" s="489"/>
+      <c r="D31" s="489"/>
+      <c r="E31" s="489"/>
+      <c r="F31" s="489"/>
+      <c r="G31" s="488" t="s">
         <v>139</v>
       </c>
-      <c r="H31" s="486"/>
-      <c r="I31" s="486"/>
-      <c r="J31" s="556"/>
-      <c r="K31" s="485" t="s">
+      <c r="H31" s="489"/>
+      <c r="I31" s="489"/>
+      <c r="J31" s="559"/>
+      <c r="K31" s="488" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="486"/>
-      <c r="M31" s="486"/>
-      <c r="N31" s="556"/>
-      <c r="O31" s="485" t="s">
+      <c r="L31" s="489"/>
+      <c r="M31" s="489"/>
+      <c r="N31" s="559"/>
+      <c r="O31" s="488" t="s">
         <v>138</v>
       </c>
-      <c r="P31" s="486"/>
-      <c r="Q31" s="486"/>
-      <c r="R31" s="556"/>
+      <c r="P31" s="489"/>
+      <c r="Q31" s="489"/>
+      <c r="R31" s="559"/>
     </row>
     <row r="32" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="460" t="s">
+      <c r="B32" s="463" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="461"/>
-      <c r="D32" s="461"/>
-      <c r="E32" s="461"/>
-      <c r="F32" s="461"/>
-      <c r="G32" s="460" t="s">
+      <c r="C32" s="464"/>
+      <c r="D32" s="464"/>
+      <c r="E32" s="464"/>
+      <c r="F32" s="464"/>
+      <c r="G32" s="463" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="461"/>
-      <c r="I32" s="461"/>
-      <c r="J32" s="535"/>
-      <c r="K32" s="460" t="s">
+      <c r="H32" s="464"/>
+      <c r="I32" s="464"/>
+      <c r="J32" s="538"/>
+      <c r="K32" s="463" t="s">
         <v>142</v>
       </c>
-      <c r="L32" s="461"/>
-      <c r="M32" s="461"/>
-      <c r="N32" s="535"/>
-      <c r="O32" s="460" t="s">
+      <c r="L32" s="464"/>
+      <c r="M32" s="464"/>
+      <c r="N32" s="538"/>
+      <c r="O32" s="463" t="s">
         <v>142</v>
       </c>
-      <c r="P32" s="461"/>
-      <c r="Q32" s="461"/>
-      <c r="R32" s="535"/>
+      <c r="P32" s="464"/>
+      <c r="Q32" s="464"/>
+      <c r="R32" s="538"/>
     </row>
     <row r="33" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="545" t="s">
+      <c r="B33" s="548" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="546"/>
-      <c r="D33" s="546"/>
-      <c r="E33" s="546"/>
-      <c r="F33" s="547"/>
-      <c r="G33" s="463" t="s">
+      <c r="C33" s="549"/>
+      <c r="D33" s="549"/>
+      <c r="E33" s="549"/>
+      <c r="F33" s="550"/>
+      <c r="G33" s="466" t="s">
         <v>147</v>
       </c>
-      <c r="H33" s="464"/>
-      <c r="I33" s="464"/>
-      <c r="J33" s="534"/>
-      <c r="K33" s="463" t="s">
+      <c r="H33" s="467"/>
+      <c r="I33" s="467"/>
+      <c r="J33" s="537"/>
+      <c r="K33" s="466" t="s">
         <v>165</v>
       </c>
-      <c r="L33" s="464"/>
-      <c r="M33" s="464"/>
-      <c r="N33" s="534"/>
-      <c r="O33" s="463"/>
-      <c r="P33" s="464"/>
-      <c r="Q33" s="464"/>
-      <c r="R33" s="534"/>
+      <c r="L33" s="467"/>
+      <c r="M33" s="467"/>
+      <c r="N33" s="537"/>
+      <c r="O33" s="466"/>
+      <c r="P33" s="467"/>
+      <c r="Q33" s="467"/>
+      <c r="R33" s="537"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="515" t="s">
+      <c r="B34" s="518" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="516"/>
-      <c r="D34" s="516"/>
-      <c r="E34" s="516"/>
-      <c r="F34" s="517"/>
-      <c r="G34" s="502" t="s">
+      <c r="C34" s="519"/>
+      <c r="D34" s="519"/>
+      <c r="E34" s="519"/>
+      <c r="F34" s="520"/>
+      <c r="G34" s="505" t="s">
         <v>151</v>
       </c>
-      <c r="H34" s="503"/>
-      <c r="I34" s="503"/>
-      <c r="J34" s="504"/>
-      <c r="K34" s="502" t="s">
+      <c r="H34" s="506"/>
+      <c r="I34" s="506"/>
+      <c r="J34" s="507"/>
+      <c r="K34" s="505" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="503"/>
-      <c r="M34" s="503"/>
-      <c r="N34" s="504"/>
-      <c r="O34" s="502" t="s">
+      <c r="L34" s="506"/>
+      <c r="M34" s="506"/>
+      <c r="N34" s="507"/>
+      <c r="O34" s="505" t="s">
         <v>166</v>
       </c>
-      <c r="P34" s="503"/>
-      <c r="Q34" s="503"/>
-      <c r="R34" s="504"/>
+      <c r="P34" s="506"/>
+      <c r="Q34" s="506"/>
+      <c r="R34" s="507"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="518"/>
-      <c r="C35" s="519"/>
-      <c r="D35" s="519"/>
-      <c r="E35" s="519"/>
-      <c r="F35" s="520"/>
-      <c r="G35" s="505"/>
-      <c r="H35" s="506"/>
-      <c r="I35" s="506"/>
-      <c r="J35" s="507"/>
-      <c r="K35" s="505"/>
-      <c r="L35" s="506"/>
-      <c r="M35" s="506"/>
-      <c r="N35" s="507"/>
-      <c r="O35" s="505"/>
-      <c r="P35" s="506"/>
-      <c r="Q35" s="506"/>
-      <c r="R35" s="507"/>
+      <c r="B35" s="521"/>
+      <c r="C35" s="522"/>
+      <c r="D35" s="522"/>
+      <c r="E35" s="522"/>
+      <c r="F35" s="523"/>
+      <c r="G35" s="508"/>
+      <c r="H35" s="509"/>
+      <c r="I35" s="509"/>
+      <c r="J35" s="510"/>
+      <c r="K35" s="508"/>
+      <c r="L35" s="509"/>
+      <c r="M35" s="509"/>
+      <c r="N35" s="510"/>
+      <c r="O35" s="508"/>
+      <c r="P35" s="509"/>
+      <c r="Q35" s="509"/>
+      <c r="R35" s="510"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="518"/>
-      <c r="C36" s="519"/>
-      <c r="D36" s="519"/>
-      <c r="E36" s="519"/>
-      <c r="F36" s="520"/>
-      <c r="G36" s="505"/>
-      <c r="H36" s="506"/>
-      <c r="I36" s="506"/>
-      <c r="J36" s="507"/>
-      <c r="K36" s="505"/>
-      <c r="L36" s="506"/>
-      <c r="M36" s="506"/>
-      <c r="N36" s="507"/>
-      <c r="O36" s="505"/>
-      <c r="P36" s="506"/>
-      <c r="Q36" s="506"/>
-      <c r="R36" s="507"/>
+      <c r="B36" s="521"/>
+      <c r="C36" s="522"/>
+      <c r="D36" s="522"/>
+      <c r="E36" s="522"/>
+      <c r="F36" s="523"/>
+      <c r="G36" s="508"/>
+      <c r="H36" s="509"/>
+      <c r="I36" s="509"/>
+      <c r="J36" s="510"/>
+      <c r="K36" s="508"/>
+      <c r="L36" s="509"/>
+      <c r="M36" s="509"/>
+      <c r="N36" s="510"/>
+      <c r="O36" s="508"/>
+      <c r="P36" s="509"/>
+      <c r="Q36" s="509"/>
+      <c r="R36" s="510"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="518"/>
-      <c r="C37" s="519"/>
-      <c r="D37" s="519"/>
-      <c r="E37" s="519"/>
-      <c r="F37" s="520"/>
-      <c r="G37" s="505"/>
-      <c r="H37" s="506"/>
-      <c r="I37" s="506"/>
-      <c r="J37" s="507"/>
-      <c r="K37" s="505"/>
-      <c r="L37" s="506"/>
-      <c r="M37" s="506"/>
-      <c r="N37" s="507"/>
-      <c r="O37" s="505"/>
-      <c r="P37" s="506"/>
-      <c r="Q37" s="506"/>
-      <c r="R37" s="507"/>
+      <c r="B37" s="521"/>
+      <c r="C37" s="522"/>
+      <c r="D37" s="522"/>
+      <c r="E37" s="522"/>
+      <c r="F37" s="523"/>
+      <c r="G37" s="508"/>
+      <c r="H37" s="509"/>
+      <c r="I37" s="509"/>
+      <c r="J37" s="510"/>
+      <c r="K37" s="508"/>
+      <c r="L37" s="509"/>
+      <c r="M37" s="509"/>
+      <c r="N37" s="510"/>
+      <c r="O37" s="508"/>
+      <c r="P37" s="509"/>
+      <c r="Q37" s="509"/>
+      <c r="R37" s="510"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="518"/>
-      <c r="C38" s="519"/>
-      <c r="D38" s="519"/>
-      <c r="E38" s="519"/>
-      <c r="F38" s="520"/>
-      <c r="G38" s="505"/>
-      <c r="H38" s="506"/>
-      <c r="I38" s="506"/>
-      <c r="J38" s="507"/>
-      <c r="K38" s="505"/>
-      <c r="L38" s="506"/>
-      <c r="M38" s="506"/>
-      <c r="N38" s="507"/>
-      <c r="O38" s="505"/>
-      <c r="P38" s="506"/>
-      <c r="Q38" s="506"/>
-      <c r="R38" s="507"/>
+      <c r="B38" s="521"/>
+      <c r="C38" s="522"/>
+      <c r="D38" s="522"/>
+      <c r="E38" s="522"/>
+      <c r="F38" s="523"/>
+      <c r="G38" s="508"/>
+      <c r="H38" s="509"/>
+      <c r="I38" s="509"/>
+      <c r="J38" s="510"/>
+      <c r="K38" s="508"/>
+      <c r="L38" s="509"/>
+      <c r="M38" s="509"/>
+      <c r="N38" s="510"/>
+      <c r="O38" s="508"/>
+      <c r="P38" s="509"/>
+      <c r="Q38" s="509"/>
+      <c r="R38" s="510"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="518"/>
-      <c r="C39" s="519"/>
-      <c r="D39" s="519"/>
-      <c r="E39" s="519"/>
-      <c r="F39" s="520"/>
-      <c r="G39" s="505"/>
-      <c r="H39" s="506"/>
-      <c r="I39" s="506"/>
-      <c r="J39" s="507"/>
-      <c r="K39" s="505"/>
-      <c r="L39" s="506"/>
-      <c r="M39" s="506"/>
-      <c r="N39" s="507"/>
-      <c r="O39" s="505"/>
-      <c r="P39" s="506"/>
-      <c r="Q39" s="506"/>
-      <c r="R39" s="507"/>
+      <c r="B39" s="521"/>
+      <c r="C39" s="522"/>
+      <c r="D39" s="522"/>
+      <c r="E39" s="522"/>
+      <c r="F39" s="523"/>
+      <c r="G39" s="508"/>
+      <c r="H39" s="509"/>
+      <c r="I39" s="509"/>
+      <c r="J39" s="510"/>
+      <c r="K39" s="508"/>
+      <c r="L39" s="509"/>
+      <c r="M39" s="509"/>
+      <c r="N39" s="510"/>
+      <c r="O39" s="508"/>
+      <c r="P39" s="509"/>
+      <c r="Q39" s="509"/>
+      <c r="R39" s="510"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="518"/>
-      <c r="C40" s="519"/>
-      <c r="D40" s="519"/>
-      <c r="E40" s="519"/>
-      <c r="F40" s="520"/>
-      <c r="G40" s="505"/>
-      <c r="H40" s="506"/>
-      <c r="I40" s="506"/>
-      <c r="J40" s="507"/>
-      <c r="K40" s="505"/>
-      <c r="L40" s="506"/>
-      <c r="M40" s="506"/>
-      <c r="N40" s="507"/>
-      <c r="O40" s="505"/>
-      <c r="P40" s="506"/>
-      <c r="Q40" s="506"/>
-      <c r="R40" s="507"/>
+      <c r="B40" s="521"/>
+      <c r="C40" s="522"/>
+      <c r="D40" s="522"/>
+      <c r="E40" s="522"/>
+      <c r="F40" s="523"/>
+      <c r="G40" s="508"/>
+      <c r="H40" s="509"/>
+      <c r="I40" s="509"/>
+      <c r="J40" s="510"/>
+      <c r="K40" s="508"/>
+      <c r="L40" s="509"/>
+      <c r="M40" s="509"/>
+      <c r="N40" s="510"/>
+      <c r="O40" s="508"/>
+      <c r="P40" s="509"/>
+      <c r="Q40" s="509"/>
+      <c r="R40" s="510"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="518"/>
-      <c r="C41" s="519"/>
-      <c r="D41" s="519"/>
-      <c r="E41" s="519"/>
-      <c r="F41" s="520"/>
-      <c r="G41" s="505"/>
-      <c r="H41" s="506"/>
-      <c r="I41" s="506"/>
-      <c r="J41" s="507"/>
-      <c r="K41" s="505"/>
-      <c r="L41" s="506"/>
-      <c r="M41" s="506"/>
-      <c r="N41" s="507"/>
-      <c r="O41" s="505"/>
-      <c r="P41" s="506"/>
-      <c r="Q41" s="506"/>
-      <c r="R41" s="507"/>
+      <c r="B41" s="521"/>
+      <c r="C41" s="522"/>
+      <c r="D41" s="522"/>
+      <c r="E41" s="522"/>
+      <c r="F41" s="523"/>
+      <c r="G41" s="508"/>
+      <c r="H41" s="509"/>
+      <c r="I41" s="509"/>
+      <c r="J41" s="510"/>
+      <c r="K41" s="508"/>
+      <c r="L41" s="509"/>
+      <c r="M41" s="509"/>
+      <c r="N41" s="510"/>
+      <c r="O41" s="508"/>
+      <c r="P41" s="509"/>
+      <c r="Q41" s="509"/>
+      <c r="R41" s="510"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="518"/>
-      <c r="C42" s="519"/>
-      <c r="D42" s="519"/>
-      <c r="E42" s="519"/>
-      <c r="F42" s="520"/>
-      <c r="G42" s="505"/>
-      <c r="H42" s="506"/>
-      <c r="I42" s="506"/>
-      <c r="J42" s="507"/>
-      <c r="K42" s="505"/>
-      <c r="L42" s="506"/>
-      <c r="M42" s="506"/>
-      <c r="N42" s="507"/>
-      <c r="O42" s="505"/>
-      <c r="P42" s="506"/>
-      <c r="Q42" s="506"/>
-      <c r="R42" s="507"/>
+      <c r="B42" s="521"/>
+      <c r="C42" s="522"/>
+      <c r="D42" s="522"/>
+      <c r="E42" s="522"/>
+      <c r="F42" s="523"/>
+      <c r="G42" s="508"/>
+      <c r="H42" s="509"/>
+      <c r="I42" s="509"/>
+      <c r="J42" s="510"/>
+      <c r="K42" s="508"/>
+      <c r="L42" s="509"/>
+      <c r="M42" s="509"/>
+      <c r="N42" s="510"/>
+      <c r="O42" s="508"/>
+      <c r="P42" s="509"/>
+      <c r="Q42" s="509"/>
+      <c r="R42" s="510"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="518"/>
-      <c r="C43" s="519"/>
-      <c r="D43" s="519"/>
-      <c r="E43" s="519"/>
-      <c r="F43" s="520"/>
-      <c r="G43" s="505"/>
-      <c r="H43" s="506"/>
-      <c r="I43" s="506"/>
-      <c r="J43" s="507"/>
-      <c r="K43" s="505"/>
-      <c r="L43" s="506"/>
-      <c r="M43" s="506"/>
-      <c r="N43" s="507"/>
-      <c r="O43" s="505"/>
-      <c r="P43" s="506"/>
-      <c r="Q43" s="506"/>
-      <c r="R43" s="507"/>
+      <c r="B43" s="521"/>
+      <c r="C43" s="522"/>
+      <c r="D43" s="522"/>
+      <c r="E43" s="522"/>
+      <c r="F43" s="523"/>
+      <c r="G43" s="508"/>
+      <c r="H43" s="509"/>
+      <c r="I43" s="509"/>
+      <c r="J43" s="510"/>
+      <c r="K43" s="508"/>
+      <c r="L43" s="509"/>
+      <c r="M43" s="509"/>
+      <c r="N43" s="510"/>
+      <c r="O43" s="508"/>
+      <c r="P43" s="509"/>
+      <c r="Q43" s="509"/>
+      <c r="R43" s="510"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="518"/>
-      <c r="C44" s="519"/>
-      <c r="D44" s="519"/>
-      <c r="E44" s="519"/>
-      <c r="F44" s="520"/>
-      <c r="G44" s="505"/>
-      <c r="H44" s="506"/>
-      <c r="I44" s="506"/>
-      <c r="J44" s="507"/>
-      <c r="K44" s="505"/>
-      <c r="L44" s="506"/>
-      <c r="M44" s="506"/>
-      <c r="N44" s="507"/>
-      <c r="O44" s="505"/>
-      <c r="P44" s="506"/>
-      <c r="Q44" s="506"/>
-      <c r="R44" s="507"/>
+      <c r="B44" s="521"/>
+      <c r="C44" s="522"/>
+      <c r="D44" s="522"/>
+      <c r="E44" s="522"/>
+      <c r="F44" s="523"/>
+      <c r="G44" s="508"/>
+      <c r="H44" s="509"/>
+      <c r="I44" s="509"/>
+      <c r="J44" s="510"/>
+      <c r="K44" s="508"/>
+      <c r="L44" s="509"/>
+      <c r="M44" s="509"/>
+      <c r="N44" s="510"/>
+      <c r="O44" s="508"/>
+      <c r="P44" s="509"/>
+      <c r="Q44" s="509"/>
+      <c r="R44" s="510"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="518"/>
-      <c r="C45" s="519"/>
-      <c r="D45" s="519"/>
-      <c r="E45" s="519"/>
-      <c r="F45" s="520"/>
-      <c r="G45" s="505"/>
-      <c r="H45" s="506"/>
-      <c r="I45" s="506"/>
-      <c r="J45" s="507"/>
-      <c r="K45" s="505"/>
-      <c r="L45" s="506"/>
-      <c r="M45" s="506"/>
-      <c r="N45" s="507"/>
-      <c r="O45" s="505"/>
-      <c r="P45" s="506"/>
-      <c r="Q45" s="506"/>
-      <c r="R45" s="507"/>
+      <c r="B45" s="521"/>
+      <c r="C45" s="522"/>
+      <c r="D45" s="522"/>
+      <c r="E45" s="522"/>
+      <c r="F45" s="523"/>
+      <c r="G45" s="508"/>
+      <c r="H45" s="509"/>
+      <c r="I45" s="509"/>
+      <c r="J45" s="510"/>
+      <c r="K45" s="508"/>
+      <c r="L45" s="509"/>
+      <c r="M45" s="509"/>
+      <c r="N45" s="510"/>
+      <c r="O45" s="508"/>
+      <c r="P45" s="509"/>
+      <c r="Q45" s="509"/>
+      <c r="R45" s="510"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="518"/>
-      <c r="C46" s="519"/>
-      <c r="D46" s="519"/>
-      <c r="E46" s="519"/>
-      <c r="F46" s="520"/>
-      <c r="G46" s="505"/>
-      <c r="H46" s="506"/>
-      <c r="I46" s="506"/>
-      <c r="J46" s="507"/>
-      <c r="K46" s="505"/>
-      <c r="L46" s="506"/>
-      <c r="M46" s="506"/>
-      <c r="N46" s="507"/>
-      <c r="O46" s="505"/>
-      <c r="P46" s="506"/>
-      <c r="Q46" s="506"/>
-      <c r="R46" s="507"/>
+      <c r="B46" s="521"/>
+      <c r="C46" s="522"/>
+      <c r="D46" s="522"/>
+      <c r="E46" s="522"/>
+      <c r="F46" s="523"/>
+      <c r="G46" s="508"/>
+      <c r="H46" s="509"/>
+      <c r="I46" s="509"/>
+      <c r="J46" s="510"/>
+      <c r="K46" s="508"/>
+      <c r="L46" s="509"/>
+      <c r="M46" s="509"/>
+      <c r="N46" s="510"/>
+      <c r="O46" s="508"/>
+      <c r="P46" s="509"/>
+      <c r="Q46" s="509"/>
+      <c r="R46" s="510"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="518"/>
-      <c r="C47" s="519"/>
-      <c r="D47" s="519"/>
-      <c r="E47" s="519"/>
-      <c r="F47" s="520"/>
-      <c r="G47" s="505"/>
-      <c r="H47" s="506"/>
-      <c r="I47" s="506"/>
-      <c r="J47" s="507"/>
-      <c r="K47" s="505"/>
-      <c r="L47" s="506"/>
-      <c r="M47" s="506"/>
-      <c r="N47" s="507"/>
-      <c r="O47" s="505"/>
-      <c r="P47" s="506"/>
-      <c r="Q47" s="506"/>
-      <c r="R47" s="507"/>
+      <c r="B47" s="521"/>
+      <c r="C47" s="522"/>
+      <c r="D47" s="522"/>
+      <c r="E47" s="522"/>
+      <c r="F47" s="523"/>
+      <c r="G47" s="508"/>
+      <c r="H47" s="509"/>
+      <c r="I47" s="509"/>
+      <c r="J47" s="510"/>
+      <c r="K47" s="508"/>
+      <c r="L47" s="509"/>
+      <c r="M47" s="509"/>
+      <c r="N47" s="510"/>
+      <c r="O47" s="508"/>
+      <c r="P47" s="509"/>
+      <c r="Q47" s="509"/>
+      <c r="R47" s="510"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="518"/>
-      <c r="C48" s="519"/>
-      <c r="D48" s="519"/>
-      <c r="E48" s="519"/>
-      <c r="F48" s="520"/>
-      <c r="G48" s="505"/>
-      <c r="H48" s="506"/>
-      <c r="I48" s="506"/>
-      <c r="J48" s="507"/>
-      <c r="K48" s="505"/>
-      <c r="L48" s="506"/>
-      <c r="M48" s="506"/>
-      <c r="N48" s="507"/>
-      <c r="O48" s="505"/>
-      <c r="P48" s="506"/>
-      <c r="Q48" s="506"/>
-      <c r="R48" s="507"/>
+      <c r="B48" s="521"/>
+      <c r="C48" s="522"/>
+      <c r="D48" s="522"/>
+      <c r="E48" s="522"/>
+      <c r="F48" s="523"/>
+      <c r="G48" s="508"/>
+      <c r="H48" s="509"/>
+      <c r="I48" s="509"/>
+      <c r="J48" s="510"/>
+      <c r="K48" s="508"/>
+      <c r="L48" s="509"/>
+      <c r="M48" s="509"/>
+      <c r="N48" s="510"/>
+      <c r="O48" s="508"/>
+      <c r="P48" s="509"/>
+      <c r="Q48" s="509"/>
+      <c r="R48" s="510"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="518"/>
-      <c r="C49" s="519"/>
-      <c r="D49" s="519"/>
-      <c r="E49" s="519"/>
-      <c r="F49" s="520"/>
-      <c r="G49" s="505"/>
-      <c r="H49" s="506"/>
-      <c r="I49" s="506"/>
-      <c r="J49" s="507"/>
-      <c r="K49" s="505"/>
-      <c r="L49" s="506"/>
-      <c r="M49" s="506"/>
-      <c r="N49" s="507"/>
-      <c r="O49" s="505"/>
-      <c r="P49" s="506"/>
-      <c r="Q49" s="506"/>
-      <c r="R49" s="507"/>
+      <c r="B49" s="521"/>
+      <c r="C49" s="522"/>
+      <c r="D49" s="522"/>
+      <c r="E49" s="522"/>
+      <c r="F49" s="523"/>
+      <c r="G49" s="508"/>
+      <c r="H49" s="509"/>
+      <c r="I49" s="509"/>
+      <c r="J49" s="510"/>
+      <c r="K49" s="508"/>
+      <c r="L49" s="509"/>
+      <c r="M49" s="509"/>
+      <c r="N49" s="510"/>
+      <c r="O49" s="508"/>
+      <c r="P49" s="509"/>
+      <c r="Q49" s="509"/>
+      <c r="R49" s="510"/>
     </row>
     <row r="50" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="521"/>
-      <c r="C50" s="522"/>
-      <c r="D50" s="522"/>
-      <c r="E50" s="522"/>
-      <c r="F50" s="523"/>
-      <c r="G50" s="508"/>
-      <c r="H50" s="509"/>
-      <c r="I50" s="509"/>
-      <c r="J50" s="510"/>
-      <c r="K50" s="508"/>
-      <c r="L50" s="509"/>
-      <c r="M50" s="509"/>
-      <c r="N50" s="510"/>
-      <c r="O50" s="508"/>
-      <c r="P50" s="509"/>
-      <c r="Q50" s="509"/>
-      <c r="R50" s="510"/>
+      <c r="B50" s="524"/>
+      <c r="C50" s="525"/>
+      <c r="D50" s="525"/>
+      <c r="E50" s="525"/>
+      <c r="F50" s="526"/>
+      <c r="G50" s="511"/>
+      <c r="H50" s="512"/>
+      <c r="I50" s="512"/>
+      <c r="J50" s="513"/>
+      <c r="K50" s="511"/>
+      <c r="L50" s="512"/>
+      <c r="M50" s="512"/>
+      <c r="N50" s="513"/>
+      <c r="O50" s="511"/>
+      <c r="P50" s="512"/>
+      <c r="Q50" s="512"/>
+      <c r="R50" s="513"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -34709,7 +34711,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
   <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:Y167"/>
+  <dimension ref="A1:Y168"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.125" style="6" bestFit="1" customWidth="1"/>
@@ -36029,27 +36031,27 @@
         <v>279</v>
       </c>
       <c r="E39" s="429">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="F39" s="430">
-        <v>46196.6875</v>
+        <v>46198.21875</v>
       </c>
       <c r="G39" s="430">
         <f>F39+(H39/24)</f>
-        <v>46198.6875</v>
+        <v>46200.21875</v>
       </c>
       <c r="H39" s="428">
         <v>48</v>
       </c>
       <c r="I39" s="430">
         <f>G39+(J39/24)</f>
-        <v>46200.6875</v>
+        <v>46202.21875</v>
       </c>
       <c r="J39" s="431">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="182" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="379" t="s">
         <v>278</v>
       </c>
@@ -36083,71 +36085,71 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="262" t="s">
+    <row r="41" spans="1:10" s="182" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="247" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="189" t="s">
+      <c r="B41" s="184" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="122" t="s">
+      <c r="C41" s="123" t="s">
         <v>273</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="402" t="s">
         <v>276</v>
       </c>
-      <c r="E41" s="239">
-        <v>46191</v>
-      </c>
-      <c r="F41" s="188">
-        <v>46193.708333333336</v>
-      </c>
-      <c r="G41" s="188">
+      <c r="E41" s="240">
+        <v>46193</v>
+      </c>
+      <c r="F41" s="183">
+        <v>46195.239583333336</v>
+      </c>
+      <c r="G41" s="183">
         <f>F41+(H41/24)</f>
-        <v>46196.708333333336</v>
-      </c>
-      <c r="H41" s="189">
+        <v>46198.239583333336</v>
+      </c>
+      <c r="H41" s="184">
         <v>72</v>
       </c>
-      <c r="I41" s="188">
+      <c r="I41" s="183">
         <f>G41+(J41/24)</f>
-        <v>46198.708333333336</v>
-      </c>
-      <c r="J41" s="190">
+        <v>46200.239583333336</v>
+      </c>
+      <c r="J41" s="127">
         <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="262" t="s">
+      <c r="A42" s="254" t="s">
         <v>278</v>
       </c>
-      <c r="B42" s="189" t="s">
+      <c r="B42" s="170" t="s">
         <v>160</v>
       </c>
-      <c r="C42" s="122" t="s">
+      <c r="C42" s="187" t="s">
         <v>281</v>
       </c>
-      <c r="D42" s="122" t="s">
+      <c r="D42" s="187" t="s">
         <v>282</v>
       </c>
-      <c r="E42" s="239">
-        <v>46204</v>
-      </c>
-      <c r="F42" s="188">
-        <v>46207.875</v>
-      </c>
-      <c r="G42" s="188">
+      <c r="E42" s="242">
+        <v>46206</v>
+      </c>
+      <c r="F42" s="181">
+        <v>46209.40625</v>
+      </c>
+      <c r="G42" s="181">
         <f t="shared" si="2"/>
-        <v>46210.875</v>
-      </c>
-      <c r="H42" s="189">
+        <v>46212.40625</v>
+      </c>
+      <c r="H42" s="170">
         <v>72</v>
       </c>
-      <c r="I42" s="188">
+      <c r="I42" s="181">
         <f t="shared" si="3"/>
-        <v>46212.875</v>
-      </c>
-      <c r="J42" s="190">
+        <v>46214.40625</v>
+      </c>
+      <c r="J42" s="191">
         <v>48</v>
       </c>
     </row>
@@ -36165,21 +36167,21 @@
         <v>283</v>
       </c>
       <c r="E43" s="54">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="F43" s="180">
-        <v>46210.510416666664</v>
+        <v>46212.041666666664</v>
       </c>
       <c r="G43" s="180">
         <f t="shared" si="2"/>
-        <v>46212.510416666664</v>
+        <v>46214.041666666664</v>
       </c>
       <c r="H43" s="32">
         <v>48</v>
       </c>
       <c r="I43" s="180">
         <f t="shared" si="3"/>
-        <v>46214.510416666664</v>
+        <v>46216.041666666664</v>
       </c>
       <c r="J43" s="126">
         <v>48</v>
@@ -36199,21 +36201,21 @@
         <v>284</v>
       </c>
       <c r="E44" s="54">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="F44" s="180">
-        <v>46217.135416666664</v>
+        <v>46218.666666666664</v>
       </c>
       <c r="G44" s="180">
         <f t="shared" si="2"/>
-        <v>46220.135416666664</v>
+        <v>46221.666666666664</v>
       </c>
       <c r="H44" s="32">
         <v>72</v>
       </c>
       <c r="I44" s="180">
         <f t="shared" si="3"/>
-        <v>46222.135416666664</v>
+        <v>46223.666666666664</v>
       </c>
       <c r="J44" s="126">
         <v>48</v>
@@ -36233,21 +36235,21 @@
         <v>285</v>
       </c>
       <c r="E45" s="54">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F45" s="180">
-        <v>46221.791666666664</v>
+        <v>46223.322916666664</v>
       </c>
       <c r="G45" s="180">
         <f t="shared" si="2"/>
-        <v>46222.791666666664</v>
+        <v>46224.322916666664</v>
       </c>
       <c r="H45" s="32">
         <v>24</v>
       </c>
       <c r="I45" s="180">
         <f t="shared" si="3"/>
-        <v>46224.791666666664</v>
+        <v>46226.322916666664</v>
       </c>
       <c r="J45" s="126">
         <v>48</v>
@@ -36267,21 +36269,21 @@
         <v>286</v>
       </c>
       <c r="E46" s="54">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="F46" s="180">
-        <v>46226.489583333336</v>
+        <v>46228.020833333336</v>
       </c>
       <c r="G46" s="180">
         <f t="shared" si="2"/>
-        <v>46231.489583333336</v>
+        <v>46233.020833333336</v>
       </c>
       <c r="H46" s="32">
         <v>120</v>
       </c>
       <c r="I46" s="180">
         <f t="shared" si="3"/>
-        <v>46233.489583333336</v>
+        <v>46235.020833333336</v>
       </c>
       <c r="J46" s="126">
         <v>48</v>
@@ -36301,21 +36303,21 @@
         <v>287</v>
       </c>
       <c r="E47" s="54">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="F47" s="180">
-        <v>46229.489583333336</v>
+        <v>46231.020833333336</v>
       </c>
       <c r="G47" s="180">
         <f t="shared" si="2"/>
-        <v>46231.489583333336</v>
+        <v>46233.020833333336</v>
       </c>
       <c r="H47" s="32">
         <v>48</v>
       </c>
       <c r="I47" s="180">
         <f t="shared" si="3"/>
-        <v>46233.489583333336</v>
+        <v>46235.020833333336</v>
       </c>
       <c r="J47" s="126">
         <v>48</v>
@@ -36335,21 +36337,21 @@
         <v>288</v>
       </c>
       <c r="E48" s="240">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="F48" s="183">
-        <v>46233.489583333336</v>
+        <v>46235.020833333336</v>
       </c>
       <c r="G48" s="183">
         <f t="shared" si="2"/>
-        <v>46235.489583333336</v>
+        <v>46237.020833333336</v>
       </c>
       <c r="H48" s="184">
         <v>48</v>
       </c>
       <c r="I48" s="183">
         <f t="shared" si="3"/>
-        <v>46237.489583333336</v>
+        <v>46239.020833333336</v>
       </c>
       <c r="J48" s="127">
         <v>48</v>
@@ -38109,14 +38111,14 @@
         <v>46209.291666666664</v>
       </c>
       <c r="G100" s="180">
-        <f t="shared" ref="G100:G130" si="6">F100+(H100/24)</f>
+        <f t="shared" ref="G100:G131" si="6">F100+(H100/24)</f>
         <v>46211.291666666664</v>
       </c>
       <c r="H100" s="32">
         <v>48</v>
       </c>
       <c r="I100" s="180">
-        <f t="shared" ref="I100:I120" si="7">G100+(J100/24)</f>
+        <f t="shared" ref="I100:I121" si="7">G100+(J100/24)</f>
         <v>46212.083333333328</v>
       </c>
       <c r="J100" s="126">
@@ -38443,91 +38445,91 @@
         <v>364</v>
       </c>
       <c r="E110" s="387">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="F110" s="388">
-        <v>46217.25</v>
+        <v>46228</v>
       </c>
       <c r="G110" s="388">
         <f t="shared" si="6"/>
-        <v>46219.25</v>
+        <v>46230</v>
       </c>
       <c r="H110" s="385">
         <v>48</v>
       </c>
       <c r="I110" s="388">
         <f t="shared" si="7"/>
-        <v>46219.666666666664</v>
+        <v>46230.5</v>
       </c>
       <c r="J110" s="389">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="262" t="s">
+    <row r="111" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="384" t="s">
         <v>278</v>
       </c>
-      <c r="B111" s="189" t="s">
+      <c r="B111" s="385" t="s">
         <v>362</v>
       </c>
-      <c r="C111" s="122" t="s">
-        <v>365</v>
-      </c>
-      <c r="D111" s="122" t="s">
-        <v>366</v>
-      </c>
-      <c r="E111" s="239">
-        <v>46220</v>
-      </c>
-      <c r="F111" s="188">
-        <v>46223</v>
-      </c>
-      <c r="G111" s="188">
+      <c r="C111" s="386" t="s">
+        <v>476</v>
+      </c>
+      <c r="D111" s="386" t="s">
+        <v>477</v>
+      </c>
+      <c r="E111" s="387">
+        <v>46229</v>
+      </c>
+      <c r="F111" s="388">
+        <v>46231.5</v>
+      </c>
+      <c r="G111" s="388">
         <f t="shared" si="6"/>
-        <v>46224.5</v>
-      </c>
-      <c r="H111" s="189">
-        <v>36</v>
-      </c>
-      <c r="I111" s="188">
+        <v>46233.5</v>
+      </c>
+      <c r="H111" s="385">
+        <v>48</v>
+      </c>
+      <c r="I111" s="388">
         <f t="shared" si="7"/>
-        <v>46224.916666666664</v>
-      </c>
-      <c r="J111" s="190">
-        <v>10</v>
+        <v>46234</v>
+      </c>
+      <c r="J111" s="389">
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="246" t="s">
+      <c r="A112" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B112" s="32" t="s">
+      <c r="B112" s="189" t="s">
         <v>362</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="122" t="s">
         <v>365</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="E112" s="54">
-        <v>46224</v>
-      </c>
-      <c r="F112" s="180">
-        <v>46226</v>
-      </c>
-      <c r="G112" s="180">
+      <c r="D112" s="122" t="s">
+        <v>366</v>
+      </c>
+      <c r="E112" s="239">
+        <v>46229</v>
+      </c>
+      <c r="F112" s="188">
+        <v>46231</v>
+      </c>
+      <c r="G112" s="188">
         <f t="shared" si="6"/>
-        <v>46228.5</v>
-      </c>
-      <c r="H112" s="32">
-        <v>60</v>
-      </c>
-      <c r="I112" s="180">
+        <v>46232.5</v>
+      </c>
+      <c r="H112" s="189">
+        <v>36</v>
+      </c>
+      <c r="I112" s="188">
         <f t="shared" si="7"/>
-        <v>46228.916666666664</v>
-      </c>
-      <c r="J112" s="126">
+        <v>46232.916666666664</v>
+      </c>
+      <c r="J112" s="190">
         <v>10</v>
       </c>
     </row>
@@ -38542,30 +38544,27 @@
         <v>365</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E113" s="54">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="F113" s="180">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="G113" s="180">
         <f t="shared" si="6"/>
-        <v>46231</v>
+        <v>46235.5</v>
       </c>
       <c r="H113" s="32">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I113" s="180">
         <f t="shared" si="7"/>
-        <v>46231.416666666664</v>
+        <v>46235.916666666664</v>
       </c>
       <c r="J113" s="126">
         <v>10</v>
-      </c>
-      <c r="U113" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.25">
@@ -38579,334 +38578,337 @@
         <v>365</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E114" s="54">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="F114" s="180">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="G114" s="180">
         <f t="shared" si="6"/>
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="H114" s="32">
         <v>72</v>
       </c>
       <c r="I114" s="180">
         <f t="shared" si="7"/>
-        <v>46233.416666666664</v>
+        <v>46239.416666666664</v>
       </c>
       <c r="J114" s="126">
         <v>10</v>
       </c>
+      <c r="U114" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="115" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="331" t="s">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A115" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B115" s="214" t="s">
+      <c r="B115" s="32" t="s">
         <v>362</v>
       </c>
-      <c r="C115" s="212" t="s">
+      <c r="C115" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="D115" s="212" t="s">
+      <c r="D115" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E115" s="54">
+        <v>46235</v>
+      </c>
+      <c r="F115" s="180">
+        <v>46236</v>
+      </c>
+      <c r="G115" s="180">
+        <f t="shared" si="6"/>
+        <v>46239</v>
+      </c>
+      <c r="H115" s="32">
+        <v>72</v>
+      </c>
+      <c r="I115" s="180">
+        <f t="shared" si="7"/>
+        <v>46239.416666666664</v>
+      </c>
+      <c r="J115" s="126">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="331" t="s">
+        <v>278</v>
+      </c>
+      <c r="B116" s="214" t="s">
+        <v>362</v>
+      </c>
+      <c r="C116" s="212" t="s">
+        <v>365</v>
+      </c>
+      <c r="D116" s="212" t="s">
         <v>370</v>
       </c>
-      <c r="E115" s="241">
-        <v>46229</v>
-      </c>
-      <c r="F115" s="213">
-        <v>46231</v>
-      </c>
-      <c r="G115" s="213">
+      <c r="E116" s="241">
+        <v>46237</v>
+      </c>
+      <c r="F116" s="213">
+        <v>46238</v>
+      </c>
+      <c r="G116" s="213">
         <f t="shared" si="6"/>
-        <v>46233.5</v>
-      </c>
-      <c r="H115" s="214">
+        <v>46240.5</v>
+      </c>
+      <c r="H116" s="214">
         <v>60</v>
       </c>
-      <c r="I115" s="213">
+      <c r="I116" s="213">
         <f t="shared" si="7"/>
-        <v>46233.916666666664</v>
-      </c>
-      <c r="J115" s="215">
+        <v>46240.916666666664</v>
+      </c>
+      <c r="J116" s="215">
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A116" s="262" t="s">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A117" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="189" t="s">
+      <c r="B117" s="189" t="s">
         <v>362</v>
       </c>
-      <c r="C116" s="122" t="s">
+      <c r="C117" s="122" t="s">
         <v>371</v>
       </c>
-      <c r="D116" s="122" t="s">
+      <c r="D117" s="122" t="s">
         <v>372</v>
       </c>
-      <c r="E116" s="239">
-        <v>46232</v>
-      </c>
-      <c r="F116" s="188">
-        <v>46233</v>
-      </c>
-      <c r="G116" s="188">
+      <c r="E117" s="239">
+        <v>46237</v>
+      </c>
+      <c r="F117" s="188">
+        <v>46238</v>
+      </c>
+      <c r="G117" s="188">
         <f t="shared" si="6"/>
-        <v>46234.5</v>
-      </c>
-      <c r="H116" s="189">
+        <v>46239.5</v>
+      </c>
+      <c r="H117" s="189">
         <v>36</v>
       </c>
-      <c r="I116" s="188">
+      <c r="I117" s="188">
         <f t="shared" si="7"/>
-        <v>46234.916666666664</v>
-      </c>
-      <c r="J116" s="190">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="331" t="s">
-        <v>278</v>
-      </c>
-      <c r="B117" s="214" t="s">
-        <v>362</v>
-      </c>
-      <c r="C117" s="212" t="s">
-        <v>371</v>
-      </c>
-      <c r="D117" s="212" t="s">
-        <v>373</v>
-      </c>
-      <c r="E117" s="241">
-        <v>46241</v>
-      </c>
-      <c r="F117" s="213">
-        <v>46243.166666666664</v>
-      </c>
-      <c r="G117" s="213">
-        <f t="shared" si="6"/>
-        <v>46244.666666666664</v>
-      </c>
-      <c r="H117" s="214">
-        <v>36</v>
-      </c>
-      <c r="I117" s="213">
-        <f t="shared" si="7"/>
-        <v>46245.083333333328</v>
-      </c>
-      <c r="J117" s="215">
+        <v>46239.916666666664</v>
+      </c>
+      <c r="J117" s="190">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="384" t="s">
+      <c r="A118" s="331" t="s">
         <v>278</v>
       </c>
-      <c r="B118" s="385" t="s">
+      <c r="B118" s="214" t="s">
         <v>362</v>
       </c>
-      <c r="C118" s="386" t="s">
+      <c r="C118" s="212" t="s">
+        <v>371</v>
+      </c>
+      <c r="D118" s="212" t="s">
+        <v>373</v>
+      </c>
+      <c r="E118" s="241">
+        <v>46246</v>
+      </c>
+      <c r="F118" s="213">
+        <v>46248.166666666664</v>
+      </c>
+      <c r="G118" s="213">
+        <f t="shared" si="6"/>
+        <v>46249.666666666664</v>
+      </c>
+      <c r="H118" s="214">
+        <v>36</v>
+      </c>
+      <c r="I118" s="213">
+        <f t="shared" si="7"/>
+        <v>46250.083333333328</v>
+      </c>
+      <c r="J118" s="215">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="384" t="s">
+        <v>278</v>
+      </c>
+      <c r="B119" s="385" t="s">
+        <v>362</v>
+      </c>
+      <c r="C119" s="386" t="s">
         <v>374</v>
       </c>
-      <c r="D118" s="386" t="s">
+      <c r="D119" s="386" t="s">
         <v>375</v>
       </c>
-      <c r="E118" s="387">
-        <v>46246</v>
-      </c>
-      <c r="F118" s="388">
-        <v>46247.416666666664</v>
-      </c>
-      <c r="G118" s="388">
+      <c r="E119" s="387">
+        <v>46251</v>
+      </c>
+      <c r="F119" s="388">
+        <v>46252.416666666664</v>
+      </c>
+      <c r="G119" s="388">
         <f t="shared" si="6"/>
-        <v>46248.666666666664</v>
-      </c>
-      <c r="H118" s="385">
+        <v>46253.666666666664</v>
+      </c>
+      <c r="H119" s="385">
         <v>30</v>
       </c>
-      <c r="I118" s="388">
+      <c r="I119" s="388">
         <f t="shared" si="7"/>
-        <v>46249.083333333328</v>
-      </c>
-      <c r="J118" s="389">
+        <v>46254.083333333328</v>
+      </c>
+      <c r="J119" s="389">
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="262" t="s">
+    <row r="120" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="262" t="s">
         <v>231</v>
       </c>
-      <c r="B119" s="189" t="s">
+      <c r="B120" s="189" t="s">
         <v>122</v>
       </c>
-      <c r="C119" s="122" t="s">
+      <c r="C120" s="122" t="s">
         <v>376</v>
       </c>
-      <c r="D119" s="411" t="s">
+      <c r="D120" s="411" t="s">
         <v>377</v>
       </c>
-      <c r="E119" s="239">
+      <c r="E120" s="239">
         <v>46159</v>
       </c>
-      <c r="F119" s="188">
+      <c r="F120" s="188">
         <v>46160.020833333336</v>
       </c>
-      <c r="G119" s="188">
+      <c r="G120" s="188">
         <f t="shared" si="6"/>
         <v>46162.020833333336</v>
       </c>
-      <c r="H119" s="189">
+      <c r="H120" s="189">
         <v>48</v>
       </c>
-      <c r="I119" s="188">
+      <c r="I120" s="188">
         <f t="shared" si="7"/>
         <v>46162.4375</v>
       </c>
-      <c r="J119" s="190">
+      <c r="J120" s="190">
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:25" s="395" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="246" t="s">
+    <row r="121" spans="1:25" s="395" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="246" t="s">
         <v>231</v>
       </c>
-      <c r="B120" s="391" t="s">
+      <c r="B121" s="391" t="s">
         <v>122</v>
       </c>
-      <c r="C120" s="392" t="s">
+      <c r="C121" s="392" t="s">
         <v>376</v>
       </c>
-      <c r="D120" s="392" t="s">
+      <c r="D121" s="392" t="s">
         <v>378</v>
       </c>
-      <c r="E120" s="393">
+      <c r="E121" s="393">
         <v>46162</v>
       </c>
-      <c r="F120" s="394">
+      <c r="F121" s="394">
         <v>46164.75</v>
       </c>
-      <c r="G120" s="394">
+      <c r="G121" s="394">
         <f t="shared" si="6"/>
         <v>46167.25</v>
       </c>
-      <c r="H120" s="391">
+      <c r="H121" s="391">
         <v>60</v>
       </c>
-      <c r="I120" s="394">
+      <c r="I121" s="394">
         <f t="shared" si="7"/>
         <v>46167.666666666664</v>
       </c>
-      <c r="J120" s="412">
+      <c r="J121" s="412">
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="246" t="s">
+    <row r="122" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="246" t="s">
         <v>231</v>
       </c>
-      <c r="B121" s="32" t="s">
+      <c r="B122" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="C122" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="D121" s="390" t="s">
+      <c r="D122" s="390" t="s">
         <v>380</v>
       </c>
-      <c r="E121" s="54">
+      <c r="E122" s="54">
         <v>46168</v>
       </c>
-      <c r="F121" s="180">
+      <c r="F122" s="180">
         <v>46170.75</v>
       </c>
-      <c r="G121" s="180">
+      <c r="G122" s="180">
         <f t="shared" si="6"/>
         <v>46174.083333333336</v>
       </c>
-      <c r="H121" s="32">
+      <c r="H122" s="32">
         <v>80</v>
       </c>
-      <c r="I121" s="180">
+      <c r="I122" s="180">
         <v>46174.083333333336</v>
       </c>
-      <c r="J121" s="126">
+      <c r="J122" s="126">
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="331" t="s">
+    <row r="123" spans="1:25" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="331" t="s">
         <v>231</v>
       </c>
-      <c r="B122" s="214" t="s">
+      <c r="B123" s="214" t="s">
         <v>122</v>
       </c>
-      <c r="C122" s="212" t="s">
+      <c r="C123" s="212" t="s">
         <v>379</v>
       </c>
-      <c r="D122" s="253" t="s">
+      <c r="D123" s="253" t="s">
         <v>381</v>
       </c>
-      <c r="E122" s="241">
+      <c r="E123" s="241">
         <v>46170</v>
       </c>
-      <c r="F122" s="213">
+      <c r="F123" s="213">
         <v>46172.25</v>
       </c>
-      <c r="G122" s="213">
+      <c r="G123" s="213">
         <f t="shared" si="6"/>
         <v>46176.416666666664</v>
       </c>
-      <c r="H122" s="214">
+      <c r="H123" s="214">
         <v>100</v>
       </c>
-      <c r="I122" s="213">
+      <c r="I123" s="213">
         <v>46174.083333333336</v>
       </c>
-      <c r="J122" s="215">
+      <c r="J123" s="215">
         <v>10</v>
       </c>
-      <c r="Y122" s="1" t="s">
+      <c r="Y123" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="123" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="262" t="s">
-        <v>278</v>
-      </c>
-      <c r="B123" s="189" t="s">
-        <v>163</v>
-      </c>
-      <c r="C123" s="122" t="s">
-        <v>382</v>
-      </c>
-      <c r="D123" s="122" t="s">
-        <v>383</v>
-      </c>
-      <c r="E123" s="239">
-        <v>46193</v>
-      </c>
-      <c r="F123" s="188">
-        <v>46195.875</v>
-      </c>
-      <c r="G123" s="188">
-        <f t="shared" si="6"/>
-        <v>46198.875</v>
-      </c>
-      <c r="H123" s="189">
-        <v>72</v>
-      </c>
-      <c r="I123" s="188">
-        <f t="shared" ref="I123:I163" si="8">G123+(J123/24)</f>
-        <v>46199.875</v>
-      </c>
-      <c r="J123" s="190">
-        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -38919,31 +38921,31 @@
       <c r="C124" s="122" t="s">
         <v>382</v>
       </c>
-      <c r="D124" s="123" t="s">
-        <v>384</v>
-      </c>
-      <c r="E124" s="240">
-        <v>46195</v>
-      </c>
-      <c r="F124" s="183">
-        <v>46197.375</v>
-      </c>
-      <c r="G124" s="205">
-        <f t="shared" ref="G124" si="9">F124+(H124/24)</f>
-        <v>46200.375</v>
-      </c>
-      <c r="H124" s="184">
+      <c r="D124" s="122" t="s">
+        <v>383</v>
+      </c>
+      <c r="E124" s="239">
+        <v>46193</v>
+      </c>
+      <c r="F124" s="188">
+        <v>46195.875</v>
+      </c>
+      <c r="G124" s="188">
+        <f t="shared" si="6"/>
+        <v>46198.875</v>
+      </c>
+      <c r="H124" s="189">
         <v>72</v>
       </c>
-      <c r="I124" s="205">
-        <f t="shared" ref="I124" si="10">G124+(J124/24)</f>
-        <v>46200.875</v>
-      </c>
-      <c r="J124" s="127">
-        <v>12</v>
+      <c r="I124" s="188">
+        <f t="shared" ref="I124:I164" si="8">G124+(J124/24)</f>
+        <v>46199.875</v>
+      </c>
+      <c r="J124" s="190">
+        <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="262" t="s">
         <v>278</v>
       </c>
@@ -38953,27 +38955,27 @@
       <c r="C125" s="122" t="s">
         <v>382</v>
       </c>
-      <c r="D125" s="345" t="s">
-        <v>385</v>
-      </c>
-      <c r="E125" s="421">
-        <v>46200</v>
-      </c>
-      <c r="F125" s="422">
-        <v>46201.375</v>
-      </c>
-      <c r="G125" s="422">
-        <f>F125+(H125/24)</f>
-        <v>46204.875</v>
-      </c>
-      <c r="H125" s="344">
-        <v>84</v>
-      </c>
-      <c r="I125" s="422">
-        <f>G125+(J125/24)</f>
-        <v>46205.375</v>
-      </c>
-      <c r="J125" s="348">
+      <c r="D125" s="123" t="s">
+        <v>384</v>
+      </c>
+      <c r="E125" s="240">
+        <v>46195</v>
+      </c>
+      <c r="F125" s="183">
+        <v>46197.375</v>
+      </c>
+      <c r="G125" s="205">
+        <f t="shared" ref="G125" si="9">F125+(H125/24)</f>
+        <v>46200.375</v>
+      </c>
+      <c r="H125" s="184">
+        <v>72</v>
+      </c>
+      <c r="I125" s="205">
+        <f t="shared" ref="I125" si="10">G125+(J125/24)</f>
+        <v>46200.875</v>
+      </c>
+      <c r="J125" s="127">
         <v>12</v>
       </c>
     </row>
@@ -38985,33 +38987,33 @@
         <v>163</v>
       </c>
       <c r="C126" s="122" t="s">
-        <v>386</v>
-      </c>
-      <c r="D126" s="420" t="s">
-        <v>387</v>
-      </c>
-      <c r="E126" s="406">
-        <v>46202</v>
-      </c>
-      <c r="F126" s="407">
-        <v>46203.5625</v>
+        <v>382</v>
+      </c>
+      <c r="D126" s="345" t="s">
+        <v>385</v>
+      </c>
+      <c r="E126" s="421">
+        <v>46200</v>
+      </c>
+      <c r="F126" s="422">
+        <v>46201.375</v>
       </c>
       <c r="G126" s="422">
-        <f t="shared" ref="G126:G129" si="11">F126+(H126/24)</f>
-        <v>46205.0625</v>
-      </c>
-      <c r="H126" s="404">
-        <v>36</v>
+        <f>F126+(H126/24)</f>
+        <v>46204.875</v>
+      </c>
+      <c r="H126" s="344">
+        <v>84</v>
       </c>
       <c r="I126" s="422">
-        <f t="shared" ref="I126:I129" si="12">G126+(J126/24)</f>
-        <v>46205.5625</v>
+        <f>G126+(J126/24)</f>
+        <v>46205.375</v>
       </c>
       <c r="J126" s="348">
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="262" t="s">
         <v>278</v>
       </c>
@@ -39021,197 +39023,197 @@
       <c r="C127" s="122" t="s">
         <v>386</v>
       </c>
-      <c r="D127" s="426" t="s">
+      <c r="D127" s="420" t="s">
+        <v>387</v>
+      </c>
+      <c r="E127" s="406">
+        <v>46202</v>
+      </c>
+      <c r="F127" s="407">
+        <v>46203.5625</v>
+      </c>
+      <c r="G127" s="422">
+        <f t="shared" ref="G127:G130" si="11">F127+(H127/24)</f>
+        <v>46205.0625</v>
+      </c>
+      <c r="H127" s="404">
+        <v>36</v>
+      </c>
+      <c r="I127" s="422">
+        <f t="shared" ref="I127:I130" si="12">G127+(J127/24)</f>
+        <v>46205.5625</v>
+      </c>
+      <c r="J127" s="348">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A128" s="262" t="s">
+        <v>278</v>
+      </c>
+      <c r="B128" s="189" t="s">
+        <v>163</v>
+      </c>
+      <c r="C128" s="122" t="s">
+        <v>386</v>
+      </c>
+      <c r="D128" s="426" t="s">
         <v>388</v>
       </c>
-      <c r="E127" s="239">
+      <c r="E128" s="239">
         <v>46208</v>
       </c>
-      <c r="F127" s="188">
+      <c r="F128" s="188">
         <v>46209.791666666664</v>
       </c>
-      <c r="G127" s="422">
+      <c r="G128" s="422">
         <f t="shared" si="11"/>
         <v>46211.291666666664</v>
       </c>
-      <c r="H127" s="189">
+      <c r="H128" s="189">
         <v>36</v>
       </c>
-      <c r="I127" s="422">
+      <c r="I128" s="422">
         <f t="shared" si="12"/>
         <v>46211.791666666664</v>
       </c>
-      <c r="J127" s="348">
+      <c r="J128" s="348">
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A128" s="262" t="s">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B128" s="189" t="s">
+      <c r="B129" s="189" t="s">
         <v>163</v>
       </c>
-      <c r="C128" s="122" t="s">
+      <c r="C129" s="122" t="s">
         <v>386</v>
       </c>
-      <c r="D128" s="122" t="s">
+      <c r="D129" s="122" t="s">
         <v>389</v>
       </c>
-      <c r="E128" s="239">
+      <c r="E129" s="239">
         <v>46213</v>
       </c>
-      <c r="F128" s="188">
+      <c r="F129" s="188">
         <v>46214</v>
       </c>
-      <c r="G128" s="422">
+      <c r="G129" s="422">
         <f t="shared" si="11"/>
         <v>46215.5</v>
       </c>
-      <c r="H128" s="189">
+      <c r="H129" s="189">
         <v>36</v>
       </c>
-      <c r="I128" s="422">
+      <c r="I129" s="422">
         <f t="shared" si="12"/>
         <v>46216</v>
       </c>
-      <c r="J128" s="348">
+      <c r="J129" s="348">
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="262" t="s">
+    <row r="130" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B129" s="189" t="s">
+      <c r="B130" s="189" t="s">
         <v>163</v>
       </c>
-      <c r="C129" s="122" t="s">
+      <c r="C130" s="122" t="s">
         <v>386</v>
       </c>
-      <c r="D129" s="426" t="s">
+      <c r="D130" s="426" t="s">
         <v>390</v>
       </c>
-      <c r="E129" s="239">
+      <c r="E130" s="239">
         <v>46217</v>
       </c>
-      <c r="F129" s="188">
+      <c r="F130" s="188">
         <v>46218.875</v>
       </c>
-      <c r="G129" s="422">
+      <c r="G130" s="422">
         <f t="shared" si="11"/>
         <v>46220.375</v>
       </c>
-      <c r="H129" s="189">
+      <c r="H130" s="189">
         <v>36</v>
       </c>
-      <c r="I129" s="422">
+      <c r="I130" s="422">
         <f t="shared" si="12"/>
         <v>46220.875</v>
       </c>
-      <c r="J129" s="348">
+      <c r="J130" s="348">
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="414" t="s">
+    <row r="131" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="414" t="s">
         <v>231</v>
       </c>
-      <c r="B130" s="415" t="s">
+      <c r="B131" s="415" t="s">
         <v>64</v>
       </c>
-      <c r="C130" s="416" t="s">
+      <c r="C131" s="416" t="s">
         <v>391</v>
       </c>
-      <c r="D130" s="416" t="s">
+      <c r="D131" s="416" t="s">
         <v>392</v>
       </c>
-      <c r="E130" s="417">
+      <c r="E131" s="417">
         <v>46162</v>
       </c>
-      <c r="F130" s="417">
+      <c r="F131" s="417">
         <v>46164</v>
       </c>
-      <c r="G130" s="418">
+      <c r="G131" s="418">
         <f t="shared" si="6"/>
         <v>46164.416666666664</v>
       </c>
-      <c r="H130" s="415">
+      <c r="H131" s="415">
         <v>10</v>
       </c>
-      <c r="I130" s="418">
+      <c r="I131" s="418">
         <f t="shared" si="8"/>
         <v>46164.833333333328</v>
       </c>
-      <c r="J130" s="419">
+      <c r="J131" s="419">
         <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="380" t="s">
-        <v>231</v>
-      </c>
-      <c r="B131" s="350" t="s">
-        <v>64</v>
-      </c>
-      <c r="C131" s="349" t="s">
-        <v>391</v>
-      </c>
-      <c r="D131" s="349" t="s">
-        <v>393</v>
-      </c>
-      <c r="E131" s="351">
-        <v>46163</v>
-      </c>
-      <c r="F131" s="351">
-        <v>46165</v>
-      </c>
-      <c r="G131" s="352">
-        <f>F130+(H130/24)</f>
-        <v>46164.416666666664</v>
-      </c>
-      <c r="H131" s="350">
-        <v>5</v>
-      </c>
-      <c r="I131" s="352">
-        <f t="shared" si="8"/>
-        <v>46164.625</v>
-      </c>
-      <c r="J131" s="381">
-        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="380" t="s">
         <v>231</v>
       </c>
-      <c r="B132" s="354" t="s">
+      <c r="B132" s="350" t="s">
         <v>64</v>
       </c>
-      <c r="C132" s="353" t="s">
+      <c r="C132" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="D132" s="185" t="s">
-        <v>394</v>
-      </c>
-      <c r="E132" s="355">
-        <v>46166</v>
-      </c>
-      <c r="F132" s="355">
-        <v>46168</v>
-      </c>
-      <c r="G132" s="356">
-        <f t="shared" ref="G132:G163" si="13">F132+(H132/24)</f>
-        <v>46168.208333333336</v>
-      </c>
-      <c r="H132" s="354">
+      <c r="D132" s="349" t="s">
+        <v>393</v>
+      </c>
+      <c r="E132" s="351">
+        <v>46163</v>
+      </c>
+      <c r="F132" s="351">
+        <v>46165</v>
+      </c>
+      <c r="G132" s="352">
+        <f>F131+(H131/24)</f>
+        <v>46164.416666666664</v>
+      </c>
+      <c r="H132" s="350">
         <v>5</v>
       </c>
-      <c r="I132" s="356">
+      <c r="I132" s="352">
         <f t="shared" si="8"/>
-        <v>46168.416666666672</v>
-      </c>
-      <c r="J132" s="382">
+        <v>46164.625</v>
+      </c>
+      <c r="J132" s="381">
         <v>5</v>
       </c>
     </row>
@@ -39225,129 +39227,129 @@
       <c r="C133" s="353" t="s">
         <v>391</v>
       </c>
-      <c r="D133" s="413" t="s">
+      <c r="D133" s="185" t="s">
+        <v>394</v>
+      </c>
+      <c r="E133" s="355">
+        <v>46166</v>
+      </c>
+      <c r="F133" s="355">
+        <v>46168</v>
+      </c>
+      <c r="G133" s="356">
+        <f t="shared" ref="G133:G164" si="13">F133+(H133/24)</f>
+        <v>46168.208333333336</v>
+      </c>
+      <c r="H133" s="354">
+        <v>5</v>
+      </c>
+      <c r="I133" s="356">
+        <f t="shared" si="8"/>
+        <v>46168.416666666672</v>
+      </c>
+      <c r="J133" s="382">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="380" t="s">
+        <v>231</v>
+      </c>
+      <c r="B134" s="354" t="s">
+        <v>64</v>
+      </c>
+      <c r="C134" s="353" t="s">
+        <v>391</v>
+      </c>
+      <c r="D134" s="413" t="s">
         <v>395</v>
       </c>
-      <c r="E133" s="355">
+      <c r="E134" s="355">
         <v>46170</v>
       </c>
-      <c r="F133" s="355">
+      <c r="F134" s="355">
         <v>46172</v>
       </c>
-      <c r="G133" s="356">
+      <c r="G134" s="356">
         <f t="shared" si="13"/>
         <v>46172.416666666664</v>
       </c>
-      <c r="H133" s="354">
+      <c r="H134" s="354">
         <v>10</v>
       </c>
-      <c r="I133" s="356">
+      <c r="I134" s="356">
         <f t="shared" si="8"/>
         <v>46172.833333333328</v>
       </c>
-      <c r="J133" s="382">
+      <c r="J134" s="382">
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="383" t="s">
+    <row r="135" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="383" t="s">
         <v>278</v>
       </c>
-      <c r="B134" s="404" t="s">
+      <c r="B135" s="404" t="s">
         <v>396</v>
       </c>
-      <c r="C134" s="383" t="s">
+      <c r="C135" s="383" t="s">
         <v>397</v>
       </c>
-      <c r="D134" s="420" t="s">
+      <c r="D135" s="420" t="s">
         <v>398</v>
       </c>
-      <c r="E134" s="406">
+      <c r="E135" s="406">
         <v>46261</v>
       </c>
-      <c r="F134" s="407">
+      <c r="F135" s="407">
         <v>46266.25</v>
       </c>
-      <c r="G134" s="407">
+      <c r="G135" s="407">
         <f t="shared" si="13"/>
         <v>46388.25</v>
       </c>
-      <c r="H134" s="404">
+      <c r="H135" s="404">
         <v>2928</v>
       </c>
-      <c r="I134" s="407">
+      <c r="I135" s="407">
         <f t="shared" si="8"/>
         <v>46388.583333333336</v>
       </c>
-      <c r="J134" s="404">
+      <c r="J135" s="404">
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="262" t="s">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="262" t="s">
         <v>278</v>
       </c>
-      <c r="B135" s="189" t="s">
+      <c r="B136" s="189" t="s">
         <v>232</v>
       </c>
-      <c r="C135" s="122" t="s">
+      <c r="C136" s="122" t="s">
         <v>399</v>
       </c>
-      <c r="D135" s="405" t="s">
+      <c r="D136" s="405" t="s">
         <v>400</v>
       </c>
-      <c r="E135" s="239">
+      <c r="E136" s="239">
         <v>46184</v>
       </c>
-      <c r="F135" s="188">
+      <c r="F136" s="188">
         <v>46188.739583333336</v>
       </c>
-      <c r="G135" s="188">
+      <c r="G136" s="188">
         <f t="shared" si="13"/>
         <v>46190.239583333336</v>
       </c>
-      <c r="H135" s="189">
+      <c r="H136" s="189">
         <v>36</v>
       </c>
-      <c r="I135" s="188">
+      <c r="I136" s="188">
         <f t="shared" si="8"/>
         <v>46190.90625</v>
       </c>
-      <c r="J135" s="190">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="246" t="s">
-        <v>278</v>
-      </c>
-      <c r="B136" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="D136" s="397" t="s">
-        <v>401</v>
-      </c>
-      <c r="E136" s="54">
-        <v>46187</v>
-      </c>
-      <c r="F136" s="180">
-        <v>46189.34375</v>
-      </c>
-      <c r="G136" s="180">
-        <f t="shared" si="13"/>
-        <v>46190.34375</v>
-      </c>
-      <c r="H136" s="32">
-        <v>24</v>
-      </c>
-      <c r="I136" s="180">
-        <f t="shared" si="8"/>
-        <v>46191.010416666664</v>
-      </c>
-      <c r="J136" s="126">
+      <c r="J136" s="190">
         <v>16</v>
       </c>
     </row>
@@ -39361,25 +39363,25 @@
       <c r="C137" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D137" s="392" t="s">
-        <v>402</v>
-      </c>
-      <c r="E137" s="393">
-        <v>46190</v>
-      </c>
-      <c r="F137" s="394">
-        <v>46192.697916666664</v>
-      </c>
-      <c r="G137" s="394">
+      <c r="D137" s="397" t="s">
+        <v>401</v>
+      </c>
+      <c r="E137" s="54">
+        <v>46187</v>
+      </c>
+      <c r="F137" s="180">
+        <v>46189.34375</v>
+      </c>
+      <c r="G137" s="180">
         <f t="shared" si="13"/>
-        <v>46194.197916666664</v>
-      </c>
-      <c r="H137" s="391">
-        <v>36</v>
-      </c>
-      <c r="I137" s="394">
+        <v>46190.34375</v>
+      </c>
+      <c r="H137" s="32">
+        <v>24</v>
+      </c>
+      <c r="I137" s="180">
         <f t="shared" si="8"/>
-        <v>46194.864583333328</v>
+        <v>46191.010416666664</v>
       </c>
       <c r="J137" s="126">
         <v>16</v>
@@ -39396,24 +39398,24 @@
         <v>399</v>
       </c>
       <c r="D138" s="392" t="s">
-        <v>403</v>
-      </c>
-      <c r="E138" s="54">
-        <v>46191</v>
-      </c>
-      <c r="F138" s="180">
-        <v>46194.09375</v>
-      </c>
-      <c r="G138" s="180">
+        <v>402</v>
+      </c>
+      <c r="E138" s="393">
+        <v>46190</v>
+      </c>
+      <c r="F138" s="394">
+        <v>46192.697916666664</v>
+      </c>
+      <c r="G138" s="394">
         <f t="shared" si="13"/>
-        <v>46196.09375</v>
-      </c>
-      <c r="H138" s="32">
-        <v>48</v>
-      </c>
-      <c r="I138" s="180">
+        <v>46194.197916666664</v>
+      </c>
+      <c r="H138" s="391">
+        <v>36</v>
+      </c>
+      <c r="I138" s="394">
         <f t="shared" si="8"/>
-        <v>46196.760416666664</v>
+        <v>46194.864583333328</v>
       </c>
       <c r="J138" s="126">
         <v>16</v>
@@ -39430,24 +39432,24 @@
         <v>399</v>
       </c>
       <c r="D139" s="392" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E139" s="54">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="F139" s="180">
-        <v>46198.40625</v>
+        <v>46194.09375</v>
       </c>
       <c r="G139" s="180">
         <f t="shared" si="13"/>
-        <v>46199.40625</v>
+        <v>46196.09375</v>
       </c>
       <c r="H139" s="32">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I139" s="180">
         <f t="shared" si="8"/>
-        <v>46200.072916666664</v>
+        <v>46196.760416666664</v>
       </c>
       <c r="J139" s="126">
         <v>16</v>
@@ -39463,164 +39465,164 @@
       <c r="C140" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D140" s="397" t="s">
-        <v>405</v>
+      <c r="D140" s="392" t="s">
+        <v>404</v>
       </c>
       <c r="E140" s="54">
-        <v>46207</v>
+        <v>46196</v>
       </c>
       <c r="F140" s="180">
-        <v>46209.036111111112</v>
+        <v>46198.40625</v>
       </c>
       <c r="G140" s="180">
         <f t="shared" si="13"/>
-        <v>46210.036111111112</v>
+        <v>46199.40625</v>
       </c>
       <c r="H140" s="32">
         <v>24</v>
       </c>
       <c r="I140" s="180">
         <f t="shared" si="8"/>
-        <v>46210.702777777777</v>
+        <v>46200.072916666664</v>
       </c>
       <c r="J140" s="126">
         <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="379" t="s">
+      <c r="A141" s="246" t="s">
         <v>278</v>
       </c>
-      <c r="B141" s="243" t="s">
+      <c r="B141" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="C141" s="244" t="s">
+      <c r="C141" s="7" t="s">
         <v>399</v>
       </c>
       <c r="D141" s="397" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E141" s="54">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="F141" s="180">
-        <v>46211.036111111112</v>
-      </c>
-      <c r="G141" s="245">
-        <f>F141+(H141/24)</f>
-        <v>46212.036111111112</v>
+        <v>46209.036111111112</v>
+      </c>
+      <c r="G141" s="180">
+        <f t="shared" si="13"/>
+        <v>46210.036111111112</v>
       </c>
       <c r="H141" s="32">
         <v>24</v>
       </c>
-      <c r="I141" s="245">
-        <f>G141+(J141/24)</f>
-        <v>46212.702777777777</v>
+      <c r="I141" s="180">
+        <f t="shared" si="8"/>
+        <v>46210.702777777777</v>
       </c>
       <c r="J141" s="126">
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="400" t="s">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" s="379" t="s">
         <v>278</v>
       </c>
-      <c r="B142" s="401" t="s">
+      <c r="B142" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="C142" s="402" t="s">
+      <c r="C142" s="244" t="s">
         <v>399</v>
       </c>
-      <c r="D142" s="403" t="s">
+      <c r="D142" s="397" t="s">
+        <v>406</v>
+      </c>
+      <c r="E142" s="54">
+        <v>46209</v>
+      </c>
+      <c r="F142" s="180">
+        <v>46211.036111111112</v>
+      </c>
+      <c r="G142" s="245">
+        <f>F142+(H142/24)</f>
+        <v>46212.036111111112</v>
+      </c>
+      <c r="H142" s="32">
+        <v>24</v>
+      </c>
+      <c r="I142" s="245">
+        <f>G142+(J142/24)</f>
+        <v>46212.702777777777</v>
+      </c>
+      <c r="J142" s="126">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="400" t="s">
+        <v>278</v>
+      </c>
+      <c r="B143" s="401" t="s">
+        <v>232</v>
+      </c>
+      <c r="C143" s="402" t="s">
+        <v>399</v>
+      </c>
+      <c r="D143" s="403" t="s">
         <v>407</v>
       </c>
-      <c r="E142" s="240">
+      <c r="E143" s="240">
         <v>46217</v>
       </c>
-      <c r="F142" s="183">
+      <c r="F143" s="183">
         <v>46219.691666666666</v>
       </c>
-      <c r="G142" s="205">
-        <f>F142+(H142/24)</f>
+      <c r="G143" s="205">
+        <f>F143+(H143/24)</f>
         <v>46220.691666666666</v>
       </c>
-      <c r="H142" s="184">
+      <c r="H143" s="184">
         <v>24</v>
       </c>
-      <c r="I142" s="205">
-        <f>G142+(J142/24)</f>
+      <c r="I143" s="205">
+        <f>G143+(J143/24)</f>
         <v>46221.35833333333</v>
       </c>
-      <c r="J142" s="127">
+      <c r="J143" s="127">
         <v>16</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="187" t="s">
-        <v>278</v>
-      </c>
-      <c r="B143" s="170" t="s">
-        <v>64</v>
-      </c>
-      <c r="C143" s="187" t="s">
-        <v>408</v>
-      </c>
-      <c r="D143" s="398" t="s">
-        <v>409</v>
-      </c>
-      <c r="E143" s="242">
-        <v>46193</v>
-      </c>
-      <c r="F143" s="181">
-        <v>46195.25</v>
-      </c>
-      <c r="G143" s="181">
-        <f>F143+(H143/24)</f>
-        <v>46197.25</v>
-      </c>
-      <c r="H143" s="399">
-        <v>48</v>
-      </c>
-      <c r="I143" s="181">
-        <f>G143+(J143/24)</f>
-        <v>46197.5</v>
-      </c>
-      <c r="J143" s="399">
-        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="335" t="s">
+      <c r="A144" s="187" t="s">
         <v>278</v>
       </c>
-      <c r="B144" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D144" s="423" t="s">
-        <v>411</v>
-      </c>
-      <c r="E144" s="54">
-        <v>46191</v>
-      </c>
-      <c r="F144" s="180">
-        <v>46194.833333333336</v>
-      </c>
-      <c r="G144" s="180">
+      <c r="B144" s="170" t="s">
+        <v>64</v>
+      </c>
+      <c r="C144" s="187" t="s">
+        <v>408</v>
+      </c>
+      <c r="D144" s="398" t="s">
+        <v>409</v>
+      </c>
+      <c r="E144" s="242">
+        <v>46193</v>
+      </c>
+      <c r="F144" s="181">
+        <v>46195.25</v>
+      </c>
+      <c r="G144" s="181">
         <f>F144+(H144/24)</f>
-        <v>46201.854166666672</v>
-      </c>
-      <c r="H144" s="32">
-        <v>168.5</v>
-      </c>
-      <c r="I144" s="180">
+        <v>46197.25</v>
+      </c>
+      <c r="H144" s="399">
+        <v>48</v>
+      </c>
+      <c r="I144" s="181">
         <f>G144+(J144/24)</f>
-        <v>46203.354166666672</v>
-      </c>
-      <c r="J144" s="32">
-        <v>36</v>
+        <v>46197.5</v>
+      </c>
+      <c r="J144" s="399">
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.25">
@@ -39631,27 +39633,27 @@
         <v>20</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="D145" s="390" t="s">
-        <v>413</v>
+        <v>410</v>
+      </c>
+      <c r="D145" s="423" t="s">
+        <v>411</v>
       </c>
       <c r="E145" s="54">
-        <v>46930</v>
-      </c>
-      <c r="F145" s="336">
-        <v>46201.854166666664</v>
+        <v>46191</v>
+      </c>
+      <c r="F145" s="180">
+        <v>46194.833333333336</v>
       </c>
       <c r="G145" s="180">
-        <f t="shared" si="13"/>
-        <v>46207.229166666664</v>
+        <f>F145+(H145/24)</f>
+        <v>46201.854166666672</v>
       </c>
       <c r="H145" s="32">
-        <v>129</v>
+        <v>168.5</v>
       </c>
       <c r="I145" s="180">
-        <f t="shared" si="8"/>
-        <v>46208.729166666664</v>
+        <f>G145+(J145/24)</f>
+        <v>46203.354166666672</v>
       </c>
       <c r="J145" s="32">
         <v>36</v>
@@ -39665,27 +39667,27 @@
         <v>20</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="D146" s="423" t="s">
-        <v>415</v>
+        <v>412</v>
+      </c>
+      <c r="D146" s="390" t="s">
+        <v>413</v>
       </c>
       <c r="E146" s="54">
-        <v>46186</v>
+        <v>46930</v>
       </c>
       <c r="F146" s="336">
-        <v>46189.25</v>
+        <v>46201.854166666664</v>
       </c>
       <c r="G146" s="180">
-        <f>F146+(H146/24)</f>
-        <v>46193.25</v>
+        <f t="shared" si="13"/>
+        <v>46207.229166666664</v>
       </c>
       <c r="H146" s="32">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="I146" s="180">
-        <f>G146+(J146/24)</f>
-        <v>46194.75</v>
+        <f t="shared" si="8"/>
+        <v>46208.729166666664</v>
       </c>
       <c r="J146" s="32">
         <v>36</v>
@@ -39695,50 +39697,35 @@
       <c r="A147" s="335" t="s">
         <v>278</v>
       </c>
-      <c r="B147" s="243" t="s">
+      <c r="B147" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C147" s="244" t="s">
+      <c r="C147" s="7" t="s">
         <v>414</v>
       </c>
       <c r="D147" s="423" t="s">
-        <v>416</v>
-      </c>
-      <c r="E147" s="424">
-        <v>46327</v>
+        <v>415</v>
+      </c>
+      <c r="E147" s="54">
+        <v>46186</v>
       </c>
       <c r="F147" s="336">
-        <v>46330.25</v>
-      </c>
-      <c r="G147" s="245">
-        <f t="shared" si="13"/>
-        <v>46334.25</v>
-      </c>
-      <c r="H147" s="243">
+        <v>46189.25</v>
+      </c>
+      <c r="G147" s="180">
+        <f>F147+(H147/24)</f>
+        <v>46193.25</v>
+      </c>
+      <c r="H147" s="32">
         <v>96</v>
       </c>
-      <c r="I147" s="245">
-        <f t="shared" si="8"/>
-        <v>46335.75</v>
-      </c>
-      <c r="J147" s="243">
+      <c r="I147" s="180">
+        <f>G147+(J147/24)</f>
+        <v>46194.75</v>
+      </c>
+      <c r="J147" s="32">
         <v>36</v>
       </c>
-      <c r="K147" s="425"/>
-      <c r="L147" s="425"/>
-      <c r="M147" s="425"/>
-      <c r="N147" s="425"/>
-      <c r="O147" s="425"/>
-      <c r="P147" s="425"/>
-      <c r="Q147" s="425"/>
-      <c r="R147" s="425"/>
-      <c r="S147" s="425"/>
-      <c r="T147" s="425"/>
-      <c r="U147" s="425"/>
-      <c r="V147" s="425"/>
-      <c r="W147" s="425"/>
-      <c r="X147" s="425"/>
-      <c r="Y147" s="425"/>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="335" t="s">
@@ -39751,24 +39738,24 @@
         <v>414</v>
       </c>
       <c r="D148" s="423" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E148" s="424">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="F148" s="336">
-        <v>46334.25</v>
+        <v>46330.25</v>
       </c>
       <c r="G148" s="245">
         <f t="shared" si="13"/>
-        <v>46338.25</v>
+        <v>46334.25</v>
       </c>
       <c r="H148" s="243">
         <v>96</v>
       </c>
       <c r="I148" s="245">
         <f t="shared" si="8"/>
-        <v>46339.75</v>
+        <v>46335.75</v>
       </c>
       <c r="J148" s="243">
         <v>36</v>
@@ -39800,24 +39787,24 @@
         <v>414</v>
       </c>
       <c r="D149" s="423" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E149" s="424">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="F149" s="336">
-        <v>46344.25</v>
+        <v>46334.25</v>
       </c>
       <c r="G149" s="245">
         <f t="shared" si="13"/>
-        <v>46348.25</v>
+        <v>46338.25</v>
       </c>
       <c r="H149" s="243">
         <v>96</v>
       </c>
       <c r="I149" s="245">
         <f t="shared" si="8"/>
-        <v>46349.75</v>
+        <v>46339.75</v>
       </c>
       <c r="J149" s="243">
         <v>36</v>
@@ -39849,24 +39836,24 @@
         <v>414</v>
       </c>
       <c r="D150" s="423" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E150" s="424">
-        <v>46348</v>
+        <v>46341</v>
       </c>
       <c r="F150" s="336">
-        <v>46351.25</v>
+        <v>46344.25</v>
       </c>
       <c r="G150" s="245">
         <f t="shared" si="13"/>
-        <v>46355.25</v>
+        <v>46348.25</v>
       </c>
       <c r="H150" s="243">
         <v>96</v>
       </c>
       <c r="I150" s="245">
         <f t="shared" si="8"/>
-        <v>46356.75</v>
+        <v>46349.75</v>
       </c>
       <c r="J150" s="243">
         <v>36</v>
@@ -39898,24 +39885,24 @@
         <v>414</v>
       </c>
       <c r="D151" s="423" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E151" s="424">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="F151" s="336">
-        <v>46358.25</v>
+        <v>46351.25</v>
       </c>
       <c r="G151" s="245">
         <f t="shared" si="13"/>
-        <v>46362.25</v>
+        <v>46355.25</v>
       </c>
       <c r="H151" s="243">
         <v>96</v>
       </c>
       <c r="I151" s="245">
         <f t="shared" si="8"/>
-        <v>46363.75</v>
+        <v>46356.75</v>
       </c>
       <c r="J151" s="243">
         <v>36</v>
@@ -39941,33 +39928,33 @@
         <v>278</v>
       </c>
       <c r="B152" s="243" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="C152" s="244" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D152" s="423" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E152" s="424">
-        <v>46189</v>
+        <v>46355</v>
       </c>
       <c r="F152" s="336">
-        <v>46191.583333333336</v>
+        <v>46358.25</v>
       </c>
       <c r="G152" s="245">
         <f t="shared" si="13"/>
-        <v>46193.083333333336</v>
+        <v>46362.25</v>
       </c>
       <c r="H152" s="243">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="I152" s="245">
         <f t="shared" si="8"/>
-        <v>46193.583333333336</v>
+        <v>46363.75</v>
       </c>
       <c r="J152" s="243">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K152" s="425"/>
       <c r="L152" s="425"/>
@@ -39993,31 +39980,46 @@
         <v>122</v>
       </c>
       <c r="C153" s="244" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D153" s="423" t="s">
-        <v>424</v>
-      </c>
-      <c r="E153" s="54">
-        <v>46192</v>
-      </c>
-      <c r="F153" s="180">
-        <v>46194.5625</v>
-      </c>
-      <c r="G153" s="180">
+        <v>422</v>
+      </c>
+      <c r="E153" s="424">
+        <v>46189</v>
+      </c>
+      <c r="F153" s="336">
+        <v>46191.583333333336</v>
+      </c>
+      <c r="G153" s="245">
         <f t="shared" si="13"/>
-        <v>46196.0625</v>
+        <v>46193.083333333336</v>
       </c>
       <c r="H153" s="243">
         <v>36</v>
       </c>
-      <c r="I153" s="180">
+      <c r="I153" s="245">
         <f t="shared" si="8"/>
-        <v>46196.5625</v>
+        <v>46193.583333333336</v>
       </c>
       <c r="J153" s="243">
         <v>12</v>
       </c>
+      <c r="K153" s="425"/>
+      <c r="L153" s="425"/>
+      <c r="M153" s="425"/>
+      <c r="N153" s="425"/>
+      <c r="O153" s="425"/>
+      <c r="P153" s="425"/>
+      <c r="Q153" s="425"/>
+      <c r="R153" s="425"/>
+      <c r="S153" s="425"/>
+      <c r="T153" s="425"/>
+      <c r="U153" s="425"/>
+      <c r="V153" s="425"/>
+      <c r="W153" s="425"/>
+      <c r="X153" s="425"/>
+      <c r="Y153" s="425"/>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="335" t="s">
@@ -40030,24 +40032,24 @@
         <v>423</v>
       </c>
       <c r="D154" s="423" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E154" s="54">
-        <v>46197</v>
+        <v>46192</v>
       </c>
       <c r="F154" s="180">
-        <v>46199.916666666664</v>
+        <v>46194.5625</v>
       </c>
       <c r="G154" s="180">
         <f t="shared" si="13"/>
-        <v>46201.416666666664</v>
+        <v>46196.0625</v>
       </c>
       <c r="H154" s="243">
         <v>36</v>
       </c>
       <c r="I154" s="180">
         <f t="shared" si="8"/>
-        <v>46201.916666666664</v>
+        <v>46196.5625</v>
       </c>
       <c r="J154" s="243">
         <v>12</v>
@@ -40064,24 +40066,24 @@
         <v>423</v>
       </c>
       <c r="D155" s="423" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E155" s="54">
-        <v>46203</v>
+        <v>46197</v>
       </c>
       <c r="F155" s="180">
-        <v>46205.375</v>
+        <v>46199.916666666664</v>
       </c>
       <c r="G155" s="180">
         <f t="shared" si="13"/>
-        <v>46206.875</v>
+        <v>46201.416666666664</v>
       </c>
       <c r="H155" s="243">
         <v>36</v>
       </c>
       <c r="I155" s="180">
         <f t="shared" si="8"/>
-        <v>46207.375</v>
+        <v>46201.916666666664</v>
       </c>
       <c r="J155" s="243">
         <v>12</v>
@@ -40098,24 +40100,24 @@
         <v>423</v>
       </c>
       <c r="D156" s="423" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E156" s="54">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="F156" s="180">
-        <v>46217.229166666664</v>
+        <v>46205.375</v>
       </c>
       <c r="G156" s="180">
         <f t="shared" si="13"/>
-        <v>46218.729166666664</v>
+        <v>46206.875</v>
       </c>
       <c r="H156" s="243">
         <v>36</v>
       </c>
       <c r="I156" s="180">
         <f t="shared" si="8"/>
-        <v>46219.229166666664</v>
+        <v>46207.375</v>
       </c>
       <c r="J156" s="243">
         <v>12</v>
@@ -40132,10 +40134,10 @@
         <v>423</v>
       </c>
       <c r="D157" s="423" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E157" s="54">
-        <v>46215</v>
+        <v>46206</v>
       </c>
       <c r="F157" s="180">
         <v>46217.229166666664</v>
@@ -40166,24 +40168,24 @@
         <v>423</v>
       </c>
       <c r="D158" s="423" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E158" s="54">
-        <v>46219</v>
+        <v>46215</v>
       </c>
       <c r="F158" s="180">
-        <v>46221.1875</v>
+        <v>46217.229166666664</v>
       </c>
       <c r="G158" s="180">
         <f t="shared" si="13"/>
-        <v>46222.6875</v>
+        <v>46218.729166666664</v>
       </c>
       <c r="H158" s="243">
         <v>36</v>
       </c>
       <c r="I158" s="180">
         <f t="shared" si="8"/>
-        <v>46223.1875</v>
+        <v>46219.229166666664</v>
       </c>
       <c r="J158" s="243">
         <v>12</v>
@@ -40200,24 +40202,24 @@
         <v>423</v>
       </c>
       <c r="D159" s="423" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E159" s="54">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="F159" s="180">
-        <v>46226.729166666664</v>
+        <v>46221.1875</v>
       </c>
       <c r="G159" s="180">
         <f t="shared" si="13"/>
-        <v>46228.229166666664</v>
+        <v>46222.6875</v>
       </c>
       <c r="H159" s="243">
         <v>36</v>
       </c>
       <c r="I159" s="180">
         <f t="shared" si="8"/>
-        <v>46228.729166666664</v>
+        <v>46223.1875</v>
       </c>
       <c r="J159" s="243">
         <v>12</v>
@@ -40234,24 +40236,24 @@
         <v>423</v>
       </c>
       <c r="D160" s="423" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E160" s="54">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="F160" s="180">
-        <v>46232.645833333336</v>
+        <v>46226.729166666664</v>
       </c>
       <c r="G160" s="180">
         <f t="shared" si="13"/>
-        <v>46234.145833333336</v>
+        <v>46228.229166666664</v>
       </c>
       <c r="H160" s="243">
         <v>36</v>
       </c>
       <c r="I160" s="180">
         <f t="shared" si="8"/>
-        <v>46234.645833333336</v>
+        <v>46228.729166666664</v>
       </c>
       <c r="J160" s="243">
         <v>12</v>
@@ -40268,24 +40270,24 @@
         <v>423</v>
       </c>
       <c r="D161" s="423" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E161" s="54">
-        <v>46235</v>
+        <v>46230</v>
       </c>
       <c r="F161" s="180">
-        <v>46237.833333333336</v>
+        <v>46232.645833333336</v>
       </c>
       <c r="G161" s="180">
         <f t="shared" si="13"/>
-        <v>46239.333333333336</v>
+        <v>46234.145833333336</v>
       </c>
       <c r="H161" s="243">
         <v>36</v>
       </c>
       <c r="I161" s="180">
         <f t="shared" si="8"/>
-        <v>46239.833333333336</v>
+        <v>46234.645833333336</v>
       </c>
       <c r="J161" s="243">
         <v>12</v>
@@ -40302,95 +40304,95 @@
         <v>423</v>
       </c>
       <c r="D162" s="423" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E162" s="54">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="F162" s="180">
-        <v>46240.75</v>
+        <v>46237.833333333336</v>
       </c>
       <c r="G162" s="180">
         <f t="shared" si="13"/>
-        <v>46242.25</v>
+        <v>46239.333333333336</v>
       </c>
       <c r="H162" s="243">
         <v>36</v>
       </c>
       <c r="I162" s="180">
         <f t="shared" si="8"/>
-        <v>46242.75</v>
+        <v>46239.833333333336</v>
       </c>
       <c r="J162" s="243">
         <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="433" t="s">
+      <c r="A163" s="335" t="s">
         <v>278</v>
       </c>
-      <c r="B163" s="408" t="s">
+      <c r="B163" s="243" t="s">
         <v>122</v>
       </c>
-      <c r="C163" s="410" t="s">
+      <c r="C163" s="244" t="s">
         <v>423</v>
       </c>
-      <c r="D163" s="434" t="s">
+      <c r="D163" s="423" t="s">
+        <v>433</v>
+      </c>
+      <c r="E163" s="54">
+        <v>46238</v>
+      </c>
+      <c r="F163" s="180">
+        <v>46240.75</v>
+      </c>
+      <c r="G163" s="180">
+        <f t="shared" si="13"/>
+        <v>46242.25</v>
+      </c>
+      <c r="H163" s="243">
+        <v>36</v>
+      </c>
+      <c r="I163" s="180">
+        <f t="shared" si="8"/>
+        <v>46242.75</v>
+      </c>
+      <c r="J163" s="243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="433" t="s">
+        <v>278</v>
+      </c>
+      <c r="B164" s="408" t="s">
+        <v>122</v>
+      </c>
+      <c r="C164" s="410" t="s">
+        <v>423</v>
+      </c>
+      <c r="D164" s="434" t="s">
         <v>434</v>
       </c>
-      <c r="E163" s="241">
+      <c r="E164" s="241">
         <v>46245</v>
       </c>
-      <c r="F163" s="213">
+      <c r="F164" s="213">
         <v>46247.479166666664</v>
       </c>
-      <c r="G163" s="213">
+      <c r="G164" s="213">
         <f t="shared" si="13"/>
         <v>46248.979166666664</v>
       </c>
-      <c r="H163" s="408">
+      <c r="H164" s="408">
         <v>36</v>
       </c>
-      <c r="I163" s="213">
+      <c r="I164" s="213">
         <f t="shared" si="8"/>
         <v>46249.479166666664</v>
       </c>
-      <c r="J163" s="408">
+      <c r="J164" s="408">
         <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="435" t="s">
-        <v>278</v>
-      </c>
-      <c r="B164" s="354" t="s">
-        <v>64</v>
-      </c>
-      <c r="C164" s="435" t="s">
-        <v>435</v>
-      </c>
-      <c r="D164" s="436" t="s">
-        <v>436</v>
-      </c>
-      <c r="E164" s="355">
-        <v>46184</v>
-      </c>
-      <c r="F164" s="356">
-        <v>46185</v>
-      </c>
-      <c r="G164" s="181">
-        <f>F164+(H164/24)</f>
-        <v>46187</v>
-      </c>
-      <c r="H164" s="399">
-        <v>48</v>
-      </c>
-      <c r="I164" s="181">
-        <f>G164+(J164/24)</f>
-        <v>46187.25</v>
-      </c>
-      <c r="J164" s="437">
-        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -40400,57 +40402,57 @@
       <c r="B165" s="354" t="s">
         <v>64</v>
       </c>
-      <c r="C165" s="349" t="s">
-        <v>437</v>
-      </c>
-      <c r="D165" s="435" t="s">
-        <v>473</v>
+      <c r="C165" s="435" t="s">
+        <v>435</v>
+      </c>
+      <c r="D165" s="436" t="s">
+        <v>436</v>
       </c>
       <c r="E165" s="355">
-        <v>46191</v>
+        <v>46184</v>
       </c>
       <c r="F165" s="356">
-        <v>46192</v>
-      </c>
-      <c r="G165" s="336">
+        <v>46185</v>
+      </c>
+      <c r="G165" s="181">
         <f>F165+(H165/24)</f>
-        <v>46194</v>
+        <v>46187</v>
       </c>
       <c r="H165" s="399">
         <v>48</v>
       </c>
-      <c r="I165" s="336">
+      <c r="I165" s="181">
         <f>G165+(J165/24)</f>
-        <v>46194.25</v>
+        <v>46187.25</v>
       </c>
       <c r="J165" s="437">
         <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="349" t="s">
+      <c r="A166" s="435" t="s">
         <v>278</v>
       </c>
-      <c r="B166" s="350" t="s">
+      <c r="B166" s="354" t="s">
         <v>64</v>
       </c>
       <c r="C166" s="349" t="s">
-        <v>474</v>
-      </c>
-      <c r="D166" s="349" t="s">
-        <v>475</v>
-      </c>
-      <c r="E166" s="564">
+        <v>437</v>
+      </c>
+      <c r="D166" s="435" t="s">
+        <v>473</v>
+      </c>
+      <c r="E166" s="355">
         <v>46191</v>
       </c>
-      <c r="F166" s="563">
+      <c r="F166" s="356">
         <v>46192</v>
       </c>
       <c r="G166" s="336">
         <f>F166+(H166/24)</f>
         <v>46194</v>
       </c>
-      <c r="H166" s="565">
+      <c r="H166" s="399">
         <v>48</v>
       </c>
       <c r="I166" s="336">
@@ -40469,34 +40471,68 @@
         <v>64</v>
       </c>
       <c r="C167" s="349" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="D167" s="349" t="s">
-        <v>439</v>
-      </c>
-      <c r="E167" s="351">
-        <v>46198</v>
-      </c>
-      <c r="F167" s="352">
-        <v>46199.25</v>
+        <v>475</v>
+      </c>
+      <c r="E167" s="439">
+        <v>46191</v>
+      </c>
+      <c r="F167" s="438">
+        <v>46192</v>
       </c>
       <c r="G167" s="336">
         <f>F167+(H167/24)</f>
-        <v>46201.25</v>
-      </c>
-      <c r="H167" s="565">
+        <v>46194</v>
+      </c>
+      <c r="H167" s="440">
         <v>48</v>
       </c>
       <c r="I167" s="336">
         <f>G167+(J167/24)</f>
-        <v>46201.5</v>
+        <v>46194.25</v>
       </c>
       <c r="J167" s="437">
         <v>6</v>
       </c>
     </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="349" t="s">
+        <v>278</v>
+      </c>
+      <c r="B168" s="350" t="s">
+        <v>64</v>
+      </c>
+      <c r="C168" s="349" t="s">
+        <v>438</v>
+      </c>
+      <c r="D168" s="349" t="s">
+        <v>439</v>
+      </c>
+      <c r="E168" s="351">
+        <v>46198</v>
+      </c>
+      <c r="F168" s="352">
+        <v>46199.25</v>
+      </c>
+      <c r="G168" s="336">
+        <f>F168+(H168/24)</f>
+        <v>46201.25</v>
+      </c>
+      <c r="H168" s="440">
+        <v>48</v>
+      </c>
+      <c r="I168" s="336">
+        <f>G168+(J168/24)</f>
+        <v>46201.5</v>
+      </c>
+      <c r="J168" s="437">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J163" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
+  <autoFilter ref="A1:J164" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
     <filterColumn colId="0">
       <filters blank="1">
         <filter val="Planned"/>
@@ -40505,20 +40541,20 @@
   </autoFilter>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D144" r:id="rId1" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:61104:" xr:uid="{D17E0007-350A-4606-AF8D-4F4113C58BAF}"/>
-    <hyperlink ref="D147" r:id="rId2" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60703:" xr:uid="{2CE69447-1583-4285-A3C6-E44253861F50}"/>
-    <hyperlink ref="D148" r:id="rId3" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60704:" xr:uid="{9B646115-87F0-4E9B-A26C-E8EDC2346D02}"/>
-    <hyperlink ref="D149" r:id="rId4" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60705:" xr:uid="{E88F1C80-86A4-402C-A7FA-01CE4B12C622}"/>
-    <hyperlink ref="D150" r:id="rId5" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60706:" xr:uid="{ED524307-DD66-4DB1-9398-118E3CD28160}"/>
-    <hyperlink ref="D151" r:id="rId6" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60707:" xr:uid="{2A3CDFC3-31C8-44B2-8428-4BB6443AB947}"/>
-    <hyperlink ref="D146" r:id="rId7" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60493:" xr:uid="{F26E0D90-75CF-4C75-BE7C-46BD69259230}"/>
-    <hyperlink ref="C152" r:id="rId8" xr:uid="{4BF92AC9-6F81-47D3-BADE-793677667278}"/>
-    <hyperlink ref="D153" r:id="rId9" xr:uid="{E005730F-31E3-4D24-9CAD-7F0A40A90785}"/>
-    <hyperlink ref="D154" r:id="rId10" xr:uid="{CD88DAD3-3FF4-4E5B-8E2B-399AE5F81F59}"/>
-    <hyperlink ref="D155" r:id="rId11" xr:uid="{E7B658C7-FFEB-4978-9A4E-D4E57D76FD92}"/>
-    <hyperlink ref="D156" r:id="rId12" xr:uid="{BB857F62-9EFB-4532-9E08-F51A99F5A052}"/>
-    <hyperlink ref="D157" r:id="rId13" xr:uid="{EC5EC0AC-3F5B-4A38-BEE4-5ABDE438163E}"/>
-    <hyperlink ref="D158" r:id="rId14" xr:uid="{42CF593B-3B32-4FD3-BF01-D92D8C273D20}"/>
+    <hyperlink ref="D145" r:id="rId1" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:61104:" xr:uid="{D17E0007-350A-4606-AF8D-4F4113C58BAF}"/>
+    <hyperlink ref="D148" r:id="rId2" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60703:" xr:uid="{2CE69447-1583-4285-A3C6-E44253861F50}"/>
+    <hyperlink ref="D149" r:id="rId3" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60704:" xr:uid="{9B646115-87F0-4E9B-A26C-E8EDC2346D02}"/>
+    <hyperlink ref="D150" r:id="rId4" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60705:" xr:uid="{E88F1C80-86A4-402C-A7FA-01CE4B12C622}"/>
+    <hyperlink ref="D151" r:id="rId5" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60706:" xr:uid="{ED524307-DD66-4DB1-9398-118E3CD28160}"/>
+    <hyperlink ref="D152" r:id="rId6" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60707:" xr:uid="{2A3CDFC3-31C8-44B2-8428-4BB6443AB947}"/>
+    <hyperlink ref="D147" r:id="rId7" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60493:" xr:uid="{F26E0D90-75CF-4C75-BE7C-46BD69259230}"/>
+    <hyperlink ref="C153" r:id="rId8" xr:uid="{4BF92AC9-6F81-47D3-BADE-793677667278}"/>
+    <hyperlink ref="D154" r:id="rId9" xr:uid="{E005730F-31E3-4D24-9CAD-7F0A40A90785}"/>
+    <hyperlink ref="D155" r:id="rId10" xr:uid="{CD88DAD3-3FF4-4E5B-8E2B-399AE5F81F59}"/>
+    <hyperlink ref="D156" r:id="rId11" xr:uid="{E7B658C7-FFEB-4978-9A4E-D4E57D76FD92}"/>
+    <hyperlink ref="D157" r:id="rId12" xr:uid="{BB857F62-9EFB-4532-9E08-F51A99F5A052}"/>
+    <hyperlink ref="D158" r:id="rId13" xr:uid="{EC5EC0AC-3F5B-4A38-BEE4-5ABDE438163E}"/>
+    <hyperlink ref="D159" r:id="rId14" xr:uid="{42CF593B-3B32-4FD3-BF01-D92D8C273D20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
@@ -40537,24 +40573,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="557" t="s">
+      <c r="B1" s="560" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="558"/>
-      <c r="D1" s="558"/>
-      <c r="E1" s="559"/>
-      <c r="F1" s="557" t="s">
+      <c r="C1" s="561"/>
+      <c r="D1" s="561"/>
+      <c r="E1" s="562"/>
+      <c r="F1" s="560" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="558"/>
-      <c r="H1" s="558"/>
-      <c r="I1" s="559"/>
-      <c r="J1" s="557" t="s">
+      <c r="G1" s="561"/>
+      <c r="H1" s="561"/>
+      <c r="I1" s="562"/>
+      <c r="J1" s="560" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="558"/>
-      <c r="L1" s="558"/>
-      <c r="M1" s="559"/>
+      <c r="K1" s="561"/>
+      <c r="L1" s="561"/>
+      <c r="M1" s="562"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="70"/>
@@ -40797,11 +40833,11 @@
       <c r="D13" s="94"/>
       <c r="E13" s="95"/>
       <c r="F13" s="96"/>
-      <c r="G13" s="560" t="s">
+      <c r="G13" s="563" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="561"/>
-      <c r="I13" s="562"/>
+      <c r="H13" s="564"/>
+      <c r="I13" s="565"/>
       <c r="J13" s="98" t="s">
         <v>465</v>
       </c>

--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8828" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B711C60B-ECB9-4E9D-B31F-35C84BC9D311}"/>
+  <xr:revisionPtr revIDLastSave="8844" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5878055-B7A9-4B9D-A15C-A979FE1DE677}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-4590" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="11_17_2025 Spot Hire Update" sheetId="2" r:id="rId1"/>
@@ -4736,6 +4736,15 @@
     <xf numFmtId="14" fontId="10" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4745,13 +4754,139 @@
     <xf numFmtId="0" fontId="19" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -4763,6 +4898,42 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4793,175 +4964,7 @@
     <xf numFmtId="14" fontId="10" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -5022,9 +5025,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -29340,56 +29340,56 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="475">
+      <c r="G7" s="532">
         <v>2026</v>
       </c>
-      <c r="H7" s="475"/>
-      <c r="I7" s="475"/>
-      <c r="J7" s="475"/>
-      <c r="K7" s="475"/>
-      <c r="L7" s="475"/>
-      <c r="M7" s="475"/>
-      <c r="N7" s="475"/>
-      <c r="O7" s="475"/>
-      <c r="P7" s="475"/>
-      <c r="Q7" s="475"/>
-      <c r="R7" s="475"/>
-      <c r="S7" s="475"/>
-      <c r="T7" s="475"/>
-      <c r="U7" s="475"/>
-      <c r="V7" s="475"/>
-      <c r="W7" s="475"/>
-      <c r="X7" s="475"/>
-      <c r="Y7" s="475"/>
-      <c r="Z7" s="475"/>
-      <c r="AA7" s="475"/>
-      <c r="AB7" s="475"/>
-      <c r="AC7" s="475"/>
-      <c r="AD7" s="475"/>
-      <c r="AE7" s="475"/>
-      <c r="AF7" s="475"/>
-      <c r="AG7" s="475"/>
-      <c r="AH7" s="475"/>
-      <c r="AI7" s="475"/>
-      <c r="AJ7" s="475"/>
-      <c r="AK7" s="475"/>
-      <c r="AL7" s="475"/>
-      <c r="AM7" s="475"/>
-      <c r="AN7" s="475"/>
-      <c r="AO7" s="475"/>
-      <c r="AP7" s="475"/>
-      <c r="AQ7" s="475"/>
-      <c r="AR7" s="475"/>
-      <c r="AS7" s="475"/>
-      <c r="AT7" s="475"/>
-      <c r="AU7" s="475"/>
-      <c r="AV7" s="475"/>
-      <c r="AW7" s="475"/>
-      <c r="AX7" s="475"/>
-      <c r="AY7" s="475"/>
-      <c r="AZ7" s="475"/>
-      <c r="BA7" s="475"/>
-      <c r="BB7" s="475"/>
+      <c r="H7" s="532"/>
+      <c r="I7" s="532"/>
+      <c r="J7" s="532"/>
+      <c r="K7" s="532"/>
+      <c r="L7" s="532"/>
+      <c r="M7" s="532"/>
+      <c r="N7" s="532"/>
+      <c r="O7" s="532"/>
+      <c r="P7" s="532"/>
+      <c r="Q7" s="532"/>
+      <c r="R7" s="532"/>
+      <c r="S7" s="532"/>
+      <c r="T7" s="532"/>
+      <c r="U7" s="532"/>
+      <c r="V7" s="532"/>
+      <c r="W7" s="532"/>
+      <c r="X7" s="532"/>
+      <c r="Y7" s="532"/>
+      <c r="Z7" s="532"/>
+      <c r="AA7" s="532"/>
+      <c r="AB7" s="532"/>
+      <c r="AC7" s="532"/>
+      <c r="AD7" s="532"/>
+      <c r="AE7" s="532"/>
+      <c r="AF7" s="532"/>
+      <c r="AG7" s="532"/>
+      <c r="AH7" s="532"/>
+      <c r="AI7" s="532"/>
+      <c r="AJ7" s="532"/>
+      <c r="AK7" s="532"/>
+      <c r="AL7" s="532"/>
+      <c r="AM7" s="532"/>
+      <c r="AN7" s="532"/>
+      <c r="AO7" s="532"/>
+      <c r="AP7" s="532"/>
+      <c r="AQ7" s="532"/>
+      <c r="AR7" s="532"/>
+      <c r="AS7" s="532"/>
+      <c r="AT7" s="532"/>
+      <c r="AU7" s="532"/>
+      <c r="AV7" s="532"/>
+      <c r="AW7" s="532"/>
+      <c r="AX7" s="532"/>
+      <c r="AY7" s="532"/>
+      <c r="AZ7" s="532"/>
+      <c r="BA7" s="532"/>
+      <c r="BB7" s="532"/>
     </row>
     <row r="8" spans="1:71" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="40"/>
@@ -29400,78 +29400,78 @@
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="487" t="s">
+      <c r="G8" s="526" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="487"/>
-      <c r="I8" s="487"/>
-      <c r="J8" s="487"/>
-      <c r="K8" s="482" t="s">
+      <c r="H8" s="526"/>
+      <c r="I8" s="526"/>
+      <c r="J8" s="526"/>
+      <c r="K8" s="527" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="482"/>
-      <c r="M8" s="482"/>
-      <c r="N8" s="482"/>
-      <c r="O8" s="483" t="s">
+      <c r="L8" s="527"/>
+      <c r="M8" s="527"/>
+      <c r="N8" s="527"/>
+      <c r="O8" s="528" t="s">
         <v>74</v>
       </c>
-      <c r="P8" s="483"/>
-      <c r="Q8" s="483"/>
-      <c r="R8" s="483"/>
-      <c r="S8" s="481" t="s">
+      <c r="P8" s="528"/>
+      <c r="Q8" s="528"/>
+      <c r="R8" s="528"/>
+      <c r="S8" s="538" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="481"/>
-      <c r="U8" s="481"/>
-      <c r="V8" s="481"/>
-      <c r="W8" s="482" t="s">
+      <c r="T8" s="538"/>
+      <c r="U8" s="538"/>
+      <c r="V8" s="538"/>
+      <c r="W8" s="527" t="s">
         <v>76</v>
       </c>
-      <c r="X8" s="482"/>
-      <c r="Y8" s="482"/>
-      <c r="Z8" s="482"/>
-      <c r="AA8" s="483" t="s">
+      <c r="X8" s="527"/>
+      <c r="Y8" s="527"/>
+      <c r="Z8" s="527"/>
+      <c r="AA8" s="528" t="s">
         <v>77</v>
       </c>
-      <c r="AB8" s="483"/>
-      <c r="AC8" s="483"/>
-      <c r="AD8" s="483"/>
-      <c r="AE8" s="480" t="s">
+      <c r="AB8" s="528"/>
+      <c r="AC8" s="528"/>
+      <c r="AD8" s="528"/>
+      <c r="AE8" s="537" t="s">
         <v>78</v>
       </c>
-      <c r="AF8" s="480"/>
-      <c r="AG8" s="480"/>
-      <c r="AH8" s="480"/>
-      <c r="AI8" s="476" t="s">
+      <c r="AF8" s="537"/>
+      <c r="AG8" s="537"/>
+      <c r="AH8" s="537"/>
+      <c r="AI8" s="533" t="s">
         <v>79</v>
       </c>
-      <c r="AJ8" s="476"/>
-      <c r="AK8" s="476"/>
-      <c r="AL8" s="476"/>
-      <c r="AM8" s="477" t="s">
+      <c r="AJ8" s="533"/>
+      <c r="AK8" s="533"/>
+      <c r="AL8" s="533"/>
+      <c r="AM8" s="534" t="s">
         <v>80</v>
       </c>
-      <c r="AN8" s="477"/>
-      <c r="AO8" s="477"/>
-      <c r="AP8" s="477"/>
-      <c r="AQ8" s="476" t="s">
+      <c r="AN8" s="534"/>
+      <c r="AO8" s="534"/>
+      <c r="AP8" s="534"/>
+      <c r="AQ8" s="533" t="s">
         <v>81</v>
       </c>
-      <c r="AR8" s="476"/>
-      <c r="AS8" s="476"/>
-      <c r="AT8" s="476"/>
-      <c r="AU8" s="477" t="s">
+      <c r="AR8" s="533"/>
+      <c r="AS8" s="533"/>
+      <c r="AT8" s="533"/>
+      <c r="AU8" s="534" t="s">
         <v>82</v>
       </c>
-      <c r="AV8" s="477"/>
-      <c r="AW8" s="477"/>
-      <c r="AX8" s="477"/>
-      <c r="AY8" s="476" t="s">
+      <c r="AV8" s="534"/>
+      <c r="AW8" s="534"/>
+      <c r="AX8" s="534"/>
+      <c r="AY8" s="533" t="s">
         <v>83</v>
       </c>
-      <c r="AZ8" s="476"/>
-      <c r="BA8" s="476"/>
-      <c r="BB8" s="476"/>
+      <c r="AZ8" s="533"/>
+      <c r="BA8" s="533"/>
+      <c r="BB8" s="533"/>
       <c r="BC8" s="8"/>
       <c r="BD8" s="8"/>
       <c r="BE8" s="8"/>
@@ -29688,42 +29688,42 @@
       <c r="P10" s="231"/>
       <c r="Q10" s="231"/>
       <c r="R10" s="378"/>
-      <c r="S10" s="484"/>
-      <c r="T10" s="485"/>
-      <c r="U10" s="485"/>
-      <c r="V10" s="485"/>
-      <c r="W10" s="485"/>
-      <c r="X10" s="485"/>
-      <c r="Y10" s="485"/>
-      <c r="Z10" s="485"/>
-      <c r="AA10" s="485"/>
-      <c r="AB10" s="485"/>
-      <c r="AC10" s="485"/>
-      <c r="AD10" s="486"/>
-      <c r="AE10" s="478"/>
-      <c r="AF10" s="479"/>
-      <c r="AG10" s="479"/>
-      <c r="AH10" s="479"/>
-      <c r="AI10" s="479"/>
-      <c r="AJ10" s="479"/>
-      <c r="AK10" s="479"/>
-      <c r="AL10" s="479"/>
-      <c r="AM10" s="479"/>
-      <c r="AN10" s="479"/>
-      <c r="AO10" s="479"/>
-      <c r="AP10" s="479"/>
-      <c r="AQ10" s="478"/>
-      <c r="AR10" s="479"/>
-      <c r="AS10" s="479"/>
-      <c r="AT10" s="479"/>
-      <c r="AU10" s="479"/>
-      <c r="AV10" s="479"/>
-      <c r="AW10" s="479"/>
-      <c r="AX10" s="479"/>
-      <c r="AY10" s="479"/>
-      <c r="AZ10" s="479"/>
-      <c r="BA10" s="479"/>
-      <c r="BB10" s="479"/>
+      <c r="S10" s="523"/>
+      <c r="T10" s="524"/>
+      <c r="U10" s="524"/>
+      <c r="V10" s="524"/>
+      <c r="W10" s="524"/>
+      <c r="X10" s="524"/>
+      <c r="Y10" s="524"/>
+      <c r="Z10" s="524"/>
+      <c r="AA10" s="524"/>
+      <c r="AB10" s="524"/>
+      <c r="AC10" s="524"/>
+      <c r="AD10" s="525"/>
+      <c r="AE10" s="535"/>
+      <c r="AF10" s="536"/>
+      <c r="AG10" s="536"/>
+      <c r="AH10" s="536"/>
+      <c r="AI10" s="536"/>
+      <c r="AJ10" s="536"/>
+      <c r="AK10" s="536"/>
+      <c r="AL10" s="536"/>
+      <c r="AM10" s="536"/>
+      <c r="AN10" s="536"/>
+      <c r="AO10" s="536"/>
+      <c r="AP10" s="536"/>
+      <c r="AQ10" s="535"/>
+      <c r="AR10" s="536"/>
+      <c r="AS10" s="536"/>
+      <c r="AT10" s="536"/>
+      <c r="AU10" s="536"/>
+      <c r="AV10" s="536"/>
+      <c r="AW10" s="536"/>
+      <c r="AX10" s="536"/>
+      <c r="AY10" s="536"/>
+      <c r="AZ10" s="536"/>
+      <c r="BA10" s="536"/>
+      <c r="BB10" s="536"/>
       <c r="BC10" s="9"/>
       <c r="BD10" s="9"/>
       <c r="BE10" s="9"/>
@@ -31063,7 +31063,7 @@
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="150"/>
-      <c r="B31" s="503"/>
+      <c r="B31" s="480"/>
       <c r="C31" s="116" t="s">
         <v>44</v>
       </c>
@@ -31127,7 +31127,7 @@
     </row>
     <row r="32" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="150"/>
-      <c r="B32" s="503"/>
+      <c r="B32" s="480"/>
       <c r="C32" s="363" t="s">
         <v>44</v>
       </c>
@@ -31191,7 +31191,7 @@
     </row>
     <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="150"/>
-      <c r="B33" s="504"/>
+      <c r="B33" s="481"/>
       <c r="C33" s="363" t="s">
         <v>44</v>
       </c>
@@ -31584,7 +31584,7 @@
     </row>
     <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="150"/>
-      <c r="B39" s="536" t="s">
+      <c r="B39" s="507" t="s">
         <v>118</v>
       </c>
       <c r="C39" s="116" t="s">
@@ -31650,7 +31650,7 @@
     </row>
     <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="150"/>
-      <c r="B40" s="536"/>
+      <c r="B40" s="507"/>
       <c r="C40" s="116" t="s">
         <v>113</v>
       </c>
@@ -31714,7 +31714,7 @@
     </row>
     <row r="41" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="150"/>
-      <c r="B41" s="536"/>
+      <c r="B41" s="507"/>
       <c r="C41" s="116" t="s">
         <v>113</v>
       </c>
@@ -31778,7 +31778,7 @@
     </row>
     <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="150"/>
-      <c r="B42" s="514" t="s">
+      <c r="B42" s="485" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="223" t="s">
@@ -31844,7 +31844,7 @@
     </row>
     <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="150"/>
-      <c r="B43" s="514"/>
+      <c r="B43" s="485"/>
       <c r="C43" s="223" t="s">
         <v>113</v>
       </c>
@@ -31908,7 +31908,7 @@
     </row>
     <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="150"/>
-      <c r="B44" s="514"/>
+      <c r="B44" s="485"/>
       <c r="C44" s="223" t="s">
         <v>113</v>
       </c>
@@ -32231,49 +32231,49 @@
     </row>
     <row r="49" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="150"/>
-      <c r="B49" s="515" t="s">
+      <c r="B49" s="486" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="516"/>
-      <c r="D49" s="516"/>
-      <c r="E49" s="516"/>
-      <c r="F49" s="517"/>
-      <c r="G49" s="491" t="s">
+      <c r="C49" s="487"/>
+      <c r="D49" s="487"/>
+      <c r="E49" s="487"/>
+      <c r="F49" s="488"/>
+      <c r="G49" s="482" t="s">
         <v>132</v>
       </c>
-      <c r="H49" s="492"/>
-      <c r="I49" s="492"/>
-      <c r="J49" s="493"/>
-      <c r="K49" s="491" t="s">
+      <c r="H49" s="483"/>
+      <c r="I49" s="483"/>
+      <c r="J49" s="484"/>
+      <c r="K49" s="482" t="s">
         <v>133</v>
       </c>
-      <c r="L49" s="492"/>
-      <c r="M49" s="492"/>
-      <c r="N49" s="493"/>
-      <c r="O49" s="491" t="s">
+      <c r="L49" s="483"/>
+      <c r="M49" s="483"/>
+      <c r="N49" s="484"/>
+      <c r="O49" s="482" t="s">
         <v>134</v>
       </c>
-      <c r="P49" s="492"/>
-      <c r="Q49" s="492"/>
-      <c r="R49" s="493"/>
-      <c r="S49" s="491" t="s">
+      <c r="P49" s="483"/>
+      <c r="Q49" s="483"/>
+      <c r="R49" s="484"/>
+      <c r="S49" s="482" t="s">
         <v>135</v>
       </c>
-      <c r="T49" s="492"/>
-      <c r="U49" s="492"/>
-      <c r="V49" s="493"/>
-      <c r="W49" s="491" t="s">
+      <c r="T49" s="483"/>
+      <c r="U49" s="483"/>
+      <c r="V49" s="484"/>
+      <c r="W49" s="482" t="s">
         <v>133</v>
       </c>
-      <c r="X49" s="492"/>
-      <c r="Y49" s="492"/>
-      <c r="Z49" s="493"/>
-      <c r="AA49" s="491" t="s">
+      <c r="X49" s="483"/>
+      <c r="Y49" s="483"/>
+      <c r="Z49" s="484"/>
+      <c r="AA49" s="482" t="s">
         <v>136</v>
       </c>
-      <c r="AB49" s="492"/>
-      <c r="AC49" s="492"/>
-      <c r="AD49" s="493"/>
+      <c r="AB49" s="483"/>
+      <c r="AC49" s="483"/>
+      <c r="AD49" s="484"/>
       <c r="AE49" s="192"/>
       <c r="AF49" s="192"/>
       <c r="AG49" s="192"/>
@@ -32301,49 +32301,49 @@
     </row>
     <row r="50" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="150"/>
-      <c r="B50" s="488" t="s">
+      <c r="B50" s="508" t="s">
         <v>137</v>
       </c>
-      <c r="C50" s="489"/>
-      <c r="D50" s="489"/>
-      <c r="E50" s="489"/>
-      <c r="F50" s="490"/>
-      <c r="G50" s="469" t="s">
+      <c r="C50" s="509"/>
+      <c r="D50" s="509"/>
+      <c r="E50" s="509"/>
+      <c r="F50" s="510"/>
+      <c r="G50" s="514" t="s">
         <v>136</v>
       </c>
-      <c r="H50" s="470"/>
-      <c r="I50" s="470"/>
-      <c r="J50" s="471"/>
-      <c r="K50" s="469" t="s">
+      <c r="H50" s="515"/>
+      <c r="I50" s="515"/>
+      <c r="J50" s="516"/>
+      <c r="K50" s="514" t="s">
         <v>138</v>
       </c>
-      <c r="L50" s="470"/>
-      <c r="M50" s="470"/>
-      <c r="N50" s="471"/>
-      <c r="O50" s="488" t="s">
+      <c r="L50" s="515"/>
+      <c r="M50" s="515"/>
+      <c r="N50" s="516"/>
+      <c r="O50" s="508" t="s">
         <v>139</v>
       </c>
-      <c r="P50" s="489"/>
-      <c r="Q50" s="489"/>
-      <c r="R50" s="490"/>
-      <c r="S50" s="488" t="s">
+      <c r="P50" s="509"/>
+      <c r="Q50" s="509"/>
+      <c r="R50" s="510"/>
+      <c r="S50" s="508" t="s">
         <v>138</v>
       </c>
-      <c r="T50" s="489"/>
-      <c r="U50" s="489"/>
-      <c r="V50" s="490"/>
-      <c r="W50" s="488" t="s">
+      <c r="T50" s="509"/>
+      <c r="U50" s="509"/>
+      <c r="V50" s="510"/>
+      <c r="W50" s="508" t="s">
         <v>138</v>
       </c>
-      <c r="X50" s="489"/>
-      <c r="Y50" s="489"/>
-      <c r="Z50" s="490"/>
-      <c r="AA50" s="488" t="s">
+      <c r="X50" s="509"/>
+      <c r="Y50" s="509"/>
+      <c r="Z50" s="510"/>
+      <c r="AA50" s="508" t="s">
         <v>138</v>
       </c>
-      <c r="AB50" s="489"/>
-      <c r="AC50" s="489"/>
-      <c r="AD50" s="490"/>
+      <c r="AB50" s="509"/>
+      <c r="AC50" s="509"/>
+      <c r="AD50" s="510"/>
       <c r="AE50" s="192"/>
       <c r="AF50" s="192"/>
       <c r="AG50" s="192"/>
@@ -32371,45 +32371,45 @@
     </row>
     <row r="51" spans="1:54" ht="20.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="150"/>
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="466" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="465"/>
-      <c r="G51" s="472" t="s">
+      <c r="C51" s="467"/>
+      <c r="D51" s="467"/>
+      <c r="E51" s="467"/>
+      <c r="F51" s="468"/>
+      <c r="G51" s="529" t="s">
         <v>141</v>
       </c>
-      <c r="H51" s="473"/>
-      <c r="I51" s="473"/>
-      <c r="J51" s="474"/>
-      <c r="K51" s="497" t="s">
+      <c r="H51" s="530"/>
+      <c r="I51" s="530"/>
+      <c r="J51" s="531"/>
+      <c r="K51" s="517" t="s">
         <v>142</v>
       </c>
-      <c r="L51" s="498"/>
-      <c r="M51" s="498"/>
-      <c r="N51" s="499"/>
-      <c r="O51" s="463" t="s">
+      <c r="L51" s="518"/>
+      <c r="M51" s="518"/>
+      <c r="N51" s="519"/>
+      <c r="O51" s="466" t="s">
         <v>143</v>
       </c>
-      <c r="P51" s="464"/>
-      <c r="Q51" s="464"/>
-      <c r="R51" s="465"/>
-      <c r="S51" s="463"/>
-      <c r="T51" s="464"/>
-      <c r="U51" s="464"/>
-      <c r="V51" s="465"/>
-      <c r="W51" s="463" t="s">
+      <c r="P51" s="467"/>
+      <c r="Q51" s="467"/>
+      <c r="R51" s="468"/>
+      <c r="S51" s="466"/>
+      <c r="T51" s="467"/>
+      <c r="U51" s="467"/>
+      <c r="V51" s="468"/>
+      <c r="W51" s="466" t="s">
         <v>143</v>
       </c>
-      <c r="X51" s="464"/>
-      <c r="Y51" s="464"/>
-      <c r="Z51" s="465"/>
-      <c r="AA51" s="463"/>
-      <c r="AB51" s="464"/>
-      <c r="AC51" s="464"/>
-      <c r="AD51" s="538"/>
+      <c r="X51" s="467"/>
+      <c r="Y51" s="467"/>
+      <c r="Z51" s="468"/>
+      <c r="AA51" s="466"/>
+      <c r="AB51" s="467"/>
+      <c r="AC51" s="467"/>
+      <c r="AD51" s="479"/>
       <c r="AE51" s="192"/>
       <c r="AF51" s="192"/>
       <c r="AG51" s="192"/>
@@ -32437,43 +32437,43 @@
     </row>
     <row r="52" spans="1:54" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="150"/>
-      <c r="B52" s="466" t="s">
+      <c r="B52" s="463" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="467"/>
-      <c r="D52" s="467"/>
-      <c r="E52" s="467"/>
-      <c r="F52" s="468"/>
-      <c r="G52" s="494" t="s">
+      <c r="C52" s="464"/>
+      <c r="D52" s="464"/>
+      <c r="E52" s="464"/>
+      <c r="F52" s="465"/>
+      <c r="G52" s="511" t="s">
         <v>145</v>
       </c>
-      <c r="H52" s="495"/>
-      <c r="I52" s="495"/>
-      <c r="J52" s="496"/>
-      <c r="K52" s="500" t="s">
+      <c r="H52" s="512"/>
+      <c r="I52" s="512"/>
+      <c r="J52" s="513"/>
+      <c r="K52" s="520" t="s">
         <v>146</v>
       </c>
-      <c r="L52" s="501"/>
-      <c r="M52" s="501"/>
-      <c r="N52" s="502"/>
-      <c r="O52" s="500" t="s">
+      <c r="L52" s="521"/>
+      <c r="M52" s="521"/>
+      <c r="N52" s="522"/>
+      <c r="O52" s="520" t="s">
         <v>147</v>
       </c>
-      <c r="P52" s="501"/>
-      <c r="Q52" s="501"/>
-      <c r="R52" s="502"/>
-      <c r="S52" s="466"/>
-      <c r="T52" s="467"/>
-      <c r="U52" s="467"/>
-      <c r="V52" s="468"/>
-      <c r="W52" s="466"/>
-      <c r="X52" s="467"/>
-      <c r="Y52" s="467"/>
-      <c r="Z52" s="468"/>
-      <c r="AA52" s="466"/>
-      <c r="AB52" s="467"/>
-      <c r="AC52" s="467"/>
-      <c r="AD52" s="537"/>
+      <c r="P52" s="521"/>
+      <c r="Q52" s="521"/>
+      <c r="R52" s="522"/>
+      <c r="S52" s="463"/>
+      <c r="T52" s="464"/>
+      <c r="U52" s="464"/>
+      <c r="V52" s="465"/>
+      <c r="W52" s="463"/>
+      <c r="X52" s="464"/>
+      <c r="Y52" s="464"/>
+      <c r="Z52" s="465"/>
+      <c r="AA52" s="463"/>
+      <c r="AB52" s="464"/>
+      <c r="AC52" s="464"/>
+      <c r="AD52" s="478"/>
       <c r="AE52" s="192"/>
       <c r="AF52" s="192"/>
       <c r="AG52" s="192"/>
@@ -32501,49 +32501,49 @@
     </row>
     <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="150"/>
-      <c r="B53" s="518" t="s">
+      <c r="B53" s="489" t="s">
         <v>148</v>
       </c>
-      <c r="C53" s="519"/>
-      <c r="D53" s="519"/>
-      <c r="E53" s="519"/>
-      <c r="F53" s="520"/>
-      <c r="G53" s="527" t="s">
+      <c r="C53" s="490"/>
+      <c r="D53" s="490"/>
+      <c r="E53" s="490"/>
+      <c r="F53" s="491"/>
+      <c r="G53" s="498" t="s">
         <v>149</v>
       </c>
-      <c r="H53" s="528"/>
-      <c r="I53" s="528"/>
-      <c r="J53" s="529"/>
-      <c r="K53" s="527" t="s">
+      <c r="H53" s="499"/>
+      <c r="I53" s="499"/>
+      <c r="J53" s="500"/>
+      <c r="K53" s="498" t="s">
         <v>150</v>
       </c>
-      <c r="L53" s="528"/>
-      <c r="M53" s="528"/>
-      <c r="N53" s="529"/>
-      <c r="O53" s="505" t="s">
+      <c r="L53" s="499"/>
+      <c r="M53" s="499"/>
+      <c r="N53" s="500"/>
+      <c r="O53" s="469" t="s">
         <v>151</v>
       </c>
-      <c r="P53" s="506"/>
-      <c r="Q53" s="506"/>
-      <c r="R53" s="507"/>
-      <c r="S53" s="505" t="s">
+      <c r="P53" s="470"/>
+      <c r="Q53" s="470"/>
+      <c r="R53" s="471"/>
+      <c r="S53" s="469" t="s">
         <v>152</v>
       </c>
-      <c r="T53" s="506"/>
-      <c r="U53" s="506"/>
-      <c r="V53" s="507"/>
-      <c r="W53" s="505" t="s">
+      <c r="T53" s="470"/>
+      <c r="U53" s="470"/>
+      <c r="V53" s="471"/>
+      <c r="W53" s="469" t="s">
         <v>153</v>
       </c>
-      <c r="X53" s="506"/>
-      <c r="Y53" s="506"/>
-      <c r="Z53" s="507"/>
-      <c r="AA53" s="505" t="s">
+      <c r="X53" s="470"/>
+      <c r="Y53" s="470"/>
+      <c r="Z53" s="471"/>
+      <c r="AA53" s="469" t="s">
         <v>154</v>
       </c>
-      <c r="AB53" s="506"/>
-      <c r="AC53" s="506"/>
-      <c r="AD53" s="507"/>
+      <c r="AB53" s="470"/>
+      <c r="AC53" s="470"/>
+      <c r="AD53" s="471"/>
       <c r="AE53" s="150"/>
       <c r="AF53" s="150"/>
       <c r="AG53" s="150"/>
@@ -32573,35 +32573,35 @@
     </row>
     <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="150"/>
-      <c r="B54" s="521"/>
-      <c r="C54" s="522"/>
-      <c r="D54" s="522"/>
-      <c r="E54" s="522"/>
-      <c r="F54" s="523"/>
-      <c r="G54" s="530"/>
-      <c r="H54" s="531"/>
-      <c r="I54" s="531"/>
-      <c r="J54" s="532"/>
-      <c r="K54" s="530"/>
-      <c r="L54" s="531"/>
-      <c r="M54" s="531"/>
-      <c r="N54" s="532"/>
-      <c r="O54" s="508"/>
-      <c r="P54" s="509"/>
-      <c r="Q54" s="509"/>
-      <c r="R54" s="510"/>
-      <c r="S54" s="508"/>
-      <c r="T54" s="509"/>
-      <c r="U54" s="509"/>
-      <c r="V54" s="510"/>
-      <c r="W54" s="508"/>
-      <c r="X54" s="509"/>
-      <c r="Y54" s="509"/>
-      <c r="Z54" s="510"/>
-      <c r="AA54" s="508"/>
-      <c r="AB54" s="509"/>
-      <c r="AC54" s="509"/>
-      <c r="AD54" s="510"/>
+      <c r="B54" s="492"/>
+      <c r="C54" s="493"/>
+      <c r="D54" s="493"/>
+      <c r="E54" s="493"/>
+      <c r="F54" s="494"/>
+      <c r="G54" s="501"/>
+      <c r="H54" s="502"/>
+      <c r="I54" s="502"/>
+      <c r="J54" s="503"/>
+      <c r="K54" s="501"/>
+      <c r="L54" s="502"/>
+      <c r="M54" s="502"/>
+      <c r="N54" s="503"/>
+      <c r="O54" s="472"/>
+      <c r="P54" s="473"/>
+      <c r="Q54" s="473"/>
+      <c r="R54" s="474"/>
+      <c r="S54" s="472"/>
+      <c r="T54" s="473"/>
+      <c r="U54" s="473"/>
+      <c r="V54" s="474"/>
+      <c r="W54" s="472"/>
+      <c r="X54" s="473"/>
+      <c r="Y54" s="473"/>
+      <c r="Z54" s="474"/>
+      <c r="AA54" s="472"/>
+      <c r="AB54" s="473"/>
+      <c r="AC54" s="473"/>
+      <c r="AD54" s="474"/>
       <c r="AE54" s="150"/>
       <c r="AF54" s="150"/>
       <c r="AG54" s="150"/>
@@ -32628,35 +32628,35 @@
       <c r="BB54" s="150"/>
     </row>
     <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="521"/>
-      <c r="C55" s="522"/>
-      <c r="D55" s="522"/>
-      <c r="E55" s="522"/>
-      <c r="F55" s="523"/>
-      <c r="G55" s="530"/>
-      <c r="H55" s="531"/>
-      <c r="I55" s="531"/>
-      <c r="J55" s="532"/>
-      <c r="K55" s="530"/>
-      <c r="L55" s="531"/>
-      <c r="M55" s="531"/>
-      <c r="N55" s="532"/>
-      <c r="O55" s="508"/>
-      <c r="P55" s="509"/>
-      <c r="Q55" s="509"/>
-      <c r="R55" s="510"/>
-      <c r="S55" s="508"/>
-      <c r="T55" s="509"/>
-      <c r="U55" s="509"/>
-      <c r="V55" s="510"/>
-      <c r="W55" s="508"/>
-      <c r="X55" s="509"/>
-      <c r="Y55" s="509"/>
-      <c r="Z55" s="510"/>
-      <c r="AA55" s="508"/>
-      <c r="AB55" s="509"/>
-      <c r="AC55" s="509"/>
-      <c r="AD55" s="510"/>
+      <c r="B55" s="492"/>
+      <c r="C55" s="493"/>
+      <c r="D55" s="493"/>
+      <c r="E55" s="493"/>
+      <c r="F55" s="494"/>
+      <c r="G55" s="501"/>
+      <c r="H55" s="502"/>
+      <c r="I55" s="502"/>
+      <c r="J55" s="503"/>
+      <c r="K55" s="501"/>
+      <c r="L55" s="502"/>
+      <c r="M55" s="502"/>
+      <c r="N55" s="503"/>
+      <c r="O55" s="472"/>
+      <c r="P55" s="473"/>
+      <c r="Q55" s="473"/>
+      <c r="R55" s="474"/>
+      <c r="S55" s="472"/>
+      <c r="T55" s="473"/>
+      <c r="U55" s="473"/>
+      <c r="V55" s="474"/>
+      <c r="W55" s="472"/>
+      <c r="X55" s="473"/>
+      <c r="Y55" s="473"/>
+      <c r="Z55" s="474"/>
+      <c r="AA55" s="472"/>
+      <c r="AB55" s="473"/>
+      <c r="AC55" s="473"/>
+      <c r="AD55" s="474"/>
       <c r="AE55" s="150"/>
       <c r="AF55" s="150"/>
       <c r="AG55" s="150"/>
@@ -32683,447 +32683,478 @@
       <c r="BB55" s="150"/>
     </row>
     <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="521"/>
-      <c r="C56" s="522"/>
-      <c r="D56" s="522"/>
-      <c r="E56" s="522"/>
-      <c r="F56" s="523"/>
-      <c r="G56" s="530"/>
-      <c r="H56" s="531"/>
-      <c r="I56" s="531"/>
-      <c r="J56" s="532"/>
-      <c r="K56" s="530"/>
-      <c r="L56" s="531"/>
-      <c r="M56" s="531"/>
-      <c r="N56" s="532"/>
-      <c r="O56" s="508"/>
-      <c r="P56" s="509"/>
-      <c r="Q56" s="509"/>
-      <c r="R56" s="510"/>
-      <c r="S56" s="508"/>
-      <c r="T56" s="509"/>
-      <c r="U56" s="509"/>
-      <c r="V56" s="510"/>
-      <c r="W56" s="508"/>
-      <c r="X56" s="509"/>
-      <c r="Y56" s="509"/>
-      <c r="Z56" s="510"/>
-      <c r="AA56" s="508"/>
-      <c r="AB56" s="509"/>
-      <c r="AC56" s="509"/>
-      <c r="AD56" s="510"/>
+      <c r="B56" s="492"/>
+      <c r="C56" s="493"/>
+      <c r="D56" s="493"/>
+      <c r="E56" s="493"/>
+      <c r="F56" s="494"/>
+      <c r="G56" s="501"/>
+      <c r="H56" s="502"/>
+      <c r="I56" s="502"/>
+      <c r="J56" s="503"/>
+      <c r="K56" s="501"/>
+      <c r="L56" s="502"/>
+      <c r="M56" s="502"/>
+      <c r="N56" s="503"/>
+      <c r="O56" s="472"/>
+      <c r="P56" s="473"/>
+      <c r="Q56" s="473"/>
+      <c r="R56" s="474"/>
+      <c r="S56" s="472"/>
+      <c r="T56" s="473"/>
+      <c r="U56" s="473"/>
+      <c r="V56" s="474"/>
+      <c r="W56" s="472"/>
+      <c r="X56" s="473"/>
+      <c r="Y56" s="473"/>
+      <c r="Z56" s="474"/>
+      <c r="AA56" s="472"/>
+      <c r="AB56" s="473"/>
+      <c r="AC56" s="473"/>
+      <c r="AD56" s="474"/>
     </row>
     <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="521"/>
-      <c r="C57" s="522"/>
-      <c r="D57" s="522"/>
-      <c r="E57" s="522"/>
-      <c r="F57" s="523"/>
-      <c r="G57" s="530"/>
-      <c r="H57" s="531"/>
-      <c r="I57" s="531"/>
-      <c r="J57" s="532"/>
-      <c r="K57" s="530"/>
-      <c r="L57" s="531"/>
-      <c r="M57" s="531"/>
-      <c r="N57" s="532"/>
-      <c r="O57" s="508"/>
-      <c r="P57" s="509"/>
-      <c r="Q57" s="509"/>
-      <c r="R57" s="510"/>
-      <c r="S57" s="508"/>
-      <c r="T57" s="509"/>
-      <c r="U57" s="509"/>
-      <c r="V57" s="510"/>
-      <c r="W57" s="508"/>
-      <c r="X57" s="509"/>
-      <c r="Y57" s="509"/>
-      <c r="Z57" s="510"/>
-      <c r="AA57" s="508"/>
-      <c r="AB57" s="509"/>
-      <c r="AC57" s="509"/>
-      <c r="AD57" s="510"/>
+      <c r="B57" s="492"/>
+      <c r="C57" s="493"/>
+      <c r="D57" s="493"/>
+      <c r="E57" s="493"/>
+      <c r="F57" s="494"/>
+      <c r="G57" s="501"/>
+      <c r="H57" s="502"/>
+      <c r="I57" s="502"/>
+      <c r="J57" s="503"/>
+      <c r="K57" s="501"/>
+      <c r="L57" s="502"/>
+      <c r="M57" s="502"/>
+      <c r="N57" s="503"/>
+      <c r="O57" s="472"/>
+      <c r="P57" s="473"/>
+      <c r="Q57" s="473"/>
+      <c r="R57" s="474"/>
+      <c r="S57" s="472"/>
+      <c r="T57" s="473"/>
+      <c r="U57" s="473"/>
+      <c r="V57" s="474"/>
+      <c r="W57" s="472"/>
+      <c r="X57" s="473"/>
+      <c r="Y57" s="473"/>
+      <c r="Z57" s="474"/>
+      <c r="AA57" s="472"/>
+      <c r="AB57" s="473"/>
+      <c r="AC57" s="473"/>
+      <c r="AD57" s="474"/>
     </row>
     <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="521"/>
-      <c r="C58" s="522"/>
-      <c r="D58" s="522"/>
-      <c r="E58" s="522"/>
-      <c r="F58" s="523"/>
-      <c r="G58" s="530"/>
-      <c r="H58" s="531"/>
-      <c r="I58" s="531"/>
-      <c r="J58" s="532"/>
-      <c r="K58" s="530"/>
-      <c r="L58" s="531"/>
-      <c r="M58" s="531"/>
-      <c r="N58" s="532"/>
-      <c r="O58" s="508"/>
-      <c r="P58" s="509"/>
-      <c r="Q58" s="509"/>
-      <c r="R58" s="510"/>
-      <c r="S58" s="508"/>
-      <c r="T58" s="509"/>
-      <c r="U58" s="509"/>
-      <c r="V58" s="510"/>
-      <c r="W58" s="508"/>
-      <c r="X58" s="509"/>
-      <c r="Y58" s="509"/>
-      <c r="Z58" s="510"/>
-      <c r="AA58" s="508"/>
-      <c r="AB58" s="509"/>
-      <c r="AC58" s="509"/>
-      <c r="AD58" s="510"/>
+      <c r="B58" s="492"/>
+      <c r="C58" s="493"/>
+      <c r="D58" s="493"/>
+      <c r="E58" s="493"/>
+      <c r="F58" s="494"/>
+      <c r="G58" s="501"/>
+      <c r="H58" s="502"/>
+      <c r="I58" s="502"/>
+      <c r="J58" s="503"/>
+      <c r="K58" s="501"/>
+      <c r="L58" s="502"/>
+      <c r="M58" s="502"/>
+      <c r="N58" s="503"/>
+      <c r="O58" s="472"/>
+      <c r="P58" s="473"/>
+      <c r="Q58" s="473"/>
+      <c r="R58" s="474"/>
+      <c r="S58" s="472"/>
+      <c r="T58" s="473"/>
+      <c r="U58" s="473"/>
+      <c r="V58" s="474"/>
+      <c r="W58" s="472"/>
+      <c r="X58" s="473"/>
+      <c r="Y58" s="473"/>
+      <c r="Z58" s="474"/>
+      <c r="AA58" s="472"/>
+      <c r="AB58" s="473"/>
+      <c r="AC58" s="473"/>
+      <c r="AD58" s="474"/>
     </row>
     <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="521"/>
-      <c r="C59" s="522"/>
-      <c r="D59" s="522"/>
-      <c r="E59" s="522"/>
-      <c r="F59" s="523"/>
-      <c r="G59" s="530"/>
-      <c r="H59" s="531"/>
-      <c r="I59" s="531"/>
-      <c r="J59" s="532"/>
-      <c r="K59" s="530"/>
-      <c r="L59" s="531"/>
-      <c r="M59" s="531"/>
-      <c r="N59" s="532"/>
-      <c r="O59" s="508"/>
-      <c r="P59" s="509"/>
-      <c r="Q59" s="509"/>
-      <c r="R59" s="510"/>
-      <c r="S59" s="508"/>
-      <c r="T59" s="509"/>
-      <c r="U59" s="509"/>
-      <c r="V59" s="510"/>
-      <c r="W59" s="508"/>
-      <c r="X59" s="509"/>
-      <c r="Y59" s="509"/>
-      <c r="Z59" s="510"/>
-      <c r="AA59" s="508"/>
-      <c r="AB59" s="509"/>
-      <c r="AC59" s="509"/>
-      <c r="AD59" s="510"/>
+      <c r="B59" s="492"/>
+      <c r="C59" s="493"/>
+      <c r="D59" s="493"/>
+      <c r="E59" s="493"/>
+      <c r="F59" s="494"/>
+      <c r="G59" s="501"/>
+      <c r="H59" s="502"/>
+      <c r="I59" s="502"/>
+      <c r="J59" s="503"/>
+      <c r="K59" s="501"/>
+      <c r="L59" s="502"/>
+      <c r="M59" s="502"/>
+      <c r="N59" s="503"/>
+      <c r="O59" s="472"/>
+      <c r="P59" s="473"/>
+      <c r="Q59" s="473"/>
+      <c r="R59" s="474"/>
+      <c r="S59" s="472"/>
+      <c r="T59" s="473"/>
+      <c r="U59" s="473"/>
+      <c r="V59" s="474"/>
+      <c r="W59" s="472"/>
+      <c r="X59" s="473"/>
+      <c r="Y59" s="473"/>
+      <c r="Z59" s="474"/>
+      <c r="AA59" s="472"/>
+      <c r="AB59" s="473"/>
+      <c r="AC59" s="473"/>
+      <c r="AD59" s="474"/>
     </row>
     <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="521"/>
-      <c r="C60" s="522"/>
-      <c r="D60" s="522"/>
-      <c r="E60" s="522"/>
-      <c r="F60" s="523"/>
-      <c r="G60" s="530"/>
-      <c r="H60" s="531"/>
-      <c r="I60" s="531"/>
-      <c r="J60" s="532"/>
-      <c r="K60" s="530"/>
-      <c r="L60" s="531"/>
-      <c r="M60" s="531"/>
-      <c r="N60" s="532"/>
-      <c r="O60" s="508"/>
-      <c r="P60" s="509"/>
-      <c r="Q60" s="509"/>
-      <c r="R60" s="510"/>
-      <c r="S60" s="508"/>
-      <c r="T60" s="509"/>
-      <c r="U60" s="509"/>
-      <c r="V60" s="510"/>
-      <c r="W60" s="508"/>
-      <c r="X60" s="509"/>
-      <c r="Y60" s="509"/>
-      <c r="Z60" s="510"/>
-      <c r="AA60" s="508"/>
-      <c r="AB60" s="509"/>
-      <c r="AC60" s="509"/>
-      <c r="AD60" s="510"/>
+      <c r="B60" s="492"/>
+      <c r="C60" s="493"/>
+      <c r="D60" s="493"/>
+      <c r="E60" s="493"/>
+      <c r="F60" s="494"/>
+      <c r="G60" s="501"/>
+      <c r="H60" s="502"/>
+      <c r="I60" s="502"/>
+      <c r="J60" s="503"/>
+      <c r="K60" s="501"/>
+      <c r="L60" s="502"/>
+      <c r="M60" s="502"/>
+      <c r="N60" s="503"/>
+      <c r="O60" s="472"/>
+      <c r="P60" s="473"/>
+      <c r="Q60" s="473"/>
+      <c r="R60" s="474"/>
+      <c r="S60" s="472"/>
+      <c r="T60" s="473"/>
+      <c r="U60" s="473"/>
+      <c r="V60" s="474"/>
+      <c r="W60" s="472"/>
+      <c r="X60" s="473"/>
+      <c r="Y60" s="473"/>
+      <c r="Z60" s="474"/>
+      <c r="AA60" s="472"/>
+      <c r="AB60" s="473"/>
+      <c r="AC60" s="473"/>
+      <c r="AD60" s="474"/>
     </row>
     <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="521"/>
-      <c r="C61" s="522"/>
-      <c r="D61" s="522"/>
-      <c r="E61" s="522"/>
-      <c r="F61" s="523"/>
-      <c r="G61" s="530"/>
-      <c r="H61" s="531"/>
-      <c r="I61" s="531"/>
-      <c r="J61" s="532"/>
-      <c r="K61" s="530"/>
-      <c r="L61" s="531"/>
-      <c r="M61" s="531"/>
-      <c r="N61" s="532"/>
-      <c r="O61" s="508"/>
-      <c r="P61" s="509"/>
-      <c r="Q61" s="509"/>
-      <c r="R61" s="510"/>
-      <c r="S61" s="508"/>
-      <c r="T61" s="509"/>
-      <c r="U61" s="509"/>
-      <c r="V61" s="510"/>
-      <c r="W61" s="508"/>
-      <c r="X61" s="509"/>
-      <c r="Y61" s="509"/>
-      <c r="Z61" s="510"/>
-      <c r="AA61" s="508"/>
-      <c r="AB61" s="509"/>
-      <c r="AC61" s="509"/>
-      <c r="AD61" s="510"/>
+      <c r="B61" s="492"/>
+      <c r="C61" s="493"/>
+      <c r="D61" s="493"/>
+      <c r="E61" s="493"/>
+      <c r="F61" s="494"/>
+      <c r="G61" s="501"/>
+      <c r="H61" s="502"/>
+      <c r="I61" s="502"/>
+      <c r="J61" s="503"/>
+      <c r="K61" s="501"/>
+      <c r="L61" s="502"/>
+      <c r="M61" s="502"/>
+      <c r="N61" s="503"/>
+      <c r="O61" s="472"/>
+      <c r="P61" s="473"/>
+      <c r="Q61" s="473"/>
+      <c r="R61" s="474"/>
+      <c r="S61" s="472"/>
+      <c r="T61" s="473"/>
+      <c r="U61" s="473"/>
+      <c r="V61" s="474"/>
+      <c r="W61" s="472"/>
+      <c r="X61" s="473"/>
+      <c r="Y61" s="473"/>
+      <c r="Z61" s="474"/>
+      <c r="AA61" s="472"/>
+      <c r="AB61" s="473"/>
+      <c r="AC61" s="473"/>
+      <c r="AD61" s="474"/>
     </row>
     <row r="62" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="521"/>
-      <c r="C62" s="522"/>
-      <c r="D62" s="522"/>
-      <c r="E62" s="522"/>
-      <c r="F62" s="523"/>
-      <c r="G62" s="530"/>
-      <c r="H62" s="531"/>
-      <c r="I62" s="531"/>
-      <c r="J62" s="532"/>
-      <c r="K62" s="530"/>
-      <c r="L62" s="531"/>
-      <c r="M62" s="531"/>
-      <c r="N62" s="532"/>
-      <c r="O62" s="508"/>
-      <c r="P62" s="509"/>
-      <c r="Q62" s="509"/>
-      <c r="R62" s="510"/>
-      <c r="S62" s="508"/>
-      <c r="T62" s="509"/>
-      <c r="U62" s="509"/>
-      <c r="V62" s="510"/>
-      <c r="W62" s="508"/>
-      <c r="X62" s="509"/>
-      <c r="Y62" s="509"/>
-      <c r="Z62" s="510"/>
-      <c r="AA62" s="508"/>
-      <c r="AB62" s="509"/>
-      <c r="AC62" s="509"/>
-      <c r="AD62" s="510"/>
+      <c r="B62" s="492"/>
+      <c r="C62" s="493"/>
+      <c r="D62" s="493"/>
+      <c r="E62" s="493"/>
+      <c r="F62" s="494"/>
+      <c r="G62" s="501"/>
+      <c r="H62" s="502"/>
+      <c r="I62" s="502"/>
+      <c r="J62" s="503"/>
+      <c r="K62" s="501"/>
+      <c r="L62" s="502"/>
+      <c r="M62" s="502"/>
+      <c r="N62" s="503"/>
+      <c r="O62" s="472"/>
+      <c r="P62" s="473"/>
+      <c r="Q62" s="473"/>
+      <c r="R62" s="474"/>
+      <c r="S62" s="472"/>
+      <c r="T62" s="473"/>
+      <c r="U62" s="473"/>
+      <c r="V62" s="474"/>
+      <c r="W62" s="472"/>
+      <c r="X62" s="473"/>
+      <c r="Y62" s="473"/>
+      <c r="Z62" s="474"/>
+      <c r="AA62" s="472"/>
+      <c r="AB62" s="473"/>
+      <c r="AC62" s="473"/>
+      <c r="AD62" s="474"/>
     </row>
     <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="521"/>
-      <c r="C63" s="522"/>
-      <c r="D63" s="522"/>
-      <c r="E63" s="522"/>
-      <c r="F63" s="523"/>
-      <c r="G63" s="530"/>
-      <c r="H63" s="531"/>
-      <c r="I63" s="531"/>
-      <c r="J63" s="532"/>
-      <c r="K63" s="530"/>
-      <c r="L63" s="531"/>
-      <c r="M63" s="531"/>
-      <c r="N63" s="532"/>
-      <c r="O63" s="508"/>
-      <c r="P63" s="509"/>
-      <c r="Q63" s="509"/>
-      <c r="R63" s="510"/>
-      <c r="S63" s="508"/>
-      <c r="T63" s="509"/>
-      <c r="U63" s="509"/>
-      <c r="V63" s="510"/>
-      <c r="W63" s="508"/>
-      <c r="X63" s="509"/>
-      <c r="Y63" s="509"/>
-      <c r="Z63" s="510"/>
-      <c r="AA63" s="508"/>
-      <c r="AB63" s="509"/>
-      <c r="AC63" s="509"/>
-      <c r="AD63" s="510"/>
+      <c r="B63" s="492"/>
+      <c r="C63" s="493"/>
+      <c r="D63" s="493"/>
+      <c r="E63" s="493"/>
+      <c r="F63" s="494"/>
+      <c r="G63" s="501"/>
+      <c r="H63" s="502"/>
+      <c r="I63" s="502"/>
+      <c r="J63" s="503"/>
+      <c r="K63" s="501"/>
+      <c r="L63" s="502"/>
+      <c r="M63" s="502"/>
+      <c r="N63" s="503"/>
+      <c r="O63" s="472"/>
+      <c r="P63" s="473"/>
+      <c r="Q63" s="473"/>
+      <c r="R63" s="474"/>
+      <c r="S63" s="472"/>
+      <c r="T63" s="473"/>
+      <c r="U63" s="473"/>
+      <c r="V63" s="474"/>
+      <c r="W63" s="472"/>
+      <c r="X63" s="473"/>
+      <c r="Y63" s="473"/>
+      <c r="Z63" s="474"/>
+      <c r="AA63" s="472"/>
+      <c r="AB63" s="473"/>
+      <c r="AC63" s="473"/>
+      <c r="AD63" s="474"/>
     </row>
     <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="521"/>
-      <c r="C64" s="522"/>
-      <c r="D64" s="522"/>
-      <c r="E64" s="522"/>
-      <c r="F64" s="523"/>
-      <c r="G64" s="530"/>
-      <c r="H64" s="531"/>
-      <c r="I64" s="531"/>
-      <c r="J64" s="532"/>
-      <c r="K64" s="530"/>
-      <c r="L64" s="531"/>
-      <c r="M64" s="531"/>
-      <c r="N64" s="532"/>
-      <c r="O64" s="508"/>
-      <c r="P64" s="509"/>
-      <c r="Q64" s="509"/>
-      <c r="R64" s="510"/>
-      <c r="S64" s="508"/>
-      <c r="T64" s="509"/>
-      <c r="U64" s="509"/>
-      <c r="V64" s="510"/>
-      <c r="W64" s="508"/>
-      <c r="X64" s="509"/>
-      <c r="Y64" s="509"/>
-      <c r="Z64" s="510"/>
-      <c r="AA64" s="508"/>
-      <c r="AB64" s="509"/>
-      <c r="AC64" s="509"/>
-      <c r="AD64" s="510"/>
+      <c r="B64" s="492"/>
+      <c r="C64" s="493"/>
+      <c r="D64" s="493"/>
+      <c r="E64" s="493"/>
+      <c r="F64" s="494"/>
+      <c r="G64" s="501"/>
+      <c r="H64" s="502"/>
+      <c r="I64" s="502"/>
+      <c r="J64" s="503"/>
+      <c r="K64" s="501"/>
+      <c r="L64" s="502"/>
+      <c r="M64" s="502"/>
+      <c r="N64" s="503"/>
+      <c r="O64" s="472"/>
+      <c r="P64" s="473"/>
+      <c r="Q64" s="473"/>
+      <c r="R64" s="474"/>
+      <c r="S64" s="472"/>
+      <c r="T64" s="473"/>
+      <c r="U64" s="473"/>
+      <c r="V64" s="474"/>
+      <c r="W64" s="472"/>
+      <c r="X64" s="473"/>
+      <c r="Y64" s="473"/>
+      <c r="Z64" s="474"/>
+      <c r="AA64" s="472"/>
+      <c r="AB64" s="473"/>
+      <c r="AC64" s="473"/>
+      <c r="AD64" s="474"/>
     </row>
     <row r="65" spans="2:30" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="521"/>
-      <c r="C65" s="522"/>
-      <c r="D65" s="522"/>
-      <c r="E65" s="522"/>
-      <c r="F65" s="523"/>
-      <c r="G65" s="530"/>
-      <c r="H65" s="531"/>
-      <c r="I65" s="531"/>
-      <c r="J65" s="532"/>
-      <c r="K65" s="530"/>
-      <c r="L65" s="531"/>
-      <c r="M65" s="531"/>
-      <c r="N65" s="532"/>
-      <c r="O65" s="508"/>
-      <c r="P65" s="509"/>
-      <c r="Q65" s="509"/>
-      <c r="R65" s="510"/>
-      <c r="S65" s="508"/>
-      <c r="T65" s="509"/>
-      <c r="U65" s="509"/>
-      <c r="V65" s="510"/>
-      <c r="W65" s="508"/>
-      <c r="X65" s="509"/>
-      <c r="Y65" s="509"/>
-      <c r="Z65" s="510"/>
-      <c r="AA65" s="508"/>
-      <c r="AB65" s="509"/>
-      <c r="AC65" s="509"/>
-      <c r="AD65" s="510"/>
+      <c r="B65" s="492"/>
+      <c r="C65" s="493"/>
+      <c r="D65" s="493"/>
+      <c r="E65" s="493"/>
+      <c r="F65" s="494"/>
+      <c r="G65" s="501"/>
+      <c r="H65" s="502"/>
+      <c r="I65" s="502"/>
+      <c r="J65" s="503"/>
+      <c r="K65" s="501"/>
+      <c r="L65" s="502"/>
+      <c r="M65" s="502"/>
+      <c r="N65" s="503"/>
+      <c r="O65" s="472"/>
+      <c r="P65" s="473"/>
+      <c r="Q65" s="473"/>
+      <c r="R65" s="474"/>
+      <c r="S65" s="472"/>
+      <c r="T65" s="473"/>
+      <c r="U65" s="473"/>
+      <c r="V65" s="474"/>
+      <c r="W65" s="472"/>
+      <c r="X65" s="473"/>
+      <c r="Y65" s="473"/>
+      <c r="Z65" s="474"/>
+      <c r="AA65" s="472"/>
+      <c r="AB65" s="473"/>
+      <c r="AC65" s="473"/>
+      <c r="AD65" s="474"/>
     </row>
     <row r="66" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="521"/>
-      <c r="C66" s="522"/>
-      <c r="D66" s="522"/>
-      <c r="E66" s="522"/>
-      <c r="F66" s="523"/>
-      <c r="G66" s="530"/>
-      <c r="H66" s="531"/>
-      <c r="I66" s="531"/>
-      <c r="J66" s="532"/>
-      <c r="K66" s="530"/>
-      <c r="L66" s="531"/>
-      <c r="M66" s="531"/>
-      <c r="N66" s="532"/>
-      <c r="O66" s="508"/>
-      <c r="P66" s="509"/>
-      <c r="Q66" s="509"/>
-      <c r="R66" s="510"/>
-      <c r="S66" s="508"/>
-      <c r="T66" s="509"/>
-      <c r="U66" s="509"/>
-      <c r="V66" s="510"/>
-      <c r="W66" s="508"/>
-      <c r="X66" s="509"/>
-      <c r="Y66" s="509"/>
-      <c r="Z66" s="510"/>
-      <c r="AA66" s="508"/>
-      <c r="AB66" s="509"/>
-      <c r="AC66" s="509"/>
-      <c r="AD66" s="510"/>
+      <c r="B66" s="492"/>
+      <c r="C66" s="493"/>
+      <c r="D66" s="493"/>
+      <c r="E66" s="493"/>
+      <c r="F66" s="494"/>
+      <c r="G66" s="501"/>
+      <c r="H66" s="502"/>
+      <c r="I66" s="502"/>
+      <c r="J66" s="503"/>
+      <c r="K66" s="501"/>
+      <c r="L66" s="502"/>
+      <c r="M66" s="502"/>
+      <c r="N66" s="503"/>
+      <c r="O66" s="472"/>
+      <c r="P66" s="473"/>
+      <c r="Q66" s="473"/>
+      <c r="R66" s="474"/>
+      <c r="S66" s="472"/>
+      <c r="T66" s="473"/>
+      <c r="U66" s="473"/>
+      <c r="V66" s="474"/>
+      <c r="W66" s="472"/>
+      <c r="X66" s="473"/>
+      <c r="Y66" s="473"/>
+      <c r="Z66" s="474"/>
+      <c r="AA66" s="472"/>
+      <c r="AB66" s="473"/>
+      <c r="AC66" s="473"/>
+      <c r="AD66" s="474"/>
     </row>
     <row r="67" spans="2:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="521"/>
-      <c r="C67" s="522"/>
-      <c r="D67" s="522"/>
-      <c r="E67" s="522"/>
-      <c r="F67" s="523"/>
-      <c r="G67" s="530"/>
-      <c r="H67" s="531"/>
-      <c r="I67" s="531"/>
-      <c r="J67" s="532"/>
-      <c r="K67" s="530"/>
-      <c r="L67" s="531"/>
-      <c r="M67" s="531"/>
-      <c r="N67" s="532"/>
-      <c r="O67" s="508"/>
-      <c r="P67" s="509"/>
-      <c r="Q67" s="509"/>
-      <c r="R67" s="510"/>
-      <c r="S67" s="508"/>
-      <c r="T67" s="509"/>
-      <c r="U67" s="509"/>
-      <c r="V67" s="510"/>
-      <c r="W67" s="508"/>
-      <c r="X67" s="509"/>
-      <c r="Y67" s="509"/>
-      <c r="Z67" s="510"/>
-      <c r="AA67" s="508"/>
-      <c r="AB67" s="509"/>
-      <c r="AC67" s="509"/>
-      <c r="AD67" s="510"/>
+      <c r="B67" s="492"/>
+      <c r="C67" s="493"/>
+      <c r="D67" s="493"/>
+      <c r="E67" s="493"/>
+      <c r="F67" s="494"/>
+      <c r="G67" s="501"/>
+      <c r="H67" s="502"/>
+      <c r="I67" s="502"/>
+      <c r="J67" s="503"/>
+      <c r="K67" s="501"/>
+      <c r="L67" s="502"/>
+      <c r="M67" s="502"/>
+      <c r="N67" s="503"/>
+      <c r="O67" s="472"/>
+      <c r="P67" s="473"/>
+      <c r="Q67" s="473"/>
+      <c r="R67" s="474"/>
+      <c r="S67" s="472"/>
+      <c r="T67" s="473"/>
+      <c r="U67" s="473"/>
+      <c r="V67" s="474"/>
+      <c r="W67" s="472"/>
+      <c r="X67" s="473"/>
+      <c r="Y67" s="473"/>
+      <c r="Z67" s="474"/>
+      <c r="AA67" s="472"/>
+      <c r="AB67" s="473"/>
+      <c r="AC67" s="473"/>
+      <c r="AD67" s="474"/>
     </row>
     <row r="68" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="521"/>
-      <c r="C68" s="522"/>
-      <c r="D68" s="522"/>
-      <c r="E68" s="522"/>
-      <c r="F68" s="523"/>
-      <c r="G68" s="530"/>
-      <c r="H68" s="531"/>
-      <c r="I68" s="531"/>
-      <c r="J68" s="532"/>
-      <c r="K68" s="530"/>
-      <c r="L68" s="531"/>
-      <c r="M68" s="531"/>
-      <c r="N68" s="532"/>
-      <c r="O68" s="508"/>
-      <c r="P68" s="509"/>
-      <c r="Q68" s="509"/>
-      <c r="R68" s="510"/>
-      <c r="S68" s="508"/>
-      <c r="T68" s="509"/>
-      <c r="U68" s="509"/>
-      <c r="V68" s="510"/>
-      <c r="W68" s="508"/>
-      <c r="X68" s="509"/>
-      <c r="Y68" s="509"/>
-      <c r="Z68" s="510"/>
-      <c r="AA68" s="508"/>
-      <c r="AB68" s="509"/>
-      <c r="AC68" s="509"/>
-      <c r="AD68" s="510"/>
+      <c r="B68" s="492"/>
+      <c r="C68" s="493"/>
+      <c r="D68" s="493"/>
+      <c r="E68" s="493"/>
+      <c r="F68" s="494"/>
+      <c r="G68" s="501"/>
+      <c r="H68" s="502"/>
+      <c r="I68" s="502"/>
+      <c r="J68" s="503"/>
+      <c r="K68" s="501"/>
+      <c r="L68" s="502"/>
+      <c r="M68" s="502"/>
+      <c r="N68" s="503"/>
+      <c r="O68" s="472"/>
+      <c r="P68" s="473"/>
+      <c r="Q68" s="473"/>
+      <c r="R68" s="474"/>
+      <c r="S68" s="472"/>
+      <c r="T68" s="473"/>
+      <c r="U68" s="473"/>
+      <c r="V68" s="474"/>
+      <c r="W68" s="472"/>
+      <c r="X68" s="473"/>
+      <c r="Y68" s="473"/>
+      <c r="Z68" s="474"/>
+      <c r="AA68" s="472"/>
+      <c r="AB68" s="473"/>
+      <c r="AC68" s="473"/>
+      <c r="AD68" s="474"/>
     </row>
     <row r="69" spans="2:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="524"/>
-      <c r="C69" s="525"/>
-      <c r="D69" s="525"/>
-      <c r="E69" s="525"/>
-      <c r="F69" s="526"/>
-      <c r="G69" s="533"/>
-      <c r="H69" s="534"/>
-      <c r="I69" s="534"/>
-      <c r="J69" s="535"/>
-      <c r="K69" s="533"/>
-      <c r="L69" s="534"/>
-      <c r="M69" s="534"/>
-      <c r="N69" s="535"/>
-      <c r="O69" s="511"/>
-      <c r="P69" s="512"/>
-      <c r="Q69" s="512"/>
-      <c r="R69" s="513"/>
-      <c r="S69" s="511"/>
-      <c r="T69" s="512"/>
-      <c r="U69" s="512"/>
-      <c r="V69" s="513"/>
-      <c r="W69" s="511"/>
-      <c r="X69" s="512"/>
-      <c r="Y69" s="512"/>
-      <c r="Z69" s="513"/>
-      <c r="AA69" s="511"/>
-      <c r="AB69" s="512"/>
-      <c r="AC69" s="512"/>
-      <c r="AD69" s="513"/>
+      <c r="B69" s="495"/>
+      <c r="C69" s="496"/>
+      <c r="D69" s="496"/>
+      <c r="E69" s="496"/>
+      <c r="F69" s="497"/>
+      <c r="G69" s="504"/>
+      <c r="H69" s="505"/>
+      <c r="I69" s="505"/>
+      <c r="J69" s="506"/>
+      <c r="K69" s="504"/>
+      <c r="L69" s="505"/>
+      <c r="M69" s="505"/>
+      <c r="N69" s="506"/>
+      <c r="O69" s="475"/>
+      <c r="P69" s="476"/>
+      <c r="Q69" s="476"/>
+      <c r="R69" s="477"/>
+      <c r="S69" s="475"/>
+      <c r="T69" s="476"/>
+      <c r="U69" s="476"/>
+      <c r="V69" s="477"/>
+      <c r="W69" s="475"/>
+      <c r="X69" s="476"/>
+      <c r="Y69" s="476"/>
+      <c r="Z69" s="477"/>
+      <c r="AA69" s="475"/>
+      <c r="AB69" s="476"/>
+      <c r="AC69" s="476"/>
+      <c r="AD69" s="477"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="W52:Z52"/>
-    <mergeCell ref="W51:Z51"/>
-    <mergeCell ref="W53:Z69"/>
-    <mergeCell ref="AA52:AD52"/>
-    <mergeCell ref="AA51:AD51"/>
-    <mergeCell ref="AA53:AD69"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G7:BB7"/>
+    <mergeCell ref="AQ8:AT8"/>
+    <mergeCell ref="AU8:AX8"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AQ10:BB10"/>
+    <mergeCell ref="AE8:AH8"/>
+    <mergeCell ref="AI8:AL8"/>
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AE10:AP10"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="AA8:AD8"/>
+    <mergeCell ref="S10:AD10"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="AA50:AD50"/>
+    <mergeCell ref="S50:V50"/>
+    <mergeCell ref="W50:Z50"/>
+    <mergeCell ref="AA49:AD49"/>
+    <mergeCell ref="W49:Z49"/>
+    <mergeCell ref="S49:V49"/>
+    <mergeCell ref="O49:R49"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="O51:R51"/>
+    <mergeCell ref="O50:R50"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="S51:V51"/>
+    <mergeCell ref="S52:V52"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="O52:R52"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="B21:B25"/>
     <mergeCell ref="B30:B33"/>
@@ -33140,43 +33171,12 @@
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="O51:R51"/>
-    <mergeCell ref="O50:R50"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="S51:V51"/>
-    <mergeCell ref="S52:V52"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="O52:R52"/>
-    <mergeCell ref="S10:AD10"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="AA50:AD50"/>
-    <mergeCell ref="S50:V50"/>
-    <mergeCell ref="W50:Z50"/>
-    <mergeCell ref="AA49:AD49"/>
-    <mergeCell ref="W49:Z49"/>
-    <mergeCell ref="S49:V49"/>
-    <mergeCell ref="O49:R49"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G7:BB7"/>
-    <mergeCell ref="AQ8:AT8"/>
-    <mergeCell ref="AU8:AX8"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AQ10:BB10"/>
-    <mergeCell ref="AE8:AH8"/>
-    <mergeCell ref="AI8:AL8"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AE10:AP10"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="AA8:AD8"/>
+    <mergeCell ref="W52:Z52"/>
+    <mergeCell ref="W51:Z51"/>
+    <mergeCell ref="W53:Z69"/>
+    <mergeCell ref="AA52:AD52"/>
+    <mergeCell ref="AA51:AD51"/>
+    <mergeCell ref="AA53:AD69"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33337,24 +33337,24 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="545" t="s">
+      <c r="G7" s="546" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="546"/>
-      <c r="I7" s="546"/>
-      <c r="J7" s="547"/>
-      <c r="K7" s="542" t="s">
+      <c r="H7" s="547"/>
+      <c r="I7" s="547"/>
+      <c r="J7" s="548"/>
+      <c r="K7" s="543" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="543"/>
-      <c r="M7" s="543"/>
-      <c r="N7" s="544"/>
-      <c r="O7" s="539" t="s">
+      <c r="L7" s="544"/>
+      <c r="M7" s="544"/>
+      <c r="N7" s="545"/>
+      <c r="O7" s="540" t="s">
         <v>76</v>
       </c>
-      <c r="P7" s="540"/>
-      <c r="Q7" s="540"/>
-      <c r="R7" s="541"/>
+      <c r="P7" s="541"/>
+      <c r="Q7" s="541"/>
+      <c r="R7" s="542"/>
     </row>
     <row r="8" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="167"/>
@@ -33547,7 +33547,7 @@
       <c r="R13" s="224"/>
     </row>
     <row r="14" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="552" t="s">
+      <c r="B14" s="553" t="s">
         <v>159</v>
       </c>
       <c r="C14" s="146" t="s">
@@ -33576,7 +33576,7 @@
       <c r="R14" s="266"/>
     </row>
     <row r="15" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="553"/>
+      <c r="B15" s="554"/>
       <c r="C15" s="228" t="s">
         <v>93</v>
       </c>
@@ -33603,7 +33603,7 @@
       <c r="R15" s="267"/>
     </row>
     <row r="16" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="552" t="s">
+      <c r="B16" s="553" t="s">
         <v>160</v>
       </c>
       <c r="C16" s="263" t="s">
@@ -33632,7 +33632,7 @@
       <c r="R16" s="264"/>
     </row>
     <row r="17" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="554"/>
+      <c r="B17" s="555"/>
       <c r="C17" s="296" t="s">
         <v>27</v>
       </c>
@@ -33663,7 +33663,7 @@
       <c r="R17" s="271"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="555" t="s">
+      <c r="B18" s="556" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="122" t="s">
@@ -33692,7 +33692,7 @@
       <c r="R18" s="266"/>
     </row>
     <row r="19" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="556"/>
+      <c r="B19" s="557"/>
       <c r="C19" s="123" t="s">
         <v>38</v>
       </c>
@@ -33721,7 +33721,7 @@
       <c r="R19" s="266"/>
     </row>
     <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="555" t="s">
+      <c r="B20" s="556" t="s">
         <v>162</v>
       </c>
       <c r="C20" s="119" t="s">
@@ -33750,7 +33750,7 @@
       <c r="R20" s="264"/>
     </row>
     <row r="21" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="556"/>
+      <c r="B21" s="557"/>
       <c r="C21" s="284" t="s">
         <v>44</v>
       </c>
@@ -33808,7 +33808,7 @@
       <c r="R22" s="266"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="557" t="s">
+      <c r="B23" s="558" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="119" t="s">
@@ -33837,7 +33837,7 @@
       <c r="R23" s="264"/>
     </row>
     <row r="24" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="558"/>
+      <c r="B24" s="559"/>
       <c r="C24" s="124" t="s">
         <v>20</v>
       </c>
@@ -33864,7 +33864,7 @@
       <c r="R24" s="281"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="552" t="s">
+      <c r="B25" s="553" t="s">
         <v>163</v>
       </c>
       <c r="C25" s="119" t="s">
@@ -33893,7 +33893,7 @@
       <c r="R25" s="23"/>
     </row>
     <row r="26" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="553"/>
+      <c r="B26" s="554"/>
       <c r="C26" s="124" t="s">
         <v>113</v>
       </c>
@@ -34007,455 +34007,442 @@
       <c r="R29" s="312"/>
     </row>
     <row r="30" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="515" t="s">
+      <c r="B30" s="486" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="516"/>
-      <c r="D30" s="516"/>
-      <c r="E30" s="516"/>
-      <c r="F30" s="516"/>
-      <c r="G30" s="515" t="s">
+      <c r="C30" s="487"/>
+      <c r="D30" s="487"/>
+      <c r="E30" s="487"/>
+      <c r="F30" s="487"/>
+      <c r="G30" s="486" t="s">
         <v>134</v>
       </c>
-      <c r="H30" s="516"/>
-      <c r="I30" s="516"/>
-      <c r="J30" s="551"/>
-      <c r="K30" s="491" t="s">
+      <c r="H30" s="487"/>
+      <c r="I30" s="487"/>
+      <c r="J30" s="552"/>
+      <c r="K30" s="482" t="s">
         <v>135</v>
       </c>
-      <c r="L30" s="492"/>
-      <c r="M30" s="492"/>
-      <c r="N30" s="493"/>
-      <c r="O30" s="491"/>
-      <c r="P30" s="492"/>
-      <c r="Q30" s="492"/>
-      <c r="R30" s="493"/>
+      <c r="L30" s="483"/>
+      <c r="M30" s="483"/>
+      <c r="N30" s="484"/>
+      <c r="O30" s="482"/>
+      <c r="P30" s="483"/>
+      <c r="Q30" s="483"/>
+      <c r="R30" s="484"/>
     </row>
     <row r="31" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="488" t="s">
+      <c r="B31" s="508" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="489"/>
-      <c r="D31" s="489"/>
-      <c r="E31" s="489"/>
-      <c r="F31" s="489"/>
-      <c r="G31" s="488" t="s">
+      <c r="C31" s="509"/>
+      <c r="D31" s="509"/>
+      <c r="E31" s="509"/>
+      <c r="F31" s="509"/>
+      <c r="G31" s="508" t="s">
         <v>139</v>
       </c>
-      <c r="H31" s="489"/>
-      <c r="I31" s="489"/>
-      <c r="J31" s="559"/>
-      <c r="K31" s="488" t="s">
+      <c r="H31" s="509"/>
+      <c r="I31" s="509"/>
+      <c r="J31" s="539"/>
+      <c r="K31" s="508" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="489"/>
-      <c r="M31" s="489"/>
-      <c r="N31" s="559"/>
-      <c r="O31" s="488" t="s">
+      <c r="L31" s="509"/>
+      <c r="M31" s="509"/>
+      <c r="N31" s="539"/>
+      <c r="O31" s="508" t="s">
         <v>138</v>
       </c>
-      <c r="P31" s="489"/>
-      <c r="Q31" s="489"/>
-      <c r="R31" s="559"/>
+      <c r="P31" s="509"/>
+      <c r="Q31" s="509"/>
+      <c r="R31" s="539"/>
     </row>
     <row r="32" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="463" t="s">
+      <c r="B32" s="466" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="464"/>
-      <c r="D32" s="464"/>
-      <c r="E32" s="464"/>
-      <c r="F32" s="464"/>
-      <c r="G32" s="463" t="s">
+      <c r="C32" s="467"/>
+      <c r="D32" s="467"/>
+      <c r="E32" s="467"/>
+      <c r="F32" s="467"/>
+      <c r="G32" s="466" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="464"/>
-      <c r="I32" s="464"/>
-      <c r="J32" s="538"/>
-      <c r="K32" s="463" t="s">
+      <c r="H32" s="467"/>
+      <c r="I32" s="467"/>
+      <c r="J32" s="479"/>
+      <c r="K32" s="466" t="s">
         <v>142</v>
       </c>
-      <c r="L32" s="464"/>
-      <c r="M32" s="464"/>
-      <c r="N32" s="538"/>
-      <c r="O32" s="463" t="s">
+      <c r="L32" s="467"/>
+      <c r="M32" s="467"/>
+      <c r="N32" s="479"/>
+      <c r="O32" s="466" t="s">
         <v>142</v>
       </c>
-      <c r="P32" s="464"/>
-      <c r="Q32" s="464"/>
-      <c r="R32" s="538"/>
+      <c r="P32" s="467"/>
+      <c r="Q32" s="467"/>
+      <c r="R32" s="479"/>
     </row>
     <row r="33" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="548" t="s">
+      <c r="B33" s="549" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="549"/>
-      <c r="D33" s="549"/>
-      <c r="E33" s="549"/>
-      <c r="F33" s="550"/>
-      <c r="G33" s="466" t="s">
+      <c r="C33" s="550"/>
+      <c r="D33" s="550"/>
+      <c r="E33" s="550"/>
+      <c r="F33" s="551"/>
+      <c r="G33" s="463" t="s">
         <v>147</v>
       </c>
-      <c r="H33" s="467"/>
-      <c r="I33" s="467"/>
-      <c r="J33" s="537"/>
-      <c r="K33" s="466" t="s">
+      <c r="H33" s="464"/>
+      <c r="I33" s="464"/>
+      <c r="J33" s="478"/>
+      <c r="K33" s="463" t="s">
         <v>165</v>
       </c>
-      <c r="L33" s="467"/>
-      <c r="M33" s="467"/>
-      <c r="N33" s="537"/>
-      <c r="O33" s="466"/>
-      <c r="P33" s="467"/>
-      <c r="Q33" s="467"/>
-      <c r="R33" s="537"/>
+      <c r="L33" s="464"/>
+      <c r="M33" s="464"/>
+      <c r="N33" s="478"/>
+      <c r="O33" s="463"/>
+      <c r="P33" s="464"/>
+      <c r="Q33" s="464"/>
+      <c r="R33" s="478"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B34" s="518" t="s">
+      <c r="B34" s="489" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="519"/>
-      <c r="D34" s="519"/>
-      <c r="E34" s="519"/>
-      <c r="F34" s="520"/>
-      <c r="G34" s="505" t="s">
+      <c r="C34" s="490"/>
+      <c r="D34" s="490"/>
+      <c r="E34" s="490"/>
+      <c r="F34" s="491"/>
+      <c r="G34" s="469" t="s">
         <v>151</v>
       </c>
-      <c r="H34" s="506"/>
-      <c r="I34" s="506"/>
-      <c r="J34" s="507"/>
-      <c r="K34" s="505" t="s">
+      <c r="H34" s="470"/>
+      <c r="I34" s="470"/>
+      <c r="J34" s="471"/>
+      <c r="K34" s="469" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="506"/>
-      <c r="M34" s="506"/>
-      <c r="N34" s="507"/>
-      <c r="O34" s="505" t="s">
+      <c r="L34" s="470"/>
+      <c r="M34" s="470"/>
+      <c r="N34" s="471"/>
+      <c r="O34" s="469" t="s">
         <v>166</v>
       </c>
-      <c r="P34" s="506"/>
-      <c r="Q34" s="506"/>
-      <c r="R34" s="507"/>
+      <c r="P34" s="470"/>
+      <c r="Q34" s="470"/>
+      <c r="R34" s="471"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="521"/>
-      <c r="C35" s="522"/>
-      <c r="D35" s="522"/>
-      <c r="E35" s="522"/>
-      <c r="F35" s="523"/>
-      <c r="G35" s="508"/>
-      <c r="H35" s="509"/>
-      <c r="I35" s="509"/>
-      <c r="J35" s="510"/>
-      <c r="K35" s="508"/>
-      <c r="L35" s="509"/>
-      <c r="M35" s="509"/>
-      <c r="N35" s="510"/>
-      <c r="O35" s="508"/>
-      <c r="P35" s="509"/>
-      <c r="Q35" s="509"/>
-      <c r="R35" s="510"/>
+      <c r="B35" s="492"/>
+      <c r="C35" s="493"/>
+      <c r="D35" s="493"/>
+      <c r="E35" s="493"/>
+      <c r="F35" s="494"/>
+      <c r="G35" s="472"/>
+      <c r="H35" s="473"/>
+      <c r="I35" s="473"/>
+      <c r="J35" s="474"/>
+      <c r="K35" s="472"/>
+      <c r="L35" s="473"/>
+      <c r="M35" s="473"/>
+      <c r="N35" s="474"/>
+      <c r="O35" s="472"/>
+      <c r="P35" s="473"/>
+      <c r="Q35" s="473"/>
+      <c r="R35" s="474"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B36" s="521"/>
-      <c r="C36" s="522"/>
-      <c r="D36" s="522"/>
-      <c r="E36" s="522"/>
-      <c r="F36" s="523"/>
-      <c r="G36" s="508"/>
-      <c r="H36" s="509"/>
-      <c r="I36" s="509"/>
-      <c r="J36" s="510"/>
-      <c r="K36" s="508"/>
-      <c r="L36" s="509"/>
-      <c r="M36" s="509"/>
-      <c r="N36" s="510"/>
-      <c r="O36" s="508"/>
-      <c r="P36" s="509"/>
-      <c r="Q36" s="509"/>
-      <c r="R36" s="510"/>
+      <c r="B36" s="492"/>
+      <c r="C36" s="493"/>
+      <c r="D36" s="493"/>
+      <c r="E36" s="493"/>
+      <c r="F36" s="494"/>
+      <c r="G36" s="472"/>
+      <c r="H36" s="473"/>
+      <c r="I36" s="473"/>
+      <c r="J36" s="474"/>
+      <c r="K36" s="472"/>
+      <c r="L36" s="473"/>
+      <c r="M36" s="473"/>
+      <c r="N36" s="474"/>
+      <c r="O36" s="472"/>
+      <c r="P36" s="473"/>
+      <c r="Q36" s="473"/>
+      <c r="R36" s="474"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="521"/>
-      <c r="C37" s="522"/>
-      <c r="D37" s="522"/>
-      <c r="E37" s="522"/>
-      <c r="F37" s="523"/>
-      <c r="G37" s="508"/>
-      <c r="H37" s="509"/>
-      <c r="I37" s="509"/>
-      <c r="J37" s="510"/>
-      <c r="K37" s="508"/>
-      <c r="L37" s="509"/>
-      <c r="M37" s="509"/>
-      <c r="N37" s="510"/>
-      <c r="O37" s="508"/>
-      <c r="P37" s="509"/>
-      <c r="Q37" s="509"/>
-      <c r="R37" s="510"/>
+      <c r="B37" s="492"/>
+      <c r="C37" s="493"/>
+      <c r="D37" s="493"/>
+      <c r="E37" s="493"/>
+      <c r="F37" s="494"/>
+      <c r="G37" s="472"/>
+      <c r="H37" s="473"/>
+      <c r="I37" s="473"/>
+      <c r="J37" s="474"/>
+      <c r="K37" s="472"/>
+      <c r="L37" s="473"/>
+      <c r="M37" s="473"/>
+      <c r="N37" s="474"/>
+      <c r="O37" s="472"/>
+      <c r="P37" s="473"/>
+      <c r="Q37" s="473"/>
+      <c r="R37" s="474"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="521"/>
-      <c r="C38" s="522"/>
-      <c r="D38" s="522"/>
-      <c r="E38" s="522"/>
-      <c r="F38" s="523"/>
-      <c r="G38" s="508"/>
-      <c r="H38" s="509"/>
-      <c r="I38" s="509"/>
-      <c r="J38" s="510"/>
-      <c r="K38" s="508"/>
-      <c r="L38" s="509"/>
-      <c r="M38" s="509"/>
-      <c r="N38" s="510"/>
-      <c r="O38" s="508"/>
-      <c r="P38" s="509"/>
-      <c r="Q38" s="509"/>
-      <c r="R38" s="510"/>
+      <c r="B38" s="492"/>
+      <c r="C38" s="493"/>
+      <c r="D38" s="493"/>
+      <c r="E38" s="493"/>
+      <c r="F38" s="494"/>
+      <c r="G38" s="472"/>
+      <c r="H38" s="473"/>
+      <c r="I38" s="473"/>
+      <c r="J38" s="474"/>
+      <c r="K38" s="472"/>
+      <c r="L38" s="473"/>
+      <c r="M38" s="473"/>
+      <c r="N38" s="474"/>
+      <c r="O38" s="472"/>
+      <c r="P38" s="473"/>
+      <c r="Q38" s="473"/>
+      <c r="R38" s="474"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="521"/>
-      <c r="C39" s="522"/>
-      <c r="D39" s="522"/>
-      <c r="E39" s="522"/>
-      <c r="F39" s="523"/>
-      <c r="G39" s="508"/>
-      <c r="H39" s="509"/>
-      <c r="I39" s="509"/>
-      <c r="J39" s="510"/>
-      <c r="K39" s="508"/>
-      <c r="L39" s="509"/>
-      <c r="M39" s="509"/>
-      <c r="N39" s="510"/>
-      <c r="O39" s="508"/>
-      <c r="P39" s="509"/>
-      <c r="Q39" s="509"/>
-      <c r="R39" s="510"/>
+      <c r="B39" s="492"/>
+      <c r="C39" s="493"/>
+      <c r="D39" s="493"/>
+      <c r="E39" s="493"/>
+      <c r="F39" s="494"/>
+      <c r="G39" s="472"/>
+      <c r="H39" s="473"/>
+      <c r="I39" s="473"/>
+      <c r="J39" s="474"/>
+      <c r="K39" s="472"/>
+      <c r="L39" s="473"/>
+      <c r="M39" s="473"/>
+      <c r="N39" s="474"/>
+      <c r="O39" s="472"/>
+      <c r="P39" s="473"/>
+      <c r="Q39" s="473"/>
+      <c r="R39" s="474"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="521"/>
-      <c r="C40" s="522"/>
-      <c r="D40" s="522"/>
-      <c r="E40" s="522"/>
-      <c r="F40" s="523"/>
-      <c r="G40" s="508"/>
-      <c r="H40" s="509"/>
-      <c r="I40" s="509"/>
-      <c r="J40" s="510"/>
-      <c r="K40" s="508"/>
-      <c r="L40" s="509"/>
-      <c r="M40" s="509"/>
-      <c r="N40" s="510"/>
-      <c r="O40" s="508"/>
-      <c r="P40" s="509"/>
-      <c r="Q40" s="509"/>
-      <c r="R40" s="510"/>
+      <c r="B40" s="492"/>
+      <c r="C40" s="493"/>
+      <c r="D40" s="493"/>
+      <c r="E40" s="493"/>
+      <c r="F40" s="494"/>
+      <c r="G40" s="472"/>
+      <c r="H40" s="473"/>
+      <c r="I40" s="473"/>
+      <c r="J40" s="474"/>
+      <c r="K40" s="472"/>
+      <c r="L40" s="473"/>
+      <c r="M40" s="473"/>
+      <c r="N40" s="474"/>
+      <c r="O40" s="472"/>
+      <c r="P40" s="473"/>
+      <c r="Q40" s="473"/>
+      <c r="R40" s="474"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="521"/>
-      <c r="C41" s="522"/>
-      <c r="D41" s="522"/>
-      <c r="E41" s="522"/>
-      <c r="F41" s="523"/>
-      <c r="G41" s="508"/>
-      <c r="H41" s="509"/>
-      <c r="I41" s="509"/>
-      <c r="J41" s="510"/>
-      <c r="K41" s="508"/>
-      <c r="L41" s="509"/>
-      <c r="M41" s="509"/>
-      <c r="N41" s="510"/>
-      <c r="O41" s="508"/>
-      <c r="P41" s="509"/>
-      <c r="Q41" s="509"/>
-      <c r="R41" s="510"/>
+      <c r="B41" s="492"/>
+      <c r="C41" s="493"/>
+      <c r="D41" s="493"/>
+      <c r="E41" s="493"/>
+      <c r="F41" s="494"/>
+      <c r="G41" s="472"/>
+      <c r="H41" s="473"/>
+      <c r="I41" s="473"/>
+      <c r="J41" s="474"/>
+      <c r="K41" s="472"/>
+      <c r="L41" s="473"/>
+      <c r="M41" s="473"/>
+      <c r="N41" s="474"/>
+      <c r="O41" s="472"/>
+      <c r="P41" s="473"/>
+      <c r="Q41" s="473"/>
+      <c r="R41" s="474"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="521"/>
-      <c r="C42" s="522"/>
-      <c r="D42" s="522"/>
-      <c r="E42" s="522"/>
-      <c r="F42" s="523"/>
-      <c r="G42" s="508"/>
-      <c r="H42" s="509"/>
-      <c r="I42" s="509"/>
-      <c r="J42" s="510"/>
-      <c r="K42" s="508"/>
-      <c r="L42" s="509"/>
-      <c r="M42" s="509"/>
-      <c r="N42" s="510"/>
-      <c r="O42" s="508"/>
-      <c r="P42" s="509"/>
-      <c r="Q42" s="509"/>
-      <c r="R42" s="510"/>
+      <c r="B42" s="492"/>
+      <c r="C42" s="493"/>
+      <c r="D42" s="493"/>
+      <c r="E42" s="493"/>
+      <c r="F42" s="494"/>
+      <c r="G42" s="472"/>
+      <c r="H42" s="473"/>
+      <c r="I42" s="473"/>
+      <c r="J42" s="474"/>
+      <c r="K42" s="472"/>
+      <c r="L42" s="473"/>
+      <c r="M42" s="473"/>
+      <c r="N42" s="474"/>
+      <c r="O42" s="472"/>
+      <c r="P42" s="473"/>
+      <c r="Q42" s="473"/>
+      <c r="R42" s="474"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="521"/>
-      <c r="C43" s="522"/>
-      <c r="D43" s="522"/>
-      <c r="E43" s="522"/>
-      <c r="F43" s="523"/>
-      <c r="G43" s="508"/>
-      <c r="H43" s="509"/>
-      <c r="I43" s="509"/>
-      <c r="J43" s="510"/>
-      <c r="K43" s="508"/>
-      <c r="L43" s="509"/>
-      <c r="M43" s="509"/>
-      <c r="N43" s="510"/>
-      <c r="O43" s="508"/>
-      <c r="P43" s="509"/>
-      <c r="Q43" s="509"/>
-      <c r="R43" s="510"/>
+      <c r="B43" s="492"/>
+      <c r="C43" s="493"/>
+      <c r="D43" s="493"/>
+      <c r="E43" s="493"/>
+      <c r="F43" s="494"/>
+      <c r="G43" s="472"/>
+      <c r="H43" s="473"/>
+      <c r="I43" s="473"/>
+      <c r="J43" s="474"/>
+      <c r="K43" s="472"/>
+      <c r="L43" s="473"/>
+      <c r="M43" s="473"/>
+      <c r="N43" s="474"/>
+      <c r="O43" s="472"/>
+      <c r="P43" s="473"/>
+      <c r="Q43" s="473"/>
+      <c r="R43" s="474"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="521"/>
-      <c r="C44" s="522"/>
-      <c r="D44" s="522"/>
-      <c r="E44" s="522"/>
-      <c r="F44" s="523"/>
-      <c r="G44" s="508"/>
-      <c r="H44" s="509"/>
-      <c r="I44" s="509"/>
-      <c r="J44" s="510"/>
-      <c r="K44" s="508"/>
-      <c r="L44" s="509"/>
-      <c r="M44" s="509"/>
-      <c r="N44" s="510"/>
-      <c r="O44" s="508"/>
-      <c r="P44" s="509"/>
-      <c r="Q44" s="509"/>
-      <c r="R44" s="510"/>
+      <c r="B44" s="492"/>
+      <c r="C44" s="493"/>
+      <c r="D44" s="493"/>
+      <c r="E44" s="493"/>
+      <c r="F44" s="494"/>
+      <c r="G44" s="472"/>
+      <c r="H44" s="473"/>
+      <c r="I44" s="473"/>
+      <c r="J44" s="474"/>
+      <c r="K44" s="472"/>
+      <c r="L44" s="473"/>
+      <c r="M44" s="473"/>
+      <c r="N44" s="474"/>
+      <c r="O44" s="472"/>
+      <c r="P44" s="473"/>
+      <c r="Q44" s="473"/>
+      <c r="R44" s="474"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="521"/>
-      <c r="C45" s="522"/>
-      <c r="D45" s="522"/>
-      <c r="E45" s="522"/>
-      <c r="F45" s="523"/>
-      <c r="G45" s="508"/>
-      <c r="H45" s="509"/>
-      <c r="I45" s="509"/>
-      <c r="J45" s="510"/>
-      <c r="K45" s="508"/>
-      <c r="L45" s="509"/>
-      <c r="M45" s="509"/>
-      <c r="N45" s="510"/>
-      <c r="O45" s="508"/>
-      <c r="P45" s="509"/>
-      <c r="Q45" s="509"/>
-      <c r="R45" s="510"/>
+      <c r="B45" s="492"/>
+      <c r="C45" s="493"/>
+      <c r="D45" s="493"/>
+      <c r="E45" s="493"/>
+      <c r="F45" s="494"/>
+      <c r="G45" s="472"/>
+      <c r="H45" s="473"/>
+      <c r="I45" s="473"/>
+      <c r="J45" s="474"/>
+      <c r="K45" s="472"/>
+      <c r="L45" s="473"/>
+      <c r="M45" s="473"/>
+      <c r="N45" s="474"/>
+      <c r="O45" s="472"/>
+      <c r="P45" s="473"/>
+      <c r="Q45" s="473"/>
+      <c r="R45" s="474"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="521"/>
-      <c r="C46" s="522"/>
-      <c r="D46" s="522"/>
-      <c r="E46" s="522"/>
-      <c r="F46" s="523"/>
-      <c r="G46" s="508"/>
-      <c r="H46" s="509"/>
-      <c r="I46" s="509"/>
-      <c r="J46" s="510"/>
-      <c r="K46" s="508"/>
-      <c r="L46" s="509"/>
-      <c r="M46" s="509"/>
-      <c r="N46" s="510"/>
-      <c r="O46" s="508"/>
-      <c r="P46" s="509"/>
-      <c r="Q46" s="509"/>
-      <c r="R46" s="510"/>
+      <c r="B46" s="492"/>
+      <c r="C46" s="493"/>
+      <c r="D46" s="493"/>
+      <c r="E46" s="493"/>
+      <c r="F46" s="494"/>
+      <c r="G46" s="472"/>
+      <c r="H46" s="473"/>
+      <c r="I46" s="473"/>
+      <c r="J46" s="474"/>
+      <c r="K46" s="472"/>
+      <c r="L46" s="473"/>
+      <c r="M46" s="473"/>
+      <c r="N46" s="474"/>
+      <c r="O46" s="472"/>
+      <c r="P46" s="473"/>
+      <c r="Q46" s="473"/>
+      <c r="R46" s="474"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="521"/>
-      <c r="C47" s="522"/>
-      <c r="D47" s="522"/>
-      <c r="E47" s="522"/>
-      <c r="F47" s="523"/>
-      <c r="G47" s="508"/>
-      <c r="H47" s="509"/>
-      <c r="I47" s="509"/>
-      <c r="J47" s="510"/>
-      <c r="K47" s="508"/>
-      <c r="L47" s="509"/>
-      <c r="M47" s="509"/>
-      <c r="N47" s="510"/>
-      <c r="O47" s="508"/>
-      <c r="P47" s="509"/>
-      <c r="Q47" s="509"/>
-      <c r="R47" s="510"/>
+      <c r="B47" s="492"/>
+      <c r="C47" s="493"/>
+      <c r="D47" s="493"/>
+      <c r="E47" s="493"/>
+      <c r="F47" s="494"/>
+      <c r="G47" s="472"/>
+      <c r="H47" s="473"/>
+      <c r="I47" s="473"/>
+      <c r="J47" s="474"/>
+      <c r="K47" s="472"/>
+      <c r="L47" s="473"/>
+      <c r="M47" s="473"/>
+      <c r="N47" s="474"/>
+      <c r="O47" s="472"/>
+      <c r="P47" s="473"/>
+      <c r="Q47" s="473"/>
+      <c r="R47" s="474"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="521"/>
-      <c r="C48" s="522"/>
-      <c r="D48" s="522"/>
-      <c r="E48" s="522"/>
-      <c r="F48" s="523"/>
-      <c r="G48" s="508"/>
-      <c r="H48" s="509"/>
-      <c r="I48" s="509"/>
-      <c r="J48" s="510"/>
-      <c r="K48" s="508"/>
-      <c r="L48" s="509"/>
-      <c r="M48" s="509"/>
-      <c r="N48" s="510"/>
-      <c r="O48" s="508"/>
-      <c r="P48" s="509"/>
-      <c r="Q48" s="509"/>
-      <c r="R48" s="510"/>
+      <c r="B48" s="492"/>
+      <c r="C48" s="493"/>
+      <c r="D48" s="493"/>
+      <c r="E48" s="493"/>
+      <c r="F48" s="494"/>
+      <c r="G48" s="472"/>
+      <c r="H48" s="473"/>
+      <c r="I48" s="473"/>
+      <c r="J48" s="474"/>
+      <c r="K48" s="472"/>
+      <c r="L48" s="473"/>
+      <c r="M48" s="473"/>
+      <c r="N48" s="474"/>
+      <c r="O48" s="472"/>
+      <c r="P48" s="473"/>
+      <c r="Q48" s="473"/>
+      <c r="R48" s="474"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B49" s="521"/>
-      <c r="C49" s="522"/>
-      <c r="D49" s="522"/>
-      <c r="E49" s="522"/>
-      <c r="F49" s="523"/>
-      <c r="G49" s="508"/>
-      <c r="H49" s="509"/>
-      <c r="I49" s="509"/>
-      <c r="J49" s="510"/>
-      <c r="K49" s="508"/>
-      <c r="L49" s="509"/>
-      <c r="M49" s="509"/>
-      <c r="N49" s="510"/>
-      <c r="O49" s="508"/>
-      <c r="P49" s="509"/>
-      <c r="Q49" s="509"/>
-      <c r="R49" s="510"/>
+      <c r="B49" s="492"/>
+      <c r="C49" s="493"/>
+      <c r="D49" s="493"/>
+      <c r="E49" s="493"/>
+      <c r="F49" s="494"/>
+      <c r="G49" s="472"/>
+      <c r="H49" s="473"/>
+      <c r="I49" s="473"/>
+      <c r="J49" s="474"/>
+      <c r="K49" s="472"/>
+      <c r="L49" s="473"/>
+      <c r="M49" s="473"/>
+      <c r="N49" s="474"/>
+      <c r="O49" s="472"/>
+      <c r="P49" s="473"/>
+      <c r="Q49" s="473"/>
+      <c r="R49" s="474"/>
     </row>
     <row r="50" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="524"/>
-      <c r="C50" s="525"/>
-      <c r="D50" s="525"/>
-      <c r="E50" s="525"/>
-      <c r="F50" s="526"/>
-      <c r="G50" s="511"/>
-      <c r="H50" s="512"/>
-      <c r="I50" s="512"/>
-      <c r="J50" s="513"/>
-      <c r="K50" s="511"/>
-      <c r="L50" s="512"/>
-      <c r="M50" s="512"/>
-      <c r="N50" s="513"/>
-      <c r="O50" s="511"/>
-      <c r="P50" s="512"/>
-      <c r="Q50" s="512"/>
-      <c r="R50" s="513"/>
+      <c r="B50" s="495"/>
+      <c r="C50" s="496"/>
+      <c r="D50" s="496"/>
+      <c r="E50" s="496"/>
+      <c r="F50" s="497"/>
+      <c r="G50" s="475"/>
+      <c r="H50" s="476"/>
+      <c r="I50" s="476"/>
+      <c r="J50" s="477"/>
+      <c r="K50" s="475"/>
+      <c r="L50" s="476"/>
+      <c r="M50" s="476"/>
+      <c r="N50" s="477"/>
+      <c r="O50" s="475"/>
+      <c r="P50" s="476"/>
+      <c r="Q50" s="476"/>
+      <c r="R50" s="477"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="G34:J50"/>
-    <mergeCell ref="K34:N50"/>
-    <mergeCell ref="O34:R50"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="O31:R31"/>
     <mergeCell ref="O7:R7"/>
     <mergeCell ref="K7:N7"/>
     <mergeCell ref="G7:J7"/>
@@ -34472,6 +34459,19 @@
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="O32:R32"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="G34:J50"/>
+    <mergeCell ref="K34:N50"/>
+    <mergeCell ref="O34:R50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -39333,21 +39333,21 @@
         <v>400</v>
       </c>
       <c r="E136" s="239">
-        <v>46184</v>
+        <v>46186</v>
       </c>
       <c r="F136" s="188">
-        <v>46188.739583333336</v>
+        <v>46190.197916666664</v>
       </c>
       <c r="G136" s="188">
         <f t="shared" si="13"/>
-        <v>46190.239583333336</v>
+        <v>46191.697916666664</v>
       </c>
       <c r="H136" s="189">
         <v>36</v>
       </c>
       <c r="I136" s="188">
         <f t="shared" si="8"/>
-        <v>46190.90625</v>
+        <v>46192.364583333328</v>
       </c>
       <c r="J136" s="190">
         <v>16</v>
@@ -39367,21 +39367,21 @@
         <v>401</v>
       </c>
       <c r="E137" s="54">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="F137" s="180">
-        <v>46189.34375</v>
+        <v>46190.802083333336</v>
       </c>
       <c r="G137" s="180">
         <f t="shared" si="13"/>
-        <v>46190.34375</v>
+        <v>46191.802083333336</v>
       </c>
       <c r="H137" s="32">
         <v>24</v>
       </c>
       <c r="I137" s="180">
         <f t="shared" si="8"/>
-        <v>46191.010416666664</v>
+        <v>46192.46875</v>
       </c>
       <c r="J137" s="126">
         <v>16</v>
@@ -39401,21 +39401,21 @@
         <v>402</v>
       </c>
       <c r="E138" s="393">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="F138" s="394">
-        <v>46192.697916666664</v>
+        <v>46194.15625</v>
       </c>
       <c r="G138" s="394">
         <f t="shared" si="13"/>
-        <v>46194.197916666664</v>
+        <v>46195.65625</v>
       </c>
       <c r="H138" s="391">
         <v>36</v>
       </c>
       <c r="I138" s="394">
         <f t="shared" si="8"/>
-        <v>46194.864583333328</v>
+        <v>46196.322916666664</v>
       </c>
       <c r="J138" s="126">
         <v>16</v>
@@ -39435,21 +39435,21 @@
         <v>403</v>
       </c>
       <c r="E139" s="54">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="F139" s="180">
-        <v>46194.09375</v>
+        <v>46195.552083333336</v>
       </c>
       <c r="G139" s="180">
         <f t="shared" si="13"/>
-        <v>46196.09375</v>
+        <v>46197.552083333336</v>
       </c>
       <c r="H139" s="32">
         <v>48</v>
       </c>
       <c r="I139" s="180">
         <f t="shared" si="8"/>
-        <v>46196.760416666664</v>
+        <v>46198.21875</v>
       </c>
       <c r="J139" s="126">
         <v>16</v>
@@ -39469,21 +39469,21 @@
         <v>404</v>
       </c>
       <c r="E140" s="54">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F140" s="180">
-        <v>46198.40625</v>
+        <v>46199.864583333336</v>
       </c>
       <c r="G140" s="180">
         <f t="shared" si="13"/>
-        <v>46199.40625</v>
+        <v>46200.864583333336</v>
       </c>
       <c r="H140" s="32">
         <v>24</v>
       </c>
       <c r="I140" s="180">
         <f t="shared" si="8"/>
-        <v>46200.072916666664</v>
+        <v>46201.53125</v>
       </c>
       <c r="J140" s="126">
         <v>16</v>
@@ -39503,21 +39503,21 @@
         <v>405</v>
       </c>
       <c r="E141" s="54">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="F141" s="180">
-        <v>46209.036111111112</v>
+        <v>46210.494444444441</v>
       </c>
       <c r="G141" s="180">
         <f t="shared" si="13"/>
-        <v>46210.036111111112</v>
+        <v>46211.494444444441</v>
       </c>
       <c r="H141" s="32">
         <v>24</v>
       </c>
       <c r="I141" s="180">
         <f t="shared" si="8"/>
-        <v>46210.702777777777</v>
+        <v>46212.161111111105</v>
       </c>
       <c r="J141" s="126">
         <v>16</v>
@@ -39537,21 +39537,21 @@
         <v>406</v>
       </c>
       <c r="E142" s="54">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F142" s="180">
-        <v>46211.036111111112</v>
+        <v>46212.494444444441</v>
       </c>
       <c r="G142" s="245">
         <f>F142+(H142/24)</f>
-        <v>46212.036111111112</v>
+        <v>46213.494444444441</v>
       </c>
       <c r="H142" s="32">
         <v>24</v>
       </c>
       <c r="I142" s="245">
         <f>G142+(J142/24)</f>
-        <v>46212.702777777777</v>
+        <v>46214.161111111105</v>
       </c>
       <c r="J142" s="126">
         <v>16</v>
@@ -39571,21 +39571,21 @@
         <v>407</v>
       </c>
       <c r="E143" s="240">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="F143" s="183">
-        <v>46219.691666666666</v>
+        <v>46221.15</v>
       </c>
       <c r="G143" s="205">
         <f>F143+(H143/24)</f>
-        <v>46220.691666666666</v>
+        <v>46222.15</v>
       </c>
       <c r="H143" s="184">
         <v>24</v>
       </c>
       <c r="I143" s="205">
         <f>G143+(J143/24)</f>
-        <v>46221.35833333333</v>
+        <v>46222.816666666666</v>
       </c>
       <c r="J143" s="127">
         <v>16</v>
@@ -41091,12 +41091,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
+      <Value>1</Value>
+    </TaxCatchAll>
+    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
+        </TermInfo>
+      </Terms>
+    </SAEFSecurityClassificationTaxHTField0>
+    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41421,33 +41436,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b2778aaa-fd83-416e-8091-738aa96f6cd3">
-      <Value>1</Value>
-    </TaxCatchAll>
-    <ShortDescription xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <Sub_x002d_category xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-    <SAEFSecurityClassificationTaxHTField0 xmlns="http://schemas.microsoft.com/sharepoint/v3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Confidential</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">e4bc29b2-6e76-48cc-b090-8b544c0802ae</TermId>
-        </TermInfo>
-      </Terms>
-    </SAEFSecurityClassificationTaxHTField0>
-    <FocusArea xmlns="91455a6e-8899-4f67-a6e4-e187ec74b863" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
+    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -41473,13 +41477,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C73227B-6E13-4F91-A067-CFE89F5B7659}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
-    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9322" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3ED4D5B-26F2-4487-BBC7-10DC5A2CCC9F}"/>
+  <xr:revisionPtr revIDLastSave="9406" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BCAF647-7368-47B7-858C-288D29875442}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="11_17_2025 Spot Hire Update" sheetId="2" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="488">
   <si>
     <t xml:space="preserve">Top Hole </t>
   </si>
@@ -1956,9 +1956,6 @@
     <t>GL 02 OSV / Drill 12 1/4''x 14 3/4'' section</t>
   </si>
   <si>
-    <t>7/54/2026</t>
-  </si>
-  <si>
     <t>GL 02 OSV-24 Hours- Whipstock BHA / SLB 12-1/4" BHA</t>
   </si>
   <si>
@@ -1975,10 +1972,10 @@
   </si>
   <si>
     <t xml:space="preserve">	
-GL 06 OSV / 48 hrs / 15,000 bbl of 16 ppg WBM</t>
-  </si>
-  <si>
-    <t>GL 12 OSV / 24 hrs / 12-1/4" &amp; 11.97" Casing, Casing Rack Back Tools, 12-1/4" Hanger</t>
+GL 05 OSV / 48 hrs / 15,000 bbl of 16 ppg WBM</t>
+  </si>
+  <si>
+    <t>GL 11 OSV / 24 hrs / 12-1/4" &amp; 11.97" Casing, Casing Rack Back Tools, 12-1/4" Hanger</t>
   </si>
 </sst>
 </file>
@@ -36108,21 +36105,21 @@
         <v>279</v>
       </c>
       <c r="E39" s="425">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="F39" s="426">
-        <v>46201.3125</v>
+        <v>46202.46875</v>
       </c>
       <c r="G39" s="426">
         <f>F39+(H39/24)</f>
-        <v>46203.3125</v>
+        <v>46204.46875</v>
       </c>
       <c r="H39" s="424">
         <v>48</v>
       </c>
       <c r="I39" s="426">
         <f>G39+(J39/24)</f>
-        <v>46205.3125</v>
+        <v>46206.46875</v>
       </c>
       <c r="J39" s="427">
         <v>48</v>
@@ -36210,21 +36207,21 @@
         <v>281</v>
       </c>
       <c r="E42" s="241">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="F42" s="213">
-        <v>46198.333333333336</v>
+        <v>46198.96875</v>
       </c>
       <c r="G42" s="180">
         <f>F42+(H42/24)</f>
-        <v>46200.333333333336</v>
+        <v>46200.96875</v>
       </c>
       <c r="H42" s="214">
         <v>48</v>
       </c>
       <c r="I42" s="180">
         <f>G42+(J42/24)</f>
-        <v>46202.333333333336</v>
+        <v>46202.96875</v>
       </c>
       <c r="J42" s="215">
         <v>48</v>
@@ -36278,21 +36275,21 @@
         <v>284</v>
       </c>
       <c r="E44" s="242">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F44" s="181">
-        <v>46212.5</v>
+        <v>46213.65625</v>
       </c>
       <c r="G44" s="181">
         <f t="shared" si="2"/>
-        <v>46215.5</v>
+        <v>46216.65625</v>
       </c>
       <c r="H44" s="170">
         <v>72</v>
       </c>
       <c r="I44" s="181">
         <f t="shared" si="3"/>
-        <v>46217.5</v>
+        <v>46218.65625</v>
       </c>
       <c r="J44" s="191">
         <v>48</v>
@@ -36312,21 +36309,21 @@
         <v>285</v>
       </c>
       <c r="E45" s="54">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="F45" s="180">
-        <v>46215.135416666664</v>
+        <v>46216.291666666664</v>
       </c>
       <c r="G45" s="180">
         <f t="shared" si="2"/>
-        <v>46217.135416666664</v>
+        <v>46218.291666666664</v>
       </c>
       <c r="H45" s="32">
         <v>48</v>
       </c>
       <c r="I45" s="180">
         <f t="shared" si="3"/>
-        <v>46219.135416666664</v>
+        <v>46220.291666666664</v>
       </c>
       <c r="J45" s="126">
         <v>48</v>
@@ -36346,21 +36343,21 @@
         <v>286</v>
       </c>
       <c r="E46" s="54">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F46" s="180">
-        <v>46221.760416666664</v>
+        <v>46222.916666666664</v>
       </c>
       <c r="G46" s="180">
         <f t="shared" si="2"/>
-        <v>46224.760416666664</v>
+        <v>46225.916666666664</v>
       </c>
       <c r="H46" s="32">
         <v>72</v>
       </c>
       <c r="I46" s="180">
         <f t="shared" si="3"/>
-        <v>46226.760416666664</v>
+        <v>46227.916666666664</v>
       </c>
       <c r="J46" s="126">
         <v>48</v>
@@ -36380,21 +36377,21 @@
         <v>287</v>
       </c>
       <c r="E47" s="54">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="F47" s="180">
-        <v>46226.416666666664</v>
+        <v>46227.572916666664</v>
       </c>
       <c r="G47" s="180">
         <f t="shared" si="2"/>
-        <v>46227.416666666664</v>
+        <v>46228.572916666664</v>
       </c>
       <c r="H47" s="32">
         <v>24</v>
       </c>
       <c r="I47" s="180">
         <f t="shared" si="3"/>
-        <v>46229.416666666664</v>
+        <v>46230.572916666664</v>
       </c>
       <c r="J47" s="126">
         <v>48</v>
@@ -36413,22 +36410,22 @@
       <c r="D48" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="E48" s="54" t="s">
-        <v>481</v>
+      <c r="E48" s="54">
+        <v>46229</v>
       </c>
       <c r="F48" s="180">
-        <v>46231.114583333336</v>
+        <v>46232.270833333336</v>
       </c>
       <c r="G48" s="180">
         <f t="shared" si="2"/>
-        <v>46236.114583333336</v>
+        <v>46237.270833333336</v>
       </c>
       <c r="H48" s="32">
         <v>120</v>
       </c>
       <c r="I48" s="180">
         <f t="shared" si="3"/>
-        <v>46238.114583333336</v>
+        <v>46239.270833333336</v>
       </c>
       <c r="J48" s="126">
         <v>48</v>
@@ -36448,21 +36445,21 @@
         <v>289</v>
       </c>
       <c r="E49" s="54">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F49" s="180">
-        <v>46234.114583333336</v>
+        <v>46235.270833333336</v>
       </c>
       <c r="G49" s="180">
         <f t="shared" si="2"/>
-        <v>46236.114583333336</v>
+        <v>46237.270833333336</v>
       </c>
       <c r="H49" s="32">
         <v>48</v>
       </c>
       <c r="I49" s="180">
         <f t="shared" si="3"/>
-        <v>46238.114583333336</v>
+        <v>46239.270833333336</v>
       </c>
       <c r="J49" s="126">
         <v>48</v>
@@ -36482,21 +36479,21 @@
         <v>290</v>
       </c>
       <c r="E50" s="240">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F50" s="183">
-        <v>46238.114583333336</v>
+        <v>46239.270833333336</v>
       </c>
       <c r="G50" s="183">
         <f t="shared" si="2"/>
-        <v>46240.114583333336</v>
+        <v>46241.270833333336</v>
       </c>
       <c r="H50" s="184">
         <v>48</v>
       </c>
       <c r="I50" s="183">
         <f t="shared" si="3"/>
-        <v>46242.114583333336</v>
+        <v>46243.270833333336</v>
       </c>
       <c r="J50" s="127">
         <v>48</v>
@@ -38170,7 +38167,7 @@
     </row>
     <row r="100" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="246" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>311</v>
@@ -38247,24 +38244,24 @@
         <v>348</v>
       </c>
       <c r="D102" s="187" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E102" s="242">
         <v>46198</v>
       </c>
       <c r="F102" s="181">
-        <v>46200.291666666664</v>
+        <v>46199.75</v>
       </c>
       <c r="G102" s="188">
         <f t="shared" si="4"/>
-        <v>46201.291666666664</v>
+        <v>46200.75</v>
       </c>
       <c r="H102" s="170">
         <v>24</v>
       </c>
       <c r="I102" s="188">
         <f t="shared" si="5"/>
-        <v>46202.083333333328</v>
+        <v>46201.541666666664</v>
       </c>
       <c r="J102" s="191">
         <v>19</v>
@@ -38284,21 +38281,21 @@
         <v>350</v>
       </c>
       <c r="E103" s="54">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="F103" s="180">
-        <v>46204.53125</v>
+        <v>46204.239583333336</v>
       </c>
       <c r="G103" s="180">
         <f t="shared" si="4"/>
-        <v>46207.03125</v>
+        <v>46206.739583333336</v>
       </c>
       <c r="H103" s="32">
         <v>60</v>
       </c>
       <c r="I103" s="180">
         <f t="shared" si="5"/>
-        <v>46207.822916666664</v>
+        <v>46207.53125</v>
       </c>
       <c r="J103" s="126">
         <v>19</v>
@@ -38315,24 +38312,24 @@
         <v>348</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E104" s="54">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F104" s="180">
-        <v>46210.114583333336</v>
+        <v>46209.822916666664</v>
       </c>
       <c r="G104" s="180">
         <f t="shared" ref="G104:G133" si="6">F104+(H104/24)</f>
-        <v>46212.114583333336</v>
+        <v>46211.822916666664</v>
       </c>
       <c r="H104" s="32">
         <v>48</v>
       </c>
       <c r="I104" s="180">
         <f t="shared" ref="I104:I125" si="7">G104+(J104/24)</f>
-        <v>46212.90625</v>
+        <v>46212.614583333328</v>
       </c>
       <c r="J104" s="126">
         <v>19</v>
@@ -38349,24 +38346,24 @@
         <v>348</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E105" s="54">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="F105" s="213">
-        <v>46214.114583333336</v>
+        <v>46213.822916666664</v>
       </c>
       <c r="G105" s="180">
         <f t="shared" si="6"/>
-        <v>46215.364583333336</v>
+        <v>46215.072916666664</v>
       </c>
       <c r="H105" s="214">
         <v>30</v>
       </c>
       <c r="I105" s="180">
         <f t="shared" si="7"/>
-        <v>46216.15625</v>
+        <v>46215.864583333328</v>
       </c>
       <c r="J105" s="215">
         <v>19</v>
@@ -38389,18 +38386,18 @@
         <v>46219</v>
       </c>
       <c r="F106" s="183">
-        <v>46221.927083333336</v>
+        <v>46221.635416666664</v>
       </c>
       <c r="G106" s="183">
         <f t="shared" si="6"/>
-        <v>46223.427083333336</v>
+        <v>46223.135416666664</v>
       </c>
       <c r="H106" s="184">
         <v>36</v>
       </c>
       <c r="I106" s="183">
         <f t="shared" si="7"/>
-        <v>46224.21875</v>
+        <v>46223.927083333328</v>
       </c>
       <c r="J106" s="127">
         <v>19</v>
@@ -38655,7 +38652,7 @@
         <v>364</v>
       </c>
       <c r="D114" s="386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E114" s="387">
         <v>46229</v>
@@ -38689,7 +38686,7 @@
         <v>364</v>
       </c>
       <c r="D115" s="439" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E115" s="387">
         <v>46231</v>
@@ -39512,21 +39509,21 @@
         <v>398</v>
       </c>
       <c r="E139" s="54">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="F139" s="180">
-        <v>46194.5625</v>
+        <v>46193.291666666664</v>
       </c>
       <c r="G139" s="180">
         <f t="shared" si="13"/>
-        <v>46195.5625</v>
+        <v>46194.291666666664</v>
       </c>
       <c r="H139" s="32">
         <v>24</v>
       </c>
       <c r="I139" s="180">
         <f t="shared" si="8"/>
-        <v>46196.229166666664</v>
+        <v>46194.958333333328</v>
       </c>
       <c r="J139" s="126">
         <v>16</v>
@@ -39546,21 +39543,21 @@
         <v>399</v>
       </c>
       <c r="E140" s="393">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="F140" s="394">
-        <v>46197.020833333336</v>
+        <v>46195.729166666664</v>
       </c>
       <c r="G140" s="394">
         <f t="shared" si="13"/>
-        <v>46198.520833333336</v>
+        <v>46197.229166666664</v>
       </c>
       <c r="H140" s="391">
         <v>36</v>
       </c>
       <c r="I140" s="394">
         <f t="shared" si="8"/>
-        <v>46199.1875</v>
+        <v>46197.895833333328</v>
       </c>
       <c r="J140" s="126">
         <v>16</v>
@@ -39577,24 +39574,24 @@
         <v>396</v>
       </c>
       <c r="D141" s="438" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E141" s="54">
-        <v>46195</v>
+        <v>46194</v>
       </c>
       <c r="F141" s="180">
-        <v>46198.416666666664</v>
+        <v>46197.125</v>
       </c>
       <c r="G141" s="180">
         <f t="shared" si="13"/>
-        <v>46200.416666666664</v>
+        <v>46199.125</v>
       </c>
       <c r="H141" s="32">
         <v>48</v>
       </c>
       <c r="I141" s="180">
         <f t="shared" si="8"/>
-        <v>46201.083333333328</v>
+        <v>46199.791666666664</v>
       </c>
       <c r="J141" s="126">
         <v>16</v>
@@ -39614,21 +39611,21 @@
         <v>400</v>
       </c>
       <c r="E142" s="54">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="F142" s="180">
-        <v>46202.729166666664</v>
+        <v>46201.4375</v>
       </c>
       <c r="G142" s="180">
         <f t="shared" si="13"/>
-        <v>46203.729166666664</v>
+        <v>46202.4375</v>
       </c>
       <c r="H142" s="32">
         <v>24</v>
       </c>
       <c r="I142" s="180">
         <f t="shared" si="8"/>
-        <v>46204.395833333328</v>
+        <v>46203.104166666664</v>
       </c>
       <c r="J142" s="126">
         <v>16</v>
@@ -39645,24 +39642,24 @@
         <v>396</v>
       </c>
       <c r="D143" s="397" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E143" s="54">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="F143" s="180">
-        <v>46213.359027777777</v>
+        <v>46212.067361111112</v>
       </c>
       <c r="G143" s="180">
         <f t="shared" si="13"/>
-        <v>46214.359027777777</v>
+        <v>46213.067361111112</v>
       </c>
       <c r="H143" s="32">
         <v>24</v>
       </c>
       <c r="I143" s="180">
         <f t="shared" si="8"/>
-        <v>46215.025694444441</v>
+        <v>46213.734027777777</v>
       </c>
       <c r="J143" s="126">
         <v>16</v>
@@ -39682,21 +39679,21 @@
         <v>401</v>
       </c>
       <c r="E144" s="54">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="F144" s="180">
-        <v>46215.359027777777</v>
+        <v>46214.067361111112</v>
       </c>
       <c r="G144" s="245">
         <f t="shared" ref="G144:G153" si="14">F144+(H144/24)</f>
-        <v>46216.359027777777</v>
+        <v>46215.067361111112</v>
       </c>
       <c r="H144" s="32">
         <v>24</v>
       </c>
       <c r="I144" s="245">
         <f>G144+(J144/24)</f>
-        <v>46217.025694444441</v>
+        <v>46215.734027777777</v>
       </c>
       <c r="J144" s="126">
         <v>16</v>
@@ -39716,21 +39713,21 @@
         <v>402</v>
       </c>
       <c r="E145" s="240">
-        <v>46222</v>
+        <v>46220</v>
       </c>
       <c r="F145" s="183">
-        <v>46224.01458333333</v>
+        <v>46222.722916666666</v>
       </c>
       <c r="G145" s="205">
         <f t="shared" si="14"/>
-        <v>46225.01458333333</v>
+        <v>46223.722916666666</v>
       </c>
       <c r="H145" s="184">
         <v>24</v>
       </c>
       <c r="I145" s="205">
         <f>G145+(J145/24)</f>
-        <v>46225.681249999994</v>
+        <v>46224.38958333333</v>
       </c>
       <c r="J145" s="127">
         <v>16</v>

--- a/uploads/Asset_Activity_Tracker_MASTER.xlsx
+++ b/uploads/Asset_Activity_Tracker_MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eu001-sp.shell.com/sites/UGPTDWGOMSupplyChain/Shared Documents/SC Delivery/Logistics New Ways of Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10057" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{082D1287-C561-42F5-9975-C140488B7A1E}"/>
+  <xr:revisionPtr revIDLastSave="10112" documentId="8_{8BED3E6F-E7C2-45EA-AB2B-C6B0456C2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63627695-D43C-41C6-9D6E-3780F162F986}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Vessel Schedule" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSV Demand Tracker'!$A$1:$J$213</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="ActualBeyond">PeriodInActual*(#REF!&gt;0)</definedName>
     <definedName name="PercentComplete">PercentCompleteBeyond*PeriodInPlan</definedName>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="507">
   <si>
     <t xml:space="preserve">Top Hole </t>
   </si>
@@ -1757,10 +1757,6 @@
     <t>GL 08 OSV / 36 hrs / 9,000 bbl of 11.3 ppg SBM, SBM Chemicals, 18-1/8" x 21" BHA, 18" Casing, 18" Liner Hanger</t>
   </si>
   <si>
-    <t xml:space="preserve">	
-GL 11 OSV / 24 hrs / Weekly Groceries &amp; Rig Supplies, MI 9,000 bbls 13.2, 3,000 bbls 16.0 &amp; 1,500 bbls Unweighted</t>
-  </si>
-  <si>
     <t>GL 13 OSV / 24 hrs / 12-1/4" &amp; 11.97" Casing, Casing Rack Back Tools, 12-1/4" Hanger</t>
   </si>
   <si>
@@ -2026,10 +2022,6 @@
     <t>GL 10 OSV / 24 hrs / 18" Casing Tools, Cement Head, 3,7000 Sacks of Cement, Cement Chemicals, SBM Chemicals</t>
   </si>
   <si>
-    <t xml:space="preserve">	
-GL 12 OSV / 36 hrs / 16-1/2" x 19" BHA, 3,000 bbl 16 ppg &amp; 1,500 bbl Unweighted SBM, TOI 5-7/8 DP &amp; HWDP</t>
-  </si>
-  <si>
     <t>Vito VA-10 Drift / CTCO</t>
   </si>
   <si>
@@ -2049,6 +2041,9 @@
   </si>
   <si>
     <t>GL 06 OSV- 60 Hours- Demob</t>
+  </si>
+  <si>
+    <t>GL 12 OSV / 36 hrs / 16-1/2" x 19" BHA, 3,000 bbl 16 ppg &amp; 1,500 bbl Unweighted SBM, TOI 5-7/8 DP &amp; HWDP</t>
   </si>
 </sst>
 </file>
@@ -34285,7 +34280,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
   <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:Y214"/>
+  <dimension ref="A1:Y213"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="6" bestFit="1" customWidth="1"/>
@@ -37821,18 +37816,18 @@
         <v>46209</v>
       </c>
       <c r="F104" s="177">
-        <v>46212.125</v>
+        <v>46212.083333333336</v>
       </c>
       <c r="G104" s="177">
         <f t="shared" si="6"/>
-        <v>46214.625</v>
+        <v>46214.583333333336</v>
       </c>
       <c r="H104" s="32">
         <v>60</v>
       </c>
       <c r="I104" s="177">
         <f t="shared" si="7"/>
-        <v>46215.375</v>
+        <v>46215.333333333336</v>
       </c>
       <c r="J104" s="211">
         <v>18</v>
@@ -37855,18 +37850,18 @@
         <v>46214</v>
       </c>
       <c r="F105" s="177">
-        <v>46217.21875</v>
+        <v>46217.114583333336</v>
       </c>
       <c r="G105" s="177">
         <f t="shared" ref="G105:G138" si="8">F105+(H105/24)</f>
-        <v>46219.21875</v>
+        <v>46219.114583333336</v>
       </c>
       <c r="H105" s="32">
         <v>48</v>
       </c>
       <c r="I105" s="177">
         <f t="shared" ref="I105:I126" si="9">G105+(J105/24)</f>
-        <v>46219.96875</v>
+        <v>46219.864583333336</v>
       </c>
       <c r="J105" s="211">
         <v>18</v>
@@ -37889,18 +37884,18 @@
         <v>46218</v>
       </c>
       <c r="F106" s="177">
-        <v>46219.118750000001</v>
+        <v>46219.01458333333</v>
       </c>
       <c r="G106" s="177">
         <f t="shared" si="8"/>
-        <v>46220.368750000001</v>
+        <v>46220.26458333333</v>
       </c>
       <c r="H106" s="32">
         <v>30</v>
       </c>
       <c r="I106" s="177">
         <f t="shared" si="9"/>
-        <v>46221.118750000001</v>
+        <v>46221.01458333333</v>
       </c>
       <c r="J106" s="211">
         <v>18</v>
@@ -37923,18 +37918,18 @@
         <v>46226</v>
       </c>
       <c r="F107" s="177">
-        <v>46228.03125</v>
+        <v>46227.927083333336</v>
       </c>
       <c r="G107" s="177">
         <f t="shared" si="8"/>
-        <v>46229.53125</v>
+        <v>46229.427083333336</v>
       </c>
       <c r="H107" s="32">
         <v>36</v>
       </c>
       <c r="I107" s="177">
         <f t="shared" si="9"/>
-        <v>46230.28125</v>
+        <v>46230.177083333336</v>
       </c>
       <c r="J107" s="211">
         <v>18</v>
@@ -38229,18 +38224,18 @@
         <v>46231</v>
       </c>
       <c r="F116" s="177">
-        <v>46233</v>
+        <v>46233.041666666664</v>
       </c>
       <c r="G116" s="177">
         <f t="shared" si="8"/>
-        <v>46235</v>
+        <v>46235.041666666664</v>
       </c>
       <c r="H116" s="32">
         <v>48</v>
       </c>
       <c r="I116" s="177">
         <f t="shared" si="9"/>
-        <v>46235.5</v>
+        <v>46235.541666666664</v>
       </c>
       <c r="J116" s="32">
         <v>12</v>
@@ -38989,7 +38984,7 @@
         <v>10</v>
       </c>
       <c r="I138" s="177">
-        <f t="shared" ref="I138:I196" si="15">G138+(J138/24)</f>
+        <f t="shared" ref="I138:I195" si="15">G138+(J138/24)</f>
         <v>46164.833333333328</v>
       </c>
       <c r="J138" s="32">
@@ -39050,7 +39045,7 @@
         <v>46168</v>
       </c>
       <c r="G140" s="177">
-        <f t="shared" ref="G140:G196" si="16">F140+(H140/24)</f>
+        <f t="shared" ref="G140:G195" si="16">F140+(H140/24)</f>
         <v>46168.208333333336</v>
       </c>
       <c r="H140" s="32">
@@ -39381,24 +39376,24 @@
         <v>408</v>
       </c>
       <c r="D150" s="304" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E150" s="54">
         <v>46207</v>
       </c>
       <c r="F150" s="177">
-        <v>46209.802083333336</v>
+        <v>46209.84375</v>
       </c>
       <c r="G150" s="177">
         <f>F150+(H150/24)</f>
-        <v>46210.802083333336</v>
+        <v>46210.84375</v>
       </c>
       <c r="H150" s="32">
         <v>24</v>
       </c>
       <c r="I150" s="177">
         <f>G150+(J150/24)</f>
-        <v>46211.34375</v>
+        <v>46211.385416666664</v>
       </c>
       <c r="J150" s="32">
         <v>13</v>
@@ -39415,24 +39410,24 @@
         <v>408</v>
       </c>
       <c r="D151" s="309" t="s">
-        <v>416</v>
+        <v>506</v>
       </c>
       <c r="E151" s="54">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F151" s="177">
-        <v>46212.25</v>
+        <v>46212.5</v>
       </c>
       <c r="G151" s="177">
         <f t="shared" si="16"/>
-        <v>46213.25</v>
+        <v>46213.5</v>
       </c>
       <c r="H151" s="32">
         <v>24</v>
       </c>
       <c r="I151" s="177">
         <f t="shared" si="15"/>
-        <v>46213.791666666664</v>
+        <v>46214.041666666664</v>
       </c>
       <c r="J151" s="32">
         <v>13</v>
@@ -39449,24 +39444,24 @@
         <v>408</v>
       </c>
       <c r="D152" s="309" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="E152" s="54">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="F152" s="177">
-        <v>46212.458333333336</v>
+        <v>46216.668749999997</v>
       </c>
       <c r="G152" s="177">
-        <f t="shared" si="16"/>
-        <v>46213.958333333336</v>
+        <f>F152+(H152/24)</f>
+        <v>46217.668749999997</v>
       </c>
       <c r="H152" s="32">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I152" s="177">
-        <f t="shared" si="15"/>
-        <v>46214.5</v>
+        <f>G152+(J152/24)</f>
+        <v>46218.210416666661</v>
       </c>
       <c r="J152" s="32">
         <v>13</v>
@@ -39486,139 +39481,139 @@
         <v>417</v>
       </c>
       <c r="E153" s="54">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="F153" s="177">
-        <v>46216.533333333333</v>
+        <v>46217.818749999999</v>
       </c>
       <c r="G153" s="177">
         <f>F153+(H153/24)</f>
-        <v>46217.533333333333</v>
+        <v>46218.818749999999</v>
       </c>
       <c r="H153" s="32">
         <v>24</v>
       </c>
       <c r="I153" s="177">
         <f>G153+(J153/24)</f>
-        <v>46218.074999999997</v>
+        <v>46219.360416666663</v>
       </c>
       <c r="J153" s="32">
         <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="212" t="s">
         <v>282</v>
       </c>
-      <c r="B154" s="32" t="s">
+      <c r="B154" s="211" t="s">
         <v>232</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="212" t="s">
         <v>408</v>
       </c>
       <c r="D154" s="309" t="s">
         <v>418</v>
       </c>
       <c r="E154" s="54">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="F154" s="177">
-        <v>46217.777083333334</v>
-      </c>
-      <c r="G154" s="177">
-        <f>F154+(H154/24)</f>
-        <v>46218.777083333334</v>
+        <v>46227.323611111111</v>
+      </c>
+      <c r="G154" s="213">
+        <f t="shared" ref="G154:G165" si="17">F154+(H154/24)</f>
+        <v>46228.323611111111</v>
       </c>
       <c r="H154" s="32">
         <v>24</v>
       </c>
-      <c r="I154" s="177">
+      <c r="I154" s="213">
         <f>G154+(J154/24)</f>
-        <v>46219.318749999999</v>
+        <v>46228.865277777775</v>
       </c>
       <c r="J154" s="32">
         <v>13</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A155" s="212" t="s">
-        <v>282</v>
-      </c>
-      <c r="B155" s="211" t="s">
-        <v>232</v>
-      </c>
-      <c r="C155" s="212" t="s">
-        <v>408</v>
-      </c>
-      <c r="D155" s="309" t="s">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B155" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>419</v>
       </c>
+      <c r="D155" s="304" t="s">
+        <v>420</v>
+      </c>
       <c r="E155" s="54">
-        <v>46225</v>
+        <v>46193</v>
       </c>
       <c r="F155" s="177">
-        <v>46227.281944444447</v>
-      </c>
-      <c r="G155" s="213">
-        <f t="shared" ref="G155:G166" si="17">F155+(H155/24)</f>
-        <v>46228.281944444447</v>
-      </c>
-      <c r="H155" s="32">
-        <v>24</v>
-      </c>
-      <c r="I155" s="213">
+        <v>46195.25</v>
+      </c>
+      <c r="G155" s="177">
+        <f t="shared" si="17"/>
+        <v>46197.25</v>
+      </c>
+      <c r="H155" s="303">
+        <v>48</v>
+      </c>
+      <c r="I155" s="177">
         <f>G155+(J155/24)</f>
-        <v>46228.823611111111</v>
-      </c>
-      <c r="J155" s="32">
-        <v>13</v>
+        <v>46197.5</v>
+      </c>
+      <c r="J155" s="303">
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B156" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="D156" s="304" t="s">
+      <c r="A156" s="7"/>
+      <c r="B156" s="32"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="304"/>
+      <c r="E156" s="54"/>
+      <c r="F156" s="177"/>
+      <c r="G156" s="177"/>
+      <c r="H156" s="32"/>
+      <c r="I156" s="177"/>
+      <c r="J156" s="32"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B157" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="E156" s="54">
-        <v>46193</v>
-      </c>
-      <c r="F156" s="177">
-        <v>46195.25</v>
-      </c>
-      <c r="G156" s="177">
+      <c r="D157" s="304" t="s">
+        <v>422</v>
+      </c>
+      <c r="E157" s="54">
+        <v>46211</v>
+      </c>
+      <c r="F157" s="177">
+        <v>46213.041666666664</v>
+      </c>
+      <c r="G157" s="177">
         <f t="shared" si="17"/>
-        <v>46197.25</v>
-      </c>
-      <c r="H156" s="303">
-        <v>48</v>
-      </c>
-      <c r="I156" s="177">
-        <f>G156+(J156/24)</f>
-        <v>46197.5</v>
-      </c>
-      <c r="J156" s="303">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="7"/>
-      <c r="B157" s="32"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="304"/>
-      <c r="E157" s="54"/>
-      <c r="F157" s="177"/>
-      <c r="G157" s="177"/>
-      <c r="H157" s="32"/>
-      <c r="I157" s="177"/>
-      <c r="J157" s="32"/>
+        <v>46216.041666666664</v>
+      </c>
+      <c r="H157" s="32">
+        <v>72</v>
+      </c>
+      <c r="I157" s="177">
+        <f t="shared" ref="I157:I159" si="18">G157+(J157/24)</f>
+        <v>46217.541666666664</v>
+      </c>
+      <c r="J157" s="32">
+        <v>36</v>
+      </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
@@ -39628,27 +39623,27 @@
         <v>20</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D158" s="304" t="s">
         <v>423</v>
       </c>
       <c r="E158" s="54">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="F158" s="177">
-        <v>46212.479166666664</v>
+        <v>46218.4375</v>
       </c>
       <c r="G158" s="177">
         <f t="shared" si="17"/>
-        <v>46215.479166666664</v>
-      </c>
-      <c r="H158" s="32">
+        <v>46221.4375</v>
+      </c>
+      <c r="H158" s="303">
         <v>72</v>
       </c>
       <c r="I158" s="177">
-        <f t="shared" ref="I158:I160" si="18">G158+(J158/24)</f>
-        <v>46216.979166666664</v>
+        <f t="shared" si="18"/>
+        <v>46222.9375</v>
       </c>
       <c r="J158" s="32">
         <v>36</v>
@@ -39662,27 +39657,27 @@
         <v>20</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D159" s="304" t="s">
         <v>424</v>
       </c>
       <c r="E159" s="54">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="F159" s="177">
-        <v>46217.875</v>
+        <v>46220.770833333336</v>
       </c>
       <c r="G159" s="177">
         <f t="shared" si="17"/>
-        <v>46220.875</v>
+        <v>46223.770833333336</v>
       </c>
       <c r="H159" s="303">
         <v>72</v>
       </c>
       <c r="I159" s="177">
         <f t="shared" si="18"/>
-        <v>46222.375</v>
+        <v>46225.270833333336</v>
       </c>
       <c r="J159" s="32">
         <v>36</v>
@@ -39696,27 +39691,27 @@
         <v>20</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D160" s="304" t="s">
         <v>425</v>
       </c>
       <c r="E160" s="54">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="F160" s="177">
-        <v>46220.208333333336</v>
+        <v>46224.6875</v>
       </c>
       <c r="G160" s="177">
         <f t="shared" si="17"/>
-        <v>46223.208333333336</v>
+        <v>46227.6875</v>
       </c>
       <c r="H160" s="303">
         <v>72</v>
       </c>
       <c r="I160" s="177">
-        <f t="shared" si="18"/>
-        <v>46224.708333333336</v>
+        <f t="shared" ref="I160:I165" si="19">G160+(J160/24)</f>
+        <v>46229.1875</v>
       </c>
       <c r="J160" s="32">
         <v>36</v>
@@ -39730,27 +39725,27 @@
         <v>20</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D161" s="304" t="s">
         <v>426</v>
       </c>
       <c r="E161" s="54">
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="F161" s="177">
-        <v>46224.125</v>
+        <v>46227.541666666664</v>
       </c>
       <c r="G161" s="177">
         <f t="shared" si="17"/>
-        <v>46227.125</v>
+        <v>46230.541666666664</v>
       </c>
       <c r="H161" s="303">
         <v>72</v>
       </c>
       <c r="I161" s="177">
-        <f t="shared" ref="I161:I166" si="19">G161+(J161/24)</f>
-        <v>46228.625</v>
+        <f t="shared" si="19"/>
+        <v>46232.041666666664</v>
       </c>
       <c r="J161" s="32">
         <v>36</v>
@@ -39764,27 +39759,27 @@
         <v>20</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D162" s="304" t="s">
         <v>427</v>
       </c>
       <c r="E162" s="54">
-        <v>46224</v>
+        <v>46235</v>
       </c>
       <c r="F162" s="177">
-        <v>46226.979166666664</v>
+        <v>46237.125</v>
       </c>
       <c r="G162" s="177">
         <f t="shared" si="17"/>
-        <v>46229.979166666664</v>
+        <v>46240.125</v>
       </c>
       <c r="H162" s="303">
         <v>72</v>
       </c>
       <c r="I162" s="177">
         <f t="shared" si="19"/>
-        <v>46231.479166666664</v>
+        <v>46241.625</v>
       </c>
       <c r="J162" s="32">
         <v>36</v>
@@ -39798,27 +39793,27 @@
         <v>20</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D163" s="304" t="s">
         <v>428</v>
       </c>
       <c r="E163" s="54">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="F163" s="177">
-        <v>46236.5625</v>
+        <v>46242.25</v>
       </c>
       <c r="G163" s="177">
         <f t="shared" si="17"/>
-        <v>46239.5625</v>
+        <v>46245.25</v>
       </c>
       <c r="H163" s="303">
         <v>72</v>
       </c>
       <c r="I163" s="177">
         <f t="shared" si="19"/>
-        <v>46241.0625</v>
+        <v>46246.75</v>
       </c>
       <c r="J163" s="32">
         <v>36</v>
@@ -39832,27 +39827,27 @@
         <v>20</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D164" s="304" t="s">
+        <v>421</v>
+      </c>
+      <c r="D164" s="6" t="s">
         <v>429</v>
       </c>
       <c r="E164" s="54">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F164" s="177">
-        <v>46241.6875</v>
+        <v>46243.3125</v>
       </c>
       <c r="G164" s="177">
         <f t="shared" si="17"/>
-        <v>46244.6875</v>
+        <v>46246.3125</v>
       </c>
       <c r="H164" s="303">
         <v>72</v>
       </c>
       <c r="I164" s="177">
         <f t="shared" si="19"/>
-        <v>46246.1875</v>
+        <v>46247.8125</v>
       </c>
       <c r="J164" s="32">
         <v>36</v>
@@ -39866,65 +39861,43 @@
         <v>20</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D165" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D165" s="304" t="s">
         <v>430</v>
       </c>
       <c r="E165" s="54">
-        <v>46240</v>
+        <v>46357</v>
       </c>
       <c r="F165" s="177">
-        <v>46242.75</v>
+        <v>46361</v>
       </c>
       <c r="G165" s="177">
         <f t="shared" si="17"/>
-        <v>46245.75</v>
+        <v>46364</v>
       </c>
       <c r="H165" s="303">
         <v>72</v>
       </c>
       <c r="I165" s="177">
         <f t="shared" si="19"/>
-        <v>46247.25</v>
+        <v>46365.5</v>
       </c>
       <c r="J165" s="32">
         <v>36</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A166" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B166" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D166" s="304" t="s">
-        <v>431</v>
-      </c>
-      <c r="E166" s="54">
-        <v>46357</v>
-      </c>
-      <c r="F166" s="177">
-        <v>46361</v>
-      </c>
-      <c r="G166" s="177">
-        <f t="shared" si="17"/>
-        <v>46364</v>
-      </c>
-      <c r="H166" s="303">
-        <v>72</v>
-      </c>
-      <c r="I166" s="177">
-        <f t="shared" si="19"/>
-        <v>46365.5</v>
-      </c>
-      <c r="J166" s="32">
-        <v>36</v>
-      </c>
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="7"/>
+      <c r="B166" s="32"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="304"/>
+      <c r="E166" s="54"/>
+      <c r="F166" s="177"/>
+      <c r="G166" s="177"/>
+      <c r="H166" s="303"/>
+      <c r="I166" s="177"/>
+      <c r="J166" s="32"/>
     </row>
     <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="7"/>
@@ -40076,23 +40049,60 @@
       <c r="C179" s="7"/>
       <c r="D179" s="304"/>
       <c r="E179" s="54"/>
-      <c r="F179" s="177"/>
+      <c r="F179" s="213"/>
       <c r="G179" s="177"/>
-      <c r="H179" s="303"/>
+      <c r="H179" s="32"/>
       <c r="I179" s="177"/>
       <c r="J179" s="32"/>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="7"/>
-      <c r="B180" s="32"/>
-      <c r="C180" s="7"/>
-      <c r="D180" s="304"/>
-      <c r="E180" s="54"/>
-      <c r="F180" s="213"/>
-      <c r="G180" s="177"/>
-      <c r="H180" s="32"/>
-      <c r="I180" s="177"/>
-      <c r="J180" s="32"/>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A180" s="212" t="s">
+        <v>282</v>
+      </c>
+      <c r="B180" s="211" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="212" t="s">
+        <v>431</v>
+      </c>
+      <c r="D180" s="310" t="s">
+        <v>432</v>
+      </c>
+      <c r="E180" s="311">
+        <v>46327</v>
+      </c>
+      <c r="F180" s="213">
+        <v>46330.25</v>
+      </c>
+      <c r="G180" s="213">
+        <f t="shared" si="16"/>
+        <v>46334.25</v>
+      </c>
+      <c r="H180" s="211">
+        <v>96</v>
+      </c>
+      <c r="I180" s="213">
+        <f t="shared" si="15"/>
+        <v>46335.75</v>
+      </c>
+      <c r="J180" s="211">
+        <v>36</v>
+      </c>
+      <c r="K180" s="312"/>
+      <c r="L180" s="312"/>
+      <c r="M180" s="312"/>
+      <c r="N180" s="312"/>
+      <c r="O180" s="312"/>
+      <c r="P180" s="312"/>
+      <c r="Q180" s="312"/>
+      <c r="R180" s="312"/>
+      <c r="S180" s="312"/>
+      <c r="T180" s="312"/>
+      <c r="U180" s="312"/>
+      <c r="V180" s="312"/>
+      <c r="W180" s="312"/>
+      <c r="X180" s="312"/>
+      <c r="Y180" s="312"/>
     </row>
     <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181" s="212" t="s">
@@ -40102,27 +40112,27 @@
         <v>20</v>
       </c>
       <c r="C181" s="212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D181" s="310" t="s">
         <v>433</v>
       </c>
       <c r="E181" s="311">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="F181" s="213">
-        <v>46330.25</v>
+        <v>46334.25</v>
       </c>
       <c r="G181" s="213">
         <f t="shared" si="16"/>
-        <v>46334.25</v>
+        <v>46338.25</v>
       </c>
       <c r="H181" s="211">
         <v>96</v>
       </c>
       <c r="I181" s="213">
         <f t="shared" si="15"/>
-        <v>46335.75</v>
+        <v>46339.75</v>
       </c>
       <c r="J181" s="211">
         <v>36</v>
@@ -40151,27 +40161,27 @@
         <v>20</v>
       </c>
       <c r="C182" s="212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D182" s="310" t="s">
         <v>434</v>
       </c>
       <c r="E182" s="311">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="F182" s="213">
-        <v>46334.25</v>
+        <v>46344.25</v>
       </c>
       <c r="G182" s="213">
         <f t="shared" si="16"/>
-        <v>46338.25</v>
+        <v>46348.25</v>
       </c>
       <c r="H182" s="211">
         <v>96</v>
       </c>
       <c r="I182" s="213">
         <f t="shared" si="15"/>
-        <v>46339.75</v>
+        <v>46349.75</v>
       </c>
       <c r="J182" s="211">
         <v>36</v>
@@ -40200,27 +40210,27 @@
         <v>20</v>
       </c>
       <c r="C183" s="212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D183" s="310" t="s">
         <v>435</v>
       </c>
       <c r="E183" s="311">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="F183" s="213">
-        <v>46344.25</v>
+        <v>46351.25</v>
       </c>
       <c r="G183" s="213">
         <f t="shared" si="16"/>
-        <v>46348.25</v>
+        <v>46355.25</v>
       </c>
       <c r="H183" s="211">
         <v>96</v>
       </c>
       <c r="I183" s="213">
         <f t="shared" si="15"/>
-        <v>46349.75</v>
+        <v>46356.75</v>
       </c>
       <c r="J183" s="211">
         <v>36</v>
@@ -40249,27 +40259,27 @@
         <v>20</v>
       </c>
       <c r="C184" s="212" t="s">
-        <v>432</v>
-      </c>
-      <c r="D184" s="310" t="s">
+        <v>431</v>
+      </c>
+      <c r="D184" s="302" t="s">
         <v>436</v>
       </c>
       <c r="E184" s="311">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="F184" s="213">
-        <v>46351.25</v>
+        <v>46358.25</v>
       </c>
       <c r="G184" s="213">
         <f t="shared" si="16"/>
-        <v>46355.25</v>
+        <v>46362.25</v>
       </c>
       <c r="H184" s="211">
         <v>96</v>
       </c>
       <c r="I184" s="213">
         <f t="shared" si="15"/>
-        <v>46356.75</v>
+        <v>46363.75</v>
       </c>
       <c r="J184" s="211">
         <v>36</v>
@@ -40297,28 +40307,28 @@
       <c r="B185" s="211" t="s">
         <v>20</v>
       </c>
-      <c r="C185" s="212" t="s">
-        <v>432</v>
+      <c r="C185" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="D185" s="302" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E185" s="311">
-        <v>46355</v>
+        <v>46235</v>
       </c>
       <c r="F185" s="213">
-        <v>46358.25</v>
+        <v>46237.25</v>
       </c>
       <c r="G185" s="213">
         <f t="shared" si="16"/>
-        <v>46362.25</v>
+        <v>46282.25</v>
       </c>
       <c r="H185" s="211">
-        <v>96</v>
+        <v>1080</v>
       </c>
       <c r="I185" s="213">
         <f t="shared" si="15"/>
-        <v>46363.75</v>
+        <v>46283.75</v>
       </c>
       <c r="J185" s="211">
         <v>36</v>
@@ -40347,10 +40357,10 @@
         <v>20</v>
       </c>
       <c r="C186" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D186" s="302" t="s">
         <v>438</v>
-      </c>
-      <c r="D186" s="302" t="s">
-        <v>439</v>
       </c>
       <c r="E186" s="311">
         <v>46235</v>
@@ -40388,167 +40398,152 @@
       <c r="X186" s="312"/>
       <c r="Y186" s="312"/>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A187" s="212" t="s">
+    <row r="187" spans="1:25" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="314" t="s">
+        <v>231</v>
+      </c>
+      <c r="B187" s="313" t="s">
+        <v>122</v>
+      </c>
+      <c r="C187" s="314" t="s">
+        <v>439</v>
+      </c>
+      <c r="D187" s="315" t="s">
+        <v>440</v>
+      </c>
+      <c r="E187" s="318">
+        <v>46193</v>
+      </c>
+      <c r="F187" s="319">
+        <v>46196.25</v>
+      </c>
+      <c r="G187" s="319">
+        <f t="shared" si="16"/>
+        <v>46197.75</v>
+      </c>
+      <c r="H187" s="313">
+        <v>36</v>
+      </c>
+      <c r="I187" s="319">
+        <f t="shared" si="15"/>
+        <v>46198.25</v>
+      </c>
+      <c r="J187" s="313">
+        <v>12</v>
+      </c>
+      <c r="K187" s="320"/>
+      <c r="L187" s="320"/>
+      <c r="M187" s="320"/>
+      <c r="N187" s="320"/>
+      <c r="O187" s="320"/>
+      <c r="P187" s="320"/>
+      <c r="Q187" s="320"/>
+      <c r="R187" s="320"/>
+      <c r="S187" s="320"/>
+      <c r="T187" s="320"/>
+      <c r="U187" s="320"/>
+      <c r="V187" s="320"/>
+      <c r="W187" s="320"/>
+      <c r="X187" s="320"/>
+      <c r="Y187" s="320"/>
+    </row>
+    <row r="188" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="314" t="s">
         <v>282</v>
-      </c>
-      <c r="B187" s="211" t="s">
-        <v>20</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="D187" s="302" t="s">
-        <v>439</v>
-      </c>
-      <c r="E187" s="311">
-        <v>46235</v>
-      </c>
-      <c r="F187" s="213">
-        <v>46237.25</v>
-      </c>
-      <c r="G187" s="213">
-        <f t="shared" si="16"/>
-        <v>46282.25</v>
-      </c>
-      <c r="H187" s="211">
-        <v>1080</v>
-      </c>
-      <c r="I187" s="213">
-        <f t="shared" si="15"/>
-        <v>46283.75</v>
-      </c>
-      <c r="J187" s="211">
-        <v>36</v>
-      </c>
-      <c r="K187" s="312"/>
-      <c r="L187" s="312"/>
-      <c r="M187" s="312"/>
-      <c r="N187" s="312"/>
-      <c r="O187" s="312"/>
-      <c r="P187" s="312"/>
-      <c r="Q187" s="312"/>
-      <c r="R187" s="312"/>
-      <c r="S187" s="312"/>
-      <c r="T187" s="312"/>
-      <c r="U187" s="312"/>
-      <c r="V187" s="312"/>
-      <c r="W187" s="312"/>
-      <c r="X187" s="312"/>
-      <c r="Y187" s="312"/>
-    </row>
-    <row r="188" spans="1:25" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="314" t="s">
-        <v>231</v>
       </c>
       <c r="B188" s="313" t="s">
         <v>122</v>
       </c>
       <c r="C188" s="314" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D188" s="315" t="s">
-        <v>441</v>
-      </c>
-      <c r="E188" s="318">
-        <v>46193</v>
-      </c>
-      <c r="F188" s="319">
-        <v>46196.25</v>
-      </c>
-      <c r="G188" s="319">
+        <v>442</v>
+      </c>
+      <c r="E188" s="316">
+        <v>46209</v>
+      </c>
+      <c r="F188" s="317">
+        <v>46211.375</v>
+      </c>
+      <c r="G188" s="317">
         <f t="shared" si="16"/>
-        <v>46197.75</v>
+        <v>46213.375</v>
       </c>
       <c r="H188" s="313">
-        <v>36</v>
-      </c>
-      <c r="I188" s="319">
+        <v>48</v>
+      </c>
+      <c r="I188" s="317">
         <f t="shared" si="15"/>
-        <v>46198.25</v>
+        <v>46213.875</v>
       </c>
       <c r="J188" s="313">
         <v>12</v>
       </c>
-      <c r="K188" s="320"/>
-      <c r="L188" s="320"/>
-      <c r="M188" s="320"/>
-      <c r="N188" s="320"/>
-      <c r="O188" s="320"/>
-      <c r="P188" s="320"/>
-      <c r="Q188" s="320"/>
-      <c r="R188" s="320"/>
-      <c r="S188" s="320"/>
-      <c r="T188" s="320"/>
-      <c r="U188" s="320"/>
-      <c r="V188" s="320"/>
-      <c r="W188" s="320"/>
-      <c r="X188" s="320"/>
-      <c r="Y188" s="320"/>
     </row>
-    <row r="189" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="314" t="s">
+    <row r="189" spans="1:25" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="314"/>
+      <c r="B189" s="313"/>
+      <c r="C189" s="314"/>
+      <c r="D189" s="329" t="s">
+        <v>443</v>
+      </c>
+      <c r="E189" s="316">
+        <v>46222</v>
+      </c>
+      <c r="F189" s="317">
+        <v>46224.53125</v>
+      </c>
+      <c r="G189" s="317">
+        <f t="shared" ref="G189" si="20">F189+(H189/24)</f>
+        <v>46227.03125</v>
+      </c>
+      <c r="H189" s="313">
+        <v>60</v>
+      </c>
+      <c r="I189" s="317">
+        <f t="shared" ref="I189" si="21">G189+(J189/24)</f>
+        <v>46227.572916666664</v>
+      </c>
+      <c r="J189" s="313">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="314" t="s">
         <v>282</v>
       </c>
-      <c r="B189" s="313" t="s">
+      <c r="B190" s="313" t="s">
         <v>122</v>
       </c>
-      <c r="C189" s="314" t="s">
-        <v>442</v>
-      </c>
-      <c r="D189" s="315" t="s">
-        <v>443</v>
-      </c>
-      <c r="E189" s="316">
-        <v>46209</v>
-      </c>
-      <c r="F189" s="317">
-        <v>46211.375</v>
-      </c>
-      <c r="G189" s="317">
+      <c r="C190" s="314" t="s">
+        <v>441</v>
+      </c>
+      <c r="D190" s="315" t="s">
+        <v>444</v>
+      </c>
+      <c r="E190" s="316">
+        <v>46228</v>
+      </c>
+      <c r="F190" s="317">
+        <v>46230.1875</v>
+      </c>
+      <c r="G190" s="317">
         <f t="shared" si="16"/>
-        <v>46213.375</v>
-      </c>
-      <c r="H189" s="313">
+        <v>46232.1875</v>
+      </c>
+      <c r="H190" s="313">
         <v>48</v>
       </c>
-      <c r="I189" s="317">
+      <c r="I190" s="317">
         <f t="shared" si="15"/>
-        <v>46213.875</v>
-      </c>
-      <c r="J189" s="313">
+        <v>46232.6875</v>
+      </c>
+      <c r="J190" s="313">
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:25" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="314"/>
-      <c r="B190" s="313"/>
-      <c r="C190" s="314"/>
-      <c r="D190" s="329" t="s">
-        <v>444</v>
-      </c>
-      <c r="E190" s="316">
-        <v>46222</v>
-      </c>
-      <c r="F190" s="317">
-        <v>46224.53125</v>
-      </c>
-      <c r="G190" s="317">
-        <f t="shared" ref="G190" si="20">F190+(H190/24)</f>
-        <v>46227.03125</v>
-      </c>
-      <c r="H190" s="313">
-        <v>60</v>
-      </c>
-      <c r="I190" s="317">
-        <f t="shared" ref="I190" si="21">G190+(J190/24)</f>
-        <v>46227.572916666664</v>
-      </c>
-      <c r="J190" s="313">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="191" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="314" t="s">
         <v>282</v>
       </c>
@@ -40556,33 +40551,33 @@
         <v>122</v>
       </c>
       <c r="C191" s="314" t="s">
-        <v>442</v>
-      </c>
-      <c r="D191" s="315" t="s">
+        <v>441</v>
+      </c>
+      <c r="D191" s="328" t="s">
         <v>445</v>
       </c>
       <c r="E191" s="316">
-        <v>46228</v>
+        <v>46233</v>
       </c>
       <c r="F191" s="317">
-        <v>46230.1875</v>
+        <v>46235.729166666664</v>
       </c>
       <c r="G191" s="317">
         <f t="shared" si="16"/>
-        <v>46232.1875</v>
+        <v>46238.729166666664</v>
       </c>
       <c r="H191" s="313">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I191" s="317">
         <f t="shared" si="15"/>
-        <v>46232.6875</v>
+        <v>46239.229166666664</v>
       </c>
       <c r="J191" s="313">
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:25" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="314" t="s">
         <v>282</v>
       </c>
@@ -40590,33 +40585,33 @@
         <v>122</v>
       </c>
       <c r="C192" s="314" t="s">
-        <v>442</v>
-      </c>
-      <c r="D192" s="328" t="s">
+        <v>441</v>
+      </c>
+      <c r="D192" s="315" t="s">
         <v>446</v>
       </c>
       <c r="E192" s="316">
-        <v>46233</v>
+        <v>46242</v>
       </c>
       <c r="F192" s="317">
-        <v>46235.729166666664</v>
+        <v>46244.645833333336</v>
       </c>
       <c r="G192" s="317">
         <f t="shared" si="16"/>
-        <v>46238.729166666664</v>
+        <v>46246.645833333336</v>
       </c>
       <c r="H192" s="313">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="I192" s="317">
         <f t="shared" si="15"/>
-        <v>46239.229166666664</v>
+        <v>46247.145833333336</v>
       </c>
       <c r="J192" s="313">
         <v>12</v>
       </c>
     </row>
-    <row r="193" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="314" t="s">
         <v>282</v>
       </c>
@@ -40624,27 +40619,27 @@
         <v>122</v>
       </c>
       <c r="C193" s="314" t="s">
-        <v>442</v>
-      </c>
-      <c r="D193" s="315" t="s">
+        <v>441</v>
+      </c>
+      <c r="D193" s="328" t="s">
         <v>447</v>
       </c>
       <c r="E193" s="316">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="F193" s="317">
-        <v>46244.645833333336</v>
+        <v>46247.833333333336</v>
       </c>
       <c r="G193" s="317">
         <f t="shared" si="16"/>
-        <v>46246.645833333336</v>
+        <v>46249.833333333336</v>
       </c>
       <c r="H193" s="313">
         <v>48</v>
       </c>
       <c r="I193" s="317">
         <f t="shared" si="15"/>
-        <v>46247.145833333336</v>
+        <v>46250.333333333336</v>
       </c>
       <c r="J193" s="313">
         <v>12</v>
@@ -40658,27 +40653,27 @@
         <v>122</v>
       </c>
       <c r="C194" s="314" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D194" s="328" t="s">
         <v>448</v>
       </c>
       <c r="E194" s="316">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="F194" s="317">
-        <v>46247.833333333336</v>
+        <v>46250.75</v>
       </c>
       <c r="G194" s="317">
         <f t="shared" si="16"/>
-        <v>46249.833333333336</v>
+        <v>46252.75</v>
       </c>
       <c r="H194" s="313">
         <v>48</v>
       </c>
       <c r="I194" s="317">
         <f t="shared" si="15"/>
-        <v>46250.333333333336</v>
+        <v>46253.25</v>
       </c>
       <c r="J194" s="313">
         <v>12</v>
@@ -40692,95 +40687,95 @@
         <v>122</v>
       </c>
       <c r="C195" s="314" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D195" s="328" t="s">
         <v>449</v>
       </c>
       <c r="E195" s="316">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="F195" s="317">
-        <v>46250.75</v>
+        <v>46252.479166666664</v>
       </c>
       <c r="G195" s="317">
         <f t="shared" si="16"/>
-        <v>46252.75</v>
+        <v>46254.979166666664</v>
       </c>
       <c r="H195" s="313">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I195" s="317">
         <f t="shared" si="15"/>
-        <v>46253.25</v>
+        <v>46255.479166666664</v>
       </c>
       <c r="J195" s="313">
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:10" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="314" t="s">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="212" t="s">
+        <v>231</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C196" s="212" t="s">
+        <v>450</v>
+      </c>
+      <c r="D196" s="310" t="s">
+        <v>451</v>
+      </c>
+      <c r="E196" s="54">
+        <v>46184</v>
+      </c>
+      <c r="F196" s="177">
+        <v>46185</v>
+      </c>
+      <c r="G196" s="177">
+        <f t="shared" ref="G196:G213" si="22">F196+(H196/24)</f>
+        <v>46187</v>
+      </c>
+      <c r="H196" s="303">
+        <v>48</v>
+      </c>
+      <c r="I196" s="177">
+        <f t="shared" ref="I196:I213" si="23">G196+(J196/24)</f>
+        <v>46187.25</v>
+      </c>
+      <c r="J196" s="211">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" s="212" t="s">
         <v>282</v>
-      </c>
-      <c r="B196" s="313" t="s">
-        <v>122</v>
-      </c>
-      <c r="C196" s="314" t="s">
-        <v>442</v>
-      </c>
-      <c r="D196" s="328" t="s">
-        <v>450</v>
-      </c>
-      <c r="E196" s="316">
-        <v>46250</v>
-      </c>
-      <c r="F196" s="317">
-        <v>46252.479166666664</v>
-      </c>
-      <c r="G196" s="317">
-        <f t="shared" si="16"/>
-        <v>46254.979166666664</v>
-      </c>
-      <c r="H196" s="313">
-        <v>60</v>
-      </c>
-      <c r="I196" s="317">
-        <f t="shared" si="15"/>
-        <v>46255.479166666664</v>
-      </c>
-      <c r="J196" s="313">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="212" t="s">
-        <v>231</v>
       </c>
       <c r="B197" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C197" s="212" t="s">
-        <v>451</v>
-      </c>
-      <c r="D197" s="310" t="s">
+      <c r="C197" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D197" s="212" t="s">
         <v>452</v>
       </c>
       <c r="E197" s="54">
-        <v>46184</v>
+        <v>46207</v>
       </c>
       <c r="F197" s="177">
-        <v>46185</v>
-      </c>
-      <c r="G197" s="177">
-        <f t="shared" ref="G197:G214" si="22">F197+(H197/24)</f>
-        <v>46187</v>
+        <v>46208.645833333336</v>
+      </c>
+      <c r="G197" s="213">
+        <f t="shared" si="22"/>
+        <v>46210.645833333336</v>
       </c>
       <c r="H197" s="303">
         <v>48</v>
       </c>
-      <c r="I197" s="177">
-        <f t="shared" ref="I197:I214" si="23">G197+(J197/24)</f>
-        <v>46187.25</v>
+      <c r="I197" s="213">
+        <f t="shared" si="23"/>
+        <v>46210.895833333336</v>
       </c>
       <c r="J197" s="211">
         <v>6</v>
@@ -40794,98 +40789,98 @@
         <v>64</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D198" s="212" t="s">
         <v>453</v>
       </c>
       <c r="E198" s="54">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="F198" s="177">
-        <v>46208.645833333336</v>
+        <v>46210.375</v>
       </c>
       <c r="G198" s="213">
         <f t="shared" si="22"/>
-        <v>46210.645833333336</v>
+        <v>46212.375</v>
       </c>
       <c r="H198" s="303">
         <v>48</v>
       </c>
       <c r="I198" s="213">
         <f t="shared" si="23"/>
-        <v>46210.895833333336</v>
+        <v>46212.625</v>
       </c>
       <c r="J198" s="211">
         <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A199" s="212" t="s">
+      <c r="A199" s="7" t="s">
         <v>282</v>
       </c>
       <c r="B199" s="32" t="s">
         <v>64</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="D199" s="212" t="s">
         <v>454</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="E199" s="54">
         <v>46208</v>
       </c>
       <c r="F199" s="177">
-        <v>46210.375</v>
+        <v>46212.875</v>
       </c>
       <c r="G199" s="213">
         <f t="shared" si="22"/>
-        <v>46212.375</v>
-      </c>
-      <c r="H199" s="303">
+        <v>46214.875</v>
+      </c>
+      <c r="H199" s="327">
         <v>48</v>
       </c>
       <c r="I199" s="213">
         <f t="shared" si="23"/>
-        <v>46212.625</v>
+        <v>46215.125</v>
       </c>
       <c r="J199" s="211">
         <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A200" s="7" t="s">
+      <c r="A200" s="212" t="s">
         <v>282</v>
       </c>
-      <c r="B200" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="D200" s="7" t="s">
+      <c r="B200" s="211" t="s">
+        <v>160</v>
+      </c>
+      <c r="C200" s="212" t="s">
         <v>456</v>
       </c>
+      <c r="D200" s="212" t="s">
+        <v>457</v>
+      </c>
       <c r="E200" s="54">
-        <v>46208</v>
+        <v>46237</v>
       </c>
       <c r="F200" s="177">
-        <v>46212.875</v>
+        <v>46240.916666666664</v>
       </c>
       <c r="G200" s="213">
         <f t="shared" si="22"/>
-        <v>46214.875</v>
-      </c>
-      <c r="H200" s="327">
-        <v>48</v>
+        <v>46243.916666666664</v>
+      </c>
+      <c r="H200" s="32">
+        <v>72</v>
       </c>
       <c r="I200" s="213">
         <f t="shared" si="23"/>
-        <v>46215.125</v>
-      </c>
-      <c r="J200" s="211">
-        <v>6</v>
+        <v>46245.416666666664</v>
+      </c>
+      <c r="J200" s="32">
+        <v>36</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
@@ -40896,27 +40891,27 @@
         <v>160</v>
       </c>
       <c r="C201" s="212" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D201" s="212" t="s">
         <v>458</v>
       </c>
       <c r="E201" s="54">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F201" s="177">
-        <v>46240.916666666664</v>
+        <v>46242.541666666664</v>
       </c>
       <c r="G201" s="213">
         <f t="shared" si="22"/>
-        <v>46243.916666666664</v>
+        <v>46245.541666666664</v>
       </c>
       <c r="H201" s="32">
         <v>72</v>
       </c>
       <c r="I201" s="213">
         <f t="shared" si="23"/>
-        <v>46245.416666666664</v>
+        <v>46247.041666666664</v>
       </c>
       <c r="J201" s="32">
         <v>36</v>
@@ -40930,27 +40925,27 @@
         <v>160</v>
       </c>
       <c r="C202" s="212" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D202" s="212" t="s">
         <v>459</v>
       </c>
       <c r="E202" s="54">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="F202" s="177">
-        <v>46242.541666666664</v>
+        <v>46245.59652777778</v>
       </c>
       <c r="G202" s="213">
         <f t="shared" si="22"/>
-        <v>46245.541666666664</v>
+        <v>46248.59652777778</v>
       </c>
       <c r="H202" s="32">
         <v>72</v>
       </c>
       <c r="I202" s="213">
         <f t="shared" si="23"/>
-        <v>46247.041666666664</v>
+        <v>46250.09652777778</v>
       </c>
       <c r="J202" s="32">
         <v>36</v>
@@ -40964,27 +40959,27 @@
         <v>160</v>
       </c>
       <c r="C203" s="212" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D203" s="212" t="s">
         <v>460</v>
       </c>
       <c r="E203" s="54">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="F203" s="177">
-        <v>46245.59652777778</v>
+        <v>46248.059027777781</v>
       </c>
       <c r="G203" s="213">
         <f t="shared" si="22"/>
-        <v>46248.59652777778</v>
+        <v>46251.059027777781</v>
       </c>
       <c r="H203" s="32">
         <v>72</v>
       </c>
       <c r="I203" s="213">
         <f t="shared" si="23"/>
-        <v>46250.09652777778</v>
+        <v>46252.559027777781</v>
       </c>
       <c r="J203" s="32">
         <v>36</v>
@@ -40998,27 +40993,27 @@
         <v>160</v>
       </c>
       <c r="C204" s="212" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D204" s="212" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E204" s="54">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="F204" s="177">
-        <v>46248.059027777781</v>
+        <v>46250.017361111109</v>
       </c>
       <c r="G204" s="213">
         <f t="shared" si="22"/>
-        <v>46251.059027777781</v>
+        <v>46253.017361111109</v>
       </c>
       <c r="H204" s="32">
         <v>72</v>
       </c>
       <c r="I204" s="213">
         <f t="shared" si="23"/>
-        <v>46252.559027777781</v>
+        <v>46254.517361111109</v>
       </c>
       <c r="J204" s="32">
         <v>36</v>
@@ -41032,27 +41027,27 @@
         <v>160</v>
       </c>
       <c r="C205" s="212" t="s">
-        <v>462</v>
-      </c>
-      <c r="D205" s="212" t="s">
-        <v>463</v>
+        <v>461</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="E205" s="54">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="F205" s="177">
-        <v>46250.017361111109</v>
+        <v>46255.892361111109</v>
       </c>
       <c r="G205" s="213">
         <f t="shared" si="22"/>
-        <v>46253.017361111109</v>
+        <v>46257.892361111109</v>
       </c>
       <c r="H205" s="32">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="I205" s="213">
         <f t="shared" si="23"/>
-        <v>46254.517361111109</v>
+        <v>46259.392361111109</v>
       </c>
       <c r="J205" s="32">
         <v>36</v>
@@ -41066,27 +41061,27 @@
         <v>160</v>
       </c>
       <c r="C206" s="212" t="s">
-        <v>462</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>275</v>
+        <v>461</v>
+      </c>
+      <c r="D206" s="212" t="s">
+        <v>463</v>
       </c>
       <c r="E206" s="54">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="F206" s="177">
-        <v>46255.892361111109</v>
+        <v>46265.704861111109</v>
       </c>
       <c r="G206" s="213">
         <f t="shared" si="22"/>
-        <v>46257.892361111109</v>
+        <v>46267.704861111109</v>
       </c>
       <c r="H206" s="32">
         <v>48</v>
       </c>
       <c r="I206" s="213">
         <f t="shared" si="23"/>
-        <v>46259.392361111109</v>
+        <v>46269.204861111109</v>
       </c>
       <c r="J206" s="32">
         <v>36</v>
@@ -41100,27 +41095,27 @@
         <v>160</v>
       </c>
       <c r="C207" s="212" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D207" s="212" t="s">
-        <v>464</v>
+        <v>278</v>
       </c>
       <c r="E207" s="54">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="F207" s="177">
-        <v>46265.704861111109</v>
+        <v>46272.079861111109</v>
       </c>
       <c r="G207" s="213">
         <f t="shared" si="22"/>
-        <v>46267.704861111109</v>
+        <v>46274.079861111109</v>
       </c>
       <c r="H207" s="32">
         <v>48</v>
       </c>
       <c r="I207" s="213">
         <f t="shared" si="23"/>
-        <v>46269.204861111109</v>
+        <v>46275.579861111109</v>
       </c>
       <c r="J207" s="32">
         <v>36</v>
@@ -41131,33 +41126,33 @@
         <v>282</v>
       </c>
       <c r="B208" s="211" t="s">
-        <v>160</v>
+        <v>312</v>
       </c>
       <c r="C208" s="212" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D208" s="212" t="s">
-        <v>278</v>
+        <v>465</v>
       </c>
       <c r="E208" s="54">
-        <v>46269</v>
+        <v>46233</v>
       </c>
       <c r="F208" s="177">
-        <v>46272.079861111109</v>
+        <v>46236.072916666664</v>
       </c>
       <c r="G208" s="213">
         <f t="shared" si="22"/>
-        <v>46274.079861111109</v>
+        <v>46238.072916666664</v>
       </c>
       <c r="H208" s="32">
         <v>48</v>
       </c>
       <c r="I208" s="213">
         <f t="shared" si="23"/>
-        <v>46275.579861111109</v>
+        <v>46238.822916666664</v>
       </c>
       <c r="J208" s="32">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
@@ -41168,27 +41163,27 @@
         <v>312</v>
       </c>
       <c r="C209" s="212" t="s">
-        <v>465</v>
-      </c>
-      <c r="D209" s="212" t="s">
-        <v>466</v>
+        <v>464</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>501</v>
       </c>
       <c r="E209" s="54">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="F209" s="177">
-        <v>46236.114583333336</v>
+        <v>46237.822916666664</v>
       </c>
       <c r="G209" s="213">
         <f t="shared" si="22"/>
-        <v>46238.114583333336</v>
+        <v>46239.822916666664</v>
       </c>
       <c r="H209" s="32">
         <v>48</v>
       </c>
       <c r="I209" s="213">
         <f t="shared" si="23"/>
-        <v>46238.864583333336</v>
+        <v>46240.572916666664</v>
       </c>
       <c r="J209" s="32">
         <v>18</v>
@@ -41202,27 +41197,27 @@
         <v>312</v>
       </c>
       <c r="C210" s="212" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E210" s="54">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="F210" s="177">
-        <v>46237.864583333336</v>
+        <v>46245.49722222222</v>
       </c>
       <c r="G210" s="213">
         <f t="shared" si="22"/>
-        <v>46239.864583333336</v>
+        <v>46247.49722222222</v>
       </c>
       <c r="H210" s="32">
         <v>48</v>
       </c>
       <c r="I210" s="213">
         <f t="shared" si="23"/>
-        <v>46240.614583333336</v>
+        <v>46248.24722222222</v>
       </c>
       <c r="J210" s="32">
         <v>18</v>
@@ -41236,27 +41231,27 @@
         <v>312</v>
       </c>
       <c r="C211" s="212" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E211" s="54">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="F211" s="177">
-        <v>46245.538888888892</v>
+        <v>46251.027083333334</v>
       </c>
       <c r="G211" s="213">
         <f t="shared" si="22"/>
-        <v>46247.538888888892</v>
+        <v>46253.027083333334</v>
       </c>
       <c r="H211" s="32">
         <v>48</v>
       </c>
       <c r="I211" s="213">
         <f t="shared" si="23"/>
-        <v>46248.288888888892</v>
+        <v>46253.777083333334</v>
       </c>
       <c r="J211" s="32">
         <v>18</v>
@@ -41270,27 +41265,27 @@
         <v>312</v>
       </c>
       <c r="C212" s="212" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E212" s="54">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="F212" s="177">
-        <v>46251.068749999999</v>
+        <v>46259.619444444441</v>
       </c>
       <c r="G212" s="213">
         <f t="shared" si="22"/>
-        <v>46253.068749999999</v>
+        <v>46261.119444444441</v>
       </c>
       <c r="H212" s="32">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I212" s="213">
         <f t="shared" si="23"/>
-        <v>46253.818749999999</v>
+        <v>46261.869444444441</v>
       </c>
       <c r="J212" s="32">
         <v>18</v>
@@ -41304,68 +41299,34 @@
         <v>312</v>
       </c>
       <c r="C213" s="212" t="s">
-        <v>465</v>
-      </c>
-      <c r="D213" s="7" t="s">
-        <v>506</v>
+        <v>464</v>
+      </c>
+      <c r="D213" s="308" t="s">
+        <v>505</v>
       </c>
       <c r="E213" s="54">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="F213" s="177">
-        <v>46259.661111111112</v>
+        <v>46265.463194444441</v>
       </c>
       <c r="G213" s="213">
         <f t="shared" si="22"/>
-        <v>46261.161111111112</v>
+        <v>46267.963194444441</v>
       </c>
       <c r="H213" s="32">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I213" s="213">
         <f t="shared" si="23"/>
-        <v>46261.911111111112</v>
+        <v>46268.713194444441</v>
       </c>
       <c r="J213" s="32">
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A214" s="212" t="s">
-        <v>282</v>
-      </c>
-      <c r="B214" s="211" t="s">
-        <v>312</v>
-      </c>
-      <c r="C214" s="212" t="s">
-        <v>465</v>
-      </c>
-      <c r="D214" s="308" t="s">
-        <v>507</v>
-      </c>
-      <c r="E214" s="54">
-        <v>46262</v>
-      </c>
-      <c r="F214" s="177">
-        <v>46265.504861111112</v>
-      </c>
-      <c r="G214" s="213">
-        <f t="shared" si="22"/>
-        <v>46268.004861111112</v>
-      </c>
-      <c r="H214" s="32">
-        <v>60</v>
-      </c>
-      <c r="I214" s="213">
-        <f t="shared" si="23"/>
-        <v>46268.754861111112</v>
-      </c>
-      <c r="J214" s="32">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J214" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
+  <autoFilter ref="A1:J213" xr:uid="{E64F7A7C-F00C-4BD1-AABC-21B710242BB1}">
     <filterColumn colId="0">
       <filters>
         <filter val="Planned"/>
@@ -41374,14 +41335,14 @@
   </autoFilter>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D181" r:id="rId1" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60703:" xr:uid="{2CE69447-1583-4285-A3C6-E44253861F50}"/>
-    <hyperlink ref="D182" r:id="rId2" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60704:" xr:uid="{9B646115-87F0-4E9B-A26C-E8EDC2346D02}"/>
-    <hyperlink ref="D183" r:id="rId3" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60705:" xr:uid="{E88F1C80-86A4-402C-A7FA-01CE4B12C622}"/>
-    <hyperlink ref="D184" r:id="rId4" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60706:" xr:uid="{ED524307-DD66-4DB1-9398-118E3CD28160}"/>
-    <hyperlink ref="D185" r:id="rId5" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60707:" xr:uid="{2A3CDFC3-31C8-44B2-8428-4BB6443AB947}"/>
-    <hyperlink ref="C188" r:id="rId6" xr:uid="{4BF92AC9-6F81-47D3-BADE-793677667278}"/>
-    <hyperlink ref="D189" r:id="rId7" xr:uid="{E7B658C7-FFEB-4978-9A4E-D4E57D76FD92}"/>
-    <hyperlink ref="D191" r:id="rId8" xr:uid="{42CF593B-3B32-4FD3-BF01-D92D8C273D20}"/>
+    <hyperlink ref="D180" r:id="rId1" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60703:" xr:uid="{2CE69447-1583-4285-A3C6-E44253861F50}"/>
+    <hyperlink ref="D181" r:id="rId2" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60704:" xr:uid="{9B646115-87F0-4E9B-A26C-E8EDC2346D02}"/>
+    <hyperlink ref="D182" r:id="rId3" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60705:" xr:uid="{E88F1C80-86A4-402C-A7FA-01CE4B12C622}"/>
+    <hyperlink ref="D183" r:id="rId4" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60706:" xr:uid="{ED524307-DD66-4DB1-9398-118E3CD28160}"/>
+    <hyperlink ref="D184" r:id="rId5" display="https://app01.kabal.com/mws/f?p=1720:320:3591087192783:ADDBACK:NO::P320_PORT_TASK_ID:60707:" xr:uid="{2A3CDFC3-31C8-44B2-8428-4BB6443AB947}"/>
+    <hyperlink ref="C187" r:id="rId6" xr:uid="{4BF92AC9-6F81-47D3-BADE-793677667278}"/>
+    <hyperlink ref="D188" r:id="rId7" xr:uid="{E7B658C7-FFEB-4978-9A4E-D4E57D76FD92}"/>
+    <hyperlink ref="D190" r:id="rId8" xr:uid="{42CF593B-3B32-4FD3-BF01-D92D8C273D20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -41422,45 +41383,45 @@
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="70"/>
       <c r="B2" s="71" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>467</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="D2" s="72" t="s">
         <v>468</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="E2" s="73" t="s">
         <v>469</v>
       </c>
-      <c r="E2" s="73" t="s">
-        <v>470</v>
-      </c>
       <c r="F2" s="74" t="s">
+        <v>466</v>
+      </c>
+      <c r="G2" s="72" t="s">
         <v>467</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="H2" s="72" t="s">
         <v>468</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="I2" s="73" t="s">
         <v>469</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>470</v>
-      </c>
       <c r="J2" s="74" t="s">
+        <v>466</v>
+      </c>
+      <c r="K2" s="72" t="s">
         <v>467</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="L2" s="72" t="s">
         <v>468</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="M2" s="73" t="s">
         <v>469</v>
-      </c>
-      <c r="M2" s="73" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="75" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
@@ -41468,7 +41429,7 @@
       <c r="E3" s="76"/>
       <c r="F3" s="76"/>
       <c r="G3" s="76" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H3" s="76"/>
       <c r="I3" s="76"/>
@@ -41479,7 +41440,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B4" s="76"/>
       <c r="C4" s="76"/>
@@ -41487,7 +41448,7 @@
       <c r="E4" s="76"/>
       <c r="F4" s="76"/>
       <c r="G4" s="76" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H4" s="76"/>
       <c r="I4" s="76"/>
@@ -41498,7 +41459,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
@@ -41506,7 +41467,7 @@
       <c r="E5" s="76"/>
       <c r="F5" s="76"/>
       <c r="G5" s="76" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H5" s="76"/>
       <c r="I5" s="76"/>
@@ -41517,7 +41478,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B6" s="77"/>
       <c r="C6" s="78"/>
@@ -41525,7 +41486,7 @@
       <c r="E6" s="79"/>
       <c r="F6" s="80"/>
       <c r="G6" s="81" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H6" s="78"/>
       <c r="I6" s="79"/>
@@ -41536,7 +41497,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="75" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B7" s="77"/>
       <c r="C7" s="78"/>
@@ -41544,7 +41505,7 @@
       <c r="E7" s="79"/>
       <c r="F7" s="80"/>
       <c r="G7" s="81" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H7" s="78"/>
       <c r="I7" s="79"/>
@@ -41558,7 +41519,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="75" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B8" s="77"/>
       <c r="C8" s="78"/>
@@ -41566,7 +41527,7 @@
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="81" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H8" s="78"/>
       <c r="I8" s="79"/>
@@ -41577,7 +41538,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="82"/>
       <c r="C9" s="83"/>
@@ -41585,7 +41546,7 @@
       <c r="E9" s="84"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="84"/>
@@ -41596,7 +41557,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="75" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B10" s="87"/>
       <c r="C10" s="87"/>
@@ -41604,7 +41565,7 @@
       <c r="E10" s="87"/>
       <c r="F10" s="87"/>
       <c r="G10" s="87" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H10" s="87"/>
       <c r="I10" s="87"/>
@@ -41615,7 +41576,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="75" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B11" s="88"/>
       <c r="C11" s="89"/>
@@ -41623,7 +41584,7 @@
       <c r="E11" s="90"/>
       <c r="F11" s="91"/>
       <c r="G11" s="92" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H11" s="89"/>
       <c r="I11" s="90"/>
@@ -41634,7 +41595,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B12" s="93"/>
       <c r="C12" s="94"/>
@@ -41642,7 +41603,7 @@
       <c r="E12" s="95"/>
       <c r="F12" s="96"/>
       <c r="G12" s="97" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H12" s="94"/>
       <c r="I12" s="95"/>
@@ -41653,7 +41614,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="75" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B13" s="93"/>
       <c r="C13" s="94"/>
@@ -41666,17 +41627,17 @@
       <c r="H13" s="453"/>
       <c r="I13" s="454"/>
       <c r="J13" s="98" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K13" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L13" s="99"/>
       <c r="M13" s="100"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B14" s="101"/>
       <c r="C14" s="101" t="s">
@@ -41685,28 +41646,28 @@
       <c r="D14" s="101"/>
       <c r="E14" s="101"/>
       <c r="F14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J14" s="98" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="M14" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O14" s="69" t="s">
         <v>18</v>
@@ -41714,7 +41675,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="75" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B15" s="102"/>
       <c r="C15" s="103"/>
@@ -41749,7 +41710,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="75" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B16" s="102"/>
       <c r="C16" s="103"/>
@@ -41784,7 +41745,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>160</v>
@@ -41813,7 +41774,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="75" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>160</v>
@@ -41852,7 +41813,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="75" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B19" s="102"/>
       <c r="C19" s="103"/>
@@ -41881,15 +41842,15 @@
     </row>
     <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="111" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B20" s="112"/>
       <c r="C20" s="113"/>
       <c r="D20" s="114" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E20" s="115" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F20" s="103"/>
       <c r="G20" s="103"/>
@@ -42294,11 +42255,17 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8C99E3-3621-4A94-B7E8-DFCD24F34FA6}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="91455a6e-8899-4f67-a6e4-e187ec74b863"/>
-    <ds:schemaRef ds:uri="b2778aaa-fd83-416e-8091-738aa96f6cd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
